--- a/solutions/tools/tvSearch/idovonal/szolgalatiIdok.xlsx
+++ b/solutions/tools/tvSearch/idovonal/szolgalatiIdok.xlsx
@@ -16,6 +16,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nyers1'!$A$3:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nyers2'!$A$3:$J$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Összeítés'!$A$4:$H$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Szabályok'!$A$12:$J$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Átfedő idők'!$A$4:$AJ$304</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -228,99 +231,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblNyers1" displayName="tblNyers1" ref="A3:J204" headerRowCount="1">
-  <autoFilter ref="A3:J204"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="azonosító"/>
-    <tableColumn id="2" name="tól"/>
-    <tableColumn id="3" name="ig"/>
-    <tableColumn id="4" name="munkáltató"/>
-    <tableColumn id="5" name="jogviszony"/>
-    <tableColumn id="6" name="járulékalap"/>
-    <tableColumn id="7" name="nem_rendszeres"/>
-    <tableColumn id="8" name="járulék_összeg"/>
-    <tableColumn id="9" name="közölt_napok"/>
-    <tableColumn id="10" name="megjegyzés"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblNyers2" displayName="tblNyers2" ref="A3:J204" headerRowCount="1">
-  <autoFilter ref="A3:J204"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="azonosító"/>
-    <tableColumn id="2" name="tól"/>
-    <tableColumn id="3" name="ig"/>
-    <tableColumn id="4" name="munkáltató"/>
-    <tableColumn id="5" name="jogviszony"/>
-    <tableColumn id="6" name="járulékalap"/>
-    <tableColumn id="7" name="nem_rendszeres"/>
-    <tableColumn id="8" name="járulék_összeg"/>
-    <tableColumn id="9" name="közölt_napok"/>
-    <tableColumn id="10" name="megjegyzés"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblOsszeitesIdoszakok" displayName="tblOsszeitesIdoszakok" ref="A4:H124" headerRowCount="1">
-  <autoFilter ref="A4:H124"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="azonosító"/>
-    <tableColumn id="2" name="tól"/>
-    <tableColumn id="3" name="ig"/>
-    <tableColumn id="4" name="közölt_napok"/>
-    <tableColumn id="5" name="munkáltató"/>
-    <tableColumn id="6" name="jogviszony"/>
-    <tableColumn id="7" name="minősítés_betűjele"/>
-    <tableColumn id="8" name="megjegyzés"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblOsszeitesJogcimek" displayName="tblOsszeitesJogcimek" ref="A130:J280" headerRowCount="1">
-  <autoFilter ref="A130:J280"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="kapcsolat_azonosító"/>
-    <tableColumn id="2" name="tól"/>
-    <tableColumn id="3" name="ig"/>
-    <tableColumn id="4" name="napok"/>
-    <tableColumn id="5" name="munkáltató"/>
-    <tableColumn id="6" name="jogcím"/>
-    <tableColumn id="7" name="járulékalap"/>
-    <tableColumn id="8" name="nem_rendszeres"/>
-    <tableColumn id="9" name="járulék_összeg"/>
-    <tableColumn id="10" name="megjegyzés"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblSzabalyokJogcimek" displayName="tblSzabalyokJogcimek" ref="A12:J200" headerRowCount="1">
-  <autoFilter ref="A12:J200"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="jogcím_megnevezés"/>
-    <tableColumn id="2" name="prioritás"/>
-    <tableColumn id="3" name="alap_kód"/>
-    <tableColumn id="4" name="munkaviszony_jellegű"/>
-    <tableColumn id="5" name="minimumbér_vizsgálat"/>
-    <tableColumn id="6" name="plafon_vizsgálat"/>
-    <tableColumn id="7" name="szüneteltetés_kizárhatja"/>
-    <tableColumn id="8" name="tartozás_kizárhatja"/>
-    <tableColumn id="9" name="gyermekes_jogcím"/>
-    <tableColumn id="10" name="megjegyzés"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3109,9 +3019,6 @@
   </sheetData>
   <autoFilter ref="A3:J204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -5618,9 +5525,6 @@
   </sheetData>
   <autoFilter ref="A3:J204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -8795,11 +8699,8 @@
       <c r="J280" s="5" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:H124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -12059,10 +11960,8 @@
       <c r="J200" s="5" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A12:J200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -41748,6 +41647,7 @@
       <c r="AJ304" s="5" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:AJ304"/>
   <conditionalFormatting sqref="AB5:AB304">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AB5="X"</formula>

--- a/solutions/tools/tvSearch/idovonal/szolgalatiIdok.xlsx
+++ b/solutions/tools/tvSearch/idovonal/szolgalatiIdok.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nyers2'!$A$3:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Összeítés'!$A$4:$H$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Szabályok'!$A$12:$J$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Átfedő idők'!$A$4:$AJ$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Átfedő idők'!$A$4:$AL$304</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,8 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="# ##0"/>
+    <numFmt numFmtId="165" formatCode="yyyy.mm.dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +135,7 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11971,7 +11973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ304"/>
+  <dimension ref="A1:AL304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12010,6 +12012,8 @@
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="16" customWidth="1" min="35" max="35"/>
     <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12245,17 +12249,27 @@
           <t>megjegyzés</t>
         </is>
       </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>tól_dátum_parsolt</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>ig_dátum_parsolt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5">
-        <f>IF(AND(B5&lt;&gt;"",C5&lt;&gt;""),C5-B5+1,"")</f>
+        <f>IF(AND(AK5&lt;&gt;"",AL5&lt;&gt;""),AL5-AK5+1,"")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>IF(B5&lt;&gt;"",YEAR(B5),"")</f>
+        <f>IF(AK5&lt;&gt;"",YEAR(AK5),"")</f>
         <v/>
       </c>
       <c r="F5" s="6" t="n"/>
@@ -12343,17 +12357,25 @@
         <v/>
       </c>
       <c r="AJ5" s="5" t="n"/>
+      <c r="AK5" s="12">
+        <f>IF(B5="","",IF(ISNUMBER(B5),B5,DATE(VALUE(LEFT(B5,4)),VALUE(MID(B5,6,2)),VALUE(MID(B5,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL5" s="12">
+        <f>IF(C5="","",IF(ISNUMBER(C5),C5,DATE(VALUE(LEFT(C5,4)),VALUE(MID(C5,6,2)),VALUE(MID(C5,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5">
-        <f>IF(AND(B6&lt;&gt;"",C6&lt;&gt;""),C6-B6+1,"")</f>
+        <f>IF(AND(AK6&lt;&gt;"",AL6&lt;&gt;""),AL6-AK6+1,"")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>IF(B6&lt;&gt;"",YEAR(B6),"")</f>
+        <f>IF(AK6&lt;&gt;"",YEAR(AK6),"")</f>
         <v/>
       </c>
       <c r="F6" s="6" t="n"/>
@@ -12441,17 +12463,25 @@
         <v/>
       </c>
       <c r="AJ6" s="5" t="n"/>
+      <c r="AK6" s="12">
+        <f>IF(B6="","",IF(ISNUMBER(B6),B6,DATE(VALUE(LEFT(B6,4)),VALUE(MID(B6,6,2)),VALUE(MID(B6,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL6" s="12">
+        <f>IF(C6="","",IF(ISNUMBER(C6),C6,DATE(VALUE(LEFT(C6,4)),VALUE(MID(C6,6,2)),VALUE(MID(C6,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5">
-        <f>IF(AND(B7&lt;&gt;"",C7&lt;&gt;""),C7-B7+1,"")</f>
+        <f>IF(AND(AK7&lt;&gt;"",AL7&lt;&gt;""),AL7-AK7+1,"")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>IF(B7&lt;&gt;"",YEAR(B7),"")</f>
+        <f>IF(AK7&lt;&gt;"",YEAR(AK7),"")</f>
         <v/>
       </c>
       <c r="F7" s="6" t="n"/>
@@ -12539,17 +12569,25 @@
         <v/>
       </c>
       <c r="AJ7" s="5" t="n"/>
+      <c r="AK7" s="12">
+        <f>IF(B7="","",IF(ISNUMBER(B7),B7,DATE(VALUE(LEFT(B7,4)),VALUE(MID(B7,6,2)),VALUE(MID(B7,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL7" s="12">
+        <f>IF(C7="","",IF(ISNUMBER(C7),C7,DATE(VALUE(LEFT(C7,4)),VALUE(MID(C7,6,2)),VALUE(MID(C7,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5">
-        <f>IF(AND(B8&lt;&gt;"",C8&lt;&gt;""),C8-B8+1,"")</f>
+        <f>IF(AND(AK8&lt;&gt;"",AL8&lt;&gt;""),AL8-AK8+1,"")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>IF(B8&lt;&gt;"",YEAR(B8),"")</f>
+        <f>IF(AK8&lt;&gt;"",YEAR(AK8),"")</f>
         <v/>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -12637,17 +12675,25 @@
         <v/>
       </c>
       <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="12">
+        <f>IF(B8="","",IF(ISNUMBER(B8),B8,DATE(VALUE(LEFT(B8,4)),VALUE(MID(B8,6,2)),VALUE(MID(B8,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL8" s="12">
+        <f>IF(C8="","",IF(ISNUMBER(C8),C8,DATE(VALUE(LEFT(C8,4)),VALUE(MID(C8,6,2)),VALUE(MID(C8,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5">
-        <f>IF(AND(B9&lt;&gt;"",C9&lt;&gt;""),C9-B9+1,"")</f>
+        <f>IF(AND(AK9&lt;&gt;"",AL9&lt;&gt;""),AL9-AK9+1,"")</f>
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>IF(B9&lt;&gt;"",YEAR(B9),"")</f>
+        <f>IF(AK9&lt;&gt;"",YEAR(AK9),"")</f>
         <v/>
       </c>
       <c r="F9" s="6" t="n"/>
@@ -12735,17 +12781,25 @@
         <v/>
       </c>
       <c r="AJ9" s="5" t="n"/>
+      <c r="AK9" s="12">
+        <f>IF(B9="","",IF(ISNUMBER(B9),B9,DATE(VALUE(LEFT(B9,4)),VALUE(MID(B9,6,2)),VALUE(MID(B9,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL9" s="12">
+        <f>IF(C9="","",IF(ISNUMBER(C9),C9,DATE(VALUE(LEFT(C9,4)),VALUE(MID(C9,6,2)),VALUE(MID(C9,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5">
-        <f>IF(AND(B10&lt;&gt;"",C10&lt;&gt;""),C10-B10+1,"")</f>
+        <f>IF(AND(AK10&lt;&gt;"",AL10&lt;&gt;""),AL10-AK10+1,"")</f>
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>IF(B10&lt;&gt;"",YEAR(B10),"")</f>
+        <f>IF(AK10&lt;&gt;"",YEAR(AK10),"")</f>
         <v/>
       </c>
       <c r="F10" s="6" t="n"/>
@@ -12833,17 +12887,25 @@
         <v/>
       </c>
       <c r="AJ10" s="5" t="n"/>
+      <c r="AK10" s="12">
+        <f>IF(B10="","",IF(ISNUMBER(B10),B10,DATE(VALUE(LEFT(B10,4)),VALUE(MID(B10,6,2)),VALUE(MID(B10,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL10" s="12">
+        <f>IF(C10="","",IF(ISNUMBER(C10),C10,DATE(VALUE(LEFT(C10,4)),VALUE(MID(C10,6,2)),VALUE(MID(C10,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5">
-        <f>IF(AND(B11&lt;&gt;"",C11&lt;&gt;""),C11-B11+1,"")</f>
+        <f>IF(AND(AK11&lt;&gt;"",AL11&lt;&gt;""),AL11-AK11+1,"")</f>
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>IF(B11&lt;&gt;"",YEAR(B11),"")</f>
+        <f>IF(AK11&lt;&gt;"",YEAR(AK11),"")</f>
         <v/>
       </c>
       <c r="F11" s="6" t="n"/>
@@ -12931,17 +12993,25 @@
         <v/>
       </c>
       <c r="AJ11" s="5" t="n"/>
+      <c r="AK11" s="12">
+        <f>IF(B11="","",IF(ISNUMBER(B11),B11,DATE(VALUE(LEFT(B11,4)),VALUE(MID(B11,6,2)),VALUE(MID(B11,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL11" s="12">
+        <f>IF(C11="","",IF(ISNUMBER(C11),C11,DATE(VALUE(LEFT(C11,4)),VALUE(MID(C11,6,2)),VALUE(MID(C11,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5">
-        <f>IF(AND(B12&lt;&gt;"",C12&lt;&gt;""),C12-B12+1,"")</f>
+        <f>IF(AND(AK12&lt;&gt;"",AL12&lt;&gt;""),AL12-AK12+1,"")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>IF(B12&lt;&gt;"",YEAR(B12),"")</f>
+        <f>IF(AK12&lt;&gt;"",YEAR(AK12),"")</f>
         <v/>
       </c>
       <c r="F12" s="6" t="n"/>
@@ -13029,17 +13099,25 @@
         <v/>
       </c>
       <c r="AJ12" s="5" t="n"/>
+      <c r="AK12" s="12">
+        <f>IF(B12="","",IF(ISNUMBER(B12),B12,DATE(VALUE(LEFT(B12,4)),VALUE(MID(B12,6,2)),VALUE(MID(B12,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL12" s="12">
+        <f>IF(C12="","",IF(ISNUMBER(C12),C12,DATE(VALUE(LEFT(C12,4)),VALUE(MID(C12,6,2)),VALUE(MID(C12,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5">
-        <f>IF(AND(B13&lt;&gt;"",C13&lt;&gt;""),C13-B13+1,"")</f>
+        <f>IF(AND(AK13&lt;&gt;"",AL13&lt;&gt;""),AL13-AK13+1,"")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>IF(B13&lt;&gt;"",YEAR(B13),"")</f>
+        <f>IF(AK13&lt;&gt;"",YEAR(AK13),"")</f>
         <v/>
       </c>
       <c r="F13" s="6" t="n"/>
@@ -13127,17 +13205,25 @@
         <v/>
       </c>
       <c r="AJ13" s="5" t="n"/>
+      <c r="AK13" s="12">
+        <f>IF(B13="","",IF(ISNUMBER(B13),B13,DATE(VALUE(LEFT(B13,4)),VALUE(MID(B13,6,2)),VALUE(MID(B13,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL13" s="12">
+        <f>IF(C13="","",IF(ISNUMBER(C13),C13,DATE(VALUE(LEFT(C13,4)),VALUE(MID(C13,6,2)),VALUE(MID(C13,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5">
-        <f>IF(AND(B14&lt;&gt;"",C14&lt;&gt;""),C14-B14+1,"")</f>
+        <f>IF(AND(AK14&lt;&gt;"",AL14&lt;&gt;""),AL14-AK14+1,"")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>IF(B14&lt;&gt;"",YEAR(B14),"")</f>
+        <f>IF(AK14&lt;&gt;"",YEAR(AK14),"")</f>
         <v/>
       </c>
       <c r="F14" s="6" t="n"/>
@@ -13225,17 +13311,25 @@
         <v/>
       </c>
       <c r="AJ14" s="5" t="n"/>
+      <c r="AK14" s="12">
+        <f>IF(B14="","",IF(ISNUMBER(B14),B14,DATE(VALUE(LEFT(B14,4)),VALUE(MID(B14,6,2)),VALUE(MID(B14,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL14" s="12">
+        <f>IF(C14="","",IF(ISNUMBER(C14),C14,DATE(VALUE(LEFT(C14,4)),VALUE(MID(C14,6,2)),VALUE(MID(C14,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5">
-        <f>IF(AND(B15&lt;&gt;"",C15&lt;&gt;""),C15-B15+1,"")</f>
+        <f>IF(AND(AK15&lt;&gt;"",AL15&lt;&gt;""),AL15-AK15+1,"")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>IF(B15&lt;&gt;"",YEAR(B15),"")</f>
+        <f>IF(AK15&lt;&gt;"",YEAR(AK15),"")</f>
         <v/>
       </c>
       <c r="F15" s="6" t="n"/>
@@ -13323,17 +13417,25 @@
         <v/>
       </c>
       <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="12">
+        <f>IF(B15="","",IF(ISNUMBER(B15),B15,DATE(VALUE(LEFT(B15,4)),VALUE(MID(B15,6,2)),VALUE(MID(B15,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL15" s="12">
+        <f>IF(C15="","",IF(ISNUMBER(C15),C15,DATE(VALUE(LEFT(C15,4)),VALUE(MID(C15,6,2)),VALUE(MID(C15,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5">
-        <f>IF(AND(B16&lt;&gt;"",C16&lt;&gt;""),C16-B16+1,"")</f>
+        <f>IF(AND(AK16&lt;&gt;"",AL16&lt;&gt;""),AL16-AK16+1,"")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>IF(B16&lt;&gt;"",YEAR(B16),"")</f>
+        <f>IF(AK16&lt;&gt;"",YEAR(AK16),"")</f>
         <v/>
       </c>
       <c r="F16" s="6" t="n"/>
@@ -13421,17 +13523,25 @@
         <v/>
       </c>
       <c r="AJ16" s="5" t="n"/>
+      <c r="AK16" s="12">
+        <f>IF(B16="","",IF(ISNUMBER(B16),B16,DATE(VALUE(LEFT(B16,4)),VALUE(MID(B16,6,2)),VALUE(MID(B16,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL16" s="12">
+        <f>IF(C16="","",IF(ISNUMBER(C16),C16,DATE(VALUE(LEFT(C16,4)),VALUE(MID(C16,6,2)),VALUE(MID(C16,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5">
-        <f>IF(AND(B17&lt;&gt;"",C17&lt;&gt;""),C17-B17+1,"")</f>
+        <f>IF(AND(AK17&lt;&gt;"",AL17&lt;&gt;""),AL17-AK17+1,"")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>IF(B17&lt;&gt;"",YEAR(B17),"")</f>
+        <f>IF(AK17&lt;&gt;"",YEAR(AK17),"")</f>
         <v/>
       </c>
       <c r="F17" s="6" t="n"/>
@@ -13519,17 +13629,25 @@
         <v/>
       </c>
       <c r="AJ17" s="5" t="n"/>
+      <c r="AK17" s="12">
+        <f>IF(B17="","",IF(ISNUMBER(B17),B17,DATE(VALUE(LEFT(B17,4)),VALUE(MID(B17,6,2)),VALUE(MID(B17,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL17" s="12">
+        <f>IF(C17="","",IF(ISNUMBER(C17),C17,DATE(VALUE(LEFT(C17,4)),VALUE(MID(C17,6,2)),VALUE(MID(C17,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5">
-        <f>IF(AND(B18&lt;&gt;"",C18&lt;&gt;""),C18-B18+1,"")</f>
+        <f>IF(AND(AK18&lt;&gt;"",AL18&lt;&gt;""),AL18-AK18+1,"")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>IF(B18&lt;&gt;"",YEAR(B18),"")</f>
+        <f>IF(AK18&lt;&gt;"",YEAR(AK18),"")</f>
         <v/>
       </c>
       <c r="F18" s="6" t="n"/>
@@ -13617,17 +13735,25 @@
         <v/>
       </c>
       <c r="AJ18" s="5" t="n"/>
+      <c r="AK18" s="12">
+        <f>IF(B18="","",IF(ISNUMBER(B18),B18,DATE(VALUE(LEFT(B18,4)),VALUE(MID(B18,6,2)),VALUE(MID(B18,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL18" s="12">
+        <f>IF(C18="","",IF(ISNUMBER(C18),C18,DATE(VALUE(LEFT(C18,4)),VALUE(MID(C18,6,2)),VALUE(MID(C18,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5">
-        <f>IF(AND(B19&lt;&gt;"",C19&lt;&gt;""),C19-B19+1,"")</f>
+        <f>IF(AND(AK19&lt;&gt;"",AL19&lt;&gt;""),AL19-AK19+1,"")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>IF(B19&lt;&gt;"",YEAR(B19),"")</f>
+        <f>IF(AK19&lt;&gt;"",YEAR(AK19),"")</f>
         <v/>
       </c>
       <c r="F19" s="6" t="n"/>
@@ -13715,17 +13841,25 @@
         <v/>
       </c>
       <c r="AJ19" s="5" t="n"/>
+      <c r="AK19" s="12">
+        <f>IF(B19="","",IF(ISNUMBER(B19),B19,DATE(VALUE(LEFT(B19,4)),VALUE(MID(B19,6,2)),VALUE(MID(B19,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL19" s="12">
+        <f>IF(C19="","",IF(ISNUMBER(C19),C19,DATE(VALUE(LEFT(C19,4)),VALUE(MID(C19,6,2)),VALUE(MID(C19,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5">
-        <f>IF(AND(B20&lt;&gt;"",C20&lt;&gt;""),C20-B20+1,"")</f>
+        <f>IF(AND(AK20&lt;&gt;"",AL20&lt;&gt;""),AL20-AK20+1,"")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>IF(B20&lt;&gt;"",YEAR(B20),"")</f>
+        <f>IF(AK20&lt;&gt;"",YEAR(AK20),"")</f>
         <v/>
       </c>
       <c r="F20" s="6" t="n"/>
@@ -13813,17 +13947,25 @@
         <v/>
       </c>
       <c r="AJ20" s="5" t="n"/>
+      <c r="AK20" s="12">
+        <f>IF(B20="","",IF(ISNUMBER(B20),B20,DATE(VALUE(LEFT(B20,4)),VALUE(MID(B20,6,2)),VALUE(MID(B20,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL20" s="12">
+        <f>IF(C20="","",IF(ISNUMBER(C20),C20,DATE(VALUE(LEFT(C20,4)),VALUE(MID(C20,6,2)),VALUE(MID(C20,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5">
-        <f>IF(AND(B21&lt;&gt;"",C21&lt;&gt;""),C21-B21+1,"")</f>
+        <f>IF(AND(AK21&lt;&gt;"",AL21&lt;&gt;""),AL21-AK21+1,"")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>IF(B21&lt;&gt;"",YEAR(B21),"")</f>
+        <f>IF(AK21&lt;&gt;"",YEAR(AK21),"")</f>
         <v/>
       </c>
       <c r="F21" s="6" t="n"/>
@@ -13911,17 +14053,25 @@
         <v/>
       </c>
       <c r="AJ21" s="5" t="n"/>
+      <c r="AK21" s="12">
+        <f>IF(B21="","",IF(ISNUMBER(B21),B21,DATE(VALUE(LEFT(B21,4)),VALUE(MID(B21,6,2)),VALUE(MID(B21,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL21" s="12">
+        <f>IF(C21="","",IF(ISNUMBER(C21),C21,DATE(VALUE(LEFT(C21,4)),VALUE(MID(C21,6,2)),VALUE(MID(C21,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="5">
-        <f>IF(AND(B22&lt;&gt;"",C22&lt;&gt;""),C22-B22+1,"")</f>
+        <f>IF(AND(AK22&lt;&gt;"",AL22&lt;&gt;""),AL22-AK22+1,"")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>IF(B22&lt;&gt;"",YEAR(B22),"")</f>
+        <f>IF(AK22&lt;&gt;"",YEAR(AK22),"")</f>
         <v/>
       </c>
       <c r="F22" s="6" t="n"/>
@@ -14009,17 +14159,25 @@
         <v/>
       </c>
       <c r="AJ22" s="5" t="n"/>
+      <c r="AK22" s="12">
+        <f>IF(B22="","",IF(ISNUMBER(B22),B22,DATE(VALUE(LEFT(B22,4)),VALUE(MID(B22,6,2)),VALUE(MID(B22,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL22" s="12">
+        <f>IF(C22="","",IF(ISNUMBER(C22),C22,DATE(VALUE(LEFT(C22,4)),VALUE(MID(C22,6,2)),VALUE(MID(C22,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="5">
-        <f>IF(AND(B23&lt;&gt;"",C23&lt;&gt;""),C23-B23+1,"")</f>
+        <f>IF(AND(AK23&lt;&gt;"",AL23&lt;&gt;""),AL23-AK23+1,"")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>IF(B23&lt;&gt;"",YEAR(B23),"")</f>
+        <f>IF(AK23&lt;&gt;"",YEAR(AK23),"")</f>
         <v/>
       </c>
       <c r="F23" s="6" t="n"/>
@@ -14107,17 +14265,25 @@
         <v/>
       </c>
       <c r="AJ23" s="5" t="n"/>
+      <c r="AK23" s="12">
+        <f>IF(B23="","",IF(ISNUMBER(B23),B23,DATE(VALUE(LEFT(B23,4)),VALUE(MID(B23,6,2)),VALUE(MID(B23,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL23" s="12">
+        <f>IF(C23="","",IF(ISNUMBER(C23),C23,DATE(VALUE(LEFT(C23,4)),VALUE(MID(C23,6,2)),VALUE(MID(C23,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5">
-        <f>IF(AND(B24&lt;&gt;"",C24&lt;&gt;""),C24-B24+1,"")</f>
+        <f>IF(AND(AK24&lt;&gt;"",AL24&lt;&gt;""),AL24-AK24+1,"")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>IF(B24&lt;&gt;"",YEAR(B24),"")</f>
+        <f>IF(AK24&lt;&gt;"",YEAR(AK24),"")</f>
         <v/>
       </c>
       <c r="F24" s="6" t="n"/>
@@ -14205,17 +14371,25 @@
         <v/>
       </c>
       <c r="AJ24" s="5" t="n"/>
+      <c r="AK24" s="12">
+        <f>IF(B24="","",IF(ISNUMBER(B24),B24,DATE(VALUE(LEFT(B24,4)),VALUE(MID(B24,6,2)),VALUE(MID(B24,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL24" s="12">
+        <f>IF(C24="","",IF(ISNUMBER(C24),C24,DATE(VALUE(LEFT(C24,4)),VALUE(MID(C24,6,2)),VALUE(MID(C24,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5">
-        <f>IF(AND(B25&lt;&gt;"",C25&lt;&gt;""),C25-B25+1,"")</f>
+        <f>IF(AND(AK25&lt;&gt;"",AL25&lt;&gt;""),AL25-AK25+1,"")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>IF(B25&lt;&gt;"",YEAR(B25),"")</f>
+        <f>IF(AK25&lt;&gt;"",YEAR(AK25),"")</f>
         <v/>
       </c>
       <c r="F25" s="6" t="n"/>
@@ -14303,17 +14477,25 @@
         <v/>
       </c>
       <c r="AJ25" s="5" t="n"/>
+      <c r="AK25" s="12">
+        <f>IF(B25="","",IF(ISNUMBER(B25),B25,DATE(VALUE(LEFT(B25,4)),VALUE(MID(B25,6,2)),VALUE(MID(B25,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL25" s="12">
+        <f>IF(C25="","",IF(ISNUMBER(C25),C25,DATE(VALUE(LEFT(C25,4)),VALUE(MID(C25,6,2)),VALUE(MID(C25,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="5">
-        <f>IF(AND(B26&lt;&gt;"",C26&lt;&gt;""),C26-B26+1,"")</f>
+        <f>IF(AND(AK26&lt;&gt;"",AL26&lt;&gt;""),AL26-AK26+1,"")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>IF(B26&lt;&gt;"",YEAR(B26),"")</f>
+        <f>IF(AK26&lt;&gt;"",YEAR(AK26),"")</f>
         <v/>
       </c>
       <c r="F26" s="6" t="n"/>
@@ -14401,17 +14583,25 @@
         <v/>
       </c>
       <c r="AJ26" s="5" t="n"/>
+      <c r="AK26" s="12">
+        <f>IF(B26="","",IF(ISNUMBER(B26),B26,DATE(VALUE(LEFT(B26,4)),VALUE(MID(B26,6,2)),VALUE(MID(B26,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL26" s="12">
+        <f>IF(C26="","",IF(ISNUMBER(C26),C26,DATE(VALUE(LEFT(C26,4)),VALUE(MID(C26,6,2)),VALUE(MID(C26,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5">
-        <f>IF(AND(B27&lt;&gt;"",C27&lt;&gt;""),C27-B27+1,"")</f>
+        <f>IF(AND(AK27&lt;&gt;"",AL27&lt;&gt;""),AL27-AK27+1,"")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>IF(B27&lt;&gt;"",YEAR(B27),"")</f>
+        <f>IF(AK27&lt;&gt;"",YEAR(AK27),"")</f>
         <v/>
       </c>
       <c r="F27" s="6" t="n"/>
@@ -14499,17 +14689,25 @@
         <v/>
       </c>
       <c r="AJ27" s="5" t="n"/>
+      <c r="AK27" s="12">
+        <f>IF(B27="","",IF(ISNUMBER(B27),B27,DATE(VALUE(LEFT(B27,4)),VALUE(MID(B27,6,2)),VALUE(MID(B27,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL27" s="12">
+        <f>IF(C27="","",IF(ISNUMBER(C27),C27,DATE(VALUE(LEFT(C27,4)),VALUE(MID(C27,6,2)),VALUE(MID(C27,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="5">
-        <f>IF(AND(B28&lt;&gt;"",C28&lt;&gt;""),C28-B28+1,"")</f>
+        <f>IF(AND(AK28&lt;&gt;"",AL28&lt;&gt;""),AL28-AK28+1,"")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>IF(B28&lt;&gt;"",YEAR(B28),"")</f>
+        <f>IF(AK28&lt;&gt;"",YEAR(AK28),"")</f>
         <v/>
       </c>
       <c r="F28" s="6" t="n"/>
@@ -14597,17 +14795,25 @@
         <v/>
       </c>
       <c r="AJ28" s="5" t="n"/>
+      <c r="AK28" s="12">
+        <f>IF(B28="","",IF(ISNUMBER(B28),B28,DATE(VALUE(LEFT(B28,4)),VALUE(MID(B28,6,2)),VALUE(MID(B28,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL28" s="12">
+        <f>IF(C28="","",IF(ISNUMBER(C28),C28,DATE(VALUE(LEFT(C28,4)),VALUE(MID(C28,6,2)),VALUE(MID(C28,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="5">
-        <f>IF(AND(B29&lt;&gt;"",C29&lt;&gt;""),C29-B29+1,"")</f>
+        <f>IF(AND(AK29&lt;&gt;"",AL29&lt;&gt;""),AL29-AK29+1,"")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>IF(B29&lt;&gt;"",YEAR(B29),"")</f>
+        <f>IF(AK29&lt;&gt;"",YEAR(AK29),"")</f>
         <v/>
       </c>
       <c r="F29" s="6" t="n"/>
@@ -14695,17 +14901,25 @@
         <v/>
       </c>
       <c r="AJ29" s="5" t="n"/>
+      <c r="AK29" s="12">
+        <f>IF(B29="","",IF(ISNUMBER(B29),B29,DATE(VALUE(LEFT(B29,4)),VALUE(MID(B29,6,2)),VALUE(MID(B29,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL29" s="12">
+        <f>IF(C29="","",IF(ISNUMBER(C29),C29,DATE(VALUE(LEFT(C29,4)),VALUE(MID(C29,6,2)),VALUE(MID(C29,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5">
-        <f>IF(AND(B30&lt;&gt;"",C30&lt;&gt;""),C30-B30+1,"")</f>
+        <f>IF(AND(AK30&lt;&gt;"",AL30&lt;&gt;""),AL30-AK30+1,"")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>IF(B30&lt;&gt;"",YEAR(B30),"")</f>
+        <f>IF(AK30&lt;&gt;"",YEAR(AK30),"")</f>
         <v/>
       </c>
       <c r="F30" s="6" t="n"/>
@@ -14793,17 +15007,25 @@
         <v/>
       </c>
       <c r="AJ30" s="5" t="n"/>
+      <c r="AK30" s="12">
+        <f>IF(B30="","",IF(ISNUMBER(B30),B30,DATE(VALUE(LEFT(B30,4)),VALUE(MID(B30,6,2)),VALUE(MID(B30,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL30" s="12">
+        <f>IF(C30="","",IF(ISNUMBER(C30),C30,DATE(VALUE(LEFT(C30,4)),VALUE(MID(C30,6,2)),VALUE(MID(C30,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5">
-        <f>IF(AND(B31&lt;&gt;"",C31&lt;&gt;""),C31-B31+1,"")</f>
+        <f>IF(AND(AK31&lt;&gt;"",AL31&lt;&gt;""),AL31-AK31+1,"")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>IF(B31&lt;&gt;"",YEAR(B31),"")</f>
+        <f>IF(AK31&lt;&gt;"",YEAR(AK31),"")</f>
         <v/>
       </c>
       <c r="F31" s="6" t="n"/>
@@ -14891,17 +15113,25 @@
         <v/>
       </c>
       <c r="AJ31" s="5" t="n"/>
+      <c r="AK31" s="12">
+        <f>IF(B31="","",IF(ISNUMBER(B31),B31,DATE(VALUE(LEFT(B31,4)),VALUE(MID(B31,6,2)),VALUE(MID(B31,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL31" s="12">
+        <f>IF(C31="","",IF(ISNUMBER(C31),C31,DATE(VALUE(LEFT(C31,4)),VALUE(MID(C31,6,2)),VALUE(MID(C31,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5">
-        <f>IF(AND(B32&lt;&gt;"",C32&lt;&gt;""),C32-B32+1,"")</f>
+        <f>IF(AND(AK32&lt;&gt;"",AL32&lt;&gt;""),AL32-AK32+1,"")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>IF(B32&lt;&gt;"",YEAR(B32),"")</f>
+        <f>IF(AK32&lt;&gt;"",YEAR(AK32),"")</f>
         <v/>
       </c>
       <c r="F32" s="6" t="n"/>
@@ -14989,17 +15219,25 @@
         <v/>
       </c>
       <c r="AJ32" s="5" t="n"/>
+      <c r="AK32" s="12">
+        <f>IF(B32="","",IF(ISNUMBER(B32),B32,DATE(VALUE(LEFT(B32,4)),VALUE(MID(B32,6,2)),VALUE(MID(B32,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL32" s="12">
+        <f>IF(C32="","",IF(ISNUMBER(C32),C32,DATE(VALUE(LEFT(C32,4)),VALUE(MID(C32,6,2)),VALUE(MID(C32,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5">
-        <f>IF(AND(B33&lt;&gt;"",C33&lt;&gt;""),C33-B33+1,"")</f>
+        <f>IF(AND(AK33&lt;&gt;"",AL33&lt;&gt;""),AL33-AK33+1,"")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>IF(B33&lt;&gt;"",YEAR(B33),"")</f>
+        <f>IF(AK33&lt;&gt;"",YEAR(AK33),"")</f>
         <v/>
       </c>
       <c r="F33" s="6" t="n"/>
@@ -15087,17 +15325,25 @@
         <v/>
       </c>
       <c r="AJ33" s="5" t="n"/>
+      <c r="AK33" s="12">
+        <f>IF(B33="","",IF(ISNUMBER(B33),B33,DATE(VALUE(LEFT(B33,4)),VALUE(MID(B33,6,2)),VALUE(MID(B33,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL33" s="12">
+        <f>IF(C33="","",IF(ISNUMBER(C33),C33,DATE(VALUE(LEFT(C33,4)),VALUE(MID(C33,6,2)),VALUE(MID(C33,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5">
-        <f>IF(AND(B34&lt;&gt;"",C34&lt;&gt;""),C34-B34+1,"")</f>
+        <f>IF(AND(AK34&lt;&gt;"",AL34&lt;&gt;""),AL34-AK34+1,"")</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>IF(B34&lt;&gt;"",YEAR(B34),"")</f>
+        <f>IF(AK34&lt;&gt;"",YEAR(AK34),"")</f>
         <v/>
       </c>
       <c r="F34" s="6" t="n"/>
@@ -15185,17 +15431,25 @@
         <v/>
       </c>
       <c r="AJ34" s="5" t="n"/>
+      <c r="AK34" s="12">
+        <f>IF(B34="","",IF(ISNUMBER(B34),B34,DATE(VALUE(LEFT(B34,4)),VALUE(MID(B34,6,2)),VALUE(MID(B34,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL34" s="12">
+        <f>IF(C34="","",IF(ISNUMBER(C34),C34,DATE(VALUE(LEFT(C34,4)),VALUE(MID(C34,6,2)),VALUE(MID(C34,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5">
-        <f>IF(AND(B35&lt;&gt;"",C35&lt;&gt;""),C35-B35+1,"")</f>
+        <f>IF(AND(AK35&lt;&gt;"",AL35&lt;&gt;""),AL35-AK35+1,"")</f>
         <v/>
       </c>
       <c r="E35" s="5">
-        <f>IF(B35&lt;&gt;"",YEAR(B35),"")</f>
+        <f>IF(AK35&lt;&gt;"",YEAR(AK35),"")</f>
         <v/>
       </c>
       <c r="F35" s="6" t="n"/>
@@ -15283,17 +15537,25 @@
         <v/>
       </c>
       <c r="AJ35" s="5" t="n"/>
+      <c r="AK35" s="12">
+        <f>IF(B35="","",IF(ISNUMBER(B35),B35,DATE(VALUE(LEFT(B35,4)),VALUE(MID(B35,6,2)),VALUE(MID(B35,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL35" s="12">
+        <f>IF(C35="","",IF(ISNUMBER(C35),C35,DATE(VALUE(LEFT(C35,4)),VALUE(MID(C35,6,2)),VALUE(MID(C35,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="5">
-        <f>IF(AND(B36&lt;&gt;"",C36&lt;&gt;""),C36-B36+1,"")</f>
+        <f>IF(AND(AK36&lt;&gt;"",AL36&lt;&gt;""),AL36-AK36+1,"")</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>IF(B36&lt;&gt;"",YEAR(B36),"")</f>
+        <f>IF(AK36&lt;&gt;"",YEAR(AK36),"")</f>
         <v/>
       </c>
       <c r="F36" s="6" t="n"/>
@@ -15381,17 +15643,25 @@
         <v/>
       </c>
       <c r="AJ36" s="5" t="n"/>
+      <c r="AK36" s="12">
+        <f>IF(B36="","",IF(ISNUMBER(B36),B36,DATE(VALUE(LEFT(B36,4)),VALUE(MID(B36,6,2)),VALUE(MID(B36,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL36" s="12">
+        <f>IF(C36="","",IF(ISNUMBER(C36),C36,DATE(VALUE(LEFT(C36,4)),VALUE(MID(C36,6,2)),VALUE(MID(C36,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5">
-        <f>IF(AND(B37&lt;&gt;"",C37&lt;&gt;""),C37-B37+1,"")</f>
+        <f>IF(AND(AK37&lt;&gt;"",AL37&lt;&gt;""),AL37-AK37+1,"")</f>
         <v/>
       </c>
       <c r="E37" s="5">
-        <f>IF(B37&lt;&gt;"",YEAR(B37),"")</f>
+        <f>IF(AK37&lt;&gt;"",YEAR(AK37),"")</f>
         <v/>
       </c>
       <c r="F37" s="6" t="n"/>
@@ -15479,17 +15749,25 @@
         <v/>
       </c>
       <c r="AJ37" s="5" t="n"/>
+      <c r="AK37" s="12">
+        <f>IF(B37="","",IF(ISNUMBER(B37),B37,DATE(VALUE(LEFT(B37,4)),VALUE(MID(B37,6,2)),VALUE(MID(B37,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL37" s="12">
+        <f>IF(C37="","",IF(ISNUMBER(C37),C37,DATE(VALUE(LEFT(C37,4)),VALUE(MID(C37,6,2)),VALUE(MID(C37,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
       <c r="D38" s="5">
-        <f>IF(AND(B38&lt;&gt;"",C38&lt;&gt;""),C38-B38+1,"")</f>
+        <f>IF(AND(AK38&lt;&gt;"",AL38&lt;&gt;""),AL38-AK38+1,"")</f>
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>IF(B38&lt;&gt;"",YEAR(B38),"")</f>
+        <f>IF(AK38&lt;&gt;"",YEAR(AK38),"")</f>
         <v/>
       </c>
       <c r="F38" s="6" t="n"/>
@@ -15577,17 +15855,25 @@
         <v/>
       </c>
       <c r="AJ38" s="5" t="n"/>
+      <c r="AK38" s="12">
+        <f>IF(B38="","",IF(ISNUMBER(B38),B38,DATE(VALUE(LEFT(B38,4)),VALUE(MID(B38,6,2)),VALUE(MID(B38,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL38" s="12">
+        <f>IF(C38="","",IF(ISNUMBER(C38),C38,DATE(VALUE(LEFT(C38,4)),VALUE(MID(C38,6,2)),VALUE(MID(C38,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="5">
-        <f>IF(AND(B39&lt;&gt;"",C39&lt;&gt;""),C39-B39+1,"")</f>
+        <f>IF(AND(AK39&lt;&gt;"",AL39&lt;&gt;""),AL39-AK39+1,"")</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>IF(B39&lt;&gt;"",YEAR(B39),"")</f>
+        <f>IF(AK39&lt;&gt;"",YEAR(AK39),"")</f>
         <v/>
       </c>
       <c r="F39" s="6" t="n"/>
@@ -15675,17 +15961,25 @@
         <v/>
       </c>
       <c r="AJ39" s="5" t="n"/>
+      <c r="AK39" s="12">
+        <f>IF(B39="","",IF(ISNUMBER(B39),B39,DATE(VALUE(LEFT(B39,4)),VALUE(MID(B39,6,2)),VALUE(MID(B39,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL39" s="12">
+        <f>IF(C39="","",IF(ISNUMBER(C39),C39,DATE(VALUE(LEFT(C39,4)),VALUE(MID(C39,6,2)),VALUE(MID(C39,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="5">
-        <f>IF(AND(B40&lt;&gt;"",C40&lt;&gt;""),C40-B40+1,"")</f>
+        <f>IF(AND(AK40&lt;&gt;"",AL40&lt;&gt;""),AL40-AK40+1,"")</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(B40&lt;&gt;"",YEAR(B40),"")</f>
+        <f>IF(AK40&lt;&gt;"",YEAR(AK40),"")</f>
         <v/>
       </c>
       <c r="F40" s="6" t="n"/>
@@ -15773,17 +16067,25 @@
         <v/>
       </c>
       <c r="AJ40" s="5" t="n"/>
+      <c r="AK40" s="12">
+        <f>IF(B40="","",IF(ISNUMBER(B40),B40,DATE(VALUE(LEFT(B40,4)),VALUE(MID(B40,6,2)),VALUE(MID(B40,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL40" s="12">
+        <f>IF(C40="","",IF(ISNUMBER(C40),C40,DATE(VALUE(LEFT(C40,4)),VALUE(MID(C40,6,2)),VALUE(MID(C40,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5">
-        <f>IF(AND(B41&lt;&gt;"",C41&lt;&gt;""),C41-B41+1,"")</f>
+        <f>IF(AND(AK41&lt;&gt;"",AL41&lt;&gt;""),AL41-AK41+1,"")</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>IF(B41&lt;&gt;"",YEAR(B41),"")</f>
+        <f>IF(AK41&lt;&gt;"",YEAR(AK41),"")</f>
         <v/>
       </c>
       <c r="F41" s="6" t="n"/>
@@ -15871,17 +16173,25 @@
         <v/>
       </c>
       <c r="AJ41" s="5" t="n"/>
+      <c r="AK41" s="12">
+        <f>IF(B41="","",IF(ISNUMBER(B41),B41,DATE(VALUE(LEFT(B41,4)),VALUE(MID(B41,6,2)),VALUE(MID(B41,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL41" s="12">
+        <f>IF(C41="","",IF(ISNUMBER(C41),C41,DATE(VALUE(LEFT(C41,4)),VALUE(MID(C41,6,2)),VALUE(MID(C41,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="5">
-        <f>IF(AND(B42&lt;&gt;"",C42&lt;&gt;""),C42-B42+1,"")</f>
+        <f>IF(AND(AK42&lt;&gt;"",AL42&lt;&gt;""),AL42-AK42+1,"")</f>
         <v/>
       </c>
       <c r="E42" s="5">
-        <f>IF(B42&lt;&gt;"",YEAR(B42),"")</f>
+        <f>IF(AK42&lt;&gt;"",YEAR(AK42),"")</f>
         <v/>
       </c>
       <c r="F42" s="6" t="n"/>
@@ -15969,17 +16279,25 @@
         <v/>
       </c>
       <c r="AJ42" s="5" t="n"/>
+      <c r="AK42" s="12">
+        <f>IF(B42="","",IF(ISNUMBER(B42),B42,DATE(VALUE(LEFT(B42,4)),VALUE(MID(B42,6,2)),VALUE(MID(B42,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL42" s="12">
+        <f>IF(C42="","",IF(ISNUMBER(C42),C42,DATE(VALUE(LEFT(C42,4)),VALUE(MID(C42,6,2)),VALUE(MID(C42,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5">
-        <f>IF(AND(B43&lt;&gt;"",C43&lt;&gt;""),C43-B43+1,"")</f>
+        <f>IF(AND(AK43&lt;&gt;"",AL43&lt;&gt;""),AL43-AK43+1,"")</f>
         <v/>
       </c>
       <c r="E43" s="5">
-        <f>IF(B43&lt;&gt;"",YEAR(B43),"")</f>
+        <f>IF(AK43&lt;&gt;"",YEAR(AK43),"")</f>
         <v/>
       </c>
       <c r="F43" s="6" t="n"/>
@@ -16067,17 +16385,25 @@
         <v/>
       </c>
       <c r="AJ43" s="5" t="n"/>
+      <c r="AK43" s="12">
+        <f>IF(B43="","",IF(ISNUMBER(B43),B43,DATE(VALUE(LEFT(B43,4)),VALUE(MID(B43,6,2)),VALUE(MID(B43,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL43" s="12">
+        <f>IF(C43="","",IF(ISNUMBER(C43),C43,DATE(VALUE(LEFT(C43,4)),VALUE(MID(C43,6,2)),VALUE(MID(C43,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="5">
-        <f>IF(AND(B44&lt;&gt;"",C44&lt;&gt;""),C44-B44+1,"")</f>
+        <f>IF(AND(AK44&lt;&gt;"",AL44&lt;&gt;""),AL44-AK44+1,"")</f>
         <v/>
       </c>
       <c r="E44" s="5">
-        <f>IF(B44&lt;&gt;"",YEAR(B44),"")</f>
+        <f>IF(AK44&lt;&gt;"",YEAR(AK44),"")</f>
         <v/>
       </c>
       <c r="F44" s="6" t="n"/>
@@ -16165,17 +16491,25 @@
         <v/>
       </c>
       <c r="AJ44" s="5" t="n"/>
+      <c r="AK44" s="12">
+        <f>IF(B44="","",IF(ISNUMBER(B44),B44,DATE(VALUE(LEFT(B44,4)),VALUE(MID(B44,6,2)),VALUE(MID(B44,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL44" s="12">
+        <f>IF(C44="","",IF(ISNUMBER(C44),C44,DATE(VALUE(LEFT(C44,4)),VALUE(MID(C44,6,2)),VALUE(MID(C44,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5">
-        <f>IF(AND(B45&lt;&gt;"",C45&lt;&gt;""),C45-B45+1,"")</f>
+        <f>IF(AND(AK45&lt;&gt;"",AL45&lt;&gt;""),AL45-AK45+1,"")</f>
         <v/>
       </c>
       <c r="E45" s="5">
-        <f>IF(B45&lt;&gt;"",YEAR(B45),"")</f>
+        <f>IF(AK45&lt;&gt;"",YEAR(AK45),"")</f>
         <v/>
       </c>
       <c r="F45" s="6" t="n"/>
@@ -16263,17 +16597,25 @@
         <v/>
       </c>
       <c r="AJ45" s="5" t="n"/>
+      <c r="AK45" s="12">
+        <f>IF(B45="","",IF(ISNUMBER(B45),B45,DATE(VALUE(LEFT(B45,4)),VALUE(MID(B45,6,2)),VALUE(MID(B45,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL45" s="12">
+        <f>IF(C45="","",IF(ISNUMBER(C45),C45,DATE(VALUE(LEFT(C45,4)),VALUE(MID(C45,6,2)),VALUE(MID(C45,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="5">
-        <f>IF(AND(B46&lt;&gt;"",C46&lt;&gt;""),C46-B46+1,"")</f>
+        <f>IF(AND(AK46&lt;&gt;"",AL46&lt;&gt;""),AL46-AK46+1,"")</f>
         <v/>
       </c>
       <c r="E46" s="5">
-        <f>IF(B46&lt;&gt;"",YEAR(B46),"")</f>
+        <f>IF(AK46&lt;&gt;"",YEAR(AK46),"")</f>
         <v/>
       </c>
       <c r="F46" s="6" t="n"/>
@@ -16361,17 +16703,25 @@
         <v/>
       </c>
       <c r="AJ46" s="5" t="n"/>
+      <c r="AK46" s="12">
+        <f>IF(B46="","",IF(ISNUMBER(B46),B46,DATE(VALUE(LEFT(B46,4)),VALUE(MID(B46,6,2)),VALUE(MID(B46,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL46" s="12">
+        <f>IF(C46="","",IF(ISNUMBER(C46),C46,DATE(VALUE(LEFT(C46,4)),VALUE(MID(C46,6,2)),VALUE(MID(C46,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="5">
-        <f>IF(AND(B47&lt;&gt;"",C47&lt;&gt;""),C47-B47+1,"")</f>
+        <f>IF(AND(AK47&lt;&gt;"",AL47&lt;&gt;""),AL47-AK47+1,"")</f>
         <v/>
       </c>
       <c r="E47" s="5">
-        <f>IF(B47&lt;&gt;"",YEAR(B47),"")</f>
+        <f>IF(AK47&lt;&gt;"",YEAR(AK47),"")</f>
         <v/>
       </c>
       <c r="F47" s="6" t="n"/>
@@ -16459,17 +16809,25 @@
         <v/>
       </c>
       <c r="AJ47" s="5" t="n"/>
+      <c r="AK47" s="12">
+        <f>IF(B47="","",IF(ISNUMBER(B47),B47,DATE(VALUE(LEFT(B47,4)),VALUE(MID(B47,6,2)),VALUE(MID(B47,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL47" s="12">
+        <f>IF(C47="","",IF(ISNUMBER(C47),C47,DATE(VALUE(LEFT(C47,4)),VALUE(MID(C47,6,2)),VALUE(MID(C47,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="5">
-        <f>IF(AND(B48&lt;&gt;"",C48&lt;&gt;""),C48-B48+1,"")</f>
+        <f>IF(AND(AK48&lt;&gt;"",AL48&lt;&gt;""),AL48-AK48+1,"")</f>
         <v/>
       </c>
       <c r="E48" s="5">
-        <f>IF(B48&lt;&gt;"",YEAR(B48),"")</f>
+        <f>IF(AK48&lt;&gt;"",YEAR(AK48),"")</f>
         <v/>
       </c>
       <c r="F48" s="6" t="n"/>
@@ -16557,17 +16915,25 @@
         <v/>
       </c>
       <c r="AJ48" s="5" t="n"/>
+      <c r="AK48" s="12">
+        <f>IF(B48="","",IF(ISNUMBER(B48),B48,DATE(VALUE(LEFT(B48,4)),VALUE(MID(B48,6,2)),VALUE(MID(B48,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL48" s="12">
+        <f>IF(C48="","",IF(ISNUMBER(C48),C48,DATE(VALUE(LEFT(C48,4)),VALUE(MID(C48,6,2)),VALUE(MID(C48,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="5">
-        <f>IF(AND(B49&lt;&gt;"",C49&lt;&gt;""),C49-B49+1,"")</f>
+        <f>IF(AND(AK49&lt;&gt;"",AL49&lt;&gt;""),AL49-AK49+1,"")</f>
         <v/>
       </c>
       <c r="E49" s="5">
-        <f>IF(B49&lt;&gt;"",YEAR(B49),"")</f>
+        <f>IF(AK49&lt;&gt;"",YEAR(AK49),"")</f>
         <v/>
       </c>
       <c r="F49" s="6" t="n"/>
@@ -16655,17 +17021,25 @@
         <v/>
       </c>
       <c r="AJ49" s="5" t="n"/>
+      <c r="AK49" s="12">
+        <f>IF(B49="","",IF(ISNUMBER(B49),B49,DATE(VALUE(LEFT(B49,4)),VALUE(MID(B49,6,2)),VALUE(MID(B49,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL49" s="12">
+        <f>IF(C49="","",IF(ISNUMBER(C49),C49,DATE(VALUE(LEFT(C49,4)),VALUE(MID(C49,6,2)),VALUE(MID(C49,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="5">
-        <f>IF(AND(B50&lt;&gt;"",C50&lt;&gt;""),C50-B50+1,"")</f>
+        <f>IF(AND(AK50&lt;&gt;"",AL50&lt;&gt;""),AL50-AK50+1,"")</f>
         <v/>
       </c>
       <c r="E50" s="5">
-        <f>IF(B50&lt;&gt;"",YEAR(B50),"")</f>
+        <f>IF(AK50&lt;&gt;"",YEAR(AK50),"")</f>
         <v/>
       </c>
       <c r="F50" s="6" t="n"/>
@@ -16753,17 +17127,25 @@
         <v/>
       </c>
       <c r="AJ50" s="5" t="n"/>
+      <c r="AK50" s="12">
+        <f>IF(B50="","",IF(ISNUMBER(B50),B50,DATE(VALUE(LEFT(B50,4)),VALUE(MID(B50,6,2)),VALUE(MID(B50,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL50" s="12">
+        <f>IF(C50="","",IF(ISNUMBER(C50),C50,DATE(VALUE(LEFT(C50,4)),VALUE(MID(C50,6,2)),VALUE(MID(C50,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="5">
-        <f>IF(AND(B51&lt;&gt;"",C51&lt;&gt;""),C51-B51+1,"")</f>
+        <f>IF(AND(AK51&lt;&gt;"",AL51&lt;&gt;""),AL51-AK51+1,"")</f>
         <v/>
       </c>
       <c r="E51" s="5">
-        <f>IF(B51&lt;&gt;"",YEAR(B51),"")</f>
+        <f>IF(AK51&lt;&gt;"",YEAR(AK51),"")</f>
         <v/>
       </c>
       <c r="F51" s="6" t="n"/>
@@ -16851,17 +17233,25 @@
         <v/>
       </c>
       <c r="AJ51" s="5" t="n"/>
+      <c r="AK51" s="12">
+        <f>IF(B51="","",IF(ISNUMBER(B51),B51,DATE(VALUE(LEFT(B51,4)),VALUE(MID(B51,6,2)),VALUE(MID(B51,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL51" s="12">
+        <f>IF(C51="","",IF(ISNUMBER(C51),C51,DATE(VALUE(LEFT(C51,4)),VALUE(MID(C51,6,2)),VALUE(MID(C51,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="5" t="n"/>
       <c r="D52" s="5">
-        <f>IF(AND(B52&lt;&gt;"",C52&lt;&gt;""),C52-B52+1,"")</f>
+        <f>IF(AND(AK52&lt;&gt;"",AL52&lt;&gt;""),AL52-AK52+1,"")</f>
         <v/>
       </c>
       <c r="E52" s="5">
-        <f>IF(B52&lt;&gt;"",YEAR(B52),"")</f>
+        <f>IF(AK52&lt;&gt;"",YEAR(AK52),"")</f>
         <v/>
       </c>
       <c r="F52" s="6" t="n"/>
@@ -16949,17 +17339,25 @@
         <v/>
       </c>
       <c r="AJ52" s="5" t="n"/>
+      <c r="AK52" s="12">
+        <f>IF(B52="","",IF(ISNUMBER(B52),B52,DATE(VALUE(LEFT(B52,4)),VALUE(MID(B52,6,2)),VALUE(MID(B52,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL52" s="12">
+        <f>IF(C52="","",IF(ISNUMBER(C52),C52,DATE(VALUE(LEFT(C52,4)),VALUE(MID(C52,6,2)),VALUE(MID(C52,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5">
-        <f>IF(AND(B53&lt;&gt;"",C53&lt;&gt;""),C53-B53+1,"")</f>
+        <f>IF(AND(AK53&lt;&gt;"",AL53&lt;&gt;""),AL53-AK53+1,"")</f>
         <v/>
       </c>
       <c r="E53" s="5">
-        <f>IF(B53&lt;&gt;"",YEAR(B53),"")</f>
+        <f>IF(AK53&lt;&gt;"",YEAR(AK53),"")</f>
         <v/>
       </c>
       <c r="F53" s="6" t="n"/>
@@ -17047,17 +17445,25 @@
         <v/>
       </c>
       <c r="AJ53" s="5" t="n"/>
+      <c r="AK53" s="12">
+        <f>IF(B53="","",IF(ISNUMBER(B53),B53,DATE(VALUE(LEFT(B53,4)),VALUE(MID(B53,6,2)),VALUE(MID(B53,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL53" s="12">
+        <f>IF(C53="","",IF(ISNUMBER(C53),C53,DATE(VALUE(LEFT(C53,4)),VALUE(MID(C53,6,2)),VALUE(MID(C53,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="5" t="n"/>
       <c r="D54" s="5">
-        <f>IF(AND(B54&lt;&gt;"",C54&lt;&gt;""),C54-B54+1,"")</f>
+        <f>IF(AND(AK54&lt;&gt;"",AL54&lt;&gt;""),AL54-AK54+1,"")</f>
         <v/>
       </c>
       <c r="E54" s="5">
-        <f>IF(B54&lt;&gt;"",YEAR(B54),"")</f>
+        <f>IF(AK54&lt;&gt;"",YEAR(AK54),"")</f>
         <v/>
       </c>
       <c r="F54" s="6" t="n"/>
@@ -17145,17 +17551,25 @@
         <v/>
       </c>
       <c r="AJ54" s="5" t="n"/>
+      <c r="AK54" s="12">
+        <f>IF(B54="","",IF(ISNUMBER(B54),B54,DATE(VALUE(LEFT(B54,4)),VALUE(MID(B54,6,2)),VALUE(MID(B54,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL54" s="12">
+        <f>IF(C54="","",IF(ISNUMBER(C54),C54,DATE(VALUE(LEFT(C54,4)),VALUE(MID(C54,6,2)),VALUE(MID(C54,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5">
-        <f>IF(AND(B55&lt;&gt;"",C55&lt;&gt;""),C55-B55+1,"")</f>
+        <f>IF(AND(AK55&lt;&gt;"",AL55&lt;&gt;""),AL55-AK55+1,"")</f>
         <v/>
       </c>
       <c r="E55" s="5">
-        <f>IF(B55&lt;&gt;"",YEAR(B55),"")</f>
+        <f>IF(AK55&lt;&gt;"",YEAR(AK55),"")</f>
         <v/>
       </c>
       <c r="F55" s="6" t="n"/>
@@ -17243,17 +17657,25 @@
         <v/>
       </c>
       <c r="AJ55" s="5" t="n"/>
+      <c r="AK55" s="12">
+        <f>IF(B55="","",IF(ISNUMBER(B55),B55,DATE(VALUE(LEFT(B55,4)),VALUE(MID(B55,6,2)),VALUE(MID(B55,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL55" s="12">
+        <f>IF(C55="","",IF(ISNUMBER(C55),C55,DATE(VALUE(LEFT(C55,4)),VALUE(MID(C55,6,2)),VALUE(MID(C55,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="5" t="n"/>
       <c r="D56" s="5">
-        <f>IF(AND(B56&lt;&gt;"",C56&lt;&gt;""),C56-B56+1,"")</f>
+        <f>IF(AND(AK56&lt;&gt;"",AL56&lt;&gt;""),AL56-AK56+1,"")</f>
         <v/>
       </c>
       <c r="E56" s="5">
-        <f>IF(B56&lt;&gt;"",YEAR(B56),"")</f>
+        <f>IF(AK56&lt;&gt;"",YEAR(AK56),"")</f>
         <v/>
       </c>
       <c r="F56" s="6" t="n"/>
@@ -17341,17 +17763,25 @@
         <v/>
       </c>
       <c r="AJ56" s="5" t="n"/>
+      <c r="AK56" s="12">
+        <f>IF(B56="","",IF(ISNUMBER(B56),B56,DATE(VALUE(LEFT(B56,4)),VALUE(MID(B56,6,2)),VALUE(MID(B56,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL56" s="12">
+        <f>IF(C56="","",IF(ISNUMBER(C56),C56,DATE(VALUE(LEFT(C56,4)),VALUE(MID(C56,6,2)),VALUE(MID(C56,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="5" t="n"/>
       <c r="D57" s="5">
-        <f>IF(AND(B57&lt;&gt;"",C57&lt;&gt;""),C57-B57+1,"")</f>
+        <f>IF(AND(AK57&lt;&gt;"",AL57&lt;&gt;""),AL57-AK57+1,"")</f>
         <v/>
       </c>
       <c r="E57" s="5">
-        <f>IF(B57&lt;&gt;"",YEAR(B57),"")</f>
+        <f>IF(AK57&lt;&gt;"",YEAR(AK57),"")</f>
         <v/>
       </c>
       <c r="F57" s="6" t="n"/>
@@ -17439,17 +17869,25 @@
         <v/>
       </c>
       <c r="AJ57" s="5" t="n"/>
+      <c r="AK57" s="12">
+        <f>IF(B57="","",IF(ISNUMBER(B57),B57,DATE(VALUE(LEFT(B57,4)),VALUE(MID(B57,6,2)),VALUE(MID(B57,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL57" s="12">
+        <f>IF(C57="","",IF(ISNUMBER(C57),C57,DATE(VALUE(LEFT(C57,4)),VALUE(MID(C57,6,2)),VALUE(MID(C57,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="n"/>
       <c r="D58" s="5">
-        <f>IF(AND(B58&lt;&gt;"",C58&lt;&gt;""),C58-B58+1,"")</f>
+        <f>IF(AND(AK58&lt;&gt;"",AL58&lt;&gt;""),AL58-AK58+1,"")</f>
         <v/>
       </c>
       <c r="E58" s="5">
-        <f>IF(B58&lt;&gt;"",YEAR(B58),"")</f>
+        <f>IF(AK58&lt;&gt;"",YEAR(AK58),"")</f>
         <v/>
       </c>
       <c r="F58" s="6" t="n"/>
@@ -17537,17 +17975,25 @@
         <v/>
       </c>
       <c r="AJ58" s="5" t="n"/>
+      <c r="AK58" s="12">
+        <f>IF(B58="","",IF(ISNUMBER(B58),B58,DATE(VALUE(LEFT(B58,4)),VALUE(MID(B58,6,2)),VALUE(MID(B58,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL58" s="12">
+        <f>IF(C58="","",IF(ISNUMBER(C58),C58,DATE(VALUE(LEFT(C58,4)),VALUE(MID(C58,6,2)),VALUE(MID(C58,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="5" t="n"/>
       <c r="D59" s="5">
-        <f>IF(AND(B59&lt;&gt;"",C59&lt;&gt;""),C59-B59+1,"")</f>
+        <f>IF(AND(AK59&lt;&gt;"",AL59&lt;&gt;""),AL59-AK59+1,"")</f>
         <v/>
       </c>
       <c r="E59" s="5">
-        <f>IF(B59&lt;&gt;"",YEAR(B59),"")</f>
+        <f>IF(AK59&lt;&gt;"",YEAR(AK59),"")</f>
         <v/>
       </c>
       <c r="F59" s="6" t="n"/>
@@ -17635,17 +18081,25 @@
         <v/>
       </c>
       <c r="AJ59" s="5" t="n"/>
+      <c r="AK59" s="12">
+        <f>IF(B59="","",IF(ISNUMBER(B59),B59,DATE(VALUE(LEFT(B59,4)),VALUE(MID(B59,6,2)),VALUE(MID(B59,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL59" s="12">
+        <f>IF(C59="","",IF(ISNUMBER(C59),C59,DATE(VALUE(LEFT(C59,4)),VALUE(MID(C59,6,2)),VALUE(MID(C59,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="5" t="n"/>
       <c r="D60" s="5">
-        <f>IF(AND(B60&lt;&gt;"",C60&lt;&gt;""),C60-B60+1,"")</f>
+        <f>IF(AND(AK60&lt;&gt;"",AL60&lt;&gt;""),AL60-AK60+1,"")</f>
         <v/>
       </c>
       <c r="E60" s="5">
-        <f>IF(B60&lt;&gt;"",YEAR(B60),"")</f>
+        <f>IF(AK60&lt;&gt;"",YEAR(AK60),"")</f>
         <v/>
       </c>
       <c r="F60" s="6" t="n"/>
@@ -17733,17 +18187,25 @@
         <v/>
       </c>
       <c r="AJ60" s="5" t="n"/>
+      <c r="AK60" s="12">
+        <f>IF(B60="","",IF(ISNUMBER(B60),B60,DATE(VALUE(LEFT(B60,4)),VALUE(MID(B60,6,2)),VALUE(MID(B60,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL60" s="12">
+        <f>IF(C60="","",IF(ISNUMBER(C60),C60,DATE(VALUE(LEFT(C60,4)),VALUE(MID(C60,6,2)),VALUE(MID(C60,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="5" t="n"/>
       <c r="D61" s="5">
-        <f>IF(AND(B61&lt;&gt;"",C61&lt;&gt;""),C61-B61+1,"")</f>
+        <f>IF(AND(AK61&lt;&gt;"",AL61&lt;&gt;""),AL61-AK61+1,"")</f>
         <v/>
       </c>
       <c r="E61" s="5">
-        <f>IF(B61&lt;&gt;"",YEAR(B61),"")</f>
+        <f>IF(AK61&lt;&gt;"",YEAR(AK61),"")</f>
         <v/>
       </c>
       <c r="F61" s="6" t="n"/>
@@ -17831,17 +18293,25 @@
         <v/>
       </c>
       <c r="AJ61" s="5" t="n"/>
+      <c r="AK61" s="12">
+        <f>IF(B61="","",IF(ISNUMBER(B61),B61,DATE(VALUE(LEFT(B61,4)),VALUE(MID(B61,6,2)),VALUE(MID(B61,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL61" s="12">
+        <f>IF(C61="","",IF(ISNUMBER(C61),C61,DATE(VALUE(LEFT(C61,4)),VALUE(MID(C61,6,2)),VALUE(MID(C61,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="5" t="n"/>
       <c r="D62" s="5">
-        <f>IF(AND(B62&lt;&gt;"",C62&lt;&gt;""),C62-B62+1,"")</f>
+        <f>IF(AND(AK62&lt;&gt;"",AL62&lt;&gt;""),AL62-AK62+1,"")</f>
         <v/>
       </c>
       <c r="E62" s="5">
-        <f>IF(B62&lt;&gt;"",YEAR(B62),"")</f>
+        <f>IF(AK62&lt;&gt;"",YEAR(AK62),"")</f>
         <v/>
       </c>
       <c r="F62" s="6" t="n"/>
@@ -17929,17 +18399,25 @@
         <v/>
       </c>
       <c r="AJ62" s="5" t="n"/>
+      <c r="AK62" s="12">
+        <f>IF(B62="","",IF(ISNUMBER(B62),B62,DATE(VALUE(LEFT(B62,4)),VALUE(MID(B62,6,2)),VALUE(MID(B62,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL62" s="12">
+        <f>IF(C62="","",IF(ISNUMBER(C62),C62,DATE(VALUE(LEFT(C62,4)),VALUE(MID(C62,6,2)),VALUE(MID(C62,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="5" t="n"/>
       <c r="D63" s="5">
-        <f>IF(AND(B63&lt;&gt;"",C63&lt;&gt;""),C63-B63+1,"")</f>
+        <f>IF(AND(AK63&lt;&gt;"",AL63&lt;&gt;""),AL63-AK63+1,"")</f>
         <v/>
       </c>
       <c r="E63" s="5">
-        <f>IF(B63&lt;&gt;"",YEAR(B63),"")</f>
+        <f>IF(AK63&lt;&gt;"",YEAR(AK63),"")</f>
         <v/>
       </c>
       <c r="F63" s="6" t="n"/>
@@ -18027,17 +18505,25 @@
         <v/>
       </c>
       <c r="AJ63" s="5" t="n"/>
+      <c r="AK63" s="12">
+        <f>IF(B63="","",IF(ISNUMBER(B63),B63,DATE(VALUE(LEFT(B63,4)),VALUE(MID(B63,6,2)),VALUE(MID(B63,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL63" s="12">
+        <f>IF(C63="","",IF(ISNUMBER(C63),C63,DATE(VALUE(LEFT(C63,4)),VALUE(MID(C63,6,2)),VALUE(MID(C63,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="5" t="n"/>
       <c r="D64" s="5">
-        <f>IF(AND(B64&lt;&gt;"",C64&lt;&gt;""),C64-B64+1,"")</f>
+        <f>IF(AND(AK64&lt;&gt;"",AL64&lt;&gt;""),AL64-AK64+1,"")</f>
         <v/>
       </c>
       <c r="E64" s="5">
-        <f>IF(B64&lt;&gt;"",YEAR(B64),"")</f>
+        <f>IF(AK64&lt;&gt;"",YEAR(AK64),"")</f>
         <v/>
       </c>
       <c r="F64" s="6" t="n"/>
@@ -18125,17 +18611,25 @@
         <v/>
       </c>
       <c r="AJ64" s="5" t="n"/>
+      <c r="AK64" s="12">
+        <f>IF(B64="","",IF(ISNUMBER(B64),B64,DATE(VALUE(LEFT(B64,4)),VALUE(MID(B64,6,2)),VALUE(MID(B64,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL64" s="12">
+        <f>IF(C64="","",IF(ISNUMBER(C64),C64,DATE(VALUE(LEFT(C64,4)),VALUE(MID(C64,6,2)),VALUE(MID(C64,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="5">
-        <f>IF(AND(B65&lt;&gt;"",C65&lt;&gt;""),C65-B65+1,"")</f>
+        <f>IF(AND(AK65&lt;&gt;"",AL65&lt;&gt;""),AL65-AK65+1,"")</f>
         <v/>
       </c>
       <c r="E65" s="5">
-        <f>IF(B65&lt;&gt;"",YEAR(B65),"")</f>
+        <f>IF(AK65&lt;&gt;"",YEAR(AK65),"")</f>
         <v/>
       </c>
       <c r="F65" s="6" t="n"/>
@@ -18223,17 +18717,25 @@
         <v/>
       </c>
       <c r="AJ65" s="5" t="n"/>
+      <c r="AK65" s="12">
+        <f>IF(B65="","",IF(ISNUMBER(B65),B65,DATE(VALUE(LEFT(B65,4)),VALUE(MID(B65,6,2)),VALUE(MID(B65,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL65" s="12">
+        <f>IF(C65="","",IF(ISNUMBER(C65),C65,DATE(VALUE(LEFT(C65,4)),VALUE(MID(C65,6,2)),VALUE(MID(C65,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="5" t="n"/>
       <c r="D66" s="5">
-        <f>IF(AND(B66&lt;&gt;"",C66&lt;&gt;""),C66-B66+1,"")</f>
+        <f>IF(AND(AK66&lt;&gt;"",AL66&lt;&gt;""),AL66-AK66+1,"")</f>
         <v/>
       </c>
       <c r="E66" s="5">
-        <f>IF(B66&lt;&gt;"",YEAR(B66),"")</f>
+        <f>IF(AK66&lt;&gt;"",YEAR(AK66),"")</f>
         <v/>
       </c>
       <c r="F66" s="6" t="n"/>
@@ -18321,17 +18823,25 @@
         <v/>
       </c>
       <c r="AJ66" s="5" t="n"/>
+      <c r="AK66" s="12">
+        <f>IF(B66="","",IF(ISNUMBER(B66),B66,DATE(VALUE(LEFT(B66,4)),VALUE(MID(B66,6,2)),VALUE(MID(B66,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL66" s="12">
+        <f>IF(C66="","",IF(ISNUMBER(C66),C66,DATE(VALUE(LEFT(C66,4)),VALUE(MID(C66,6,2)),VALUE(MID(C66,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="5" t="n"/>
       <c r="D67" s="5">
-        <f>IF(AND(B67&lt;&gt;"",C67&lt;&gt;""),C67-B67+1,"")</f>
+        <f>IF(AND(AK67&lt;&gt;"",AL67&lt;&gt;""),AL67-AK67+1,"")</f>
         <v/>
       </c>
       <c r="E67" s="5">
-        <f>IF(B67&lt;&gt;"",YEAR(B67),"")</f>
+        <f>IF(AK67&lt;&gt;"",YEAR(AK67),"")</f>
         <v/>
       </c>
       <c r="F67" s="6" t="n"/>
@@ -18419,17 +18929,25 @@
         <v/>
       </c>
       <c r="AJ67" s="5" t="n"/>
+      <c r="AK67" s="12">
+        <f>IF(B67="","",IF(ISNUMBER(B67),B67,DATE(VALUE(LEFT(B67,4)),VALUE(MID(B67,6,2)),VALUE(MID(B67,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL67" s="12">
+        <f>IF(C67="","",IF(ISNUMBER(C67),C67,DATE(VALUE(LEFT(C67,4)),VALUE(MID(C67,6,2)),VALUE(MID(C67,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="5" t="n"/>
       <c r="D68" s="5">
-        <f>IF(AND(B68&lt;&gt;"",C68&lt;&gt;""),C68-B68+1,"")</f>
+        <f>IF(AND(AK68&lt;&gt;"",AL68&lt;&gt;""),AL68-AK68+1,"")</f>
         <v/>
       </c>
       <c r="E68" s="5">
-        <f>IF(B68&lt;&gt;"",YEAR(B68),"")</f>
+        <f>IF(AK68&lt;&gt;"",YEAR(AK68),"")</f>
         <v/>
       </c>
       <c r="F68" s="6" t="n"/>
@@ -18517,17 +19035,25 @@
         <v/>
       </c>
       <c r="AJ68" s="5" t="n"/>
+      <c r="AK68" s="12">
+        <f>IF(B68="","",IF(ISNUMBER(B68),B68,DATE(VALUE(LEFT(B68,4)),VALUE(MID(B68,6,2)),VALUE(MID(B68,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL68" s="12">
+        <f>IF(C68="","",IF(ISNUMBER(C68),C68,DATE(VALUE(LEFT(C68,4)),VALUE(MID(C68,6,2)),VALUE(MID(C68,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="5">
-        <f>IF(AND(B69&lt;&gt;"",C69&lt;&gt;""),C69-B69+1,"")</f>
+        <f>IF(AND(AK69&lt;&gt;"",AL69&lt;&gt;""),AL69-AK69+1,"")</f>
         <v/>
       </c>
       <c r="E69" s="5">
-        <f>IF(B69&lt;&gt;"",YEAR(B69),"")</f>
+        <f>IF(AK69&lt;&gt;"",YEAR(AK69),"")</f>
         <v/>
       </c>
       <c r="F69" s="6" t="n"/>
@@ -18615,17 +19141,25 @@
         <v/>
       </c>
       <c r="AJ69" s="5" t="n"/>
+      <c r="AK69" s="12">
+        <f>IF(B69="","",IF(ISNUMBER(B69),B69,DATE(VALUE(LEFT(B69,4)),VALUE(MID(B69,6,2)),VALUE(MID(B69,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL69" s="12">
+        <f>IF(C69="","",IF(ISNUMBER(C69),C69,DATE(VALUE(LEFT(C69,4)),VALUE(MID(C69,6,2)),VALUE(MID(C69,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="5" t="n"/>
       <c r="D70" s="5">
-        <f>IF(AND(B70&lt;&gt;"",C70&lt;&gt;""),C70-B70+1,"")</f>
+        <f>IF(AND(AK70&lt;&gt;"",AL70&lt;&gt;""),AL70-AK70+1,"")</f>
         <v/>
       </c>
       <c r="E70" s="5">
-        <f>IF(B70&lt;&gt;"",YEAR(B70),"")</f>
+        <f>IF(AK70&lt;&gt;"",YEAR(AK70),"")</f>
         <v/>
       </c>
       <c r="F70" s="6" t="n"/>
@@ -18713,17 +19247,25 @@
         <v/>
       </c>
       <c r="AJ70" s="5" t="n"/>
+      <c r="AK70" s="12">
+        <f>IF(B70="","",IF(ISNUMBER(B70),B70,DATE(VALUE(LEFT(B70,4)),VALUE(MID(B70,6,2)),VALUE(MID(B70,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL70" s="12">
+        <f>IF(C70="","",IF(ISNUMBER(C70),C70,DATE(VALUE(LEFT(C70,4)),VALUE(MID(C70,6,2)),VALUE(MID(C70,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="5" t="n"/>
       <c r="D71" s="5">
-        <f>IF(AND(B71&lt;&gt;"",C71&lt;&gt;""),C71-B71+1,"")</f>
+        <f>IF(AND(AK71&lt;&gt;"",AL71&lt;&gt;""),AL71-AK71+1,"")</f>
         <v/>
       </c>
       <c r="E71" s="5">
-        <f>IF(B71&lt;&gt;"",YEAR(B71),"")</f>
+        <f>IF(AK71&lt;&gt;"",YEAR(AK71),"")</f>
         <v/>
       </c>
       <c r="F71" s="6" t="n"/>
@@ -18811,17 +19353,25 @@
         <v/>
       </c>
       <c r="AJ71" s="5" t="n"/>
+      <c r="AK71" s="12">
+        <f>IF(B71="","",IF(ISNUMBER(B71),B71,DATE(VALUE(LEFT(B71,4)),VALUE(MID(B71,6,2)),VALUE(MID(B71,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL71" s="12">
+        <f>IF(C71="","",IF(ISNUMBER(C71),C71,DATE(VALUE(LEFT(C71,4)),VALUE(MID(C71,6,2)),VALUE(MID(C71,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="5" t="n"/>
       <c r="D72" s="5">
-        <f>IF(AND(B72&lt;&gt;"",C72&lt;&gt;""),C72-B72+1,"")</f>
+        <f>IF(AND(AK72&lt;&gt;"",AL72&lt;&gt;""),AL72-AK72+1,"")</f>
         <v/>
       </c>
       <c r="E72" s="5">
-        <f>IF(B72&lt;&gt;"",YEAR(B72),"")</f>
+        <f>IF(AK72&lt;&gt;"",YEAR(AK72),"")</f>
         <v/>
       </c>
       <c r="F72" s="6" t="n"/>
@@ -18909,17 +19459,25 @@
         <v/>
       </c>
       <c r="AJ72" s="5" t="n"/>
+      <c r="AK72" s="12">
+        <f>IF(B72="","",IF(ISNUMBER(B72),B72,DATE(VALUE(LEFT(B72,4)),VALUE(MID(B72,6,2)),VALUE(MID(B72,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL72" s="12">
+        <f>IF(C72="","",IF(ISNUMBER(C72),C72,DATE(VALUE(LEFT(C72,4)),VALUE(MID(C72,6,2)),VALUE(MID(C72,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="5" t="n"/>
       <c r="D73" s="5">
-        <f>IF(AND(B73&lt;&gt;"",C73&lt;&gt;""),C73-B73+1,"")</f>
+        <f>IF(AND(AK73&lt;&gt;"",AL73&lt;&gt;""),AL73-AK73+1,"")</f>
         <v/>
       </c>
       <c r="E73" s="5">
-        <f>IF(B73&lt;&gt;"",YEAR(B73),"")</f>
+        <f>IF(AK73&lt;&gt;"",YEAR(AK73),"")</f>
         <v/>
       </c>
       <c r="F73" s="6" t="n"/>
@@ -19007,17 +19565,25 @@
         <v/>
       </c>
       <c r="AJ73" s="5" t="n"/>
+      <c r="AK73" s="12">
+        <f>IF(B73="","",IF(ISNUMBER(B73),B73,DATE(VALUE(LEFT(B73,4)),VALUE(MID(B73,6,2)),VALUE(MID(B73,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL73" s="12">
+        <f>IF(C73="","",IF(ISNUMBER(C73),C73,DATE(VALUE(LEFT(C73,4)),VALUE(MID(C73,6,2)),VALUE(MID(C73,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="5">
-        <f>IF(AND(B74&lt;&gt;"",C74&lt;&gt;""),C74-B74+1,"")</f>
+        <f>IF(AND(AK74&lt;&gt;"",AL74&lt;&gt;""),AL74-AK74+1,"")</f>
         <v/>
       </c>
       <c r="E74" s="5">
-        <f>IF(B74&lt;&gt;"",YEAR(B74),"")</f>
+        <f>IF(AK74&lt;&gt;"",YEAR(AK74),"")</f>
         <v/>
       </c>
       <c r="F74" s="6" t="n"/>
@@ -19105,17 +19671,25 @@
         <v/>
       </c>
       <c r="AJ74" s="5" t="n"/>
+      <c r="AK74" s="12">
+        <f>IF(B74="","",IF(ISNUMBER(B74),B74,DATE(VALUE(LEFT(B74,4)),VALUE(MID(B74,6,2)),VALUE(MID(B74,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL74" s="12">
+        <f>IF(C74="","",IF(ISNUMBER(C74),C74,DATE(VALUE(LEFT(C74,4)),VALUE(MID(C74,6,2)),VALUE(MID(C74,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="5" t="n"/>
       <c r="D75" s="5">
-        <f>IF(AND(B75&lt;&gt;"",C75&lt;&gt;""),C75-B75+1,"")</f>
+        <f>IF(AND(AK75&lt;&gt;"",AL75&lt;&gt;""),AL75-AK75+1,"")</f>
         <v/>
       </c>
       <c r="E75" s="5">
-        <f>IF(B75&lt;&gt;"",YEAR(B75),"")</f>
+        <f>IF(AK75&lt;&gt;"",YEAR(AK75),"")</f>
         <v/>
       </c>
       <c r="F75" s="6" t="n"/>
@@ -19203,17 +19777,25 @@
         <v/>
       </c>
       <c r="AJ75" s="5" t="n"/>
+      <c r="AK75" s="12">
+        <f>IF(B75="","",IF(ISNUMBER(B75),B75,DATE(VALUE(LEFT(B75,4)),VALUE(MID(B75,6,2)),VALUE(MID(B75,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL75" s="12">
+        <f>IF(C75="","",IF(ISNUMBER(C75),C75,DATE(VALUE(LEFT(C75,4)),VALUE(MID(C75,6,2)),VALUE(MID(C75,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="5" t="n"/>
       <c r="D76" s="5">
-        <f>IF(AND(B76&lt;&gt;"",C76&lt;&gt;""),C76-B76+1,"")</f>
+        <f>IF(AND(AK76&lt;&gt;"",AL76&lt;&gt;""),AL76-AK76+1,"")</f>
         <v/>
       </c>
       <c r="E76" s="5">
-        <f>IF(B76&lt;&gt;"",YEAR(B76),"")</f>
+        <f>IF(AK76&lt;&gt;"",YEAR(AK76),"")</f>
         <v/>
       </c>
       <c r="F76" s="6" t="n"/>
@@ -19301,17 +19883,25 @@
         <v/>
       </c>
       <c r="AJ76" s="5" t="n"/>
+      <c r="AK76" s="12">
+        <f>IF(B76="","",IF(ISNUMBER(B76),B76,DATE(VALUE(LEFT(B76,4)),VALUE(MID(B76,6,2)),VALUE(MID(B76,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL76" s="12">
+        <f>IF(C76="","",IF(ISNUMBER(C76),C76,DATE(VALUE(LEFT(C76,4)),VALUE(MID(C76,6,2)),VALUE(MID(C76,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="5" t="n"/>
       <c r="D77" s="5">
-        <f>IF(AND(B77&lt;&gt;"",C77&lt;&gt;""),C77-B77+1,"")</f>
+        <f>IF(AND(AK77&lt;&gt;"",AL77&lt;&gt;""),AL77-AK77+1,"")</f>
         <v/>
       </c>
       <c r="E77" s="5">
-        <f>IF(B77&lt;&gt;"",YEAR(B77),"")</f>
+        <f>IF(AK77&lt;&gt;"",YEAR(AK77),"")</f>
         <v/>
       </c>
       <c r="F77" s="6" t="n"/>
@@ -19399,17 +19989,25 @@
         <v/>
       </c>
       <c r="AJ77" s="5" t="n"/>
+      <c r="AK77" s="12">
+        <f>IF(B77="","",IF(ISNUMBER(B77),B77,DATE(VALUE(LEFT(B77,4)),VALUE(MID(B77,6,2)),VALUE(MID(B77,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL77" s="12">
+        <f>IF(C77="","",IF(ISNUMBER(C77),C77,DATE(VALUE(LEFT(C77,4)),VALUE(MID(C77,6,2)),VALUE(MID(C77,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="5" t="n"/>
       <c r="D78" s="5">
-        <f>IF(AND(B78&lt;&gt;"",C78&lt;&gt;""),C78-B78+1,"")</f>
+        <f>IF(AND(AK78&lt;&gt;"",AL78&lt;&gt;""),AL78-AK78+1,"")</f>
         <v/>
       </c>
       <c r="E78" s="5">
-        <f>IF(B78&lt;&gt;"",YEAR(B78),"")</f>
+        <f>IF(AK78&lt;&gt;"",YEAR(AK78),"")</f>
         <v/>
       </c>
       <c r="F78" s="6" t="n"/>
@@ -19497,17 +20095,25 @@
         <v/>
       </c>
       <c r="AJ78" s="5" t="n"/>
+      <c r="AK78" s="12">
+        <f>IF(B78="","",IF(ISNUMBER(B78),B78,DATE(VALUE(LEFT(B78,4)),VALUE(MID(B78,6,2)),VALUE(MID(B78,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL78" s="12">
+        <f>IF(C78="","",IF(ISNUMBER(C78),C78,DATE(VALUE(LEFT(C78,4)),VALUE(MID(C78,6,2)),VALUE(MID(C78,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="5" t="n"/>
       <c r="D79" s="5">
-        <f>IF(AND(B79&lt;&gt;"",C79&lt;&gt;""),C79-B79+1,"")</f>
+        <f>IF(AND(AK79&lt;&gt;"",AL79&lt;&gt;""),AL79-AK79+1,"")</f>
         <v/>
       </c>
       <c r="E79" s="5">
-        <f>IF(B79&lt;&gt;"",YEAR(B79),"")</f>
+        <f>IF(AK79&lt;&gt;"",YEAR(AK79),"")</f>
         <v/>
       </c>
       <c r="F79" s="6" t="n"/>
@@ -19595,17 +20201,25 @@
         <v/>
       </c>
       <c r="AJ79" s="5" t="n"/>
+      <c r="AK79" s="12">
+        <f>IF(B79="","",IF(ISNUMBER(B79),B79,DATE(VALUE(LEFT(B79,4)),VALUE(MID(B79,6,2)),VALUE(MID(B79,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL79" s="12">
+        <f>IF(C79="","",IF(ISNUMBER(C79),C79,DATE(VALUE(LEFT(C79,4)),VALUE(MID(C79,6,2)),VALUE(MID(C79,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="5" t="n"/>
       <c r="D80" s="5">
-        <f>IF(AND(B80&lt;&gt;"",C80&lt;&gt;""),C80-B80+1,"")</f>
+        <f>IF(AND(AK80&lt;&gt;"",AL80&lt;&gt;""),AL80-AK80+1,"")</f>
         <v/>
       </c>
       <c r="E80" s="5">
-        <f>IF(B80&lt;&gt;"",YEAR(B80),"")</f>
+        <f>IF(AK80&lt;&gt;"",YEAR(AK80),"")</f>
         <v/>
       </c>
       <c r="F80" s="6" t="n"/>
@@ -19693,17 +20307,25 @@
         <v/>
       </c>
       <c r="AJ80" s="5" t="n"/>
+      <c r="AK80" s="12">
+        <f>IF(B80="","",IF(ISNUMBER(B80),B80,DATE(VALUE(LEFT(B80,4)),VALUE(MID(B80,6,2)),VALUE(MID(B80,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL80" s="12">
+        <f>IF(C80="","",IF(ISNUMBER(C80),C80,DATE(VALUE(LEFT(C80,4)),VALUE(MID(C80,6,2)),VALUE(MID(C80,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="5" t="n"/>
       <c r="D81" s="5">
-        <f>IF(AND(B81&lt;&gt;"",C81&lt;&gt;""),C81-B81+1,"")</f>
+        <f>IF(AND(AK81&lt;&gt;"",AL81&lt;&gt;""),AL81-AK81+1,"")</f>
         <v/>
       </c>
       <c r="E81" s="5">
-        <f>IF(B81&lt;&gt;"",YEAR(B81),"")</f>
+        <f>IF(AK81&lt;&gt;"",YEAR(AK81),"")</f>
         <v/>
       </c>
       <c r="F81" s="6" t="n"/>
@@ -19791,17 +20413,25 @@
         <v/>
       </c>
       <c r="AJ81" s="5" t="n"/>
+      <c r="AK81" s="12">
+        <f>IF(B81="","",IF(ISNUMBER(B81),B81,DATE(VALUE(LEFT(B81,4)),VALUE(MID(B81,6,2)),VALUE(MID(B81,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL81" s="12">
+        <f>IF(C81="","",IF(ISNUMBER(C81),C81,DATE(VALUE(LEFT(C81,4)),VALUE(MID(C81,6,2)),VALUE(MID(C81,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="5" t="n"/>
       <c r="D82" s="5">
-        <f>IF(AND(B82&lt;&gt;"",C82&lt;&gt;""),C82-B82+1,"")</f>
+        <f>IF(AND(AK82&lt;&gt;"",AL82&lt;&gt;""),AL82-AK82+1,"")</f>
         <v/>
       </c>
       <c r="E82" s="5">
-        <f>IF(B82&lt;&gt;"",YEAR(B82),"")</f>
+        <f>IF(AK82&lt;&gt;"",YEAR(AK82),"")</f>
         <v/>
       </c>
       <c r="F82" s="6" t="n"/>
@@ -19889,17 +20519,25 @@
         <v/>
       </c>
       <c r="AJ82" s="5" t="n"/>
+      <c r="AK82" s="12">
+        <f>IF(B82="","",IF(ISNUMBER(B82),B82,DATE(VALUE(LEFT(B82,4)),VALUE(MID(B82,6,2)),VALUE(MID(B82,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL82" s="12">
+        <f>IF(C82="","",IF(ISNUMBER(C82),C82,DATE(VALUE(LEFT(C82,4)),VALUE(MID(C82,6,2)),VALUE(MID(C82,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="5" t="n"/>
       <c r="D83" s="5">
-        <f>IF(AND(B83&lt;&gt;"",C83&lt;&gt;""),C83-B83+1,"")</f>
+        <f>IF(AND(AK83&lt;&gt;"",AL83&lt;&gt;""),AL83-AK83+1,"")</f>
         <v/>
       </c>
       <c r="E83" s="5">
-        <f>IF(B83&lt;&gt;"",YEAR(B83),"")</f>
+        <f>IF(AK83&lt;&gt;"",YEAR(AK83),"")</f>
         <v/>
       </c>
       <c r="F83" s="6" t="n"/>
@@ -19987,17 +20625,25 @@
         <v/>
       </c>
       <c r="AJ83" s="5" t="n"/>
+      <c r="AK83" s="12">
+        <f>IF(B83="","",IF(ISNUMBER(B83),B83,DATE(VALUE(LEFT(B83,4)),VALUE(MID(B83,6,2)),VALUE(MID(B83,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL83" s="12">
+        <f>IF(C83="","",IF(ISNUMBER(C83),C83,DATE(VALUE(LEFT(C83,4)),VALUE(MID(C83,6,2)),VALUE(MID(C83,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="5" t="n"/>
       <c r="D84" s="5">
-        <f>IF(AND(B84&lt;&gt;"",C84&lt;&gt;""),C84-B84+1,"")</f>
+        <f>IF(AND(AK84&lt;&gt;"",AL84&lt;&gt;""),AL84-AK84+1,"")</f>
         <v/>
       </c>
       <c r="E84" s="5">
-        <f>IF(B84&lt;&gt;"",YEAR(B84),"")</f>
+        <f>IF(AK84&lt;&gt;"",YEAR(AK84),"")</f>
         <v/>
       </c>
       <c r="F84" s="6" t="n"/>
@@ -20085,17 +20731,25 @@
         <v/>
       </c>
       <c r="AJ84" s="5" t="n"/>
+      <c r="AK84" s="12">
+        <f>IF(B84="","",IF(ISNUMBER(B84),B84,DATE(VALUE(LEFT(B84,4)),VALUE(MID(B84,6,2)),VALUE(MID(B84,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL84" s="12">
+        <f>IF(C84="","",IF(ISNUMBER(C84),C84,DATE(VALUE(LEFT(C84,4)),VALUE(MID(C84,6,2)),VALUE(MID(C84,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="5" t="n"/>
       <c r="D85" s="5">
-        <f>IF(AND(B85&lt;&gt;"",C85&lt;&gt;""),C85-B85+1,"")</f>
+        <f>IF(AND(AK85&lt;&gt;"",AL85&lt;&gt;""),AL85-AK85+1,"")</f>
         <v/>
       </c>
       <c r="E85" s="5">
-        <f>IF(B85&lt;&gt;"",YEAR(B85),"")</f>
+        <f>IF(AK85&lt;&gt;"",YEAR(AK85),"")</f>
         <v/>
       </c>
       <c r="F85" s="6" t="n"/>
@@ -20183,17 +20837,25 @@
         <v/>
       </c>
       <c r="AJ85" s="5" t="n"/>
+      <c r="AK85" s="12">
+        <f>IF(B85="","",IF(ISNUMBER(B85),B85,DATE(VALUE(LEFT(B85,4)),VALUE(MID(B85,6,2)),VALUE(MID(B85,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL85" s="12">
+        <f>IF(C85="","",IF(ISNUMBER(C85),C85,DATE(VALUE(LEFT(C85,4)),VALUE(MID(C85,6,2)),VALUE(MID(C85,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="5" t="n"/>
       <c r="D86" s="5">
-        <f>IF(AND(B86&lt;&gt;"",C86&lt;&gt;""),C86-B86+1,"")</f>
+        <f>IF(AND(AK86&lt;&gt;"",AL86&lt;&gt;""),AL86-AK86+1,"")</f>
         <v/>
       </c>
       <c r="E86" s="5">
-        <f>IF(B86&lt;&gt;"",YEAR(B86),"")</f>
+        <f>IF(AK86&lt;&gt;"",YEAR(AK86),"")</f>
         <v/>
       </c>
       <c r="F86" s="6" t="n"/>
@@ -20281,17 +20943,25 @@
         <v/>
       </c>
       <c r="AJ86" s="5" t="n"/>
+      <c r="AK86" s="12">
+        <f>IF(B86="","",IF(ISNUMBER(B86),B86,DATE(VALUE(LEFT(B86,4)),VALUE(MID(B86,6,2)),VALUE(MID(B86,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL86" s="12">
+        <f>IF(C86="","",IF(ISNUMBER(C86),C86,DATE(VALUE(LEFT(C86,4)),VALUE(MID(C86,6,2)),VALUE(MID(C86,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="5" t="n"/>
       <c r="D87" s="5">
-        <f>IF(AND(B87&lt;&gt;"",C87&lt;&gt;""),C87-B87+1,"")</f>
+        <f>IF(AND(AK87&lt;&gt;"",AL87&lt;&gt;""),AL87-AK87+1,"")</f>
         <v/>
       </c>
       <c r="E87" s="5">
-        <f>IF(B87&lt;&gt;"",YEAR(B87),"")</f>
+        <f>IF(AK87&lt;&gt;"",YEAR(AK87),"")</f>
         <v/>
       </c>
       <c r="F87" s="6" t="n"/>
@@ -20379,17 +21049,25 @@
         <v/>
       </c>
       <c r="AJ87" s="5" t="n"/>
+      <c r="AK87" s="12">
+        <f>IF(B87="","",IF(ISNUMBER(B87),B87,DATE(VALUE(LEFT(B87,4)),VALUE(MID(B87,6,2)),VALUE(MID(B87,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL87" s="12">
+        <f>IF(C87="","",IF(ISNUMBER(C87),C87,DATE(VALUE(LEFT(C87,4)),VALUE(MID(C87,6,2)),VALUE(MID(C87,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="5" t="n"/>
       <c r="D88" s="5">
-        <f>IF(AND(B88&lt;&gt;"",C88&lt;&gt;""),C88-B88+1,"")</f>
+        <f>IF(AND(AK88&lt;&gt;"",AL88&lt;&gt;""),AL88-AK88+1,"")</f>
         <v/>
       </c>
       <c r="E88" s="5">
-        <f>IF(B88&lt;&gt;"",YEAR(B88),"")</f>
+        <f>IF(AK88&lt;&gt;"",YEAR(AK88),"")</f>
         <v/>
       </c>
       <c r="F88" s="6" t="n"/>
@@ -20477,17 +21155,25 @@
         <v/>
       </c>
       <c r="AJ88" s="5" t="n"/>
+      <c r="AK88" s="12">
+        <f>IF(B88="","",IF(ISNUMBER(B88),B88,DATE(VALUE(LEFT(B88,4)),VALUE(MID(B88,6,2)),VALUE(MID(B88,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL88" s="12">
+        <f>IF(C88="","",IF(ISNUMBER(C88),C88,DATE(VALUE(LEFT(C88,4)),VALUE(MID(C88,6,2)),VALUE(MID(C88,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="5" t="n"/>
       <c r="D89" s="5">
-        <f>IF(AND(B89&lt;&gt;"",C89&lt;&gt;""),C89-B89+1,"")</f>
+        <f>IF(AND(AK89&lt;&gt;"",AL89&lt;&gt;""),AL89-AK89+1,"")</f>
         <v/>
       </c>
       <c r="E89" s="5">
-        <f>IF(B89&lt;&gt;"",YEAR(B89),"")</f>
+        <f>IF(AK89&lt;&gt;"",YEAR(AK89),"")</f>
         <v/>
       </c>
       <c r="F89" s="6" t="n"/>
@@ -20575,17 +21261,25 @@
         <v/>
       </c>
       <c r="AJ89" s="5" t="n"/>
+      <c r="AK89" s="12">
+        <f>IF(B89="","",IF(ISNUMBER(B89),B89,DATE(VALUE(LEFT(B89,4)),VALUE(MID(B89,6,2)),VALUE(MID(B89,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL89" s="12">
+        <f>IF(C89="","",IF(ISNUMBER(C89),C89,DATE(VALUE(LEFT(C89,4)),VALUE(MID(C89,6,2)),VALUE(MID(C89,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="5" t="n"/>
       <c r="D90" s="5">
-        <f>IF(AND(B90&lt;&gt;"",C90&lt;&gt;""),C90-B90+1,"")</f>
+        <f>IF(AND(AK90&lt;&gt;"",AL90&lt;&gt;""),AL90-AK90+1,"")</f>
         <v/>
       </c>
       <c r="E90" s="5">
-        <f>IF(B90&lt;&gt;"",YEAR(B90),"")</f>
+        <f>IF(AK90&lt;&gt;"",YEAR(AK90),"")</f>
         <v/>
       </c>
       <c r="F90" s="6" t="n"/>
@@ -20673,17 +21367,25 @@
         <v/>
       </c>
       <c r="AJ90" s="5" t="n"/>
+      <c r="AK90" s="12">
+        <f>IF(B90="","",IF(ISNUMBER(B90),B90,DATE(VALUE(LEFT(B90,4)),VALUE(MID(B90,6,2)),VALUE(MID(B90,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL90" s="12">
+        <f>IF(C90="","",IF(ISNUMBER(C90),C90,DATE(VALUE(LEFT(C90,4)),VALUE(MID(C90,6,2)),VALUE(MID(C90,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="5" t="n"/>
       <c r="D91" s="5">
-        <f>IF(AND(B91&lt;&gt;"",C91&lt;&gt;""),C91-B91+1,"")</f>
+        <f>IF(AND(AK91&lt;&gt;"",AL91&lt;&gt;""),AL91-AK91+1,"")</f>
         <v/>
       </c>
       <c r="E91" s="5">
-        <f>IF(B91&lt;&gt;"",YEAR(B91),"")</f>
+        <f>IF(AK91&lt;&gt;"",YEAR(AK91),"")</f>
         <v/>
       </c>
       <c r="F91" s="6" t="n"/>
@@ -20771,17 +21473,25 @@
         <v/>
       </c>
       <c r="AJ91" s="5" t="n"/>
+      <c r="AK91" s="12">
+        <f>IF(B91="","",IF(ISNUMBER(B91),B91,DATE(VALUE(LEFT(B91,4)),VALUE(MID(B91,6,2)),VALUE(MID(B91,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL91" s="12">
+        <f>IF(C91="","",IF(ISNUMBER(C91),C91,DATE(VALUE(LEFT(C91,4)),VALUE(MID(C91,6,2)),VALUE(MID(C91,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="5" t="n"/>
       <c r="D92" s="5">
-        <f>IF(AND(B92&lt;&gt;"",C92&lt;&gt;""),C92-B92+1,"")</f>
+        <f>IF(AND(AK92&lt;&gt;"",AL92&lt;&gt;""),AL92-AK92+1,"")</f>
         <v/>
       </c>
       <c r="E92" s="5">
-        <f>IF(B92&lt;&gt;"",YEAR(B92),"")</f>
+        <f>IF(AK92&lt;&gt;"",YEAR(AK92),"")</f>
         <v/>
       </c>
       <c r="F92" s="6" t="n"/>
@@ -20869,17 +21579,25 @@
         <v/>
       </c>
       <c r="AJ92" s="5" t="n"/>
+      <c r="AK92" s="12">
+        <f>IF(B92="","",IF(ISNUMBER(B92),B92,DATE(VALUE(LEFT(B92,4)),VALUE(MID(B92,6,2)),VALUE(MID(B92,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL92" s="12">
+        <f>IF(C92="","",IF(ISNUMBER(C92),C92,DATE(VALUE(LEFT(C92,4)),VALUE(MID(C92,6,2)),VALUE(MID(C92,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="5" t="n"/>
       <c r="D93" s="5">
-        <f>IF(AND(B93&lt;&gt;"",C93&lt;&gt;""),C93-B93+1,"")</f>
+        <f>IF(AND(AK93&lt;&gt;"",AL93&lt;&gt;""),AL93-AK93+1,"")</f>
         <v/>
       </c>
       <c r="E93" s="5">
-        <f>IF(B93&lt;&gt;"",YEAR(B93),"")</f>
+        <f>IF(AK93&lt;&gt;"",YEAR(AK93),"")</f>
         <v/>
       </c>
       <c r="F93" s="6" t="n"/>
@@ -20967,17 +21685,25 @@
         <v/>
       </c>
       <c r="AJ93" s="5" t="n"/>
+      <c r="AK93" s="12">
+        <f>IF(B93="","",IF(ISNUMBER(B93),B93,DATE(VALUE(LEFT(B93,4)),VALUE(MID(B93,6,2)),VALUE(MID(B93,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL93" s="12">
+        <f>IF(C93="","",IF(ISNUMBER(C93),C93,DATE(VALUE(LEFT(C93,4)),VALUE(MID(C93,6,2)),VALUE(MID(C93,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="5" t="n"/>
       <c r="D94" s="5">
-        <f>IF(AND(B94&lt;&gt;"",C94&lt;&gt;""),C94-B94+1,"")</f>
+        <f>IF(AND(AK94&lt;&gt;"",AL94&lt;&gt;""),AL94-AK94+1,"")</f>
         <v/>
       </c>
       <c r="E94" s="5">
-        <f>IF(B94&lt;&gt;"",YEAR(B94),"")</f>
+        <f>IF(AK94&lt;&gt;"",YEAR(AK94),"")</f>
         <v/>
       </c>
       <c r="F94" s="6" t="n"/>
@@ -21065,17 +21791,25 @@
         <v/>
       </c>
       <c r="AJ94" s="5" t="n"/>
+      <c r="AK94" s="12">
+        <f>IF(B94="","",IF(ISNUMBER(B94),B94,DATE(VALUE(LEFT(B94,4)),VALUE(MID(B94,6,2)),VALUE(MID(B94,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL94" s="12">
+        <f>IF(C94="","",IF(ISNUMBER(C94),C94,DATE(VALUE(LEFT(C94,4)),VALUE(MID(C94,6,2)),VALUE(MID(C94,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="5">
-        <f>IF(AND(B95&lt;&gt;"",C95&lt;&gt;""),C95-B95+1,"")</f>
+        <f>IF(AND(AK95&lt;&gt;"",AL95&lt;&gt;""),AL95-AK95+1,"")</f>
         <v/>
       </c>
       <c r="E95" s="5">
-        <f>IF(B95&lt;&gt;"",YEAR(B95),"")</f>
+        <f>IF(AK95&lt;&gt;"",YEAR(AK95),"")</f>
         <v/>
       </c>
       <c r="F95" s="6" t="n"/>
@@ -21163,17 +21897,25 @@
         <v/>
       </c>
       <c r="AJ95" s="5" t="n"/>
+      <c r="AK95" s="12">
+        <f>IF(B95="","",IF(ISNUMBER(B95),B95,DATE(VALUE(LEFT(B95,4)),VALUE(MID(B95,6,2)),VALUE(MID(B95,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL95" s="12">
+        <f>IF(C95="","",IF(ISNUMBER(C95),C95,DATE(VALUE(LEFT(C95,4)),VALUE(MID(C95,6,2)),VALUE(MID(C95,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="5" t="n"/>
       <c r="D96" s="5">
-        <f>IF(AND(B96&lt;&gt;"",C96&lt;&gt;""),C96-B96+1,"")</f>
+        <f>IF(AND(AK96&lt;&gt;"",AL96&lt;&gt;""),AL96-AK96+1,"")</f>
         <v/>
       </c>
       <c r="E96" s="5">
-        <f>IF(B96&lt;&gt;"",YEAR(B96),"")</f>
+        <f>IF(AK96&lt;&gt;"",YEAR(AK96),"")</f>
         <v/>
       </c>
       <c r="F96" s="6" t="n"/>
@@ -21261,17 +22003,25 @@
         <v/>
       </c>
       <c r="AJ96" s="5" t="n"/>
+      <c r="AK96" s="12">
+        <f>IF(B96="","",IF(ISNUMBER(B96),B96,DATE(VALUE(LEFT(B96,4)),VALUE(MID(B96,6,2)),VALUE(MID(B96,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL96" s="12">
+        <f>IF(C96="","",IF(ISNUMBER(C96),C96,DATE(VALUE(LEFT(C96,4)),VALUE(MID(C96,6,2)),VALUE(MID(C96,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="5" t="n"/>
       <c r="D97" s="5">
-        <f>IF(AND(B97&lt;&gt;"",C97&lt;&gt;""),C97-B97+1,"")</f>
+        <f>IF(AND(AK97&lt;&gt;"",AL97&lt;&gt;""),AL97-AK97+1,"")</f>
         <v/>
       </c>
       <c r="E97" s="5">
-        <f>IF(B97&lt;&gt;"",YEAR(B97),"")</f>
+        <f>IF(AK97&lt;&gt;"",YEAR(AK97),"")</f>
         <v/>
       </c>
       <c r="F97" s="6" t="n"/>
@@ -21359,17 +22109,25 @@
         <v/>
       </c>
       <c r="AJ97" s="5" t="n"/>
+      <c r="AK97" s="12">
+        <f>IF(B97="","",IF(ISNUMBER(B97),B97,DATE(VALUE(LEFT(B97,4)),VALUE(MID(B97,6,2)),VALUE(MID(B97,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL97" s="12">
+        <f>IF(C97="","",IF(ISNUMBER(C97),C97,DATE(VALUE(LEFT(C97,4)),VALUE(MID(C97,6,2)),VALUE(MID(C97,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="5" t="n"/>
       <c r="D98" s="5">
-        <f>IF(AND(B98&lt;&gt;"",C98&lt;&gt;""),C98-B98+1,"")</f>
+        <f>IF(AND(AK98&lt;&gt;"",AL98&lt;&gt;""),AL98-AK98+1,"")</f>
         <v/>
       </c>
       <c r="E98" s="5">
-        <f>IF(B98&lt;&gt;"",YEAR(B98),"")</f>
+        <f>IF(AK98&lt;&gt;"",YEAR(AK98),"")</f>
         <v/>
       </c>
       <c r="F98" s="6" t="n"/>
@@ -21457,17 +22215,25 @@
         <v/>
       </c>
       <c r="AJ98" s="5" t="n"/>
+      <c r="AK98" s="12">
+        <f>IF(B98="","",IF(ISNUMBER(B98),B98,DATE(VALUE(LEFT(B98,4)),VALUE(MID(B98,6,2)),VALUE(MID(B98,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL98" s="12">
+        <f>IF(C98="","",IF(ISNUMBER(C98),C98,DATE(VALUE(LEFT(C98,4)),VALUE(MID(C98,6,2)),VALUE(MID(C98,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="5" t="n"/>
       <c r="D99" s="5">
-        <f>IF(AND(B99&lt;&gt;"",C99&lt;&gt;""),C99-B99+1,"")</f>
+        <f>IF(AND(AK99&lt;&gt;"",AL99&lt;&gt;""),AL99-AK99+1,"")</f>
         <v/>
       </c>
       <c r="E99" s="5">
-        <f>IF(B99&lt;&gt;"",YEAR(B99),"")</f>
+        <f>IF(AK99&lt;&gt;"",YEAR(AK99),"")</f>
         <v/>
       </c>
       <c r="F99" s="6" t="n"/>
@@ -21555,17 +22321,25 @@
         <v/>
       </c>
       <c r="AJ99" s="5" t="n"/>
+      <c r="AK99" s="12">
+        <f>IF(B99="","",IF(ISNUMBER(B99),B99,DATE(VALUE(LEFT(B99,4)),VALUE(MID(B99,6,2)),VALUE(MID(B99,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL99" s="12">
+        <f>IF(C99="","",IF(ISNUMBER(C99),C99,DATE(VALUE(LEFT(C99,4)),VALUE(MID(C99,6,2)),VALUE(MID(C99,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="5">
-        <f>IF(AND(B100&lt;&gt;"",C100&lt;&gt;""),C100-B100+1,"")</f>
+        <f>IF(AND(AK100&lt;&gt;"",AL100&lt;&gt;""),AL100-AK100+1,"")</f>
         <v/>
       </c>
       <c r="E100" s="5">
-        <f>IF(B100&lt;&gt;"",YEAR(B100),"")</f>
+        <f>IF(AK100&lt;&gt;"",YEAR(AK100),"")</f>
         <v/>
       </c>
       <c r="F100" s="6" t="n"/>
@@ -21653,17 +22427,25 @@
         <v/>
       </c>
       <c r="AJ100" s="5" t="n"/>
+      <c r="AK100" s="12">
+        <f>IF(B100="","",IF(ISNUMBER(B100),B100,DATE(VALUE(LEFT(B100,4)),VALUE(MID(B100,6,2)),VALUE(MID(B100,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL100" s="12">
+        <f>IF(C100="","",IF(ISNUMBER(C100),C100,DATE(VALUE(LEFT(C100,4)),VALUE(MID(C100,6,2)),VALUE(MID(C100,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="5" t="n"/>
       <c r="D101" s="5">
-        <f>IF(AND(B101&lt;&gt;"",C101&lt;&gt;""),C101-B101+1,"")</f>
+        <f>IF(AND(AK101&lt;&gt;"",AL101&lt;&gt;""),AL101-AK101+1,"")</f>
         <v/>
       </c>
       <c r="E101" s="5">
-        <f>IF(B101&lt;&gt;"",YEAR(B101),"")</f>
+        <f>IF(AK101&lt;&gt;"",YEAR(AK101),"")</f>
         <v/>
       </c>
       <c r="F101" s="6" t="n"/>
@@ -21751,17 +22533,25 @@
         <v/>
       </c>
       <c r="AJ101" s="5" t="n"/>
+      <c r="AK101" s="12">
+        <f>IF(B101="","",IF(ISNUMBER(B101),B101,DATE(VALUE(LEFT(B101,4)),VALUE(MID(B101,6,2)),VALUE(MID(B101,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL101" s="12">
+        <f>IF(C101="","",IF(ISNUMBER(C101),C101,DATE(VALUE(LEFT(C101,4)),VALUE(MID(C101,6,2)),VALUE(MID(C101,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="5" t="n"/>
       <c r="D102" s="5">
-        <f>IF(AND(B102&lt;&gt;"",C102&lt;&gt;""),C102-B102+1,"")</f>
+        <f>IF(AND(AK102&lt;&gt;"",AL102&lt;&gt;""),AL102-AK102+1,"")</f>
         <v/>
       </c>
       <c r="E102" s="5">
-        <f>IF(B102&lt;&gt;"",YEAR(B102),"")</f>
+        <f>IF(AK102&lt;&gt;"",YEAR(AK102),"")</f>
         <v/>
       </c>
       <c r="F102" s="6" t="n"/>
@@ -21849,17 +22639,25 @@
         <v/>
       </c>
       <c r="AJ102" s="5" t="n"/>
+      <c r="AK102" s="12">
+        <f>IF(B102="","",IF(ISNUMBER(B102),B102,DATE(VALUE(LEFT(B102,4)),VALUE(MID(B102,6,2)),VALUE(MID(B102,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL102" s="12">
+        <f>IF(C102="","",IF(ISNUMBER(C102),C102,DATE(VALUE(LEFT(C102,4)),VALUE(MID(C102,6,2)),VALUE(MID(C102,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="5" t="n"/>
       <c r="D103" s="5">
-        <f>IF(AND(B103&lt;&gt;"",C103&lt;&gt;""),C103-B103+1,"")</f>
+        <f>IF(AND(AK103&lt;&gt;"",AL103&lt;&gt;""),AL103-AK103+1,"")</f>
         <v/>
       </c>
       <c r="E103" s="5">
-        <f>IF(B103&lt;&gt;"",YEAR(B103),"")</f>
+        <f>IF(AK103&lt;&gt;"",YEAR(AK103),"")</f>
         <v/>
       </c>
       <c r="F103" s="6" t="n"/>
@@ -21947,17 +22745,25 @@
         <v/>
       </c>
       <c r="AJ103" s="5" t="n"/>
+      <c r="AK103" s="12">
+        <f>IF(B103="","",IF(ISNUMBER(B103),B103,DATE(VALUE(LEFT(B103,4)),VALUE(MID(B103,6,2)),VALUE(MID(B103,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL103" s="12">
+        <f>IF(C103="","",IF(ISNUMBER(C103),C103,DATE(VALUE(LEFT(C103,4)),VALUE(MID(C103,6,2)),VALUE(MID(C103,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="5" t="n"/>
       <c r="D104" s="5">
-        <f>IF(AND(B104&lt;&gt;"",C104&lt;&gt;""),C104-B104+1,"")</f>
+        <f>IF(AND(AK104&lt;&gt;"",AL104&lt;&gt;""),AL104-AK104+1,"")</f>
         <v/>
       </c>
       <c r="E104" s="5">
-        <f>IF(B104&lt;&gt;"",YEAR(B104),"")</f>
+        <f>IF(AK104&lt;&gt;"",YEAR(AK104),"")</f>
         <v/>
       </c>
       <c r="F104" s="6" t="n"/>
@@ -22045,17 +22851,25 @@
         <v/>
       </c>
       <c r="AJ104" s="5" t="n"/>
+      <c r="AK104" s="12">
+        <f>IF(B104="","",IF(ISNUMBER(B104),B104,DATE(VALUE(LEFT(B104,4)),VALUE(MID(B104,6,2)),VALUE(MID(B104,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL104" s="12">
+        <f>IF(C104="","",IF(ISNUMBER(C104),C104,DATE(VALUE(LEFT(C104,4)),VALUE(MID(C104,6,2)),VALUE(MID(C104,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="5" t="n"/>
       <c r="D105" s="5">
-        <f>IF(AND(B105&lt;&gt;"",C105&lt;&gt;""),C105-B105+1,"")</f>
+        <f>IF(AND(AK105&lt;&gt;"",AL105&lt;&gt;""),AL105-AK105+1,"")</f>
         <v/>
       </c>
       <c r="E105" s="5">
-        <f>IF(B105&lt;&gt;"",YEAR(B105),"")</f>
+        <f>IF(AK105&lt;&gt;"",YEAR(AK105),"")</f>
         <v/>
       </c>
       <c r="F105" s="6" t="n"/>
@@ -22143,17 +22957,25 @@
         <v/>
       </c>
       <c r="AJ105" s="5" t="n"/>
+      <c r="AK105" s="12">
+        <f>IF(B105="","",IF(ISNUMBER(B105),B105,DATE(VALUE(LEFT(B105,4)),VALUE(MID(B105,6,2)),VALUE(MID(B105,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL105" s="12">
+        <f>IF(C105="","",IF(ISNUMBER(C105),C105,DATE(VALUE(LEFT(C105,4)),VALUE(MID(C105,6,2)),VALUE(MID(C105,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="5" t="n"/>
       <c r="D106" s="5">
-        <f>IF(AND(B106&lt;&gt;"",C106&lt;&gt;""),C106-B106+1,"")</f>
+        <f>IF(AND(AK106&lt;&gt;"",AL106&lt;&gt;""),AL106-AK106+1,"")</f>
         <v/>
       </c>
       <c r="E106" s="5">
-        <f>IF(B106&lt;&gt;"",YEAR(B106),"")</f>
+        <f>IF(AK106&lt;&gt;"",YEAR(AK106),"")</f>
         <v/>
       </c>
       <c r="F106" s="6" t="n"/>
@@ -22241,17 +23063,25 @@
         <v/>
       </c>
       <c r="AJ106" s="5" t="n"/>
+      <c r="AK106" s="12">
+        <f>IF(B106="","",IF(ISNUMBER(B106),B106,DATE(VALUE(LEFT(B106,4)),VALUE(MID(B106,6,2)),VALUE(MID(B106,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL106" s="12">
+        <f>IF(C106="","",IF(ISNUMBER(C106),C106,DATE(VALUE(LEFT(C106,4)),VALUE(MID(C106,6,2)),VALUE(MID(C106,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="5" t="n"/>
       <c r="D107" s="5">
-        <f>IF(AND(B107&lt;&gt;"",C107&lt;&gt;""),C107-B107+1,"")</f>
+        <f>IF(AND(AK107&lt;&gt;"",AL107&lt;&gt;""),AL107-AK107+1,"")</f>
         <v/>
       </c>
       <c r="E107" s="5">
-        <f>IF(B107&lt;&gt;"",YEAR(B107),"")</f>
+        <f>IF(AK107&lt;&gt;"",YEAR(AK107),"")</f>
         <v/>
       </c>
       <c r="F107" s="6" t="n"/>
@@ -22339,17 +23169,25 @@
         <v/>
       </c>
       <c r="AJ107" s="5" t="n"/>
+      <c r="AK107" s="12">
+        <f>IF(B107="","",IF(ISNUMBER(B107),B107,DATE(VALUE(LEFT(B107,4)),VALUE(MID(B107,6,2)),VALUE(MID(B107,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL107" s="12">
+        <f>IF(C107="","",IF(ISNUMBER(C107),C107,DATE(VALUE(LEFT(C107,4)),VALUE(MID(C107,6,2)),VALUE(MID(C107,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="5" t="n"/>
       <c r="D108" s="5">
-        <f>IF(AND(B108&lt;&gt;"",C108&lt;&gt;""),C108-B108+1,"")</f>
+        <f>IF(AND(AK108&lt;&gt;"",AL108&lt;&gt;""),AL108-AK108+1,"")</f>
         <v/>
       </c>
       <c r="E108" s="5">
-        <f>IF(B108&lt;&gt;"",YEAR(B108),"")</f>
+        <f>IF(AK108&lt;&gt;"",YEAR(AK108),"")</f>
         <v/>
       </c>
       <c r="F108" s="6" t="n"/>
@@ -22437,17 +23275,25 @@
         <v/>
       </c>
       <c r="AJ108" s="5" t="n"/>
+      <c r="AK108" s="12">
+        <f>IF(B108="","",IF(ISNUMBER(B108),B108,DATE(VALUE(LEFT(B108,4)),VALUE(MID(B108,6,2)),VALUE(MID(B108,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL108" s="12">
+        <f>IF(C108="","",IF(ISNUMBER(C108),C108,DATE(VALUE(LEFT(C108,4)),VALUE(MID(C108,6,2)),VALUE(MID(C108,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="5" t="n"/>
       <c r="D109" s="5">
-        <f>IF(AND(B109&lt;&gt;"",C109&lt;&gt;""),C109-B109+1,"")</f>
+        <f>IF(AND(AK109&lt;&gt;"",AL109&lt;&gt;""),AL109-AK109+1,"")</f>
         <v/>
       </c>
       <c r="E109" s="5">
-        <f>IF(B109&lt;&gt;"",YEAR(B109),"")</f>
+        <f>IF(AK109&lt;&gt;"",YEAR(AK109),"")</f>
         <v/>
       </c>
       <c r="F109" s="6" t="n"/>
@@ -22535,17 +23381,25 @@
         <v/>
       </c>
       <c r="AJ109" s="5" t="n"/>
+      <c r="AK109" s="12">
+        <f>IF(B109="","",IF(ISNUMBER(B109),B109,DATE(VALUE(LEFT(B109,4)),VALUE(MID(B109,6,2)),VALUE(MID(B109,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL109" s="12">
+        <f>IF(C109="","",IF(ISNUMBER(C109),C109,DATE(VALUE(LEFT(C109,4)),VALUE(MID(C109,6,2)),VALUE(MID(C109,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="5" t="n"/>
       <c r="D110" s="5">
-        <f>IF(AND(B110&lt;&gt;"",C110&lt;&gt;""),C110-B110+1,"")</f>
+        <f>IF(AND(AK110&lt;&gt;"",AL110&lt;&gt;""),AL110-AK110+1,"")</f>
         <v/>
       </c>
       <c r="E110" s="5">
-        <f>IF(B110&lt;&gt;"",YEAR(B110),"")</f>
+        <f>IF(AK110&lt;&gt;"",YEAR(AK110),"")</f>
         <v/>
       </c>
       <c r="F110" s="6" t="n"/>
@@ -22633,17 +23487,25 @@
         <v/>
       </c>
       <c r="AJ110" s="5" t="n"/>
+      <c r="AK110" s="12">
+        <f>IF(B110="","",IF(ISNUMBER(B110),B110,DATE(VALUE(LEFT(B110,4)),VALUE(MID(B110,6,2)),VALUE(MID(B110,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL110" s="12">
+        <f>IF(C110="","",IF(ISNUMBER(C110),C110,DATE(VALUE(LEFT(C110,4)),VALUE(MID(C110,6,2)),VALUE(MID(C110,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="5" t="n"/>
       <c r="D111" s="5">
-        <f>IF(AND(B111&lt;&gt;"",C111&lt;&gt;""),C111-B111+1,"")</f>
+        <f>IF(AND(AK111&lt;&gt;"",AL111&lt;&gt;""),AL111-AK111+1,"")</f>
         <v/>
       </c>
       <c r="E111" s="5">
-        <f>IF(B111&lt;&gt;"",YEAR(B111),"")</f>
+        <f>IF(AK111&lt;&gt;"",YEAR(AK111),"")</f>
         <v/>
       </c>
       <c r="F111" s="6" t="n"/>
@@ -22731,17 +23593,25 @@
         <v/>
       </c>
       <c r="AJ111" s="5" t="n"/>
+      <c r="AK111" s="12">
+        <f>IF(B111="","",IF(ISNUMBER(B111),B111,DATE(VALUE(LEFT(B111,4)),VALUE(MID(B111,6,2)),VALUE(MID(B111,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL111" s="12">
+        <f>IF(C111="","",IF(ISNUMBER(C111),C111,DATE(VALUE(LEFT(C111,4)),VALUE(MID(C111,6,2)),VALUE(MID(C111,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="5" t="n"/>
       <c r="D112" s="5">
-        <f>IF(AND(B112&lt;&gt;"",C112&lt;&gt;""),C112-B112+1,"")</f>
+        <f>IF(AND(AK112&lt;&gt;"",AL112&lt;&gt;""),AL112-AK112+1,"")</f>
         <v/>
       </c>
       <c r="E112" s="5">
-        <f>IF(B112&lt;&gt;"",YEAR(B112),"")</f>
+        <f>IF(AK112&lt;&gt;"",YEAR(AK112),"")</f>
         <v/>
       </c>
       <c r="F112" s="6" t="n"/>
@@ -22829,17 +23699,25 @@
         <v/>
       </c>
       <c r="AJ112" s="5" t="n"/>
+      <c r="AK112" s="12">
+        <f>IF(B112="","",IF(ISNUMBER(B112),B112,DATE(VALUE(LEFT(B112,4)),VALUE(MID(B112,6,2)),VALUE(MID(B112,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL112" s="12">
+        <f>IF(C112="","",IF(ISNUMBER(C112),C112,DATE(VALUE(LEFT(C112,4)),VALUE(MID(C112,6,2)),VALUE(MID(C112,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="5" t="n"/>
       <c r="D113" s="5">
-        <f>IF(AND(B113&lt;&gt;"",C113&lt;&gt;""),C113-B113+1,"")</f>
+        <f>IF(AND(AK113&lt;&gt;"",AL113&lt;&gt;""),AL113-AK113+1,"")</f>
         <v/>
       </c>
       <c r="E113" s="5">
-        <f>IF(B113&lt;&gt;"",YEAR(B113),"")</f>
+        <f>IF(AK113&lt;&gt;"",YEAR(AK113),"")</f>
         <v/>
       </c>
       <c r="F113" s="6" t="n"/>
@@ -22927,17 +23805,25 @@
         <v/>
       </c>
       <c r="AJ113" s="5" t="n"/>
+      <c r="AK113" s="12">
+        <f>IF(B113="","",IF(ISNUMBER(B113),B113,DATE(VALUE(LEFT(B113,4)),VALUE(MID(B113,6,2)),VALUE(MID(B113,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL113" s="12">
+        <f>IF(C113="","",IF(ISNUMBER(C113),C113,DATE(VALUE(LEFT(C113,4)),VALUE(MID(C113,6,2)),VALUE(MID(C113,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="5" t="n"/>
       <c r="D114" s="5">
-        <f>IF(AND(B114&lt;&gt;"",C114&lt;&gt;""),C114-B114+1,"")</f>
+        <f>IF(AND(AK114&lt;&gt;"",AL114&lt;&gt;""),AL114-AK114+1,"")</f>
         <v/>
       </c>
       <c r="E114" s="5">
-        <f>IF(B114&lt;&gt;"",YEAR(B114),"")</f>
+        <f>IF(AK114&lt;&gt;"",YEAR(AK114),"")</f>
         <v/>
       </c>
       <c r="F114" s="6" t="n"/>
@@ -23025,17 +23911,25 @@
         <v/>
       </c>
       <c r="AJ114" s="5" t="n"/>
+      <c r="AK114" s="12">
+        <f>IF(B114="","",IF(ISNUMBER(B114),B114,DATE(VALUE(LEFT(B114,4)),VALUE(MID(B114,6,2)),VALUE(MID(B114,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL114" s="12">
+        <f>IF(C114="","",IF(ISNUMBER(C114),C114,DATE(VALUE(LEFT(C114,4)),VALUE(MID(C114,6,2)),VALUE(MID(C114,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="5" t="n"/>
       <c r="D115" s="5">
-        <f>IF(AND(B115&lt;&gt;"",C115&lt;&gt;""),C115-B115+1,"")</f>
+        <f>IF(AND(AK115&lt;&gt;"",AL115&lt;&gt;""),AL115-AK115+1,"")</f>
         <v/>
       </c>
       <c r="E115" s="5">
-        <f>IF(B115&lt;&gt;"",YEAR(B115),"")</f>
+        <f>IF(AK115&lt;&gt;"",YEAR(AK115),"")</f>
         <v/>
       </c>
       <c r="F115" s="6" t="n"/>
@@ -23123,17 +24017,25 @@
         <v/>
       </c>
       <c r="AJ115" s="5" t="n"/>
+      <c r="AK115" s="12">
+        <f>IF(B115="","",IF(ISNUMBER(B115),B115,DATE(VALUE(LEFT(B115,4)),VALUE(MID(B115,6,2)),VALUE(MID(B115,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL115" s="12">
+        <f>IF(C115="","",IF(ISNUMBER(C115),C115,DATE(VALUE(LEFT(C115,4)),VALUE(MID(C115,6,2)),VALUE(MID(C115,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="5" t="n"/>
       <c r="D116" s="5">
-        <f>IF(AND(B116&lt;&gt;"",C116&lt;&gt;""),C116-B116+1,"")</f>
+        <f>IF(AND(AK116&lt;&gt;"",AL116&lt;&gt;""),AL116-AK116+1,"")</f>
         <v/>
       </c>
       <c r="E116" s="5">
-        <f>IF(B116&lt;&gt;"",YEAR(B116),"")</f>
+        <f>IF(AK116&lt;&gt;"",YEAR(AK116),"")</f>
         <v/>
       </c>
       <c r="F116" s="6" t="n"/>
@@ -23221,17 +24123,25 @@
         <v/>
       </c>
       <c r="AJ116" s="5" t="n"/>
+      <c r="AK116" s="12">
+        <f>IF(B116="","",IF(ISNUMBER(B116),B116,DATE(VALUE(LEFT(B116,4)),VALUE(MID(B116,6,2)),VALUE(MID(B116,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL116" s="12">
+        <f>IF(C116="","",IF(ISNUMBER(C116),C116,DATE(VALUE(LEFT(C116,4)),VALUE(MID(C116,6,2)),VALUE(MID(C116,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="5" t="n"/>
       <c r="D117" s="5">
-        <f>IF(AND(B117&lt;&gt;"",C117&lt;&gt;""),C117-B117+1,"")</f>
+        <f>IF(AND(AK117&lt;&gt;"",AL117&lt;&gt;""),AL117-AK117+1,"")</f>
         <v/>
       </c>
       <c r="E117" s="5">
-        <f>IF(B117&lt;&gt;"",YEAR(B117),"")</f>
+        <f>IF(AK117&lt;&gt;"",YEAR(AK117),"")</f>
         <v/>
       </c>
       <c r="F117" s="6" t="n"/>
@@ -23319,17 +24229,25 @@
         <v/>
       </c>
       <c r="AJ117" s="5" t="n"/>
+      <c r="AK117" s="12">
+        <f>IF(B117="","",IF(ISNUMBER(B117),B117,DATE(VALUE(LEFT(B117,4)),VALUE(MID(B117,6,2)),VALUE(MID(B117,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL117" s="12">
+        <f>IF(C117="","",IF(ISNUMBER(C117),C117,DATE(VALUE(LEFT(C117,4)),VALUE(MID(C117,6,2)),VALUE(MID(C117,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="5" t="n"/>
       <c r="D118" s="5">
-        <f>IF(AND(B118&lt;&gt;"",C118&lt;&gt;""),C118-B118+1,"")</f>
+        <f>IF(AND(AK118&lt;&gt;"",AL118&lt;&gt;""),AL118-AK118+1,"")</f>
         <v/>
       </c>
       <c r="E118" s="5">
-        <f>IF(B118&lt;&gt;"",YEAR(B118),"")</f>
+        <f>IF(AK118&lt;&gt;"",YEAR(AK118),"")</f>
         <v/>
       </c>
       <c r="F118" s="6" t="n"/>
@@ -23417,17 +24335,25 @@
         <v/>
       </c>
       <c r="AJ118" s="5" t="n"/>
+      <c r="AK118" s="12">
+        <f>IF(B118="","",IF(ISNUMBER(B118),B118,DATE(VALUE(LEFT(B118,4)),VALUE(MID(B118,6,2)),VALUE(MID(B118,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL118" s="12">
+        <f>IF(C118="","",IF(ISNUMBER(C118),C118,DATE(VALUE(LEFT(C118,4)),VALUE(MID(C118,6,2)),VALUE(MID(C118,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="5" t="n"/>
       <c r="D119" s="5">
-        <f>IF(AND(B119&lt;&gt;"",C119&lt;&gt;""),C119-B119+1,"")</f>
+        <f>IF(AND(AK119&lt;&gt;"",AL119&lt;&gt;""),AL119-AK119+1,"")</f>
         <v/>
       </c>
       <c r="E119" s="5">
-        <f>IF(B119&lt;&gt;"",YEAR(B119),"")</f>
+        <f>IF(AK119&lt;&gt;"",YEAR(AK119),"")</f>
         <v/>
       </c>
       <c r="F119" s="6" t="n"/>
@@ -23515,17 +24441,25 @@
         <v/>
       </c>
       <c r="AJ119" s="5" t="n"/>
+      <c r="AK119" s="12">
+        <f>IF(B119="","",IF(ISNUMBER(B119),B119,DATE(VALUE(LEFT(B119,4)),VALUE(MID(B119,6,2)),VALUE(MID(B119,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL119" s="12">
+        <f>IF(C119="","",IF(ISNUMBER(C119),C119,DATE(VALUE(LEFT(C119,4)),VALUE(MID(C119,6,2)),VALUE(MID(C119,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="5" t="n"/>
       <c r="D120" s="5">
-        <f>IF(AND(B120&lt;&gt;"",C120&lt;&gt;""),C120-B120+1,"")</f>
+        <f>IF(AND(AK120&lt;&gt;"",AL120&lt;&gt;""),AL120-AK120+1,"")</f>
         <v/>
       </c>
       <c r="E120" s="5">
-        <f>IF(B120&lt;&gt;"",YEAR(B120),"")</f>
+        <f>IF(AK120&lt;&gt;"",YEAR(AK120),"")</f>
         <v/>
       </c>
       <c r="F120" s="6" t="n"/>
@@ -23613,17 +24547,25 @@
         <v/>
       </c>
       <c r="AJ120" s="5" t="n"/>
+      <c r="AK120" s="12">
+        <f>IF(B120="","",IF(ISNUMBER(B120),B120,DATE(VALUE(LEFT(B120,4)),VALUE(MID(B120,6,2)),VALUE(MID(B120,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL120" s="12">
+        <f>IF(C120="","",IF(ISNUMBER(C120),C120,DATE(VALUE(LEFT(C120,4)),VALUE(MID(C120,6,2)),VALUE(MID(C120,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="5" t="n"/>
       <c r="D121" s="5">
-        <f>IF(AND(B121&lt;&gt;"",C121&lt;&gt;""),C121-B121+1,"")</f>
+        <f>IF(AND(AK121&lt;&gt;"",AL121&lt;&gt;""),AL121-AK121+1,"")</f>
         <v/>
       </c>
       <c r="E121" s="5">
-        <f>IF(B121&lt;&gt;"",YEAR(B121),"")</f>
+        <f>IF(AK121&lt;&gt;"",YEAR(AK121),"")</f>
         <v/>
       </c>
       <c r="F121" s="6" t="n"/>
@@ -23711,17 +24653,25 @@
         <v/>
       </c>
       <c r="AJ121" s="5" t="n"/>
+      <c r="AK121" s="12">
+        <f>IF(B121="","",IF(ISNUMBER(B121),B121,DATE(VALUE(LEFT(B121,4)),VALUE(MID(B121,6,2)),VALUE(MID(B121,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL121" s="12">
+        <f>IF(C121="","",IF(ISNUMBER(C121),C121,DATE(VALUE(LEFT(C121,4)),VALUE(MID(C121,6,2)),VALUE(MID(C121,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="5" t="n"/>
       <c r="D122" s="5">
-        <f>IF(AND(B122&lt;&gt;"",C122&lt;&gt;""),C122-B122+1,"")</f>
+        <f>IF(AND(AK122&lt;&gt;"",AL122&lt;&gt;""),AL122-AK122+1,"")</f>
         <v/>
       </c>
       <c r="E122" s="5">
-        <f>IF(B122&lt;&gt;"",YEAR(B122),"")</f>
+        <f>IF(AK122&lt;&gt;"",YEAR(AK122),"")</f>
         <v/>
       </c>
       <c r="F122" s="6" t="n"/>
@@ -23809,17 +24759,25 @@
         <v/>
       </c>
       <c r="AJ122" s="5" t="n"/>
+      <c r="AK122" s="12">
+        <f>IF(B122="","",IF(ISNUMBER(B122),B122,DATE(VALUE(LEFT(B122,4)),VALUE(MID(B122,6,2)),VALUE(MID(B122,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL122" s="12">
+        <f>IF(C122="","",IF(ISNUMBER(C122),C122,DATE(VALUE(LEFT(C122,4)),VALUE(MID(C122,6,2)),VALUE(MID(C122,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="5" t="n"/>
       <c r="D123" s="5">
-        <f>IF(AND(B123&lt;&gt;"",C123&lt;&gt;""),C123-B123+1,"")</f>
+        <f>IF(AND(AK123&lt;&gt;"",AL123&lt;&gt;""),AL123-AK123+1,"")</f>
         <v/>
       </c>
       <c r="E123" s="5">
-        <f>IF(B123&lt;&gt;"",YEAR(B123),"")</f>
+        <f>IF(AK123&lt;&gt;"",YEAR(AK123),"")</f>
         <v/>
       </c>
       <c r="F123" s="6" t="n"/>
@@ -23907,17 +24865,25 @@
         <v/>
       </c>
       <c r="AJ123" s="5" t="n"/>
+      <c r="AK123" s="12">
+        <f>IF(B123="","",IF(ISNUMBER(B123),B123,DATE(VALUE(LEFT(B123,4)),VALUE(MID(B123,6,2)),VALUE(MID(B123,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL123" s="12">
+        <f>IF(C123="","",IF(ISNUMBER(C123),C123,DATE(VALUE(LEFT(C123,4)),VALUE(MID(C123,6,2)),VALUE(MID(C123,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="5" t="n"/>
       <c r="D124" s="5">
-        <f>IF(AND(B124&lt;&gt;"",C124&lt;&gt;""),C124-B124+1,"")</f>
+        <f>IF(AND(AK124&lt;&gt;"",AL124&lt;&gt;""),AL124-AK124+1,"")</f>
         <v/>
       </c>
       <c r="E124" s="5">
-        <f>IF(B124&lt;&gt;"",YEAR(B124),"")</f>
+        <f>IF(AK124&lt;&gt;"",YEAR(AK124),"")</f>
         <v/>
       </c>
       <c r="F124" s="6" t="n"/>
@@ -24005,17 +24971,25 @@
         <v/>
       </c>
       <c r="AJ124" s="5" t="n"/>
+      <c r="AK124" s="12">
+        <f>IF(B124="","",IF(ISNUMBER(B124),B124,DATE(VALUE(LEFT(B124,4)),VALUE(MID(B124,6,2)),VALUE(MID(B124,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL124" s="12">
+        <f>IF(C124="","",IF(ISNUMBER(C124),C124,DATE(VALUE(LEFT(C124,4)),VALUE(MID(C124,6,2)),VALUE(MID(C124,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="5" t="n"/>
       <c r="D125" s="5">
-        <f>IF(AND(B125&lt;&gt;"",C125&lt;&gt;""),C125-B125+1,"")</f>
+        <f>IF(AND(AK125&lt;&gt;"",AL125&lt;&gt;""),AL125-AK125+1,"")</f>
         <v/>
       </c>
       <c r="E125" s="5">
-        <f>IF(B125&lt;&gt;"",YEAR(B125),"")</f>
+        <f>IF(AK125&lt;&gt;"",YEAR(AK125),"")</f>
         <v/>
       </c>
       <c r="F125" s="6" t="n"/>
@@ -24103,17 +25077,25 @@
         <v/>
       </c>
       <c r="AJ125" s="5" t="n"/>
+      <c r="AK125" s="12">
+        <f>IF(B125="","",IF(ISNUMBER(B125),B125,DATE(VALUE(LEFT(B125,4)),VALUE(MID(B125,6,2)),VALUE(MID(B125,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL125" s="12">
+        <f>IF(C125="","",IF(ISNUMBER(C125),C125,DATE(VALUE(LEFT(C125,4)),VALUE(MID(C125,6,2)),VALUE(MID(C125,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="5" t="n"/>
       <c r="D126" s="5">
-        <f>IF(AND(B126&lt;&gt;"",C126&lt;&gt;""),C126-B126+1,"")</f>
+        <f>IF(AND(AK126&lt;&gt;"",AL126&lt;&gt;""),AL126-AK126+1,"")</f>
         <v/>
       </c>
       <c r="E126" s="5">
-        <f>IF(B126&lt;&gt;"",YEAR(B126),"")</f>
+        <f>IF(AK126&lt;&gt;"",YEAR(AK126),"")</f>
         <v/>
       </c>
       <c r="F126" s="6" t="n"/>
@@ -24201,17 +25183,25 @@
         <v/>
       </c>
       <c r="AJ126" s="5" t="n"/>
+      <c r="AK126" s="12">
+        <f>IF(B126="","",IF(ISNUMBER(B126),B126,DATE(VALUE(LEFT(B126,4)),VALUE(MID(B126,6,2)),VALUE(MID(B126,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL126" s="12">
+        <f>IF(C126="","",IF(ISNUMBER(C126),C126,DATE(VALUE(LEFT(C126,4)),VALUE(MID(C126,6,2)),VALUE(MID(C126,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="5" t="n"/>
       <c r="D127" s="5">
-        <f>IF(AND(B127&lt;&gt;"",C127&lt;&gt;""),C127-B127+1,"")</f>
+        <f>IF(AND(AK127&lt;&gt;"",AL127&lt;&gt;""),AL127-AK127+1,"")</f>
         <v/>
       </c>
       <c r="E127" s="5">
-        <f>IF(B127&lt;&gt;"",YEAR(B127),"")</f>
+        <f>IF(AK127&lt;&gt;"",YEAR(AK127),"")</f>
         <v/>
       </c>
       <c r="F127" s="6" t="n"/>
@@ -24299,17 +25289,25 @@
         <v/>
       </c>
       <c r="AJ127" s="5" t="n"/>
+      <c r="AK127" s="12">
+        <f>IF(B127="","",IF(ISNUMBER(B127),B127,DATE(VALUE(LEFT(B127,4)),VALUE(MID(B127,6,2)),VALUE(MID(B127,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL127" s="12">
+        <f>IF(C127="","",IF(ISNUMBER(C127),C127,DATE(VALUE(LEFT(C127,4)),VALUE(MID(C127,6,2)),VALUE(MID(C127,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="5" t="n"/>
       <c r="D128" s="5">
-        <f>IF(AND(B128&lt;&gt;"",C128&lt;&gt;""),C128-B128+1,"")</f>
+        <f>IF(AND(AK128&lt;&gt;"",AL128&lt;&gt;""),AL128-AK128+1,"")</f>
         <v/>
       </c>
       <c r="E128" s="5">
-        <f>IF(B128&lt;&gt;"",YEAR(B128),"")</f>
+        <f>IF(AK128&lt;&gt;"",YEAR(AK128),"")</f>
         <v/>
       </c>
       <c r="F128" s="6" t="n"/>
@@ -24397,17 +25395,25 @@
         <v/>
       </c>
       <c r="AJ128" s="5" t="n"/>
+      <c r="AK128" s="12">
+        <f>IF(B128="","",IF(ISNUMBER(B128),B128,DATE(VALUE(LEFT(B128,4)),VALUE(MID(B128,6,2)),VALUE(MID(B128,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL128" s="12">
+        <f>IF(C128="","",IF(ISNUMBER(C128),C128,DATE(VALUE(LEFT(C128,4)),VALUE(MID(C128,6,2)),VALUE(MID(C128,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="5" t="n"/>
       <c r="D129" s="5">
-        <f>IF(AND(B129&lt;&gt;"",C129&lt;&gt;""),C129-B129+1,"")</f>
+        <f>IF(AND(AK129&lt;&gt;"",AL129&lt;&gt;""),AL129-AK129+1,"")</f>
         <v/>
       </c>
       <c r="E129" s="5">
-        <f>IF(B129&lt;&gt;"",YEAR(B129),"")</f>
+        <f>IF(AK129&lt;&gt;"",YEAR(AK129),"")</f>
         <v/>
       </c>
       <c r="F129" s="6" t="n"/>
@@ -24495,17 +25501,25 @@
         <v/>
       </c>
       <c r="AJ129" s="5" t="n"/>
+      <c r="AK129" s="12">
+        <f>IF(B129="","",IF(ISNUMBER(B129),B129,DATE(VALUE(LEFT(B129,4)),VALUE(MID(B129,6,2)),VALUE(MID(B129,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL129" s="12">
+        <f>IF(C129="","",IF(ISNUMBER(C129),C129,DATE(VALUE(LEFT(C129,4)),VALUE(MID(C129,6,2)),VALUE(MID(C129,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="5" t="n"/>
       <c r="D130" s="5">
-        <f>IF(AND(B130&lt;&gt;"",C130&lt;&gt;""),C130-B130+1,"")</f>
+        <f>IF(AND(AK130&lt;&gt;"",AL130&lt;&gt;""),AL130-AK130+1,"")</f>
         <v/>
       </c>
       <c r="E130" s="5">
-        <f>IF(B130&lt;&gt;"",YEAR(B130),"")</f>
+        <f>IF(AK130&lt;&gt;"",YEAR(AK130),"")</f>
         <v/>
       </c>
       <c r="F130" s="6" t="n"/>
@@ -24593,17 +25607,25 @@
         <v/>
       </c>
       <c r="AJ130" s="5" t="n"/>
+      <c r="AK130" s="12">
+        <f>IF(B130="","",IF(ISNUMBER(B130),B130,DATE(VALUE(LEFT(B130,4)),VALUE(MID(B130,6,2)),VALUE(MID(B130,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL130" s="12">
+        <f>IF(C130="","",IF(ISNUMBER(C130),C130,DATE(VALUE(LEFT(C130,4)),VALUE(MID(C130,6,2)),VALUE(MID(C130,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="5" t="n"/>
       <c r="D131" s="5">
-        <f>IF(AND(B131&lt;&gt;"",C131&lt;&gt;""),C131-B131+1,"")</f>
+        <f>IF(AND(AK131&lt;&gt;"",AL131&lt;&gt;""),AL131-AK131+1,"")</f>
         <v/>
       </c>
       <c r="E131" s="5">
-        <f>IF(B131&lt;&gt;"",YEAR(B131),"")</f>
+        <f>IF(AK131&lt;&gt;"",YEAR(AK131),"")</f>
         <v/>
       </c>
       <c r="F131" s="6" t="n"/>
@@ -24691,17 +25713,25 @@
         <v/>
       </c>
       <c r="AJ131" s="5" t="n"/>
+      <c r="AK131" s="12">
+        <f>IF(B131="","",IF(ISNUMBER(B131),B131,DATE(VALUE(LEFT(B131,4)),VALUE(MID(B131,6,2)),VALUE(MID(B131,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL131" s="12">
+        <f>IF(C131="","",IF(ISNUMBER(C131),C131,DATE(VALUE(LEFT(C131,4)),VALUE(MID(C131,6,2)),VALUE(MID(C131,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="5" t="n"/>
       <c r="D132" s="5">
-        <f>IF(AND(B132&lt;&gt;"",C132&lt;&gt;""),C132-B132+1,"")</f>
+        <f>IF(AND(AK132&lt;&gt;"",AL132&lt;&gt;""),AL132-AK132+1,"")</f>
         <v/>
       </c>
       <c r="E132" s="5">
-        <f>IF(B132&lt;&gt;"",YEAR(B132),"")</f>
+        <f>IF(AK132&lt;&gt;"",YEAR(AK132),"")</f>
         <v/>
       </c>
       <c r="F132" s="6" t="n"/>
@@ -24789,17 +25819,25 @@
         <v/>
       </c>
       <c r="AJ132" s="5" t="n"/>
+      <c r="AK132" s="12">
+        <f>IF(B132="","",IF(ISNUMBER(B132),B132,DATE(VALUE(LEFT(B132,4)),VALUE(MID(B132,6,2)),VALUE(MID(B132,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL132" s="12">
+        <f>IF(C132="","",IF(ISNUMBER(C132),C132,DATE(VALUE(LEFT(C132,4)),VALUE(MID(C132,6,2)),VALUE(MID(C132,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="5" t="n"/>
       <c r="D133" s="5">
-        <f>IF(AND(B133&lt;&gt;"",C133&lt;&gt;""),C133-B133+1,"")</f>
+        <f>IF(AND(AK133&lt;&gt;"",AL133&lt;&gt;""),AL133-AK133+1,"")</f>
         <v/>
       </c>
       <c r="E133" s="5">
-        <f>IF(B133&lt;&gt;"",YEAR(B133),"")</f>
+        <f>IF(AK133&lt;&gt;"",YEAR(AK133),"")</f>
         <v/>
       </c>
       <c r="F133" s="6" t="n"/>
@@ -24887,17 +25925,25 @@
         <v/>
       </c>
       <c r="AJ133" s="5" t="n"/>
+      <c r="AK133" s="12">
+        <f>IF(B133="","",IF(ISNUMBER(B133),B133,DATE(VALUE(LEFT(B133,4)),VALUE(MID(B133,6,2)),VALUE(MID(B133,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL133" s="12">
+        <f>IF(C133="","",IF(ISNUMBER(C133),C133,DATE(VALUE(LEFT(C133,4)),VALUE(MID(C133,6,2)),VALUE(MID(C133,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="5" t="n"/>
       <c r="D134" s="5">
-        <f>IF(AND(B134&lt;&gt;"",C134&lt;&gt;""),C134-B134+1,"")</f>
+        <f>IF(AND(AK134&lt;&gt;"",AL134&lt;&gt;""),AL134-AK134+1,"")</f>
         <v/>
       </c>
       <c r="E134" s="5">
-        <f>IF(B134&lt;&gt;"",YEAR(B134),"")</f>
+        <f>IF(AK134&lt;&gt;"",YEAR(AK134),"")</f>
         <v/>
       </c>
       <c r="F134" s="6" t="n"/>
@@ -24985,17 +26031,25 @@
         <v/>
       </c>
       <c r="AJ134" s="5" t="n"/>
+      <c r="AK134" s="12">
+        <f>IF(B134="","",IF(ISNUMBER(B134),B134,DATE(VALUE(LEFT(B134,4)),VALUE(MID(B134,6,2)),VALUE(MID(B134,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL134" s="12">
+        <f>IF(C134="","",IF(ISNUMBER(C134),C134,DATE(VALUE(LEFT(C134,4)),VALUE(MID(C134,6,2)),VALUE(MID(C134,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="5" t="n"/>
       <c r="D135" s="5">
-        <f>IF(AND(B135&lt;&gt;"",C135&lt;&gt;""),C135-B135+1,"")</f>
+        <f>IF(AND(AK135&lt;&gt;"",AL135&lt;&gt;""),AL135-AK135+1,"")</f>
         <v/>
       </c>
       <c r="E135" s="5">
-        <f>IF(B135&lt;&gt;"",YEAR(B135),"")</f>
+        <f>IF(AK135&lt;&gt;"",YEAR(AK135),"")</f>
         <v/>
       </c>
       <c r="F135" s="6" t="n"/>
@@ -25083,17 +26137,25 @@
         <v/>
       </c>
       <c r="AJ135" s="5" t="n"/>
+      <c r="AK135" s="12">
+        <f>IF(B135="","",IF(ISNUMBER(B135),B135,DATE(VALUE(LEFT(B135,4)),VALUE(MID(B135,6,2)),VALUE(MID(B135,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL135" s="12">
+        <f>IF(C135="","",IF(ISNUMBER(C135),C135,DATE(VALUE(LEFT(C135,4)),VALUE(MID(C135,6,2)),VALUE(MID(C135,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="5" t="n"/>
       <c r="D136" s="5">
-        <f>IF(AND(B136&lt;&gt;"",C136&lt;&gt;""),C136-B136+1,"")</f>
+        <f>IF(AND(AK136&lt;&gt;"",AL136&lt;&gt;""),AL136-AK136+1,"")</f>
         <v/>
       </c>
       <c r="E136" s="5">
-        <f>IF(B136&lt;&gt;"",YEAR(B136),"")</f>
+        <f>IF(AK136&lt;&gt;"",YEAR(AK136),"")</f>
         <v/>
       </c>
       <c r="F136" s="6" t="n"/>
@@ -25181,17 +26243,25 @@
         <v/>
       </c>
       <c r="AJ136" s="5" t="n"/>
+      <c r="AK136" s="12">
+        <f>IF(B136="","",IF(ISNUMBER(B136),B136,DATE(VALUE(LEFT(B136,4)),VALUE(MID(B136,6,2)),VALUE(MID(B136,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL136" s="12">
+        <f>IF(C136="","",IF(ISNUMBER(C136),C136,DATE(VALUE(LEFT(C136,4)),VALUE(MID(C136,6,2)),VALUE(MID(C136,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="5" t="n"/>
       <c r="D137" s="5">
-        <f>IF(AND(B137&lt;&gt;"",C137&lt;&gt;""),C137-B137+1,"")</f>
+        <f>IF(AND(AK137&lt;&gt;"",AL137&lt;&gt;""),AL137-AK137+1,"")</f>
         <v/>
       </c>
       <c r="E137" s="5">
-        <f>IF(B137&lt;&gt;"",YEAR(B137),"")</f>
+        <f>IF(AK137&lt;&gt;"",YEAR(AK137),"")</f>
         <v/>
       </c>
       <c r="F137" s="6" t="n"/>
@@ -25279,17 +26349,25 @@
         <v/>
       </c>
       <c r="AJ137" s="5" t="n"/>
+      <c r="AK137" s="12">
+        <f>IF(B137="","",IF(ISNUMBER(B137),B137,DATE(VALUE(LEFT(B137,4)),VALUE(MID(B137,6,2)),VALUE(MID(B137,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL137" s="12">
+        <f>IF(C137="","",IF(ISNUMBER(C137),C137,DATE(VALUE(LEFT(C137,4)),VALUE(MID(C137,6,2)),VALUE(MID(C137,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="5" t="n"/>
       <c r="D138" s="5">
-        <f>IF(AND(B138&lt;&gt;"",C138&lt;&gt;""),C138-B138+1,"")</f>
+        <f>IF(AND(AK138&lt;&gt;"",AL138&lt;&gt;""),AL138-AK138+1,"")</f>
         <v/>
       </c>
       <c r="E138" s="5">
-        <f>IF(B138&lt;&gt;"",YEAR(B138),"")</f>
+        <f>IF(AK138&lt;&gt;"",YEAR(AK138),"")</f>
         <v/>
       </c>
       <c r="F138" s="6" t="n"/>
@@ -25377,17 +26455,25 @@
         <v/>
       </c>
       <c r="AJ138" s="5" t="n"/>
+      <c r="AK138" s="12">
+        <f>IF(B138="","",IF(ISNUMBER(B138),B138,DATE(VALUE(LEFT(B138,4)),VALUE(MID(B138,6,2)),VALUE(MID(B138,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL138" s="12">
+        <f>IF(C138="","",IF(ISNUMBER(C138),C138,DATE(VALUE(LEFT(C138,4)),VALUE(MID(C138,6,2)),VALUE(MID(C138,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="5" t="n"/>
       <c r="D139" s="5">
-        <f>IF(AND(B139&lt;&gt;"",C139&lt;&gt;""),C139-B139+1,"")</f>
+        <f>IF(AND(AK139&lt;&gt;"",AL139&lt;&gt;""),AL139-AK139+1,"")</f>
         <v/>
       </c>
       <c r="E139" s="5">
-        <f>IF(B139&lt;&gt;"",YEAR(B139),"")</f>
+        <f>IF(AK139&lt;&gt;"",YEAR(AK139),"")</f>
         <v/>
       </c>
       <c r="F139" s="6" t="n"/>
@@ -25475,17 +26561,25 @@
         <v/>
       </c>
       <c r="AJ139" s="5" t="n"/>
+      <c r="AK139" s="12">
+        <f>IF(B139="","",IF(ISNUMBER(B139),B139,DATE(VALUE(LEFT(B139,4)),VALUE(MID(B139,6,2)),VALUE(MID(B139,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL139" s="12">
+        <f>IF(C139="","",IF(ISNUMBER(C139),C139,DATE(VALUE(LEFT(C139,4)),VALUE(MID(C139,6,2)),VALUE(MID(C139,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="5" t="n"/>
       <c r="D140" s="5">
-        <f>IF(AND(B140&lt;&gt;"",C140&lt;&gt;""),C140-B140+1,"")</f>
+        <f>IF(AND(AK140&lt;&gt;"",AL140&lt;&gt;""),AL140-AK140+1,"")</f>
         <v/>
       </c>
       <c r="E140" s="5">
-        <f>IF(B140&lt;&gt;"",YEAR(B140),"")</f>
+        <f>IF(AK140&lt;&gt;"",YEAR(AK140),"")</f>
         <v/>
       </c>
       <c r="F140" s="6" t="n"/>
@@ -25573,17 +26667,25 @@
         <v/>
       </c>
       <c r="AJ140" s="5" t="n"/>
+      <c r="AK140" s="12">
+        <f>IF(B140="","",IF(ISNUMBER(B140),B140,DATE(VALUE(LEFT(B140,4)),VALUE(MID(B140,6,2)),VALUE(MID(B140,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL140" s="12">
+        <f>IF(C140="","",IF(ISNUMBER(C140),C140,DATE(VALUE(LEFT(C140,4)),VALUE(MID(C140,6,2)),VALUE(MID(C140,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="5" t="n"/>
       <c r="D141" s="5">
-        <f>IF(AND(B141&lt;&gt;"",C141&lt;&gt;""),C141-B141+1,"")</f>
+        <f>IF(AND(AK141&lt;&gt;"",AL141&lt;&gt;""),AL141-AK141+1,"")</f>
         <v/>
       </c>
       <c r="E141" s="5">
-        <f>IF(B141&lt;&gt;"",YEAR(B141),"")</f>
+        <f>IF(AK141&lt;&gt;"",YEAR(AK141),"")</f>
         <v/>
       </c>
       <c r="F141" s="6" t="n"/>
@@ -25671,17 +26773,25 @@
         <v/>
       </c>
       <c r="AJ141" s="5" t="n"/>
+      <c r="AK141" s="12">
+        <f>IF(B141="","",IF(ISNUMBER(B141),B141,DATE(VALUE(LEFT(B141,4)),VALUE(MID(B141,6,2)),VALUE(MID(B141,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL141" s="12">
+        <f>IF(C141="","",IF(ISNUMBER(C141),C141,DATE(VALUE(LEFT(C141,4)),VALUE(MID(C141,6,2)),VALUE(MID(C141,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="5" t="n"/>
       <c r="D142" s="5">
-        <f>IF(AND(B142&lt;&gt;"",C142&lt;&gt;""),C142-B142+1,"")</f>
+        <f>IF(AND(AK142&lt;&gt;"",AL142&lt;&gt;""),AL142-AK142+1,"")</f>
         <v/>
       </c>
       <c r="E142" s="5">
-        <f>IF(B142&lt;&gt;"",YEAR(B142),"")</f>
+        <f>IF(AK142&lt;&gt;"",YEAR(AK142),"")</f>
         <v/>
       </c>
       <c r="F142" s="6" t="n"/>
@@ -25769,17 +26879,25 @@
         <v/>
       </c>
       <c r="AJ142" s="5" t="n"/>
+      <c r="AK142" s="12">
+        <f>IF(B142="","",IF(ISNUMBER(B142),B142,DATE(VALUE(LEFT(B142,4)),VALUE(MID(B142,6,2)),VALUE(MID(B142,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL142" s="12">
+        <f>IF(C142="","",IF(ISNUMBER(C142),C142,DATE(VALUE(LEFT(C142,4)),VALUE(MID(C142,6,2)),VALUE(MID(C142,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="5" t="n"/>
       <c r="D143" s="5">
-        <f>IF(AND(B143&lt;&gt;"",C143&lt;&gt;""),C143-B143+1,"")</f>
+        <f>IF(AND(AK143&lt;&gt;"",AL143&lt;&gt;""),AL143-AK143+1,"")</f>
         <v/>
       </c>
       <c r="E143" s="5">
-        <f>IF(B143&lt;&gt;"",YEAR(B143),"")</f>
+        <f>IF(AK143&lt;&gt;"",YEAR(AK143),"")</f>
         <v/>
       </c>
       <c r="F143" s="6" t="n"/>
@@ -25867,17 +26985,25 @@
         <v/>
       </c>
       <c r="AJ143" s="5" t="n"/>
+      <c r="AK143" s="12">
+        <f>IF(B143="","",IF(ISNUMBER(B143),B143,DATE(VALUE(LEFT(B143,4)),VALUE(MID(B143,6,2)),VALUE(MID(B143,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL143" s="12">
+        <f>IF(C143="","",IF(ISNUMBER(C143),C143,DATE(VALUE(LEFT(C143,4)),VALUE(MID(C143,6,2)),VALUE(MID(C143,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="5" t="n"/>
       <c r="D144" s="5">
-        <f>IF(AND(B144&lt;&gt;"",C144&lt;&gt;""),C144-B144+1,"")</f>
+        <f>IF(AND(AK144&lt;&gt;"",AL144&lt;&gt;""),AL144-AK144+1,"")</f>
         <v/>
       </c>
       <c r="E144" s="5">
-        <f>IF(B144&lt;&gt;"",YEAR(B144),"")</f>
+        <f>IF(AK144&lt;&gt;"",YEAR(AK144),"")</f>
         <v/>
       </c>
       <c r="F144" s="6" t="n"/>
@@ -25965,17 +27091,25 @@
         <v/>
       </c>
       <c r="AJ144" s="5" t="n"/>
+      <c r="AK144" s="12">
+        <f>IF(B144="","",IF(ISNUMBER(B144),B144,DATE(VALUE(LEFT(B144,4)),VALUE(MID(B144,6,2)),VALUE(MID(B144,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL144" s="12">
+        <f>IF(C144="","",IF(ISNUMBER(C144),C144,DATE(VALUE(LEFT(C144,4)),VALUE(MID(C144,6,2)),VALUE(MID(C144,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="5" t="n"/>
       <c r="D145" s="5">
-        <f>IF(AND(B145&lt;&gt;"",C145&lt;&gt;""),C145-B145+1,"")</f>
+        <f>IF(AND(AK145&lt;&gt;"",AL145&lt;&gt;""),AL145-AK145+1,"")</f>
         <v/>
       </c>
       <c r="E145" s="5">
-        <f>IF(B145&lt;&gt;"",YEAR(B145),"")</f>
+        <f>IF(AK145&lt;&gt;"",YEAR(AK145),"")</f>
         <v/>
       </c>
       <c r="F145" s="6" t="n"/>
@@ -26063,17 +27197,25 @@
         <v/>
       </c>
       <c r="AJ145" s="5" t="n"/>
+      <c r="AK145" s="12">
+        <f>IF(B145="","",IF(ISNUMBER(B145),B145,DATE(VALUE(LEFT(B145,4)),VALUE(MID(B145,6,2)),VALUE(MID(B145,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL145" s="12">
+        <f>IF(C145="","",IF(ISNUMBER(C145),C145,DATE(VALUE(LEFT(C145,4)),VALUE(MID(C145,6,2)),VALUE(MID(C145,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="5" t="n"/>
       <c r="D146" s="5">
-        <f>IF(AND(B146&lt;&gt;"",C146&lt;&gt;""),C146-B146+1,"")</f>
+        <f>IF(AND(AK146&lt;&gt;"",AL146&lt;&gt;""),AL146-AK146+1,"")</f>
         <v/>
       </c>
       <c r="E146" s="5">
-        <f>IF(B146&lt;&gt;"",YEAR(B146),"")</f>
+        <f>IF(AK146&lt;&gt;"",YEAR(AK146),"")</f>
         <v/>
       </c>
       <c r="F146" s="6" t="n"/>
@@ -26161,17 +27303,25 @@
         <v/>
       </c>
       <c r="AJ146" s="5" t="n"/>
+      <c r="AK146" s="12">
+        <f>IF(B146="","",IF(ISNUMBER(B146),B146,DATE(VALUE(LEFT(B146,4)),VALUE(MID(B146,6,2)),VALUE(MID(B146,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL146" s="12">
+        <f>IF(C146="","",IF(ISNUMBER(C146),C146,DATE(VALUE(LEFT(C146,4)),VALUE(MID(C146,6,2)),VALUE(MID(C146,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="5" t="n"/>
       <c r="D147" s="5">
-        <f>IF(AND(B147&lt;&gt;"",C147&lt;&gt;""),C147-B147+1,"")</f>
+        <f>IF(AND(AK147&lt;&gt;"",AL147&lt;&gt;""),AL147-AK147+1,"")</f>
         <v/>
       </c>
       <c r="E147" s="5">
-        <f>IF(B147&lt;&gt;"",YEAR(B147),"")</f>
+        <f>IF(AK147&lt;&gt;"",YEAR(AK147),"")</f>
         <v/>
       </c>
       <c r="F147" s="6" t="n"/>
@@ -26259,17 +27409,25 @@
         <v/>
       </c>
       <c r="AJ147" s="5" t="n"/>
+      <c r="AK147" s="12">
+        <f>IF(B147="","",IF(ISNUMBER(B147),B147,DATE(VALUE(LEFT(B147,4)),VALUE(MID(B147,6,2)),VALUE(MID(B147,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL147" s="12">
+        <f>IF(C147="","",IF(ISNUMBER(C147),C147,DATE(VALUE(LEFT(C147,4)),VALUE(MID(C147,6,2)),VALUE(MID(C147,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="5" t="n"/>
       <c r="D148" s="5">
-        <f>IF(AND(B148&lt;&gt;"",C148&lt;&gt;""),C148-B148+1,"")</f>
+        <f>IF(AND(AK148&lt;&gt;"",AL148&lt;&gt;""),AL148-AK148+1,"")</f>
         <v/>
       </c>
       <c r="E148" s="5">
-        <f>IF(B148&lt;&gt;"",YEAR(B148),"")</f>
+        <f>IF(AK148&lt;&gt;"",YEAR(AK148),"")</f>
         <v/>
       </c>
       <c r="F148" s="6" t="n"/>
@@ -26357,17 +27515,25 @@
         <v/>
       </c>
       <c r="AJ148" s="5" t="n"/>
+      <c r="AK148" s="12">
+        <f>IF(B148="","",IF(ISNUMBER(B148),B148,DATE(VALUE(LEFT(B148,4)),VALUE(MID(B148,6,2)),VALUE(MID(B148,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL148" s="12">
+        <f>IF(C148="","",IF(ISNUMBER(C148),C148,DATE(VALUE(LEFT(C148,4)),VALUE(MID(C148,6,2)),VALUE(MID(C148,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="5" t="n"/>
       <c r="D149" s="5">
-        <f>IF(AND(B149&lt;&gt;"",C149&lt;&gt;""),C149-B149+1,"")</f>
+        <f>IF(AND(AK149&lt;&gt;"",AL149&lt;&gt;""),AL149-AK149+1,"")</f>
         <v/>
       </c>
       <c r="E149" s="5">
-        <f>IF(B149&lt;&gt;"",YEAR(B149),"")</f>
+        <f>IF(AK149&lt;&gt;"",YEAR(AK149),"")</f>
         <v/>
       </c>
       <c r="F149" s="6" t="n"/>
@@ -26455,17 +27621,25 @@
         <v/>
       </c>
       <c r="AJ149" s="5" t="n"/>
+      <c r="AK149" s="12">
+        <f>IF(B149="","",IF(ISNUMBER(B149),B149,DATE(VALUE(LEFT(B149,4)),VALUE(MID(B149,6,2)),VALUE(MID(B149,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL149" s="12">
+        <f>IF(C149="","",IF(ISNUMBER(C149),C149,DATE(VALUE(LEFT(C149,4)),VALUE(MID(C149,6,2)),VALUE(MID(C149,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="5" t="n"/>
       <c r="D150" s="5">
-        <f>IF(AND(B150&lt;&gt;"",C150&lt;&gt;""),C150-B150+1,"")</f>
+        <f>IF(AND(AK150&lt;&gt;"",AL150&lt;&gt;""),AL150-AK150+1,"")</f>
         <v/>
       </c>
       <c r="E150" s="5">
-        <f>IF(B150&lt;&gt;"",YEAR(B150),"")</f>
+        <f>IF(AK150&lt;&gt;"",YEAR(AK150),"")</f>
         <v/>
       </c>
       <c r="F150" s="6" t="n"/>
@@ -26553,17 +27727,25 @@
         <v/>
       </c>
       <c r="AJ150" s="5" t="n"/>
+      <c r="AK150" s="12">
+        <f>IF(B150="","",IF(ISNUMBER(B150),B150,DATE(VALUE(LEFT(B150,4)),VALUE(MID(B150,6,2)),VALUE(MID(B150,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL150" s="12">
+        <f>IF(C150="","",IF(ISNUMBER(C150),C150,DATE(VALUE(LEFT(C150,4)),VALUE(MID(C150,6,2)),VALUE(MID(C150,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="5" t="n"/>
       <c r="D151" s="5">
-        <f>IF(AND(B151&lt;&gt;"",C151&lt;&gt;""),C151-B151+1,"")</f>
+        <f>IF(AND(AK151&lt;&gt;"",AL151&lt;&gt;""),AL151-AK151+1,"")</f>
         <v/>
       </c>
       <c r="E151" s="5">
-        <f>IF(B151&lt;&gt;"",YEAR(B151),"")</f>
+        <f>IF(AK151&lt;&gt;"",YEAR(AK151),"")</f>
         <v/>
       </c>
       <c r="F151" s="6" t="n"/>
@@ -26651,17 +27833,25 @@
         <v/>
       </c>
       <c r="AJ151" s="5" t="n"/>
+      <c r="AK151" s="12">
+        <f>IF(B151="","",IF(ISNUMBER(B151),B151,DATE(VALUE(LEFT(B151,4)),VALUE(MID(B151,6,2)),VALUE(MID(B151,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL151" s="12">
+        <f>IF(C151="","",IF(ISNUMBER(C151),C151,DATE(VALUE(LEFT(C151,4)),VALUE(MID(C151,6,2)),VALUE(MID(C151,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="5" t="n"/>
       <c r="D152" s="5">
-        <f>IF(AND(B152&lt;&gt;"",C152&lt;&gt;""),C152-B152+1,"")</f>
+        <f>IF(AND(AK152&lt;&gt;"",AL152&lt;&gt;""),AL152-AK152+1,"")</f>
         <v/>
       </c>
       <c r="E152" s="5">
-        <f>IF(B152&lt;&gt;"",YEAR(B152),"")</f>
+        <f>IF(AK152&lt;&gt;"",YEAR(AK152),"")</f>
         <v/>
       </c>
       <c r="F152" s="6" t="n"/>
@@ -26749,17 +27939,25 @@
         <v/>
       </c>
       <c r="AJ152" s="5" t="n"/>
+      <c r="AK152" s="12">
+        <f>IF(B152="","",IF(ISNUMBER(B152),B152,DATE(VALUE(LEFT(B152,4)),VALUE(MID(B152,6,2)),VALUE(MID(B152,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL152" s="12">
+        <f>IF(C152="","",IF(ISNUMBER(C152),C152,DATE(VALUE(LEFT(C152,4)),VALUE(MID(C152,6,2)),VALUE(MID(C152,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="5" t="n"/>
       <c r="D153" s="5">
-        <f>IF(AND(B153&lt;&gt;"",C153&lt;&gt;""),C153-B153+1,"")</f>
+        <f>IF(AND(AK153&lt;&gt;"",AL153&lt;&gt;""),AL153-AK153+1,"")</f>
         <v/>
       </c>
       <c r="E153" s="5">
-        <f>IF(B153&lt;&gt;"",YEAR(B153),"")</f>
+        <f>IF(AK153&lt;&gt;"",YEAR(AK153),"")</f>
         <v/>
       </c>
       <c r="F153" s="6" t="n"/>
@@ -26847,17 +28045,25 @@
         <v/>
       </c>
       <c r="AJ153" s="5" t="n"/>
+      <c r="AK153" s="12">
+        <f>IF(B153="","",IF(ISNUMBER(B153),B153,DATE(VALUE(LEFT(B153,4)),VALUE(MID(B153,6,2)),VALUE(MID(B153,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL153" s="12">
+        <f>IF(C153="","",IF(ISNUMBER(C153),C153,DATE(VALUE(LEFT(C153,4)),VALUE(MID(C153,6,2)),VALUE(MID(C153,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="5" t="n"/>
       <c r="D154" s="5">
-        <f>IF(AND(B154&lt;&gt;"",C154&lt;&gt;""),C154-B154+1,"")</f>
+        <f>IF(AND(AK154&lt;&gt;"",AL154&lt;&gt;""),AL154-AK154+1,"")</f>
         <v/>
       </c>
       <c r="E154" s="5">
-        <f>IF(B154&lt;&gt;"",YEAR(B154),"")</f>
+        <f>IF(AK154&lt;&gt;"",YEAR(AK154),"")</f>
         <v/>
       </c>
       <c r="F154" s="6" t="n"/>
@@ -26945,17 +28151,25 @@
         <v/>
       </c>
       <c r="AJ154" s="5" t="n"/>
+      <c r="AK154" s="12">
+        <f>IF(B154="","",IF(ISNUMBER(B154),B154,DATE(VALUE(LEFT(B154,4)),VALUE(MID(B154,6,2)),VALUE(MID(B154,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL154" s="12">
+        <f>IF(C154="","",IF(ISNUMBER(C154),C154,DATE(VALUE(LEFT(C154,4)),VALUE(MID(C154,6,2)),VALUE(MID(C154,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="5" t="n"/>
       <c r="D155" s="5">
-        <f>IF(AND(B155&lt;&gt;"",C155&lt;&gt;""),C155-B155+1,"")</f>
+        <f>IF(AND(AK155&lt;&gt;"",AL155&lt;&gt;""),AL155-AK155+1,"")</f>
         <v/>
       </c>
       <c r="E155" s="5">
-        <f>IF(B155&lt;&gt;"",YEAR(B155),"")</f>
+        <f>IF(AK155&lt;&gt;"",YEAR(AK155),"")</f>
         <v/>
       </c>
       <c r="F155" s="6" t="n"/>
@@ -27043,17 +28257,25 @@
         <v/>
       </c>
       <c r="AJ155" s="5" t="n"/>
+      <c r="AK155" s="12">
+        <f>IF(B155="","",IF(ISNUMBER(B155),B155,DATE(VALUE(LEFT(B155,4)),VALUE(MID(B155,6,2)),VALUE(MID(B155,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL155" s="12">
+        <f>IF(C155="","",IF(ISNUMBER(C155),C155,DATE(VALUE(LEFT(C155,4)),VALUE(MID(C155,6,2)),VALUE(MID(C155,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="5" t="n"/>
       <c r="D156" s="5">
-        <f>IF(AND(B156&lt;&gt;"",C156&lt;&gt;""),C156-B156+1,"")</f>
+        <f>IF(AND(AK156&lt;&gt;"",AL156&lt;&gt;""),AL156-AK156+1,"")</f>
         <v/>
       </c>
       <c r="E156" s="5">
-        <f>IF(B156&lt;&gt;"",YEAR(B156),"")</f>
+        <f>IF(AK156&lt;&gt;"",YEAR(AK156),"")</f>
         <v/>
       </c>
       <c r="F156" s="6" t="n"/>
@@ -27141,17 +28363,25 @@
         <v/>
       </c>
       <c r="AJ156" s="5" t="n"/>
+      <c r="AK156" s="12">
+        <f>IF(B156="","",IF(ISNUMBER(B156),B156,DATE(VALUE(LEFT(B156,4)),VALUE(MID(B156,6,2)),VALUE(MID(B156,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL156" s="12">
+        <f>IF(C156="","",IF(ISNUMBER(C156),C156,DATE(VALUE(LEFT(C156,4)),VALUE(MID(C156,6,2)),VALUE(MID(C156,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="5" t="n"/>
       <c r="D157" s="5">
-        <f>IF(AND(B157&lt;&gt;"",C157&lt;&gt;""),C157-B157+1,"")</f>
+        <f>IF(AND(AK157&lt;&gt;"",AL157&lt;&gt;""),AL157-AK157+1,"")</f>
         <v/>
       </c>
       <c r="E157" s="5">
-        <f>IF(B157&lt;&gt;"",YEAR(B157),"")</f>
+        <f>IF(AK157&lt;&gt;"",YEAR(AK157),"")</f>
         <v/>
       </c>
       <c r="F157" s="6" t="n"/>
@@ -27239,17 +28469,25 @@
         <v/>
       </c>
       <c r="AJ157" s="5" t="n"/>
+      <c r="AK157" s="12">
+        <f>IF(B157="","",IF(ISNUMBER(B157),B157,DATE(VALUE(LEFT(B157,4)),VALUE(MID(B157,6,2)),VALUE(MID(B157,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL157" s="12">
+        <f>IF(C157="","",IF(ISNUMBER(C157),C157,DATE(VALUE(LEFT(C157,4)),VALUE(MID(C157,6,2)),VALUE(MID(C157,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="5" t="n"/>
       <c r="D158" s="5">
-        <f>IF(AND(B158&lt;&gt;"",C158&lt;&gt;""),C158-B158+1,"")</f>
+        <f>IF(AND(AK158&lt;&gt;"",AL158&lt;&gt;""),AL158-AK158+1,"")</f>
         <v/>
       </c>
       <c r="E158" s="5">
-        <f>IF(B158&lt;&gt;"",YEAR(B158),"")</f>
+        <f>IF(AK158&lt;&gt;"",YEAR(AK158),"")</f>
         <v/>
       </c>
       <c r="F158" s="6" t="n"/>
@@ -27337,17 +28575,25 @@
         <v/>
       </c>
       <c r="AJ158" s="5" t="n"/>
+      <c r="AK158" s="12">
+        <f>IF(B158="","",IF(ISNUMBER(B158),B158,DATE(VALUE(LEFT(B158,4)),VALUE(MID(B158,6,2)),VALUE(MID(B158,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL158" s="12">
+        <f>IF(C158="","",IF(ISNUMBER(C158),C158,DATE(VALUE(LEFT(C158,4)),VALUE(MID(C158,6,2)),VALUE(MID(C158,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="5" t="n"/>
       <c r="D159" s="5">
-        <f>IF(AND(B159&lt;&gt;"",C159&lt;&gt;""),C159-B159+1,"")</f>
+        <f>IF(AND(AK159&lt;&gt;"",AL159&lt;&gt;""),AL159-AK159+1,"")</f>
         <v/>
       </c>
       <c r="E159" s="5">
-        <f>IF(B159&lt;&gt;"",YEAR(B159),"")</f>
+        <f>IF(AK159&lt;&gt;"",YEAR(AK159),"")</f>
         <v/>
       </c>
       <c r="F159" s="6" t="n"/>
@@ -27435,17 +28681,25 @@
         <v/>
       </c>
       <c r="AJ159" s="5" t="n"/>
+      <c r="AK159" s="12">
+        <f>IF(B159="","",IF(ISNUMBER(B159),B159,DATE(VALUE(LEFT(B159,4)),VALUE(MID(B159,6,2)),VALUE(MID(B159,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL159" s="12">
+        <f>IF(C159="","",IF(ISNUMBER(C159),C159,DATE(VALUE(LEFT(C159,4)),VALUE(MID(C159,6,2)),VALUE(MID(C159,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="5" t="n"/>
       <c r="D160" s="5">
-        <f>IF(AND(B160&lt;&gt;"",C160&lt;&gt;""),C160-B160+1,"")</f>
+        <f>IF(AND(AK160&lt;&gt;"",AL160&lt;&gt;""),AL160-AK160+1,"")</f>
         <v/>
       </c>
       <c r="E160" s="5">
-        <f>IF(B160&lt;&gt;"",YEAR(B160),"")</f>
+        <f>IF(AK160&lt;&gt;"",YEAR(AK160),"")</f>
         <v/>
       </c>
       <c r="F160" s="6" t="n"/>
@@ -27533,17 +28787,25 @@
         <v/>
       </c>
       <c r="AJ160" s="5" t="n"/>
+      <c r="AK160" s="12">
+        <f>IF(B160="","",IF(ISNUMBER(B160),B160,DATE(VALUE(LEFT(B160,4)),VALUE(MID(B160,6,2)),VALUE(MID(B160,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL160" s="12">
+        <f>IF(C160="","",IF(ISNUMBER(C160),C160,DATE(VALUE(LEFT(C160,4)),VALUE(MID(C160,6,2)),VALUE(MID(C160,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="5" t="n"/>
       <c r="D161" s="5">
-        <f>IF(AND(B161&lt;&gt;"",C161&lt;&gt;""),C161-B161+1,"")</f>
+        <f>IF(AND(AK161&lt;&gt;"",AL161&lt;&gt;""),AL161-AK161+1,"")</f>
         <v/>
       </c>
       <c r="E161" s="5">
-        <f>IF(B161&lt;&gt;"",YEAR(B161),"")</f>
+        <f>IF(AK161&lt;&gt;"",YEAR(AK161),"")</f>
         <v/>
       </c>
       <c r="F161" s="6" t="n"/>
@@ -27631,17 +28893,25 @@
         <v/>
       </c>
       <c r="AJ161" s="5" t="n"/>
+      <c r="AK161" s="12">
+        <f>IF(B161="","",IF(ISNUMBER(B161),B161,DATE(VALUE(LEFT(B161,4)),VALUE(MID(B161,6,2)),VALUE(MID(B161,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL161" s="12">
+        <f>IF(C161="","",IF(ISNUMBER(C161),C161,DATE(VALUE(LEFT(C161,4)),VALUE(MID(C161,6,2)),VALUE(MID(C161,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="5" t="n"/>
       <c r="D162" s="5">
-        <f>IF(AND(B162&lt;&gt;"",C162&lt;&gt;""),C162-B162+1,"")</f>
+        <f>IF(AND(AK162&lt;&gt;"",AL162&lt;&gt;""),AL162-AK162+1,"")</f>
         <v/>
       </c>
       <c r="E162" s="5">
-        <f>IF(B162&lt;&gt;"",YEAR(B162),"")</f>
+        <f>IF(AK162&lt;&gt;"",YEAR(AK162),"")</f>
         <v/>
       </c>
       <c r="F162" s="6" t="n"/>
@@ -27729,17 +28999,25 @@
         <v/>
       </c>
       <c r="AJ162" s="5" t="n"/>
+      <c r="AK162" s="12">
+        <f>IF(B162="","",IF(ISNUMBER(B162),B162,DATE(VALUE(LEFT(B162,4)),VALUE(MID(B162,6,2)),VALUE(MID(B162,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL162" s="12">
+        <f>IF(C162="","",IF(ISNUMBER(C162),C162,DATE(VALUE(LEFT(C162,4)),VALUE(MID(C162,6,2)),VALUE(MID(C162,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="5" t="n"/>
       <c r="D163" s="5">
-        <f>IF(AND(B163&lt;&gt;"",C163&lt;&gt;""),C163-B163+1,"")</f>
+        <f>IF(AND(AK163&lt;&gt;"",AL163&lt;&gt;""),AL163-AK163+1,"")</f>
         <v/>
       </c>
       <c r="E163" s="5">
-        <f>IF(B163&lt;&gt;"",YEAR(B163),"")</f>
+        <f>IF(AK163&lt;&gt;"",YEAR(AK163),"")</f>
         <v/>
       </c>
       <c r="F163" s="6" t="n"/>
@@ -27827,17 +29105,25 @@
         <v/>
       </c>
       <c r="AJ163" s="5" t="n"/>
+      <c r="AK163" s="12">
+        <f>IF(B163="","",IF(ISNUMBER(B163),B163,DATE(VALUE(LEFT(B163,4)),VALUE(MID(B163,6,2)),VALUE(MID(B163,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL163" s="12">
+        <f>IF(C163="","",IF(ISNUMBER(C163),C163,DATE(VALUE(LEFT(C163,4)),VALUE(MID(C163,6,2)),VALUE(MID(C163,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="5" t="n"/>
       <c r="D164" s="5">
-        <f>IF(AND(B164&lt;&gt;"",C164&lt;&gt;""),C164-B164+1,"")</f>
+        <f>IF(AND(AK164&lt;&gt;"",AL164&lt;&gt;""),AL164-AK164+1,"")</f>
         <v/>
       </c>
       <c r="E164" s="5">
-        <f>IF(B164&lt;&gt;"",YEAR(B164),"")</f>
+        <f>IF(AK164&lt;&gt;"",YEAR(AK164),"")</f>
         <v/>
       </c>
       <c r="F164" s="6" t="n"/>
@@ -27925,17 +29211,25 @@
         <v/>
       </c>
       <c r="AJ164" s="5" t="n"/>
+      <c r="AK164" s="12">
+        <f>IF(B164="","",IF(ISNUMBER(B164),B164,DATE(VALUE(LEFT(B164,4)),VALUE(MID(B164,6,2)),VALUE(MID(B164,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL164" s="12">
+        <f>IF(C164="","",IF(ISNUMBER(C164),C164,DATE(VALUE(LEFT(C164,4)),VALUE(MID(C164,6,2)),VALUE(MID(C164,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="5" t="n"/>
       <c r="D165" s="5">
-        <f>IF(AND(B165&lt;&gt;"",C165&lt;&gt;""),C165-B165+1,"")</f>
+        <f>IF(AND(AK165&lt;&gt;"",AL165&lt;&gt;""),AL165-AK165+1,"")</f>
         <v/>
       </c>
       <c r="E165" s="5">
-        <f>IF(B165&lt;&gt;"",YEAR(B165),"")</f>
+        <f>IF(AK165&lt;&gt;"",YEAR(AK165),"")</f>
         <v/>
       </c>
       <c r="F165" s="6" t="n"/>
@@ -28023,17 +29317,25 @@
         <v/>
       </c>
       <c r="AJ165" s="5" t="n"/>
+      <c r="AK165" s="12">
+        <f>IF(B165="","",IF(ISNUMBER(B165),B165,DATE(VALUE(LEFT(B165,4)),VALUE(MID(B165,6,2)),VALUE(MID(B165,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL165" s="12">
+        <f>IF(C165="","",IF(ISNUMBER(C165),C165,DATE(VALUE(LEFT(C165,4)),VALUE(MID(C165,6,2)),VALUE(MID(C165,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="5" t="n"/>
       <c r="D166" s="5">
-        <f>IF(AND(B166&lt;&gt;"",C166&lt;&gt;""),C166-B166+1,"")</f>
+        <f>IF(AND(AK166&lt;&gt;"",AL166&lt;&gt;""),AL166-AK166+1,"")</f>
         <v/>
       </c>
       <c r="E166" s="5">
-        <f>IF(B166&lt;&gt;"",YEAR(B166),"")</f>
+        <f>IF(AK166&lt;&gt;"",YEAR(AK166),"")</f>
         <v/>
       </c>
       <c r="F166" s="6" t="n"/>
@@ -28121,17 +29423,25 @@
         <v/>
       </c>
       <c r="AJ166" s="5" t="n"/>
+      <c r="AK166" s="12">
+        <f>IF(B166="","",IF(ISNUMBER(B166),B166,DATE(VALUE(LEFT(B166,4)),VALUE(MID(B166,6,2)),VALUE(MID(B166,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL166" s="12">
+        <f>IF(C166="","",IF(ISNUMBER(C166),C166,DATE(VALUE(LEFT(C166,4)),VALUE(MID(C166,6,2)),VALUE(MID(C166,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="5" t="n"/>
       <c r="D167" s="5">
-        <f>IF(AND(B167&lt;&gt;"",C167&lt;&gt;""),C167-B167+1,"")</f>
+        <f>IF(AND(AK167&lt;&gt;"",AL167&lt;&gt;""),AL167-AK167+1,"")</f>
         <v/>
       </c>
       <c r="E167" s="5">
-        <f>IF(B167&lt;&gt;"",YEAR(B167),"")</f>
+        <f>IF(AK167&lt;&gt;"",YEAR(AK167),"")</f>
         <v/>
       </c>
       <c r="F167" s="6" t="n"/>
@@ -28219,17 +29529,25 @@
         <v/>
       </c>
       <c r="AJ167" s="5" t="n"/>
+      <c r="AK167" s="12">
+        <f>IF(B167="","",IF(ISNUMBER(B167),B167,DATE(VALUE(LEFT(B167,4)),VALUE(MID(B167,6,2)),VALUE(MID(B167,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL167" s="12">
+        <f>IF(C167="","",IF(ISNUMBER(C167),C167,DATE(VALUE(LEFT(C167,4)),VALUE(MID(C167,6,2)),VALUE(MID(C167,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="5" t="n"/>
       <c r="D168" s="5">
-        <f>IF(AND(B168&lt;&gt;"",C168&lt;&gt;""),C168-B168+1,"")</f>
+        <f>IF(AND(AK168&lt;&gt;"",AL168&lt;&gt;""),AL168-AK168+1,"")</f>
         <v/>
       </c>
       <c r="E168" s="5">
-        <f>IF(B168&lt;&gt;"",YEAR(B168),"")</f>
+        <f>IF(AK168&lt;&gt;"",YEAR(AK168),"")</f>
         <v/>
       </c>
       <c r="F168" s="6" t="n"/>
@@ -28317,17 +29635,25 @@
         <v/>
       </c>
       <c r="AJ168" s="5" t="n"/>
+      <c r="AK168" s="12">
+        <f>IF(B168="","",IF(ISNUMBER(B168),B168,DATE(VALUE(LEFT(B168,4)),VALUE(MID(B168,6,2)),VALUE(MID(B168,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL168" s="12">
+        <f>IF(C168="","",IF(ISNUMBER(C168),C168,DATE(VALUE(LEFT(C168,4)),VALUE(MID(C168,6,2)),VALUE(MID(C168,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="5" t="n"/>
       <c r="D169" s="5">
-        <f>IF(AND(B169&lt;&gt;"",C169&lt;&gt;""),C169-B169+1,"")</f>
+        <f>IF(AND(AK169&lt;&gt;"",AL169&lt;&gt;""),AL169-AK169+1,"")</f>
         <v/>
       </c>
       <c r="E169" s="5">
-        <f>IF(B169&lt;&gt;"",YEAR(B169),"")</f>
+        <f>IF(AK169&lt;&gt;"",YEAR(AK169),"")</f>
         <v/>
       </c>
       <c r="F169" s="6" t="n"/>
@@ -28415,17 +29741,25 @@
         <v/>
       </c>
       <c r="AJ169" s="5" t="n"/>
+      <c r="AK169" s="12">
+        <f>IF(B169="","",IF(ISNUMBER(B169),B169,DATE(VALUE(LEFT(B169,4)),VALUE(MID(B169,6,2)),VALUE(MID(B169,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL169" s="12">
+        <f>IF(C169="","",IF(ISNUMBER(C169),C169,DATE(VALUE(LEFT(C169,4)),VALUE(MID(C169,6,2)),VALUE(MID(C169,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="5" t="n"/>
       <c r="D170" s="5">
-        <f>IF(AND(B170&lt;&gt;"",C170&lt;&gt;""),C170-B170+1,"")</f>
+        <f>IF(AND(AK170&lt;&gt;"",AL170&lt;&gt;""),AL170-AK170+1,"")</f>
         <v/>
       </c>
       <c r="E170" s="5">
-        <f>IF(B170&lt;&gt;"",YEAR(B170),"")</f>
+        <f>IF(AK170&lt;&gt;"",YEAR(AK170),"")</f>
         <v/>
       </c>
       <c r="F170" s="6" t="n"/>
@@ -28513,17 +29847,25 @@
         <v/>
       </c>
       <c r="AJ170" s="5" t="n"/>
+      <c r="AK170" s="12">
+        <f>IF(B170="","",IF(ISNUMBER(B170),B170,DATE(VALUE(LEFT(B170,4)),VALUE(MID(B170,6,2)),VALUE(MID(B170,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL170" s="12">
+        <f>IF(C170="","",IF(ISNUMBER(C170),C170,DATE(VALUE(LEFT(C170,4)),VALUE(MID(C170,6,2)),VALUE(MID(C170,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="5" t="n"/>
       <c r="D171" s="5">
-        <f>IF(AND(B171&lt;&gt;"",C171&lt;&gt;""),C171-B171+1,"")</f>
+        <f>IF(AND(AK171&lt;&gt;"",AL171&lt;&gt;""),AL171-AK171+1,"")</f>
         <v/>
       </c>
       <c r="E171" s="5">
-        <f>IF(B171&lt;&gt;"",YEAR(B171),"")</f>
+        <f>IF(AK171&lt;&gt;"",YEAR(AK171),"")</f>
         <v/>
       </c>
       <c r="F171" s="6" t="n"/>
@@ -28611,17 +29953,25 @@
         <v/>
       </c>
       <c r="AJ171" s="5" t="n"/>
+      <c r="AK171" s="12">
+        <f>IF(B171="","",IF(ISNUMBER(B171),B171,DATE(VALUE(LEFT(B171,4)),VALUE(MID(B171,6,2)),VALUE(MID(B171,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL171" s="12">
+        <f>IF(C171="","",IF(ISNUMBER(C171),C171,DATE(VALUE(LEFT(C171,4)),VALUE(MID(C171,6,2)),VALUE(MID(C171,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="5" t="n"/>
       <c r="D172" s="5">
-        <f>IF(AND(B172&lt;&gt;"",C172&lt;&gt;""),C172-B172+1,"")</f>
+        <f>IF(AND(AK172&lt;&gt;"",AL172&lt;&gt;""),AL172-AK172+1,"")</f>
         <v/>
       </c>
       <c r="E172" s="5">
-        <f>IF(B172&lt;&gt;"",YEAR(B172),"")</f>
+        <f>IF(AK172&lt;&gt;"",YEAR(AK172),"")</f>
         <v/>
       </c>
       <c r="F172" s="6" t="n"/>
@@ -28709,17 +30059,25 @@
         <v/>
       </c>
       <c r="AJ172" s="5" t="n"/>
+      <c r="AK172" s="12">
+        <f>IF(B172="","",IF(ISNUMBER(B172),B172,DATE(VALUE(LEFT(B172,4)),VALUE(MID(B172,6,2)),VALUE(MID(B172,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL172" s="12">
+        <f>IF(C172="","",IF(ISNUMBER(C172),C172,DATE(VALUE(LEFT(C172,4)),VALUE(MID(C172,6,2)),VALUE(MID(C172,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="5" t="n"/>
       <c r="D173" s="5">
-        <f>IF(AND(B173&lt;&gt;"",C173&lt;&gt;""),C173-B173+1,"")</f>
+        <f>IF(AND(AK173&lt;&gt;"",AL173&lt;&gt;""),AL173-AK173+1,"")</f>
         <v/>
       </c>
       <c r="E173" s="5">
-        <f>IF(B173&lt;&gt;"",YEAR(B173),"")</f>
+        <f>IF(AK173&lt;&gt;"",YEAR(AK173),"")</f>
         <v/>
       </c>
       <c r="F173" s="6" t="n"/>
@@ -28807,17 +30165,25 @@
         <v/>
       </c>
       <c r="AJ173" s="5" t="n"/>
+      <c r="AK173" s="12">
+        <f>IF(B173="","",IF(ISNUMBER(B173),B173,DATE(VALUE(LEFT(B173,4)),VALUE(MID(B173,6,2)),VALUE(MID(B173,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL173" s="12">
+        <f>IF(C173="","",IF(ISNUMBER(C173),C173,DATE(VALUE(LEFT(C173,4)),VALUE(MID(C173,6,2)),VALUE(MID(C173,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="5" t="n"/>
       <c r="D174" s="5">
-        <f>IF(AND(B174&lt;&gt;"",C174&lt;&gt;""),C174-B174+1,"")</f>
+        <f>IF(AND(AK174&lt;&gt;"",AL174&lt;&gt;""),AL174-AK174+1,"")</f>
         <v/>
       </c>
       <c r="E174" s="5">
-        <f>IF(B174&lt;&gt;"",YEAR(B174),"")</f>
+        <f>IF(AK174&lt;&gt;"",YEAR(AK174),"")</f>
         <v/>
       </c>
       <c r="F174" s="6" t="n"/>
@@ -28905,17 +30271,25 @@
         <v/>
       </c>
       <c r="AJ174" s="5" t="n"/>
+      <c r="AK174" s="12">
+        <f>IF(B174="","",IF(ISNUMBER(B174),B174,DATE(VALUE(LEFT(B174,4)),VALUE(MID(B174,6,2)),VALUE(MID(B174,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL174" s="12">
+        <f>IF(C174="","",IF(ISNUMBER(C174),C174,DATE(VALUE(LEFT(C174,4)),VALUE(MID(C174,6,2)),VALUE(MID(C174,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="5" t="n"/>
       <c r="D175" s="5">
-        <f>IF(AND(B175&lt;&gt;"",C175&lt;&gt;""),C175-B175+1,"")</f>
+        <f>IF(AND(AK175&lt;&gt;"",AL175&lt;&gt;""),AL175-AK175+1,"")</f>
         <v/>
       </c>
       <c r="E175" s="5">
-        <f>IF(B175&lt;&gt;"",YEAR(B175),"")</f>
+        <f>IF(AK175&lt;&gt;"",YEAR(AK175),"")</f>
         <v/>
       </c>
       <c r="F175" s="6" t="n"/>
@@ -29003,17 +30377,25 @@
         <v/>
       </c>
       <c r="AJ175" s="5" t="n"/>
+      <c r="AK175" s="12">
+        <f>IF(B175="","",IF(ISNUMBER(B175),B175,DATE(VALUE(LEFT(B175,4)),VALUE(MID(B175,6,2)),VALUE(MID(B175,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL175" s="12">
+        <f>IF(C175="","",IF(ISNUMBER(C175),C175,DATE(VALUE(LEFT(C175,4)),VALUE(MID(C175,6,2)),VALUE(MID(C175,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="5" t="n"/>
       <c r="D176" s="5">
-        <f>IF(AND(B176&lt;&gt;"",C176&lt;&gt;""),C176-B176+1,"")</f>
+        <f>IF(AND(AK176&lt;&gt;"",AL176&lt;&gt;""),AL176-AK176+1,"")</f>
         <v/>
       </c>
       <c r="E176" s="5">
-        <f>IF(B176&lt;&gt;"",YEAR(B176),"")</f>
+        <f>IF(AK176&lt;&gt;"",YEAR(AK176),"")</f>
         <v/>
       </c>
       <c r="F176" s="6" t="n"/>
@@ -29101,17 +30483,25 @@
         <v/>
       </c>
       <c r="AJ176" s="5" t="n"/>
+      <c r="AK176" s="12">
+        <f>IF(B176="","",IF(ISNUMBER(B176),B176,DATE(VALUE(LEFT(B176,4)),VALUE(MID(B176,6,2)),VALUE(MID(B176,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL176" s="12">
+        <f>IF(C176="","",IF(ISNUMBER(C176),C176,DATE(VALUE(LEFT(C176,4)),VALUE(MID(C176,6,2)),VALUE(MID(C176,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="5" t="n"/>
       <c r="D177" s="5">
-        <f>IF(AND(B177&lt;&gt;"",C177&lt;&gt;""),C177-B177+1,"")</f>
+        <f>IF(AND(AK177&lt;&gt;"",AL177&lt;&gt;""),AL177-AK177+1,"")</f>
         <v/>
       </c>
       <c r="E177" s="5">
-        <f>IF(B177&lt;&gt;"",YEAR(B177),"")</f>
+        <f>IF(AK177&lt;&gt;"",YEAR(AK177),"")</f>
         <v/>
       </c>
       <c r="F177" s="6" t="n"/>
@@ -29199,17 +30589,25 @@
         <v/>
       </c>
       <c r="AJ177" s="5" t="n"/>
+      <c r="AK177" s="12">
+        <f>IF(B177="","",IF(ISNUMBER(B177),B177,DATE(VALUE(LEFT(B177,4)),VALUE(MID(B177,6,2)),VALUE(MID(B177,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL177" s="12">
+        <f>IF(C177="","",IF(ISNUMBER(C177),C177,DATE(VALUE(LEFT(C177,4)),VALUE(MID(C177,6,2)),VALUE(MID(C177,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="5" t="n"/>
       <c r="D178" s="5">
-        <f>IF(AND(B178&lt;&gt;"",C178&lt;&gt;""),C178-B178+1,"")</f>
+        <f>IF(AND(AK178&lt;&gt;"",AL178&lt;&gt;""),AL178-AK178+1,"")</f>
         <v/>
       </c>
       <c r="E178" s="5">
-        <f>IF(B178&lt;&gt;"",YEAR(B178),"")</f>
+        <f>IF(AK178&lt;&gt;"",YEAR(AK178),"")</f>
         <v/>
       </c>
       <c r="F178" s="6" t="n"/>
@@ -29297,17 +30695,25 @@
         <v/>
       </c>
       <c r="AJ178" s="5" t="n"/>
+      <c r="AK178" s="12">
+        <f>IF(B178="","",IF(ISNUMBER(B178),B178,DATE(VALUE(LEFT(B178,4)),VALUE(MID(B178,6,2)),VALUE(MID(B178,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL178" s="12">
+        <f>IF(C178="","",IF(ISNUMBER(C178),C178,DATE(VALUE(LEFT(C178,4)),VALUE(MID(C178,6,2)),VALUE(MID(C178,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="5" t="n"/>
       <c r="D179" s="5">
-        <f>IF(AND(B179&lt;&gt;"",C179&lt;&gt;""),C179-B179+1,"")</f>
+        <f>IF(AND(AK179&lt;&gt;"",AL179&lt;&gt;""),AL179-AK179+1,"")</f>
         <v/>
       </c>
       <c r="E179" s="5">
-        <f>IF(B179&lt;&gt;"",YEAR(B179),"")</f>
+        <f>IF(AK179&lt;&gt;"",YEAR(AK179),"")</f>
         <v/>
       </c>
       <c r="F179" s="6" t="n"/>
@@ -29395,17 +30801,25 @@
         <v/>
       </c>
       <c r="AJ179" s="5" t="n"/>
+      <c r="AK179" s="12">
+        <f>IF(B179="","",IF(ISNUMBER(B179),B179,DATE(VALUE(LEFT(B179,4)),VALUE(MID(B179,6,2)),VALUE(MID(B179,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL179" s="12">
+        <f>IF(C179="","",IF(ISNUMBER(C179),C179,DATE(VALUE(LEFT(C179,4)),VALUE(MID(C179,6,2)),VALUE(MID(C179,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="5" t="n"/>
       <c r="D180" s="5">
-        <f>IF(AND(B180&lt;&gt;"",C180&lt;&gt;""),C180-B180+1,"")</f>
+        <f>IF(AND(AK180&lt;&gt;"",AL180&lt;&gt;""),AL180-AK180+1,"")</f>
         <v/>
       </c>
       <c r="E180" s="5">
-        <f>IF(B180&lt;&gt;"",YEAR(B180),"")</f>
+        <f>IF(AK180&lt;&gt;"",YEAR(AK180),"")</f>
         <v/>
       </c>
       <c r="F180" s="6" t="n"/>
@@ -29493,17 +30907,25 @@
         <v/>
       </c>
       <c r="AJ180" s="5" t="n"/>
+      <c r="AK180" s="12">
+        <f>IF(B180="","",IF(ISNUMBER(B180),B180,DATE(VALUE(LEFT(B180,4)),VALUE(MID(B180,6,2)),VALUE(MID(B180,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL180" s="12">
+        <f>IF(C180="","",IF(ISNUMBER(C180),C180,DATE(VALUE(LEFT(C180,4)),VALUE(MID(C180,6,2)),VALUE(MID(C180,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="5" t="n"/>
       <c r="D181" s="5">
-        <f>IF(AND(B181&lt;&gt;"",C181&lt;&gt;""),C181-B181+1,"")</f>
+        <f>IF(AND(AK181&lt;&gt;"",AL181&lt;&gt;""),AL181-AK181+1,"")</f>
         <v/>
       </c>
       <c r="E181" s="5">
-        <f>IF(B181&lt;&gt;"",YEAR(B181),"")</f>
+        <f>IF(AK181&lt;&gt;"",YEAR(AK181),"")</f>
         <v/>
       </c>
       <c r="F181" s="6" t="n"/>
@@ -29591,17 +31013,25 @@
         <v/>
       </c>
       <c r="AJ181" s="5" t="n"/>
+      <c r="AK181" s="12">
+        <f>IF(B181="","",IF(ISNUMBER(B181),B181,DATE(VALUE(LEFT(B181,4)),VALUE(MID(B181,6,2)),VALUE(MID(B181,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL181" s="12">
+        <f>IF(C181="","",IF(ISNUMBER(C181),C181,DATE(VALUE(LEFT(C181,4)),VALUE(MID(C181,6,2)),VALUE(MID(C181,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="5" t="n"/>
       <c r="D182" s="5">
-        <f>IF(AND(B182&lt;&gt;"",C182&lt;&gt;""),C182-B182+1,"")</f>
+        <f>IF(AND(AK182&lt;&gt;"",AL182&lt;&gt;""),AL182-AK182+1,"")</f>
         <v/>
       </c>
       <c r="E182" s="5">
-        <f>IF(B182&lt;&gt;"",YEAR(B182),"")</f>
+        <f>IF(AK182&lt;&gt;"",YEAR(AK182),"")</f>
         <v/>
       </c>
       <c r="F182" s="6" t="n"/>
@@ -29689,17 +31119,25 @@
         <v/>
       </c>
       <c r="AJ182" s="5" t="n"/>
+      <c r="AK182" s="12">
+        <f>IF(B182="","",IF(ISNUMBER(B182),B182,DATE(VALUE(LEFT(B182,4)),VALUE(MID(B182,6,2)),VALUE(MID(B182,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL182" s="12">
+        <f>IF(C182="","",IF(ISNUMBER(C182),C182,DATE(VALUE(LEFT(C182,4)),VALUE(MID(C182,6,2)),VALUE(MID(C182,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="5" t="n"/>
       <c r="D183" s="5">
-        <f>IF(AND(B183&lt;&gt;"",C183&lt;&gt;""),C183-B183+1,"")</f>
+        <f>IF(AND(AK183&lt;&gt;"",AL183&lt;&gt;""),AL183-AK183+1,"")</f>
         <v/>
       </c>
       <c r="E183" s="5">
-        <f>IF(B183&lt;&gt;"",YEAR(B183),"")</f>
+        <f>IF(AK183&lt;&gt;"",YEAR(AK183),"")</f>
         <v/>
       </c>
       <c r="F183" s="6" t="n"/>
@@ -29787,17 +31225,25 @@
         <v/>
       </c>
       <c r="AJ183" s="5" t="n"/>
+      <c r="AK183" s="12">
+        <f>IF(B183="","",IF(ISNUMBER(B183),B183,DATE(VALUE(LEFT(B183,4)),VALUE(MID(B183,6,2)),VALUE(MID(B183,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL183" s="12">
+        <f>IF(C183="","",IF(ISNUMBER(C183),C183,DATE(VALUE(LEFT(C183,4)),VALUE(MID(C183,6,2)),VALUE(MID(C183,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="5" t="n"/>
       <c r="D184" s="5">
-        <f>IF(AND(B184&lt;&gt;"",C184&lt;&gt;""),C184-B184+1,"")</f>
+        <f>IF(AND(AK184&lt;&gt;"",AL184&lt;&gt;""),AL184-AK184+1,"")</f>
         <v/>
       </c>
       <c r="E184" s="5">
-        <f>IF(B184&lt;&gt;"",YEAR(B184),"")</f>
+        <f>IF(AK184&lt;&gt;"",YEAR(AK184),"")</f>
         <v/>
       </c>
       <c r="F184" s="6" t="n"/>
@@ -29885,17 +31331,25 @@
         <v/>
       </c>
       <c r="AJ184" s="5" t="n"/>
+      <c r="AK184" s="12">
+        <f>IF(B184="","",IF(ISNUMBER(B184),B184,DATE(VALUE(LEFT(B184,4)),VALUE(MID(B184,6,2)),VALUE(MID(B184,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL184" s="12">
+        <f>IF(C184="","",IF(ISNUMBER(C184),C184,DATE(VALUE(LEFT(C184,4)),VALUE(MID(C184,6,2)),VALUE(MID(C184,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="5" t="n"/>
       <c r="D185" s="5">
-        <f>IF(AND(B185&lt;&gt;"",C185&lt;&gt;""),C185-B185+1,"")</f>
+        <f>IF(AND(AK185&lt;&gt;"",AL185&lt;&gt;""),AL185-AK185+1,"")</f>
         <v/>
       </c>
       <c r="E185" s="5">
-        <f>IF(B185&lt;&gt;"",YEAR(B185),"")</f>
+        <f>IF(AK185&lt;&gt;"",YEAR(AK185),"")</f>
         <v/>
       </c>
       <c r="F185" s="6" t="n"/>
@@ -29983,17 +31437,25 @@
         <v/>
       </c>
       <c r="AJ185" s="5" t="n"/>
+      <c r="AK185" s="12">
+        <f>IF(B185="","",IF(ISNUMBER(B185),B185,DATE(VALUE(LEFT(B185,4)),VALUE(MID(B185,6,2)),VALUE(MID(B185,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL185" s="12">
+        <f>IF(C185="","",IF(ISNUMBER(C185),C185,DATE(VALUE(LEFT(C185,4)),VALUE(MID(C185,6,2)),VALUE(MID(C185,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="5" t="n"/>
       <c r="D186" s="5">
-        <f>IF(AND(B186&lt;&gt;"",C186&lt;&gt;""),C186-B186+1,"")</f>
+        <f>IF(AND(AK186&lt;&gt;"",AL186&lt;&gt;""),AL186-AK186+1,"")</f>
         <v/>
       </c>
       <c r="E186" s="5">
-        <f>IF(B186&lt;&gt;"",YEAR(B186),"")</f>
+        <f>IF(AK186&lt;&gt;"",YEAR(AK186),"")</f>
         <v/>
       </c>
       <c r="F186" s="6" t="n"/>
@@ -30081,17 +31543,25 @@
         <v/>
       </c>
       <c r="AJ186" s="5" t="n"/>
+      <c r="AK186" s="12">
+        <f>IF(B186="","",IF(ISNUMBER(B186),B186,DATE(VALUE(LEFT(B186,4)),VALUE(MID(B186,6,2)),VALUE(MID(B186,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL186" s="12">
+        <f>IF(C186="","",IF(ISNUMBER(C186),C186,DATE(VALUE(LEFT(C186,4)),VALUE(MID(C186,6,2)),VALUE(MID(C186,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="5" t="n"/>
       <c r="D187" s="5">
-        <f>IF(AND(B187&lt;&gt;"",C187&lt;&gt;""),C187-B187+1,"")</f>
+        <f>IF(AND(AK187&lt;&gt;"",AL187&lt;&gt;""),AL187-AK187+1,"")</f>
         <v/>
       </c>
       <c r="E187" s="5">
-        <f>IF(B187&lt;&gt;"",YEAR(B187),"")</f>
+        <f>IF(AK187&lt;&gt;"",YEAR(AK187),"")</f>
         <v/>
       </c>
       <c r="F187" s="6" t="n"/>
@@ -30179,17 +31649,25 @@
         <v/>
       </c>
       <c r="AJ187" s="5" t="n"/>
+      <c r="AK187" s="12">
+        <f>IF(B187="","",IF(ISNUMBER(B187),B187,DATE(VALUE(LEFT(B187,4)),VALUE(MID(B187,6,2)),VALUE(MID(B187,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL187" s="12">
+        <f>IF(C187="","",IF(ISNUMBER(C187),C187,DATE(VALUE(LEFT(C187,4)),VALUE(MID(C187,6,2)),VALUE(MID(C187,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="5" t="n"/>
       <c r="D188" s="5">
-        <f>IF(AND(B188&lt;&gt;"",C188&lt;&gt;""),C188-B188+1,"")</f>
+        <f>IF(AND(AK188&lt;&gt;"",AL188&lt;&gt;""),AL188-AK188+1,"")</f>
         <v/>
       </c>
       <c r="E188" s="5">
-        <f>IF(B188&lt;&gt;"",YEAR(B188),"")</f>
+        <f>IF(AK188&lt;&gt;"",YEAR(AK188),"")</f>
         <v/>
       </c>
       <c r="F188" s="6" t="n"/>
@@ -30277,17 +31755,25 @@
         <v/>
       </c>
       <c r="AJ188" s="5" t="n"/>
+      <c r="AK188" s="12">
+        <f>IF(B188="","",IF(ISNUMBER(B188),B188,DATE(VALUE(LEFT(B188,4)),VALUE(MID(B188,6,2)),VALUE(MID(B188,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL188" s="12">
+        <f>IF(C188="","",IF(ISNUMBER(C188),C188,DATE(VALUE(LEFT(C188,4)),VALUE(MID(C188,6,2)),VALUE(MID(C188,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="5" t="n"/>
       <c r="D189" s="5">
-        <f>IF(AND(B189&lt;&gt;"",C189&lt;&gt;""),C189-B189+1,"")</f>
+        <f>IF(AND(AK189&lt;&gt;"",AL189&lt;&gt;""),AL189-AK189+1,"")</f>
         <v/>
       </c>
       <c r="E189" s="5">
-        <f>IF(B189&lt;&gt;"",YEAR(B189),"")</f>
+        <f>IF(AK189&lt;&gt;"",YEAR(AK189),"")</f>
         <v/>
       </c>
       <c r="F189" s="6" t="n"/>
@@ -30375,17 +31861,25 @@
         <v/>
       </c>
       <c r="AJ189" s="5" t="n"/>
+      <c r="AK189" s="12">
+        <f>IF(B189="","",IF(ISNUMBER(B189),B189,DATE(VALUE(LEFT(B189,4)),VALUE(MID(B189,6,2)),VALUE(MID(B189,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL189" s="12">
+        <f>IF(C189="","",IF(ISNUMBER(C189),C189,DATE(VALUE(LEFT(C189,4)),VALUE(MID(C189,6,2)),VALUE(MID(C189,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="5" t="n"/>
       <c r="D190" s="5">
-        <f>IF(AND(B190&lt;&gt;"",C190&lt;&gt;""),C190-B190+1,"")</f>
+        <f>IF(AND(AK190&lt;&gt;"",AL190&lt;&gt;""),AL190-AK190+1,"")</f>
         <v/>
       </c>
       <c r="E190" s="5">
-        <f>IF(B190&lt;&gt;"",YEAR(B190),"")</f>
+        <f>IF(AK190&lt;&gt;"",YEAR(AK190),"")</f>
         <v/>
       </c>
       <c r="F190" s="6" t="n"/>
@@ -30473,17 +31967,25 @@
         <v/>
       </c>
       <c r="AJ190" s="5" t="n"/>
+      <c r="AK190" s="12">
+        <f>IF(B190="","",IF(ISNUMBER(B190),B190,DATE(VALUE(LEFT(B190,4)),VALUE(MID(B190,6,2)),VALUE(MID(B190,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL190" s="12">
+        <f>IF(C190="","",IF(ISNUMBER(C190),C190,DATE(VALUE(LEFT(C190,4)),VALUE(MID(C190,6,2)),VALUE(MID(C190,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="5" t="n"/>
       <c r="D191" s="5">
-        <f>IF(AND(B191&lt;&gt;"",C191&lt;&gt;""),C191-B191+1,"")</f>
+        <f>IF(AND(AK191&lt;&gt;"",AL191&lt;&gt;""),AL191-AK191+1,"")</f>
         <v/>
       </c>
       <c r="E191" s="5">
-        <f>IF(B191&lt;&gt;"",YEAR(B191),"")</f>
+        <f>IF(AK191&lt;&gt;"",YEAR(AK191),"")</f>
         <v/>
       </c>
       <c r="F191" s="6" t="n"/>
@@ -30571,17 +32073,25 @@
         <v/>
       </c>
       <c r="AJ191" s="5" t="n"/>
+      <c r="AK191" s="12">
+        <f>IF(B191="","",IF(ISNUMBER(B191),B191,DATE(VALUE(LEFT(B191,4)),VALUE(MID(B191,6,2)),VALUE(MID(B191,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL191" s="12">
+        <f>IF(C191="","",IF(ISNUMBER(C191),C191,DATE(VALUE(LEFT(C191,4)),VALUE(MID(C191,6,2)),VALUE(MID(C191,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="5" t="n"/>
       <c r="D192" s="5">
-        <f>IF(AND(B192&lt;&gt;"",C192&lt;&gt;""),C192-B192+1,"")</f>
+        <f>IF(AND(AK192&lt;&gt;"",AL192&lt;&gt;""),AL192-AK192+1,"")</f>
         <v/>
       </c>
       <c r="E192" s="5">
-        <f>IF(B192&lt;&gt;"",YEAR(B192),"")</f>
+        <f>IF(AK192&lt;&gt;"",YEAR(AK192),"")</f>
         <v/>
       </c>
       <c r="F192" s="6" t="n"/>
@@ -30669,17 +32179,25 @@
         <v/>
       </c>
       <c r="AJ192" s="5" t="n"/>
+      <c r="AK192" s="12">
+        <f>IF(B192="","",IF(ISNUMBER(B192),B192,DATE(VALUE(LEFT(B192,4)),VALUE(MID(B192,6,2)),VALUE(MID(B192,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL192" s="12">
+        <f>IF(C192="","",IF(ISNUMBER(C192),C192,DATE(VALUE(LEFT(C192,4)),VALUE(MID(C192,6,2)),VALUE(MID(C192,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="5" t="n"/>
       <c r="D193" s="5">
-        <f>IF(AND(B193&lt;&gt;"",C193&lt;&gt;""),C193-B193+1,"")</f>
+        <f>IF(AND(AK193&lt;&gt;"",AL193&lt;&gt;""),AL193-AK193+1,"")</f>
         <v/>
       </c>
       <c r="E193" s="5">
-        <f>IF(B193&lt;&gt;"",YEAR(B193),"")</f>
+        <f>IF(AK193&lt;&gt;"",YEAR(AK193),"")</f>
         <v/>
       </c>
       <c r="F193" s="6" t="n"/>
@@ -30767,17 +32285,25 @@
         <v/>
       </c>
       <c r="AJ193" s="5" t="n"/>
+      <c r="AK193" s="12">
+        <f>IF(B193="","",IF(ISNUMBER(B193),B193,DATE(VALUE(LEFT(B193,4)),VALUE(MID(B193,6,2)),VALUE(MID(B193,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL193" s="12">
+        <f>IF(C193="","",IF(ISNUMBER(C193),C193,DATE(VALUE(LEFT(C193,4)),VALUE(MID(C193,6,2)),VALUE(MID(C193,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="5" t="n"/>
       <c r="D194" s="5">
-        <f>IF(AND(B194&lt;&gt;"",C194&lt;&gt;""),C194-B194+1,"")</f>
+        <f>IF(AND(AK194&lt;&gt;"",AL194&lt;&gt;""),AL194-AK194+1,"")</f>
         <v/>
       </c>
       <c r="E194" s="5">
-        <f>IF(B194&lt;&gt;"",YEAR(B194),"")</f>
+        <f>IF(AK194&lt;&gt;"",YEAR(AK194),"")</f>
         <v/>
       </c>
       <c r="F194" s="6" t="n"/>
@@ -30865,17 +32391,25 @@
         <v/>
       </c>
       <c r="AJ194" s="5" t="n"/>
+      <c r="AK194" s="12">
+        <f>IF(B194="","",IF(ISNUMBER(B194),B194,DATE(VALUE(LEFT(B194,4)),VALUE(MID(B194,6,2)),VALUE(MID(B194,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL194" s="12">
+        <f>IF(C194="","",IF(ISNUMBER(C194),C194,DATE(VALUE(LEFT(C194,4)),VALUE(MID(C194,6,2)),VALUE(MID(C194,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="5" t="n"/>
       <c r="D195" s="5">
-        <f>IF(AND(B195&lt;&gt;"",C195&lt;&gt;""),C195-B195+1,"")</f>
+        <f>IF(AND(AK195&lt;&gt;"",AL195&lt;&gt;""),AL195-AK195+1,"")</f>
         <v/>
       </c>
       <c r="E195" s="5">
-        <f>IF(B195&lt;&gt;"",YEAR(B195),"")</f>
+        <f>IF(AK195&lt;&gt;"",YEAR(AK195),"")</f>
         <v/>
       </c>
       <c r="F195" s="6" t="n"/>
@@ -30963,17 +32497,25 @@
         <v/>
       </c>
       <c r="AJ195" s="5" t="n"/>
+      <c r="AK195" s="12">
+        <f>IF(B195="","",IF(ISNUMBER(B195),B195,DATE(VALUE(LEFT(B195,4)),VALUE(MID(B195,6,2)),VALUE(MID(B195,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL195" s="12">
+        <f>IF(C195="","",IF(ISNUMBER(C195),C195,DATE(VALUE(LEFT(C195,4)),VALUE(MID(C195,6,2)),VALUE(MID(C195,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="5" t="n"/>
       <c r="D196" s="5">
-        <f>IF(AND(B196&lt;&gt;"",C196&lt;&gt;""),C196-B196+1,"")</f>
+        <f>IF(AND(AK196&lt;&gt;"",AL196&lt;&gt;""),AL196-AK196+1,"")</f>
         <v/>
       </c>
       <c r="E196" s="5">
-        <f>IF(B196&lt;&gt;"",YEAR(B196),"")</f>
+        <f>IF(AK196&lt;&gt;"",YEAR(AK196),"")</f>
         <v/>
       </c>
       <c r="F196" s="6" t="n"/>
@@ -31061,17 +32603,25 @@
         <v/>
       </c>
       <c r="AJ196" s="5" t="n"/>
+      <c r="AK196" s="12">
+        <f>IF(B196="","",IF(ISNUMBER(B196),B196,DATE(VALUE(LEFT(B196,4)),VALUE(MID(B196,6,2)),VALUE(MID(B196,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL196" s="12">
+        <f>IF(C196="","",IF(ISNUMBER(C196),C196,DATE(VALUE(LEFT(C196,4)),VALUE(MID(C196,6,2)),VALUE(MID(C196,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="5" t="n"/>
       <c r="D197" s="5">
-        <f>IF(AND(B197&lt;&gt;"",C197&lt;&gt;""),C197-B197+1,"")</f>
+        <f>IF(AND(AK197&lt;&gt;"",AL197&lt;&gt;""),AL197-AK197+1,"")</f>
         <v/>
       </c>
       <c r="E197" s="5">
-        <f>IF(B197&lt;&gt;"",YEAR(B197),"")</f>
+        <f>IF(AK197&lt;&gt;"",YEAR(AK197),"")</f>
         <v/>
       </c>
       <c r="F197" s="6" t="n"/>
@@ -31159,17 +32709,25 @@
         <v/>
       </c>
       <c r="AJ197" s="5" t="n"/>
+      <c r="AK197" s="12">
+        <f>IF(B197="","",IF(ISNUMBER(B197),B197,DATE(VALUE(LEFT(B197,4)),VALUE(MID(B197,6,2)),VALUE(MID(B197,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL197" s="12">
+        <f>IF(C197="","",IF(ISNUMBER(C197),C197,DATE(VALUE(LEFT(C197,4)),VALUE(MID(C197,6,2)),VALUE(MID(C197,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="5" t="n"/>
       <c r="D198" s="5">
-        <f>IF(AND(B198&lt;&gt;"",C198&lt;&gt;""),C198-B198+1,"")</f>
+        <f>IF(AND(AK198&lt;&gt;"",AL198&lt;&gt;""),AL198-AK198+1,"")</f>
         <v/>
       </c>
       <c r="E198" s="5">
-        <f>IF(B198&lt;&gt;"",YEAR(B198),"")</f>
+        <f>IF(AK198&lt;&gt;"",YEAR(AK198),"")</f>
         <v/>
       </c>
       <c r="F198" s="6" t="n"/>
@@ -31257,17 +32815,25 @@
         <v/>
       </c>
       <c r="AJ198" s="5" t="n"/>
+      <c r="AK198" s="12">
+        <f>IF(B198="","",IF(ISNUMBER(B198),B198,DATE(VALUE(LEFT(B198,4)),VALUE(MID(B198,6,2)),VALUE(MID(B198,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL198" s="12">
+        <f>IF(C198="","",IF(ISNUMBER(C198),C198,DATE(VALUE(LEFT(C198,4)),VALUE(MID(C198,6,2)),VALUE(MID(C198,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="5" t="n"/>
       <c r="D199" s="5">
-        <f>IF(AND(B199&lt;&gt;"",C199&lt;&gt;""),C199-B199+1,"")</f>
+        <f>IF(AND(AK199&lt;&gt;"",AL199&lt;&gt;""),AL199-AK199+1,"")</f>
         <v/>
       </c>
       <c r="E199" s="5">
-        <f>IF(B199&lt;&gt;"",YEAR(B199),"")</f>
+        <f>IF(AK199&lt;&gt;"",YEAR(AK199),"")</f>
         <v/>
       </c>
       <c r="F199" s="6" t="n"/>
@@ -31355,17 +32921,25 @@
         <v/>
       </c>
       <c r="AJ199" s="5" t="n"/>
+      <c r="AK199" s="12">
+        <f>IF(B199="","",IF(ISNUMBER(B199),B199,DATE(VALUE(LEFT(B199,4)),VALUE(MID(B199,6,2)),VALUE(MID(B199,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL199" s="12">
+        <f>IF(C199="","",IF(ISNUMBER(C199),C199,DATE(VALUE(LEFT(C199,4)),VALUE(MID(C199,6,2)),VALUE(MID(C199,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="5" t="n"/>
       <c r="D200" s="5">
-        <f>IF(AND(B200&lt;&gt;"",C200&lt;&gt;""),C200-B200+1,"")</f>
+        <f>IF(AND(AK200&lt;&gt;"",AL200&lt;&gt;""),AL200-AK200+1,"")</f>
         <v/>
       </c>
       <c r="E200" s="5">
-        <f>IF(B200&lt;&gt;"",YEAR(B200),"")</f>
+        <f>IF(AK200&lt;&gt;"",YEAR(AK200),"")</f>
         <v/>
       </c>
       <c r="F200" s="6" t="n"/>
@@ -31453,17 +33027,25 @@
         <v/>
       </c>
       <c r="AJ200" s="5" t="n"/>
+      <c r="AK200" s="12">
+        <f>IF(B200="","",IF(ISNUMBER(B200),B200,DATE(VALUE(LEFT(B200,4)),VALUE(MID(B200,6,2)),VALUE(MID(B200,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL200" s="12">
+        <f>IF(C200="","",IF(ISNUMBER(C200),C200,DATE(VALUE(LEFT(C200,4)),VALUE(MID(C200,6,2)),VALUE(MID(C200,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="5" t="n"/>
       <c r="D201" s="5">
-        <f>IF(AND(B201&lt;&gt;"",C201&lt;&gt;""),C201-B201+1,"")</f>
+        <f>IF(AND(AK201&lt;&gt;"",AL201&lt;&gt;""),AL201-AK201+1,"")</f>
         <v/>
       </c>
       <c r="E201" s="5">
-        <f>IF(B201&lt;&gt;"",YEAR(B201),"")</f>
+        <f>IF(AK201&lt;&gt;"",YEAR(AK201),"")</f>
         <v/>
       </c>
       <c r="F201" s="6" t="n"/>
@@ -31551,17 +33133,25 @@
         <v/>
       </c>
       <c r="AJ201" s="5" t="n"/>
+      <c r="AK201" s="12">
+        <f>IF(B201="","",IF(ISNUMBER(B201),B201,DATE(VALUE(LEFT(B201,4)),VALUE(MID(B201,6,2)),VALUE(MID(B201,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL201" s="12">
+        <f>IF(C201="","",IF(ISNUMBER(C201),C201,DATE(VALUE(LEFT(C201,4)),VALUE(MID(C201,6,2)),VALUE(MID(C201,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="5" t="n"/>
       <c r="D202" s="5">
-        <f>IF(AND(B202&lt;&gt;"",C202&lt;&gt;""),C202-B202+1,"")</f>
+        <f>IF(AND(AK202&lt;&gt;"",AL202&lt;&gt;""),AL202-AK202+1,"")</f>
         <v/>
       </c>
       <c r="E202" s="5">
-        <f>IF(B202&lt;&gt;"",YEAR(B202),"")</f>
+        <f>IF(AK202&lt;&gt;"",YEAR(AK202),"")</f>
         <v/>
       </c>
       <c r="F202" s="6" t="n"/>
@@ -31649,17 +33239,25 @@
         <v/>
       </c>
       <c r="AJ202" s="5" t="n"/>
+      <c r="AK202" s="12">
+        <f>IF(B202="","",IF(ISNUMBER(B202),B202,DATE(VALUE(LEFT(B202,4)),VALUE(MID(B202,6,2)),VALUE(MID(B202,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL202" s="12">
+        <f>IF(C202="","",IF(ISNUMBER(C202),C202,DATE(VALUE(LEFT(C202,4)),VALUE(MID(C202,6,2)),VALUE(MID(C202,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="5" t="n"/>
       <c r="D203" s="5">
-        <f>IF(AND(B203&lt;&gt;"",C203&lt;&gt;""),C203-B203+1,"")</f>
+        <f>IF(AND(AK203&lt;&gt;"",AL203&lt;&gt;""),AL203-AK203+1,"")</f>
         <v/>
       </c>
       <c r="E203" s="5">
-        <f>IF(B203&lt;&gt;"",YEAR(B203),"")</f>
+        <f>IF(AK203&lt;&gt;"",YEAR(AK203),"")</f>
         <v/>
       </c>
       <c r="F203" s="6" t="n"/>
@@ -31747,17 +33345,25 @@
         <v/>
       </c>
       <c r="AJ203" s="5" t="n"/>
+      <c r="AK203" s="12">
+        <f>IF(B203="","",IF(ISNUMBER(B203),B203,DATE(VALUE(LEFT(B203,4)),VALUE(MID(B203,6,2)),VALUE(MID(B203,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL203" s="12">
+        <f>IF(C203="","",IF(ISNUMBER(C203),C203,DATE(VALUE(LEFT(C203,4)),VALUE(MID(C203,6,2)),VALUE(MID(C203,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="5" t="n"/>
       <c r="D204" s="5">
-        <f>IF(AND(B204&lt;&gt;"",C204&lt;&gt;""),C204-B204+1,"")</f>
+        <f>IF(AND(AK204&lt;&gt;"",AL204&lt;&gt;""),AL204-AK204+1,"")</f>
         <v/>
       </c>
       <c r="E204" s="5">
-        <f>IF(B204&lt;&gt;"",YEAR(B204),"")</f>
+        <f>IF(AK204&lt;&gt;"",YEAR(AK204),"")</f>
         <v/>
       </c>
       <c r="F204" s="6" t="n"/>
@@ -31845,17 +33451,25 @@
         <v/>
       </c>
       <c r="AJ204" s="5" t="n"/>
+      <c r="AK204" s="12">
+        <f>IF(B204="","",IF(ISNUMBER(B204),B204,DATE(VALUE(LEFT(B204,4)),VALUE(MID(B204,6,2)),VALUE(MID(B204,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL204" s="12">
+        <f>IF(C204="","",IF(ISNUMBER(C204),C204,DATE(VALUE(LEFT(C204,4)),VALUE(MID(C204,6,2)),VALUE(MID(C204,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="5" t="n"/>
       <c r="D205" s="5">
-        <f>IF(AND(B205&lt;&gt;"",C205&lt;&gt;""),C205-B205+1,"")</f>
+        <f>IF(AND(AK205&lt;&gt;"",AL205&lt;&gt;""),AL205-AK205+1,"")</f>
         <v/>
       </c>
       <c r="E205" s="5">
-        <f>IF(B205&lt;&gt;"",YEAR(B205),"")</f>
+        <f>IF(AK205&lt;&gt;"",YEAR(AK205),"")</f>
         <v/>
       </c>
       <c r="F205" s="6" t="n"/>
@@ -31943,17 +33557,25 @@
         <v/>
       </c>
       <c r="AJ205" s="5" t="n"/>
+      <c r="AK205" s="12">
+        <f>IF(B205="","",IF(ISNUMBER(B205),B205,DATE(VALUE(LEFT(B205,4)),VALUE(MID(B205,6,2)),VALUE(MID(B205,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL205" s="12">
+        <f>IF(C205="","",IF(ISNUMBER(C205),C205,DATE(VALUE(LEFT(C205,4)),VALUE(MID(C205,6,2)),VALUE(MID(C205,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="5" t="n"/>
       <c r="D206" s="5">
-        <f>IF(AND(B206&lt;&gt;"",C206&lt;&gt;""),C206-B206+1,"")</f>
+        <f>IF(AND(AK206&lt;&gt;"",AL206&lt;&gt;""),AL206-AK206+1,"")</f>
         <v/>
       </c>
       <c r="E206" s="5">
-        <f>IF(B206&lt;&gt;"",YEAR(B206),"")</f>
+        <f>IF(AK206&lt;&gt;"",YEAR(AK206),"")</f>
         <v/>
       </c>
       <c r="F206" s="6" t="n"/>
@@ -32041,17 +33663,25 @@
         <v/>
       </c>
       <c r="AJ206" s="5" t="n"/>
+      <c r="AK206" s="12">
+        <f>IF(B206="","",IF(ISNUMBER(B206),B206,DATE(VALUE(LEFT(B206,4)),VALUE(MID(B206,6,2)),VALUE(MID(B206,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL206" s="12">
+        <f>IF(C206="","",IF(ISNUMBER(C206),C206,DATE(VALUE(LEFT(C206,4)),VALUE(MID(C206,6,2)),VALUE(MID(C206,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="5" t="n"/>
       <c r="D207" s="5">
-        <f>IF(AND(B207&lt;&gt;"",C207&lt;&gt;""),C207-B207+1,"")</f>
+        <f>IF(AND(AK207&lt;&gt;"",AL207&lt;&gt;""),AL207-AK207+1,"")</f>
         <v/>
       </c>
       <c r="E207" s="5">
-        <f>IF(B207&lt;&gt;"",YEAR(B207),"")</f>
+        <f>IF(AK207&lt;&gt;"",YEAR(AK207),"")</f>
         <v/>
       </c>
       <c r="F207" s="6" t="n"/>
@@ -32139,17 +33769,25 @@
         <v/>
       </c>
       <c r="AJ207" s="5" t="n"/>
+      <c r="AK207" s="12">
+        <f>IF(B207="","",IF(ISNUMBER(B207),B207,DATE(VALUE(LEFT(B207,4)),VALUE(MID(B207,6,2)),VALUE(MID(B207,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL207" s="12">
+        <f>IF(C207="","",IF(ISNUMBER(C207),C207,DATE(VALUE(LEFT(C207,4)),VALUE(MID(C207,6,2)),VALUE(MID(C207,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="5" t="n"/>
       <c r="D208" s="5">
-        <f>IF(AND(B208&lt;&gt;"",C208&lt;&gt;""),C208-B208+1,"")</f>
+        <f>IF(AND(AK208&lt;&gt;"",AL208&lt;&gt;""),AL208-AK208+1,"")</f>
         <v/>
       </c>
       <c r="E208" s="5">
-        <f>IF(B208&lt;&gt;"",YEAR(B208),"")</f>
+        <f>IF(AK208&lt;&gt;"",YEAR(AK208),"")</f>
         <v/>
       </c>
       <c r="F208" s="6" t="n"/>
@@ -32237,17 +33875,25 @@
         <v/>
       </c>
       <c r="AJ208" s="5" t="n"/>
+      <c r="AK208" s="12">
+        <f>IF(B208="","",IF(ISNUMBER(B208),B208,DATE(VALUE(LEFT(B208,4)),VALUE(MID(B208,6,2)),VALUE(MID(B208,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL208" s="12">
+        <f>IF(C208="","",IF(ISNUMBER(C208),C208,DATE(VALUE(LEFT(C208,4)),VALUE(MID(C208,6,2)),VALUE(MID(C208,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="5" t="n"/>
       <c r="D209" s="5">
-        <f>IF(AND(B209&lt;&gt;"",C209&lt;&gt;""),C209-B209+1,"")</f>
+        <f>IF(AND(AK209&lt;&gt;"",AL209&lt;&gt;""),AL209-AK209+1,"")</f>
         <v/>
       </c>
       <c r="E209" s="5">
-        <f>IF(B209&lt;&gt;"",YEAR(B209),"")</f>
+        <f>IF(AK209&lt;&gt;"",YEAR(AK209),"")</f>
         <v/>
       </c>
       <c r="F209" s="6" t="n"/>
@@ -32335,17 +33981,25 @@
         <v/>
       </c>
       <c r="AJ209" s="5" t="n"/>
+      <c r="AK209" s="12">
+        <f>IF(B209="","",IF(ISNUMBER(B209),B209,DATE(VALUE(LEFT(B209,4)),VALUE(MID(B209,6,2)),VALUE(MID(B209,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL209" s="12">
+        <f>IF(C209="","",IF(ISNUMBER(C209),C209,DATE(VALUE(LEFT(C209,4)),VALUE(MID(C209,6,2)),VALUE(MID(C209,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="5" t="n"/>
       <c r="D210" s="5">
-        <f>IF(AND(B210&lt;&gt;"",C210&lt;&gt;""),C210-B210+1,"")</f>
+        <f>IF(AND(AK210&lt;&gt;"",AL210&lt;&gt;""),AL210-AK210+1,"")</f>
         <v/>
       </c>
       <c r="E210" s="5">
-        <f>IF(B210&lt;&gt;"",YEAR(B210),"")</f>
+        <f>IF(AK210&lt;&gt;"",YEAR(AK210),"")</f>
         <v/>
       </c>
       <c r="F210" s="6" t="n"/>
@@ -32433,17 +34087,25 @@
         <v/>
       </c>
       <c r="AJ210" s="5" t="n"/>
+      <c r="AK210" s="12">
+        <f>IF(B210="","",IF(ISNUMBER(B210),B210,DATE(VALUE(LEFT(B210,4)),VALUE(MID(B210,6,2)),VALUE(MID(B210,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL210" s="12">
+        <f>IF(C210="","",IF(ISNUMBER(C210),C210,DATE(VALUE(LEFT(C210,4)),VALUE(MID(C210,6,2)),VALUE(MID(C210,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="5" t="n"/>
       <c r="D211" s="5">
-        <f>IF(AND(B211&lt;&gt;"",C211&lt;&gt;""),C211-B211+1,"")</f>
+        <f>IF(AND(AK211&lt;&gt;"",AL211&lt;&gt;""),AL211-AK211+1,"")</f>
         <v/>
       </c>
       <c r="E211" s="5">
-        <f>IF(B211&lt;&gt;"",YEAR(B211),"")</f>
+        <f>IF(AK211&lt;&gt;"",YEAR(AK211),"")</f>
         <v/>
       </c>
       <c r="F211" s="6" t="n"/>
@@ -32531,17 +34193,25 @@
         <v/>
       </c>
       <c r="AJ211" s="5" t="n"/>
+      <c r="AK211" s="12">
+        <f>IF(B211="","",IF(ISNUMBER(B211),B211,DATE(VALUE(LEFT(B211,4)),VALUE(MID(B211,6,2)),VALUE(MID(B211,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL211" s="12">
+        <f>IF(C211="","",IF(ISNUMBER(C211),C211,DATE(VALUE(LEFT(C211,4)),VALUE(MID(C211,6,2)),VALUE(MID(C211,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="5" t="n"/>
       <c r="D212" s="5">
-        <f>IF(AND(B212&lt;&gt;"",C212&lt;&gt;""),C212-B212+1,"")</f>
+        <f>IF(AND(AK212&lt;&gt;"",AL212&lt;&gt;""),AL212-AK212+1,"")</f>
         <v/>
       </c>
       <c r="E212" s="5">
-        <f>IF(B212&lt;&gt;"",YEAR(B212),"")</f>
+        <f>IF(AK212&lt;&gt;"",YEAR(AK212),"")</f>
         <v/>
       </c>
       <c r="F212" s="6" t="n"/>
@@ -32629,17 +34299,25 @@
         <v/>
       </c>
       <c r="AJ212" s="5" t="n"/>
+      <c r="AK212" s="12">
+        <f>IF(B212="","",IF(ISNUMBER(B212),B212,DATE(VALUE(LEFT(B212,4)),VALUE(MID(B212,6,2)),VALUE(MID(B212,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL212" s="12">
+        <f>IF(C212="","",IF(ISNUMBER(C212),C212,DATE(VALUE(LEFT(C212,4)),VALUE(MID(C212,6,2)),VALUE(MID(C212,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="5" t="n"/>
       <c r="D213" s="5">
-        <f>IF(AND(B213&lt;&gt;"",C213&lt;&gt;""),C213-B213+1,"")</f>
+        <f>IF(AND(AK213&lt;&gt;"",AL213&lt;&gt;""),AL213-AK213+1,"")</f>
         <v/>
       </c>
       <c r="E213" s="5">
-        <f>IF(B213&lt;&gt;"",YEAR(B213),"")</f>
+        <f>IF(AK213&lt;&gt;"",YEAR(AK213),"")</f>
         <v/>
       </c>
       <c r="F213" s="6" t="n"/>
@@ -32727,17 +34405,25 @@
         <v/>
       </c>
       <c r="AJ213" s="5" t="n"/>
+      <c r="AK213" s="12">
+        <f>IF(B213="","",IF(ISNUMBER(B213),B213,DATE(VALUE(LEFT(B213,4)),VALUE(MID(B213,6,2)),VALUE(MID(B213,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL213" s="12">
+        <f>IF(C213="","",IF(ISNUMBER(C213),C213,DATE(VALUE(LEFT(C213,4)),VALUE(MID(C213,6,2)),VALUE(MID(C213,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="5" t="n"/>
       <c r="D214" s="5">
-        <f>IF(AND(B214&lt;&gt;"",C214&lt;&gt;""),C214-B214+1,"")</f>
+        <f>IF(AND(AK214&lt;&gt;"",AL214&lt;&gt;""),AL214-AK214+1,"")</f>
         <v/>
       </c>
       <c r="E214" s="5">
-        <f>IF(B214&lt;&gt;"",YEAR(B214),"")</f>
+        <f>IF(AK214&lt;&gt;"",YEAR(AK214),"")</f>
         <v/>
       </c>
       <c r="F214" s="6" t="n"/>
@@ -32825,17 +34511,25 @@
         <v/>
       </c>
       <c r="AJ214" s="5" t="n"/>
+      <c r="AK214" s="12">
+        <f>IF(B214="","",IF(ISNUMBER(B214),B214,DATE(VALUE(LEFT(B214,4)),VALUE(MID(B214,6,2)),VALUE(MID(B214,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL214" s="12">
+        <f>IF(C214="","",IF(ISNUMBER(C214),C214,DATE(VALUE(LEFT(C214,4)),VALUE(MID(C214,6,2)),VALUE(MID(C214,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="5" t="n"/>
       <c r="D215" s="5">
-        <f>IF(AND(B215&lt;&gt;"",C215&lt;&gt;""),C215-B215+1,"")</f>
+        <f>IF(AND(AK215&lt;&gt;"",AL215&lt;&gt;""),AL215-AK215+1,"")</f>
         <v/>
       </c>
       <c r="E215" s="5">
-        <f>IF(B215&lt;&gt;"",YEAR(B215),"")</f>
+        <f>IF(AK215&lt;&gt;"",YEAR(AK215),"")</f>
         <v/>
       </c>
       <c r="F215" s="6" t="n"/>
@@ -32923,17 +34617,25 @@
         <v/>
       </c>
       <c r="AJ215" s="5" t="n"/>
+      <c r="AK215" s="12">
+        <f>IF(B215="","",IF(ISNUMBER(B215),B215,DATE(VALUE(LEFT(B215,4)),VALUE(MID(B215,6,2)),VALUE(MID(B215,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL215" s="12">
+        <f>IF(C215="","",IF(ISNUMBER(C215),C215,DATE(VALUE(LEFT(C215,4)),VALUE(MID(C215,6,2)),VALUE(MID(C215,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="5" t="n"/>
       <c r="D216" s="5">
-        <f>IF(AND(B216&lt;&gt;"",C216&lt;&gt;""),C216-B216+1,"")</f>
+        <f>IF(AND(AK216&lt;&gt;"",AL216&lt;&gt;""),AL216-AK216+1,"")</f>
         <v/>
       </c>
       <c r="E216" s="5">
-        <f>IF(B216&lt;&gt;"",YEAR(B216),"")</f>
+        <f>IF(AK216&lt;&gt;"",YEAR(AK216),"")</f>
         <v/>
       </c>
       <c r="F216" s="6" t="n"/>
@@ -33021,17 +34723,25 @@
         <v/>
       </c>
       <c r="AJ216" s="5" t="n"/>
+      <c r="AK216" s="12">
+        <f>IF(B216="","",IF(ISNUMBER(B216),B216,DATE(VALUE(LEFT(B216,4)),VALUE(MID(B216,6,2)),VALUE(MID(B216,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL216" s="12">
+        <f>IF(C216="","",IF(ISNUMBER(C216),C216,DATE(VALUE(LEFT(C216,4)),VALUE(MID(C216,6,2)),VALUE(MID(C216,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="5" t="n"/>
       <c r="D217" s="5">
-        <f>IF(AND(B217&lt;&gt;"",C217&lt;&gt;""),C217-B217+1,"")</f>
+        <f>IF(AND(AK217&lt;&gt;"",AL217&lt;&gt;""),AL217-AK217+1,"")</f>
         <v/>
       </c>
       <c r="E217" s="5">
-        <f>IF(B217&lt;&gt;"",YEAR(B217),"")</f>
+        <f>IF(AK217&lt;&gt;"",YEAR(AK217),"")</f>
         <v/>
       </c>
       <c r="F217" s="6" t="n"/>
@@ -33119,17 +34829,25 @@
         <v/>
       </c>
       <c r="AJ217" s="5" t="n"/>
+      <c r="AK217" s="12">
+        <f>IF(B217="","",IF(ISNUMBER(B217),B217,DATE(VALUE(LEFT(B217,4)),VALUE(MID(B217,6,2)),VALUE(MID(B217,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL217" s="12">
+        <f>IF(C217="","",IF(ISNUMBER(C217),C217,DATE(VALUE(LEFT(C217,4)),VALUE(MID(C217,6,2)),VALUE(MID(C217,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="5" t="n"/>
       <c r="D218" s="5">
-        <f>IF(AND(B218&lt;&gt;"",C218&lt;&gt;""),C218-B218+1,"")</f>
+        <f>IF(AND(AK218&lt;&gt;"",AL218&lt;&gt;""),AL218-AK218+1,"")</f>
         <v/>
       </c>
       <c r="E218" s="5">
-        <f>IF(B218&lt;&gt;"",YEAR(B218),"")</f>
+        <f>IF(AK218&lt;&gt;"",YEAR(AK218),"")</f>
         <v/>
       </c>
       <c r="F218" s="6" t="n"/>
@@ -33217,17 +34935,25 @@
         <v/>
       </c>
       <c r="AJ218" s="5" t="n"/>
+      <c r="AK218" s="12">
+        <f>IF(B218="","",IF(ISNUMBER(B218),B218,DATE(VALUE(LEFT(B218,4)),VALUE(MID(B218,6,2)),VALUE(MID(B218,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL218" s="12">
+        <f>IF(C218="","",IF(ISNUMBER(C218),C218,DATE(VALUE(LEFT(C218,4)),VALUE(MID(C218,6,2)),VALUE(MID(C218,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="5" t="n"/>
       <c r="D219" s="5">
-        <f>IF(AND(B219&lt;&gt;"",C219&lt;&gt;""),C219-B219+1,"")</f>
+        <f>IF(AND(AK219&lt;&gt;"",AL219&lt;&gt;""),AL219-AK219+1,"")</f>
         <v/>
       </c>
       <c r="E219" s="5">
-        <f>IF(B219&lt;&gt;"",YEAR(B219),"")</f>
+        <f>IF(AK219&lt;&gt;"",YEAR(AK219),"")</f>
         <v/>
       </c>
       <c r="F219" s="6" t="n"/>
@@ -33315,17 +35041,25 @@
         <v/>
       </c>
       <c r="AJ219" s="5" t="n"/>
+      <c r="AK219" s="12">
+        <f>IF(B219="","",IF(ISNUMBER(B219),B219,DATE(VALUE(LEFT(B219,4)),VALUE(MID(B219,6,2)),VALUE(MID(B219,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL219" s="12">
+        <f>IF(C219="","",IF(ISNUMBER(C219),C219,DATE(VALUE(LEFT(C219,4)),VALUE(MID(C219,6,2)),VALUE(MID(C219,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="5" t="n"/>
       <c r="D220" s="5">
-        <f>IF(AND(B220&lt;&gt;"",C220&lt;&gt;""),C220-B220+1,"")</f>
+        <f>IF(AND(AK220&lt;&gt;"",AL220&lt;&gt;""),AL220-AK220+1,"")</f>
         <v/>
       </c>
       <c r="E220" s="5">
-        <f>IF(B220&lt;&gt;"",YEAR(B220),"")</f>
+        <f>IF(AK220&lt;&gt;"",YEAR(AK220),"")</f>
         <v/>
       </c>
       <c r="F220" s="6" t="n"/>
@@ -33413,17 +35147,25 @@
         <v/>
       </c>
       <c r="AJ220" s="5" t="n"/>
+      <c r="AK220" s="12">
+        <f>IF(B220="","",IF(ISNUMBER(B220),B220,DATE(VALUE(LEFT(B220,4)),VALUE(MID(B220,6,2)),VALUE(MID(B220,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL220" s="12">
+        <f>IF(C220="","",IF(ISNUMBER(C220),C220,DATE(VALUE(LEFT(C220,4)),VALUE(MID(C220,6,2)),VALUE(MID(C220,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="5" t="n"/>
       <c r="D221" s="5">
-        <f>IF(AND(B221&lt;&gt;"",C221&lt;&gt;""),C221-B221+1,"")</f>
+        <f>IF(AND(AK221&lt;&gt;"",AL221&lt;&gt;""),AL221-AK221+1,"")</f>
         <v/>
       </c>
       <c r="E221" s="5">
-        <f>IF(B221&lt;&gt;"",YEAR(B221),"")</f>
+        <f>IF(AK221&lt;&gt;"",YEAR(AK221),"")</f>
         <v/>
       </c>
       <c r="F221" s="6" t="n"/>
@@ -33511,17 +35253,25 @@
         <v/>
       </c>
       <c r="AJ221" s="5" t="n"/>
+      <c r="AK221" s="12">
+        <f>IF(B221="","",IF(ISNUMBER(B221),B221,DATE(VALUE(LEFT(B221,4)),VALUE(MID(B221,6,2)),VALUE(MID(B221,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL221" s="12">
+        <f>IF(C221="","",IF(ISNUMBER(C221),C221,DATE(VALUE(LEFT(C221,4)),VALUE(MID(C221,6,2)),VALUE(MID(C221,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="5" t="n"/>
       <c r="D222" s="5">
-        <f>IF(AND(B222&lt;&gt;"",C222&lt;&gt;""),C222-B222+1,"")</f>
+        <f>IF(AND(AK222&lt;&gt;"",AL222&lt;&gt;""),AL222-AK222+1,"")</f>
         <v/>
       </c>
       <c r="E222" s="5">
-        <f>IF(B222&lt;&gt;"",YEAR(B222),"")</f>
+        <f>IF(AK222&lt;&gt;"",YEAR(AK222),"")</f>
         <v/>
       </c>
       <c r="F222" s="6" t="n"/>
@@ -33609,17 +35359,25 @@
         <v/>
       </c>
       <c r="AJ222" s="5" t="n"/>
+      <c r="AK222" s="12">
+        <f>IF(B222="","",IF(ISNUMBER(B222),B222,DATE(VALUE(LEFT(B222,4)),VALUE(MID(B222,6,2)),VALUE(MID(B222,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL222" s="12">
+        <f>IF(C222="","",IF(ISNUMBER(C222),C222,DATE(VALUE(LEFT(C222,4)),VALUE(MID(C222,6,2)),VALUE(MID(C222,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="5" t="n"/>
       <c r="D223" s="5">
-        <f>IF(AND(B223&lt;&gt;"",C223&lt;&gt;""),C223-B223+1,"")</f>
+        <f>IF(AND(AK223&lt;&gt;"",AL223&lt;&gt;""),AL223-AK223+1,"")</f>
         <v/>
       </c>
       <c r="E223" s="5">
-        <f>IF(B223&lt;&gt;"",YEAR(B223),"")</f>
+        <f>IF(AK223&lt;&gt;"",YEAR(AK223),"")</f>
         <v/>
       </c>
       <c r="F223" s="6" t="n"/>
@@ -33707,17 +35465,25 @@
         <v/>
       </c>
       <c r="AJ223" s="5" t="n"/>
+      <c r="AK223" s="12">
+        <f>IF(B223="","",IF(ISNUMBER(B223),B223,DATE(VALUE(LEFT(B223,4)),VALUE(MID(B223,6,2)),VALUE(MID(B223,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL223" s="12">
+        <f>IF(C223="","",IF(ISNUMBER(C223),C223,DATE(VALUE(LEFT(C223,4)),VALUE(MID(C223,6,2)),VALUE(MID(C223,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="5" t="n"/>
       <c r="D224" s="5">
-        <f>IF(AND(B224&lt;&gt;"",C224&lt;&gt;""),C224-B224+1,"")</f>
+        <f>IF(AND(AK224&lt;&gt;"",AL224&lt;&gt;""),AL224-AK224+1,"")</f>
         <v/>
       </c>
       <c r="E224" s="5">
-        <f>IF(B224&lt;&gt;"",YEAR(B224),"")</f>
+        <f>IF(AK224&lt;&gt;"",YEAR(AK224),"")</f>
         <v/>
       </c>
       <c r="F224" s="6" t="n"/>
@@ -33805,17 +35571,25 @@
         <v/>
       </c>
       <c r="AJ224" s="5" t="n"/>
+      <c r="AK224" s="12">
+        <f>IF(B224="","",IF(ISNUMBER(B224),B224,DATE(VALUE(LEFT(B224,4)),VALUE(MID(B224,6,2)),VALUE(MID(B224,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL224" s="12">
+        <f>IF(C224="","",IF(ISNUMBER(C224),C224,DATE(VALUE(LEFT(C224,4)),VALUE(MID(C224,6,2)),VALUE(MID(C224,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="5" t="n"/>
       <c r="D225" s="5">
-        <f>IF(AND(B225&lt;&gt;"",C225&lt;&gt;""),C225-B225+1,"")</f>
+        <f>IF(AND(AK225&lt;&gt;"",AL225&lt;&gt;""),AL225-AK225+1,"")</f>
         <v/>
       </c>
       <c r="E225" s="5">
-        <f>IF(B225&lt;&gt;"",YEAR(B225),"")</f>
+        <f>IF(AK225&lt;&gt;"",YEAR(AK225),"")</f>
         <v/>
       </c>
       <c r="F225" s="6" t="n"/>
@@ -33903,17 +35677,25 @@
         <v/>
       </c>
       <c r="AJ225" s="5" t="n"/>
+      <c r="AK225" s="12">
+        <f>IF(B225="","",IF(ISNUMBER(B225),B225,DATE(VALUE(LEFT(B225,4)),VALUE(MID(B225,6,2)),VALUE(MID(B225,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL225" s="12">
+        <f>IF(C225="","",IF(ISNUMBER(C225),C225,DATE(VALUE(LEFT(C225,4)),VALUE(MID(C225,6,2)),VALUE(MID(C225,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="5" t="n"/>
       <c r="D226" s="5">
-        <f>IF(AND(B226&lt;&gt;"",C226&lt;&gt;""),C226-B226+1,"")</f>
+        <f>IF(AND(AK226&lt;&gt;"",AL226&lt;&gt;""),AL226-AK226+1,"")</f>
         <v/>
       </c>
       <c r="E226" s="5">
-        <f>IF(B226&lt;&gt;"",YEAR(B226),"")</f>
+        <f>IF(AK226&lt;&gt;"",YEAR(AK226),"")</f>
         <v/>
       </c>
       <c r="F226" s="6" t="n"/>
@@ -34001,17 +35783,25 @@
         <v/>
       </c>
       <c r="AJ226" s="5" t="n"/>
+      <c r="AK226" s="12">
+        <f>IF(B226="","",IF(ISNUMBER(B226),B226,DATE(VALUE(LEFT(B226,4)),VALUE(MID(B226,6,2)),VALUE(MID(B226,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL226" s="12">
+        <f>IF(C226="","",IF(ISNUMBER(C226),C226,DATE(VALUE(LEFT(C226,4)),VALUE(MID(C226,6,2)),VALUE(MID(C226,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="5" t="n"/>
       <c r="D227" s="5">
-        <f>IF(AND(B227&lt;&gt;"",C227&lt;&gt;""),C227-B227+1,"")</f>
+        <f>IF(AND(AK227&lt;&gt;"",AL227&lt;&gt;""),AL227-AK227+1,"")</f>
         <v/>
       </c>
       <c r="E227" s="5">
-        <f>IF(B227&lt;&gt;"",YEAR(B227),"")</f>
+        <f>IF(AK227&lt;&gt;"",YEAR(AK227),"")</f>
         <v/>
       </c>
       <c r="F227" s="6" t="n"/>
@@ -34099,17 +35889,25 @@
         <v/>
       </c>
       <c r="AJ227" s="5" t="n"/>
+      <c r="AK227" s="12">
+        <f>IF(B227="","",IF(ISNUMBER(B227),B227,DATE(VALUE(LEFT(B227,4)),VALUE(MID(B227,6,2)),VALUE(MID(B227,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL227" s="12">
+        <f>IF(C227="","",IF(ISNUMBER(C227),C227,DATE(VALUE(LEFT(C227,4)),VALUE(MID(C227,6,2)),VALUE(MID(C227,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="5" t="n"/>
       <c r="D228" s="5">
-        <f>IF(AND(B228&lt;&gt;"",C228&lt;&gt;""),C228-B228+1,"")</f>
+        <f>IF(AND(AK228&lt;&gt;"",AL228&lt;&gt;""),AL228-AK228+1,"")</f>
         <v/>
       </c>
       <c r="E228" s="5">
-        <f>IF(B228&lt;&gt;"",YEAR(B228),"")</f>
+        <f>IF(AK228&lt;&gt;"",YEAR(AK228),"")</f>
         <v/>
       </c>
       <c r="F228" s="6" t="n"/>
@@ -34197,17 +35995,25 @@
         <v/>
       </c>
       <c r="AJ228" s="5" t="n"/>
+      <c r="AK228" s="12">
+        <f>IF(B228="","",IF(ISNUMBER(B228),B228,DATE(VALUE(LEFT(B228,4)),VALUE(MID(B228,6,2)),VALUE(MID(B228,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL228" s="12">
+        <f>IF(C228="","",IF(ISNUMBER(C228),C228,DATE(VALUE(LEFT(C228,4)),VALUE(MID(C228,6,2)),VALUE(MID(C228,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="5" t="n"/>
       <c r="D229" s="5">
-        <f>IF(AND(B229&lt;&gt;"",C229&lt;&gt;""),C229-B229+1,"")</f>
+        <f>IF(AND(AK229&lt;&gt;"",AL229&lt;&gt;""),AL229-AK229+1,"")</f>
         <v/>
       </c>
       <c r="E229" s="5">
-        <f>IF(B229&lt;&gt;"",YEAR(B229),"")</f>
+        <f>IF(AK229&lt;&gt;"",YEAR(AK229),"")</f>
         <v/>
       </c>
       <c r="F229" s="6" t="n"/>
@@ -34295,17 +36101,25 @@
         <v/>
       </c>
       <c r="AJ229" s="5" t="n"/>
+      <c r="AK229" s="12">
+        <f>IF(B229="","",IF(ISNUMBER(B229),B229,DATE(VALUE(LEFT(B229,4)),VALUE(MID(B229,6,2)),VALUE(MID(B229,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL229" s="12">
+        <f>IF(C229="","",IF(ISNUMBER(C229),C229,DATE(VALUE(LEFT(C229,4)),VALUE(MID(C229,6,2)),VALUE(MID(C229,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="5" t="n"/>
       <c r="D230" s="5">
-        <f>IF(AND(B230&lt;&gt;"",C230&lt;&gt;""),C230-B230+1,"")</f>
+        <f>IF(AND(AK230&lt;&gt;"",AL230&lt;&gt;""),AL230-AK230+1,"")</f>
         <v/>
       </c>
       <c r="E230" s="5">
-        <f>IF(B230&lt;&gt;"",YEAR(B230),"")</f>
+        <f>IF(AK230&lt;&gt;"",YEAR(AK230),"")</f>
         <v/>
       </c>
       <c r="F230" s="6" t="n"/>
@@ -34393,17 +36207,25 @@
         <v/>
       </c>
       <c r="AJ230" s="5" t="n"/>
+      <c r="AK230" s="12">
+        <f>IF(B230="","",IF(ISNUMBER(B230),B230,DATE(VALUE(LEFT(B230,4)),VALUE(MID(B230,6,2)),VALUE(MID(B230,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL230" s="12">
+        <f>IF(C230="","",IF(ISNUMBER(C230),C230,DATE(VALUE(LEFT(C230,4)),VALUE(MID(C230,6,2)),VALUE(MID(C230,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="5" t="n"/>
       <c r="D231" s="5">
-        <f>IF(AND(B231&lt;&gt;"",C231&lt;&gt;""),C231-B231+1,"")</f>
+        <f>IF(AND(AK231&lt;&gt;"",AL231&lt;&gt;""),AL231-AK231+1,"")</f>
         <v/>
       </c>
       <c r="E231" s="5">
-        <f>IF(B231&lt;&gt;"",YEAR(B231),"")</f>
+        <f>IF(AK231&lt;&gt;"",YEAR(AK231),"")</f>
         <v/>
       </c>
       <c r="F231" s="6" t="n"/>
@@ -34491,17 +36313,25 @@
         <v/>
       </c>
       <c r="AJ231" s="5" t="n"/>
+      <c r="AK231" s="12">
+        <f>IF(B231="","",IF(ISNUMBER(B231),B231,DATE(VALUE(LEFT(B231,4)),VALUE(MID(B231,6,2)),VALUE(MID(B231,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL231" s="12">
+        <f>IF(C231="","",IF(ISNUMBER(C231),C231,DATE(VALUE(LEFT(C231,4)),VALUE(MID(C231,6,2)),VALUE(MID(C231,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="5" t="n"/>
       <c r="D232" s="5">
-        <f>IF(AND(B232&lt;&gt;"",C232&lt;&gt;""),C232-B232+1,"")</f>
+        <f>IF(AND(AK232&lt;&gt;"",AL232&lt;&gt;""),AL232-AK232+1,"")</f>
         <v/>
       </c>
       <c r="E232" s="5">
-        <f>IF(B232&lt;&gt;"",YEAR(B232),"")</f>
+        <f>IF(AK232&lt;&gt;"",YEAR(AK232),"")</f>
         <v/>
       </c>
       <c r="F232" s="6" t="n"/>
@@ -34589,17 +36419,25 @@
         <v/>
       </c>
       <c r="AJ232" s="5" t="n"/>
+      <c r="AK232" s="12">
+        <f>IF(B232="","",IF(ISNUMBER(B232),B232,DATE(VALUE(LEFT(B232,4)),VALUE(MID(B232,6,2)),VALUE(MID(B232,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL232" s="12">
+        <f>IF(C232="","",IF(ISNUMBER(C232),C232,DATE(VALUE(LEFT(C232,4)),VALUE(MID(C232,6,2)),VALUE(MID(C232,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="5" t="n"/>
       <c r="D233" s="5">
-        <f>IF(AND(B233&lt;&gt;"",C233&lt;&gt;""),C233-B233+1,"")</f>
+        <f>IF(AND(AK233&lt;&gt;"",AL233&lt;&gt;""),AL233-AK233+1,"")</f>
         <v/>
       </c>
       <c r="E233" s="5">
-        <f>IF(B233&lt;&gt;"",YEAR(B233),"")</f>
+        <f>IF(AK233&lt;&gt;"",YEAR(AK233),"")</f>
         <v/>
       </c>
       <c r="F233" s="6" t="n"/>
@@ -34687,17 +36525,25 @@
         <v/>
       </c>
       <c r="AJ233" s="5" t="n"/>
+      <c r="AK233" s="12">
+        <f>IF(B233="","",IF(ISNUMBER(B233),B233,DATE(VALUE(LEFT(B233,4)),VALUE(MID(B233,6,2)),VALUE(MID(B233,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL233" s="12">
+        <f>IF(C233="","",IF(ISNUMBER(C233),C233,DATE(VALUE(LEFT(C233,4)),VALUE(MID(C233,6,2)),VALUE(MID(C233,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="5" t="n"/>
       <c r="D234" s="5">
-        <f>IF(AND(B234&lt;&gt;"",C234&lt;&gt;""),C234-B234+1,"")</f>
+        <f>IF(AND(AK234&lt;&gt;"",AL234&lt;&gt;""),AL234-AK234+1,"")</f>
         <v/>
       </c>
       <c r="E234" s="5">
-        <f>IF(B234&lt;&gt;"",YEAR(B234),"")</f>
+        <f>IF(AK234&lt;&gt;"",YEAR(AK234),"")</f>
         <v/>
       </c>
       <c r="F234" s="6" t="n"/>
@@ -34785,17 +36631,25 @@
         <v/>
       </c>
       <c r="AJ234" s="5" t="n"/>
+      <c r="AK234" s="12">
+        <f>IF(B234="","",IF(ISNUMBER(B234),B234,DATE(VALUE(LEFT(B234,4)),VALUE(MID(B234,6,2)),VALUE(MID(B234,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL234" s="12">
+        <f>IF(C234="","",IF(ISNUMBER(C234),C234,DATE(VALUE(LEFT(C234,4)),VALUE(MID(C234,6,2)),VALUE(MID(C234,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="5" t="n"/>
       <c r="D235" s="5">
-        <f>IF(AND(B235&lt;&gt;"",C235&lt;&gt;""),C235-B235+1,"")</f>
+        <f>IF(AND(AK235&lt;&gt;"",AL235&lt;&gt;""),AL235-AK235+1,"")</f>
         <v/>
       </c>
       <c r="E235" s="5">
-        <f>IF(B235&lt;&gt;"",YEAR(B235),"")</f>
+        <f>IF(AK235&lt;&gt;"",YEAR(AK235),"")</f>
         <v/>
       </c>
       <c r="F235" s="6" t="n"/>
@@ -34883,17 +36737,25 @@
         <v/>
       </c>
       <c r="AJ235" s="5" t="n"/>
+      <c r="AK235" s="12">
+        <f>IF(B235="","",IF(ISNUMBER(B235),B235,DATE(VALUE(LEFT(B235,4)),VALUE(MID(B235,6,2)),VALUE(MID(B235,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL235" s="12">
+        <f>IF(C235="","",IF(ISNUMBER(C235),C235,DATE(VALUE(LEFT(C235,4)),VALUE(MID(C235,6,2)),VALUE(MID(C235,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="5" t="n"/>
       <c r="D236" s="5">
-        <f>IF(AND(B236&lt;&gt;"",C236&lt;&gt;""),C236-B236+1,"")</f>
+        <f>IF(AND(AK236&lt;&gt;"",AL236&lt;&gt;""),AL236-AK236+1,"")</f>
         <v/>
       </c>
       <c r="E236" s="5">
-        <f>IF(B236&lt;&gt;"",YEAR(B236),"")</f>
+        <f>IF(AK236&lt;&gt;"",YEAR(AK236),"")</f>
         <v/>
       </c>
       <c r="F236" s="6" t="n"/>
@@ -34981,17 +36843,25 @@
         <v/>
       </c>
       <c r="AJ236" s="5" t="n"/>
+      <c r="AK236" s="12">
+        <f>IF(B236="","",IF(ISNUMBER(B236),B236,DATE(VALUE(LEFT(B236,4)),VALUE(MID(B236,6,2)),VALUE(MID(B236,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL236" s="12">
+        <f>IF(C236="","",IF(ISNUMBER(C236),C236,DATE(VALUE(LEFT(C236,4)),VALUE(MID(C236,6,2)),VALUE(MID(C236,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="5" t="n"/>
       <c r="D237" s="5">
-        <f>IF(AND(B237&lt;&gt;"",C237&lt;&gt;""),C237-B237+1,"")</f>
+        <f>IF(AND(AK237&lt;&gt;"",AL237&lt;&gt;""),AL237-AK237+1,"")</f>
         <v/>
       </c>
       <c r="E237" s="5">
-        <f>IF(B237&lt;&gt;"",YEAR(B237),"")</f>
+        <f>IF(AK237&lt;&gt;"",YEAR(AK237),"")</f>
         <v/>
       </c>
       <c r="F237" s="6" t="n"/>
@@ -35079,17 +36949,25 @@
         <v/>
       </c>
       <c r="AJ237" s="5" t="n"/>
+      <c r="AK237" s="12">
+        <f>IF(B237="","",IF(ISNUMBER(B237),B237,DATE(VALUE(LEFT(B237,4)),VALUE(MID(B237,6,2)),VALUE(MID(B237,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL237" s="12">
+        <f>IF(C237="","",IF(ISNUMBER(C237),C237,DATE(VALUE(LEFT(C237,4)),VALUE(MID(C237,6,2)),VALUE(MID(C237,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="5" t="n"/>
       <c r="D238" s="5">
-        <f>IF(AND(B238&lt;&gt;"",C238&lt;&gt;""),C238-B238+1,"")</f>
+        <f>IF(AND(AK238&lt;&gt;"",AL238&lt;&gt;""),AL238-AK238+1,"")</f>
         <v/>
       </c>
       <c r="E238" s="5">
-        <f>IF(B238&lt;&gt;"",YEAR(B238),"")</f>
+        <f>IF(AK238&lt;&gt;"",YEAR(AK238),"")</f>
         <v/>
       </c>
       <c r="F238" s="6" t="n"/>
@@ -35177,17 +37055,25 @@
         <v/>
       </c>
       <c r="AJ238" s="5" t="n"/>
+      <c r="AK238" s="12">
+        <f>IF(B238="","",IF(ISNUMBER(B238),B238,DATE(VALUE(LEFT(B238,4)),VALUE(MID(B238,6,2)),VALUE(MID(B238,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL238" s="12">
+        <f>IF(C238="","",IF(ISNUMBER(C238),C238,DATE(VALUE(LEFT(C238,4)),VALUE(MID(C238,6,2)),VALUE(MID(C238,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="5" t="n"/>
       <c r="D239" s="5">
-        <f>IF(AND(B239&lt;&gt;"",C239&lt;&gt;""),C239-B239+1,"")</f>
+        <f>IF(AND(AK239&lt;&gt;"",AL239&lt;&gt;""),AL239-AK239+1,"")</f>
         <v/>
       </c>
       <c r="E239" s="5">
-        <f>IF(B239&lt;&gt;"",YEAR(B239),"")</f>
+        <f>IF(AK239&lt;&gt;"",YEAR(AK239),"")</f>
         <v/>
       </c>
       <c r="F239" s="6" t="n"/>
@@ -35275,17 +37161,25 @@
         <v/>
       </c>
       <c r="AJ239" s="5" t="n"/>
+      <c r="AK239" s="12">
+        <f>IF(B239="","",IF(ISNUMBER(B239),B239,DATE(VALUE(LEFT(B239,4)),VALUE(MID(B239,6,2)),VALUE(MID(B239,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL239" s="12">
+        <f>IF(C239="","",IF(ISNUMBER(C239),C239,DATE(VALUE(LEFT(C239,4)),VALUE(MID(C239,6,2)),VALUE(MID(C239,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="5" t="n"/>
       <c r="D240" s="5">
-        <f>IF(AND(B240&lt;&gt;"",C240&lt;&gt;""),C240-B240+1,"")</f>
+        <f>IF(AND(AK240&lt;&gt;"",AL240&lt;&gt;""),AL240-AK240+1,"")</f>
         <v/>
       </c>
       <c r="E240" s="5">
-        <f>IF(B240&lt;&gt;"",YEAR(B240),"")</f>
+        <f>IF(AK240&lt;&gt;"",YEAR(AK240),"")</f>
         <v/>
       </c>
       <c r="F240" s="6" t="n"/>
@@ -35373,17 +37267,25 @@
         <v/>
       </c>
       <c r="AJ240" s="5" t="n"/>
+      <c r="AK240" s="12">
+        <f>IF(B240="","",IF(ISNUMBER(B240),B240,DATE(VALUE(LEFT(B240,4)),VALUE(MID(B240,6,2)),VALUE(MID(B240,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL240" s="12">
+        <f>IF(C240="","",IF(ISNUMBER(C240),C240,DATE(VALUE(LEFT(C240,4)),VALUE(MID(C240,6,2)),VALUE(MID(C240,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="5" t="n"/>
       <c r="D241" s="5">
-        <f>IF(AND(B241&lt;&gt;"",C241&lt;&gt;""),C241-B241+1,"")</f>
+        <f>IF(AND(AK241&lt;&gt;"",AL241&lt;&gt;""),AL241-AK241+1,"")</f>
         <v/>
       </c>
       <c r="E241" s="5">
-        <f>IF(B241&lt;&gt;"",YEAR(B241),"")</f>
+        <f>IF(AK241&lt;&gt;"",YEAR(AK241),"")</f>
         <v/>
       </c>
       <c r="F241" s="6" t="n"/>
@@ -35471,17 +37373,25 @@
         <v/>
       </c>
       <c r="AJ241" s="5" t="n"/>
+      <c r="AK241" s="12">
+        <f>IF(B241="","",IF(ISNUMBER(B241),B241,DATE(VALUE(LEFT(B241,4)),VALUE(MID(B241,6,2)),VALUE(MID(B241,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL241" s="12">
+        <f>IF(C241="","",IF(ISNUMBER(C241),C241,DATE(VALUE(LEFT(C241,4)),VALUE(MID(C241,6,2)),VALUE(MID(C241,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="5" t="n"/>
       <c r="D242" s="5">
-        <f>IF(AND(B242&lt;&gt;"",C242&lt;&gt;""),C242-B242+1,"")</f>
+        <f>IF(AND(AK242&lt;&gt;"",AL242&lt;&gt;""),AL242-AK242+1,"")</f>
         <v/>
       </c>
       <c r="E242" s="5">
-        <f>IF(B242&lt;&gt;"",YEAR(B242),"")</f>
+        <f>IF(AK242&lt;&gt;"",YEAR(AK242),"")</f>
         <v/>
       </c>
       <c r="F242" s="6" t="n"/>
@@ -35569,17 +37479,25 @@
         <v/>
       </c>
       <c r="AJ242" s="5" t="n"/>
+      <c r="AK242" s="12">
+        <f>IF(B242="","",IF(ISNUMBER(B242),B242,DATE(VALUE(LEFT(B242,4)),VALUE(MID(B242,6,2)),VALUE(MID(B242,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL242" s="12">
+        <f>IF(C242="","",IF(ISNUMBER(C242),C242,DATE(VALUE(LEFT(C242,4)),VALUE(MID(C242,6,2)),VALUE(MID(C242,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="5" t="n"/>
       <c r="D243" s="5">
-        <f>IF(AND(B243&lt;&gt;"",C243&lt;&gt;""),C243-B243+1,"")</f>
+        <f>IF(AND(AK243&lt;&gt;"",AL243&lt;&gt;""),AL243-AK243+1,"")</f>
         <v/>
       </c>
       <c r="E243" s="5">
-        <f>IF(B243&lt;&gt;"",YEAR(B243),"")</f>
+        <f>IF(AK243&lt;&gt;"",YEAR(AK243),"")</f>
         <v/>
       </c>
       <c r="F243" s="6" t="n"/>
@@ -35667,17 +37585,25 @@
         <v/>
       </c>
       <c r="AJ243" s="5" t="n"/>
+      <c r="AK243" s="12">
+        <f>IF(B243="","",IF(ISNUMBER(B243),B243,DATE(VALUE(LEFT(B243,4)),VALUE(MID(B243,6,2)),VALUE(MID(B243,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL243" s="12">
+        <f>IF(C243="","",IF(ISNUMBER(C243),C243,DATE(VALUE(LEFT(C243,4)),VALUE(MID(C243,6,2)),VALUE(MID(C243,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="5" t="n"/>
       <c r="D244" s="5">
-        <f>IF(AND(B244&lt;&gt;"",C244&lt;&gt;""),C244-B244+1,"")</f>
+        <f>IF(AND(AK244&lt;&gt;"",AL244&lt;&gt;""),AL244-AK244+1,"")</f>
         <v/>
       </c>
       <c r="E244" s="5">
-        <f>IF(B244&lt;&gt;"",YEAR(B244),"")</f>
+        <f>IF(AK244&lt;&gt;"",YEAR(AK244),"")</f>
         <v/>
       </c>
       <c r="F244" s="6" t="n"/>
@@ -35765,17 +37691,25 @@
         <v/>
       </c>
       <c r="AJ244" s="5" t="n"/>
+      <c r="AK244" s="12">
+        <f>IF(B244="","",IF(ISNUMBER(B244),B244,DATE(VALUE(LEFT(B244,4)),VALUE(MID(B244,6,2)),VALUE(MID(B244,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL244" s="12">
+        <f>IF(C244="","",IF(ISNUMBER(C244),C244,DATE(VALUE(LEFT(C244,4)),VALUE(MID(C244,6,2)),VALUE(MID(C244,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="5" t="n"/>
       <c r="D245" s="5">
-        <f>IF(AND(B245&lt;&gt;"",C245&lt;&gt;""),C245-B245+1,"")</f>
+        <f>IF(AND(AK245&lt;&gt;"",AL245&lt;&gt;""),AL245-AK245+1,"")</f>
         <v/>
       </c>
       <c r="E245" s="5">
-        <f>IF(B245&lt;&gt;"",YEAR(B245),"")</f>
+        <f>IF(AK245&lt;&gt;"",YEAR(AK245),"")</f>
         <v/>
       </c>
       <c r="F245" s="6" t="n"/>
@@ -35863,17 +37797,25 @@
         <v/>
       </c>
       <c r="AJ245" s="5" t="n"/>
+      <c r="AK245" s="12">
+        <f>IF(B245="","",IF(ISNUMBER(B245),B245,DATE(VALUE(LEFT(B245,4)),VALUE(MID(B245,6,2)),VALUE(MID(B245,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL245" s="12">
+        <f>IF(C245="","",IF(ISNUMBER(C245),C245,DATE(VALUE(LEFT(C245,4)),VALUE(MID(C245,6,2)),VALUE(MID(C245,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="5" t="n"/>
       <c r="D246" s="5">
-        <f>IF(AND(B246&lt;&gt;"",C246&lt;&gt;""),C246-B246+1,"")</f>
+        <f>IF(AND(AK246&lt;&gt;"",AL246&lt;&gt;""),AL246-AK246+1,"")</f>
         <v/>
       </c>
       <c r="E246" s="5">
-        <f>IF(B246&lt;&gt;"",YEAR(B246),"")</f>
+        <f>IF(AK246&lt;&gt;"",YEAR(AK246),"")</f>
         <v/>
       </c>
       <c r="F246" s="6" t="n"/>
@@ -35961,17 +37903,25 @@
         <v/>
       </c>
       <c r="AJ246" s="5" t="n"/>
+      <c r="AK246" s="12">
+        <f>IF(B246="","",IF(ISNUMBER(B246),B246,DATE(VALUE(LEFT(B246,4)),VALUE(MID(B246,6,2)),VALUE(MID(B246,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL246" s="12">
+        <f>IF(C246="","",IF(ISNUMBER(C246),C246,DATE(VALUE(LEFT(C246,4)),VALUE(MID(C246,6,2)),VALUE(MID(C246,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="5" t="n"/>
       <c r="D247" s="5">
-        <f>IF(AND(B247&lt;&gt;"",C247&lt;&gt;""),C247-B247+1,"")</f>
+        <f>IF(AND(AK247&lt;&gt;"",AL247&lt;&gt;""),AL247-AK247+1,"")</f>
         <v/>
       </c>
       <c r="E247" s="5">
-        <f>IF(B247&lt;&gt;"",YEAR(B247),"")</f>
+        <f>IF(AK247&lt;&gt;"",YEAR(AK247),"")</f>
         <v/>
       </c>
       <c r="F247" s="6" t="n"/>
@@ -36059,17 +38009,25 @@
         <v/>
       </c>
       <c r="AJ247" s="5" t="n"/>
+      <c r="AK247" s="12">
+        <f>IF(B247="","",IF(ISNUMBER(B247),B247,DATE(VALUE(LEFT(B247,4)),VALUE(MID(B247,6,2)),VALUE(MID(B247,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL247" s="12">
+        <f>IF(C247="","",IF(ISNUMBER(C247),C247,DATE(VALUE(LEFT(C247,4)),VALUE(MID(C247,6,2)),VALUE(MID(C247,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="5" t="n"/>
       <c r="D248" s="5">
-        <f>IF(AND(B248&lt;&gt;"",C248&lt;&gt;""),C248-B248+1,"")</f>
+        <f>IF(AND(AK248&lt;&gt;"",AL248&lt;&gt;""),AL248-AK248+1,"")</f>
         <v/>
       </c>
       <c r="E248" s="5">
-        <f>IF(B248&lt;&gt;"",YEAR(B248),"")</f>
+        <f>IF(AK248&lt;&gt;"",YEAR(AK248),"")</f>
         <v/>
       </c>
       <c r="F248" s="6" t="n"/>
@@ -36157,17 +38115,25 @@
         <v/>
       </c>
       <c r="AJ248" s="5" t="n"/>
+      <c r="AK248" s="12">
+        <f>IF(B248="","",IF(ISNUMBER(B248),B248,DATE(VALUE(LEFT(B248,4)),VALUE(MID(B248,6,2)),VALUE(MID(B248,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL248" s="12">
+        <f>IF(C248="","",IF(ISNUMBER(C248),C248,DATE(VALUE(LEFT(C248,4)),VALUE(MID(C248,6,2)),VALUE(MID(C248,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="5" t="n"/>
       <c r="D249" s="5">
-        <f>IF(AND(B249&lt;&gt;"",C249&lt;&gt;""),C249-B249+1,"")</f>
+        <f>IF(AND(AK249&lt;&gt;"",AL249&lt;&gt;""),AL249-AK249+1,"")</f>
         <v/>
       </c>
       <c r="E249" s="5">
-        <f>IF(B249&lt;&gt;"",YEAR(B249),"")</f>
+        <f>IF(AK249&lt;&gt;"",YEAR(AK249),"")</f>
         <v/>
       </c>
       <c r="F249" s="6" t="n"/>
@@ -36255,17 +38221,25 @@
         <v/>
       </c>
       <c r="AJ249" s="5" t="n"/>
+      <c r="AK249" s="12">
+        <f>IF(B249="","",IF(ISNUMBER(B249),B249,DATE(VALUE(LEFT(B249,4)),VALUE(MID(B249,6,2)),VALUE(MID(B249,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL249" s="12">
+        <f>IF(C249="","",IF(ISNUMBER(C249),C249,DATE(VALUE(LEFT(C249,4)),VALUE(MID(C249,6,2)),VALUE(MID(C249,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="5" t="n"/>
       <c r="D250" s="5">
-        <f>IF(AND(B250&lt;&gt;"",C250&lt;&gt;""),C250-B250+1,"")</f>
+        <f>IF(AND(AK250&lt;&gt;"",AL250&lt;&gt;""),AL250-AK250+1,"")</f>
         <v/>
       </c>
       <c r="E250" s="5">
-        <f>IF(B250&lt;&gt;"",YEAR(B250),"")</f>
+        <f>IF(AK250&lt;&gt;"",YEAR(AK250),"")</f>
         <v/>
       </c>
       <c r="F250" s="6" t="n"/>
@@ -36353,17 +38327,25 @@
         <v/>
       </c>
       <c r="AJ250" s="5" t="n"/>
+      <c r="AK250" s="12">
+        <f>IF(B250="","",IF(ISNUMBER(B250),B250,DATE(VALUE(LEFT(B250,4)),VALUE(MID(B250,6,2)),VALUE(MID(B250,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL250" s="12">
+        <f>IF(C250="","",IF(ISNUMBER(C250),C250,DATE(VALUE(LEFT(C250,4)),VALUE(MID(C250,6,2)),VALUE(MID(C250,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="5" t="n"/>
       <c r="D251" s="5">
-        <f>IF(AND(B251&lt;&gt;"",C251&lt;&gt;""),C251-B251+1,"")</f>
+        <f>IF(AND(AK251&lt;&gt;"",AL251&lt;&gt;""),AL251-AK251+1,"")</f>
         <v/>
       </c>
       <c r="E251" s="5">
-        <f>IF(B251&lt;&gt;"",YEAR(B251),"")</f>
+        <f>IF(AK251&lt;&gt;"",YEAR(AK251),"")</f>
         <v/>
       </c>
       <c r="F251" s="6" t="n"/>
@@ -36451,17 +38433,25 @@
         <v/>
       </c>
       <c r="AJ251" s="5" t="n"/>
+      <c r="AK251" s="12">
+        <f>IF(B251="","",IF(ISNUMBER(B251),B251,DATE(VALUE(LEFT(B251,4)),VALUE(MID(B251,6,2)),VALUE(MID(B251,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL251" s="12">
+        <f>IF(C251="","",IF(ISNUMBER(C251),C251,DATE(VALUE(LEFT(C251,4)),VALUE(MID(C251,6,2)),VALUE(MID(C251,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="5" t="n"/>
       <c r="D252" s="5">
-        <f>IF(AND(B252&lt;&gt;"",C252&lt;&gt;""),C252-B252+1,"")</f>
+        <f>IF(AND(AK252&lt;&gt;"",AL252&lt;&gt;""),AL252-AK252+1,"")</f>
         <v/>
       </c>
       <c r="E252" s="5">
-        <f>IF(B252&lt;&gt;"",YEAR(B252),"")</f>
+        <f>IF(AK252&lt;&gt;"",YEAR(AK252),"")</f>
         <v/>
       </c>
       <c r="F252" s="6" t="n"/>
@@ -36549,17 +38539,25 @@
         <v/>
       </c>
       <c r="AJ252" s="5" t="n"/>
+      <c r="AK252" s="12">
+        <f>IF(B252="","",IF(ISNUMBER(B252),B252,DATE(VALUE(LEFT(B252,4)),VALUE(MID(B252,6,2)),VALUE(MID(B252,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL252" s="12">
+        <f>IF(C252="","",IF(ISNUMBER(C252),C252,DATE(VALUE(LEFT(C252,4)),VALUE(MID(C252,6,2)),VALUE(MID(C252,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="5" t="n"/>
       <c r="D253" s="5">
-        <f>IF(AND(B253&lt;&gt;"",C253&lt;&gt;""),C253-B253+1,"")</f>
+        <f>IF(AND(AK253&lt;&gt;"",AL253&lt;&gt;""),AL253-AK253+1,"")</f>
         <v/>
       </c>
       <c r="E253" s="5">
-        <f>IF(B253&lt;&gt;"",YEAR(B253),"")</f>
+        <f>IF(AK253&lt;&gt;"",YEAR(AK253),"")</f>
         <v/>
       </c>
       <c r="F253" s="6" t="n"/>
@@ -36647,17 +38645,25 @@
         <v/>
       </c>
       <c r="AJ253" s="5" t="n"/>
+      <c r="AK253" s="12">
+        <f>IF(B253="","",IF(ISNUMBER(B253),B253,DATE(VALUE(LEFT(B253,4)),VALUE(MID(B253,6,2)),VALUE(MID(B253,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL253" s="12">
+        <f>IF(C253="","",IF(ISNUMBER(C253),C253,DATE(VALUE(LEFT(C253,4)),VALUE(MID(C253,6,2)),VALUE(MID(C253,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="5" t="n"/>
       <c r="D254" s="5">
-        <f>IF(AND(B254&lt;&gt;"",C254&lt;&gt;""),C254-B254+1,"")</f>
+        <f>IF(AND(AK254&lt;&gt;"",AL254&lt;&gt;""),AL254-AK254+1,"")</f>
         <v/>
       </c>
       <c r="E254" s="5">
-        <f>IF(B254&lt;&gt;"",YEAR(B254),"")</f>
+        <f>IF(AK254&lt;&gt;"",YEAR(AK254),"")</f>
         <v/>
       </c>
       <c r="F254" s="6" t="n"/>
@@ -36745,17 +38751,25 @@
         <v/>
       </c>
       <c r="AJ254" s="5" t="n"/>
+      <c r="AK254" s="12">
+        <f>IF(B254="","",IF(ISNUMBER(B254),B254,DATE(VALUE(LEFT(B254,4)),VALUE(MID(B254,6,2)),VALUE(MID(B254,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL254" s="12">
+        <f>IF(C254="","",IF(ISNUMBER(C254),C254,DATE(VALUE(LEFT(C254,4)),VALUE(MID(C254,6,2)),VALUE(MID(C254,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="5" t="n"/>
       <c r="D255" s="5">
-        <f>IF(AND(B255&lt;&gt;"",C255&lt;&gt;""),C255-B255+1,"")</f>
+        <f>IF(AND(AK255&lt;&gt;"",AL255&lt;&gt;""),AL255-AK255+1,"")</f>
         <v/>
       </c>
       <c r="E255" s="5">
-        <f>IF(B255&lt;&gt;"",YEAR(B255),"")</f>
+        <f>IF(AK255&lt;&gt;"",YEAR(AK255),"")</f>
         <v/>
       </c>
       <c r="F255" s="6" t="n"/>
@@ -36843,17 +38857,25 @@
         <v/>
       </c>
       <c r="AJ255" s="5" t="n"/>
+      <c r="AK255" s="12">
+        <f>IF(B255="","",IF(ISNUMBER(B255),B255,DATE(VALUE(LEFT(B255,4)),VALUE(MID(B255,6,2)),VALUE(MID(B255,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL255" s="12">
+        <f>IF(C255="","",IF(ISNUMBER(C255),C255,DATE(VALUE(LEFT(C255,4)),VALUE(MID(C255,6,2)),VALUE(MID(C255,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="5" t="n"/>
       <c r="D256" s="5">
-        <f>IF(AND(B256&lt;&gt;"",C256&lt;&gt;""),C256-B256+1,"")</f>
+        <f>IF(AND(AK256&lt;&gt;"",AL256&lt;&gt;""),AL256-AK256+1,"")</f>
         <v/>
       </c>
       <c r="E256" s="5">
-        <f>IF(B256&lt;&gt;"",YEAR(B256),"")</f>
+        <f>IF(AK256&lt;&gt;"",YEAR(AK256),"")</f>
         <v/>
       </c>
       <c r="F256" s="6" t="n"/>
@@ -36941,17 +38963,25 @@
         <v/>
       </c>
       <c r="AJ256" s="5" t="n"/>
+      <c r="AK256" s="12">
+        <f>IF(B256="","",IF(ISNUMBER(B256),B256,DATE(VALUE(LEFT(B256,4)),VALUE(MID(B256,6,2)),VALUE(MID(B256,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL256" s="12">
+        <f>IF(C256="","",IF(ISNUMBER(C256),C256,DATE(VALUE(LEFT(C256,4)),VALUE(MID(C256,6,2)),VALUE(MID(C256,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="5" t="n"/>
       <c r="D257" s="5">
-        <f>IF(AND(B257&lt;&gt;"",C257&lt;&gt;""),C257-B257+1,"")</f>
+        <f>IF(AND(AK257&lt;&gt;"",AL257&lt;&gt;""),AL257-AK257+1,"")</f>
         <v/>
       </c>
       <c r="E257" s="5">
-        <f>IF(B257&lt;&gt;"",YEAR(B257),"")</f>
+        <f>IF(AK257&lt;&gt;"",YEAR(AK257),"")</f>
         <v/>
       </c>
       <c r="F257" s="6" t="n"/>
@@ -37039,17 +39069,25 @@
         <v/>
       </c>
       <c r="AJ257" s="5" t="n"/>
+      <c r="AK257" s="12">
+        <f>IF(B257="","",IF(ISNUMBER(B257),B257,DATE(VALUE(LEFT(B257,4)),VALUE(MID(B257,6,2)),VALUE(MID(B257,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL257" s="12">
+        <f>IF(C257="","",IF(ISNUMBER(C257),C257,DATE(VALUE(LEFT(C257,4)),VALUE(MID(C257,6,2)),VALUE(MID(C257,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="5" t="n"/>
       <c r="D258" s="5">
-        <f>IF(AND(B258&lt;&gt;"",C258&lt;&gt;""),C258-B258+1,"")</f>
+        <f>IF(AND(AK258&lt;&gt;"",AL258&lt;&gt;""),AL258-AK258+1,"")</f>
         <v/>
       </c>
       <c r="E258" s="5">
-        <f>IF(B258&lt;&gt;"",YEAR(B258),"")</f>
+        <f>IF(AK258&lt;&gt;"",YEAR(AK258),"")</f>
         <v/>
       </c>
       <c r="F258" s="6" t="n"/>
@@ -37137,17 +39175,25 @@
         <v/>
       </c>
       <c r="AJ258" s="5" t="n"/>
+      <c r="AK258" s="12">
+        <f>IF(B258="","",IF(ISNUMBER(B258),B258,DATE(VALUE(LEFT(B258,4)),VALUE(MID(B258,6,2)),VALUE(MID(B258,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL258" s="12">
+        <f>IF(C258="","",IF(ISNUMBER(C258),C258,DATE(VALUE(LEFT(C258,4)),VALUE(MID(C258,6,2)),VALUE(MID(C258,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="5" t="n"/>
       <c r="D259" s="5">
-        <f>IF(AND(B259&lt;&gt;"",C259&lt;&gt;""),C259-B259+1,"")</f>
+        <f>IF(AND(AK259&lt;&gt;"",AL259&lt;&gt;""),AL259-AK259+1,"")</f>
         <v/>
       </c>
       <c r="E259" s="5">
-        <f>IF(B259&lt;&gt;"",YEAR(B259),"")</f>
+        <f>IF(AK259&lt;&gt;"",YEAR(AK259),"")</f>
         <v/>
       </c>
       <c r="F259" s="6" t="n"/>
@@ -37235,17 +39281,25 @@
         <v/>
       </c>
       <c r="AJ259" s="5" t="n"/>
+      <c r="AK259" s="12">
+        <f>IF(B259="","",IF(ISNUMBER(B259),B259,DATE(VALUE(LEFT(B259,4)),VALUE(MID(B259,6,2)),VALUE(MID(B259,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL259" s="12">
+        <f>IF(C259="","",IF(ISNUMBER(C259),C259,DATE(VALUE(LEFT(C259,4)),VALUE(MID(C259,6,2)),VALUE(MID(C259,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="5" t="n"/>
       <c r="D260" s="5">
-        <f>IF(AND(B260&lt;&gt;"",C260&lt;&gt;""),C260-B260+1,"")</f>
+        <f>IF(AND(AK260&lt;&gt;"",AL260&lt;&gt;""),AL260-AK260+1,"")</f>
         <v/>
       </c>
       <c r="E260" s="5">
-        <f>IF(B260&lt;&gt;"",YEAR(B260),"")</f>
+        <f>IF(AK260&lt;&gt;"",YEAR(AK260),"")</f>
         <v/>
       </c>
       <c r="F260" s="6" t="n"/>
@@ -37333,17 +39387,25 @@
         <v/>
       </c>
       <c r="AJ260" s="5" t="n"/>
+      <c r="AK260" s="12">
+        <f>IF(B260="","",IF(ISNUMBER(B260),B260,DATE(VALUE(LEFT(B260,4)),VALUE(MID(B260,6,2)),VALUE(MID(B260,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL260" s="12">
+        <f>IF(C260="","",IF(ISNUMBER(C260),C260,DATE(VALUE(LEFT(C260,4)),VALUE(MID(C260,6,2)),VALUE(MID(C260,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="5" t="n"/>
       <c r="D261" s="5">
-        <f>IF(AND(B261&lt;&gt;"",C261&lt;&gt;""),C261-B261+1,"")</f>
+        <f>IF(AND(AK261&lt;&gt;"",AL261&lt;&gt;""),AL261-AK261+1,"")</f>
         <v/>
       </c>
       <c r="E261" s="5">
-        <f>IF(B261&lt;&gt;"",YEAR(B261),"")</f>
+        <f>IF(AK261&lt;&gt;"",YEAR(AK261),"")</f>
         <v/>
       </c>
       <c r="F261" s="6" t="n"/>
@@ -37431,17 +39493,25 @@
         <v/>
       </c>
       <c r="AJ261" s="5" t="n"/>
+      <c r="AK261" s="12">
+        <f>IF(B261="","",IF(ISNUMBER(B261),B261,DATE(VALUE(LEFT(B261,4)),VALUE(MID(B261,6,2)),VALUE(MID(B261,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL261" s="12">
+        <f>IF(C261="","",IF(ISNUMBER(C261),C261,DATE(VALUE(LEFT(C261,4)),VALUE(MID(C261,6,2)),VALUE(MID(C261,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="5" t="n"/>
       <c r="D262" s="5">
-        <f>IF(AND(B262&lt;&gt;"",C262&lt;&gt;""),C262-B262+1,"")</f>
+        <f>IF(AND(AK262&lt;&gt;"",AL262&lt;&gt;""),AL262-AK262+1,"")</f>
         <v/>
       </c>
       <c r="E262" s="5">
-        <f>IF(B262&lt;&gt;"",YEAR(B262),"")</f>
+        <f>IF(AK262&lt;&gt;"",YEAR(AK262),"")</f>
         <v/>
       </c>
       <c r="F262" s="6" t="n"/>
@@ -37529,17 +39599,25 @@
         <v/>
       </c>
       <c r="AJ262" s="5" t="n"/>
+      <c r="AK262" s="12">
+        <f>IF(B262="","",IF(ISNUMBER(B262),B262,DATE(VALUE(LEFT(B262,4)),VALUE(MID(B262,6,2)),VALUE(MID(B262,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL262" s="12">
+        <f>IF(C262="","",IF(ISNUMBER(C262),C262,DATE(VALUE(LEFT(C262,4)),VALUE(MID(C262,6,2)),VALUE(MID(C262,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="5" t="n"/>
       <c r="D263" s="5">
-        <f>IF(AND(B263&lt;&gt;"",C263&lt;&gt;""),C263-B263+1,"")</f>
+        <f>IF(AND(AK263&lt;&gt;"",AL263&lt;&gt;""),AL263-AK263+1,"")</f>
         <v/>
       </c>
       <c r="E263" s="5">
-        <f>IF(B263&lt;&gt;"",YEAR(B263),"")</f>
+        <f>IF(AK263&lt;&gt;"",YEAR(AK263),"")</f>
         <v/>
       </c>
       <c r="F263" s="6" t="n"/>
@@ -37627,17 +39705,25 @@
         <v/>
       </c>
       <c r="AJ263" s="5" t="n"/>
+      <c r="AK263" s="12">
+        <f>IF(B263="","",IF(ISNUMBER(B263),B263,DATE(VALUE(LEFT(B263,4)),VALUE(MID(B263,6,2)),VALUE(MID(B263,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL263" s="12">
+        <f>IF(C263="","",IF(ISNUMBER(C263),C263,DATE(VALUE(LEFT(C263,4)),VALUE(MID(C263,6,2)),VALUE(MID(C263,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="5" t="n"/>
       <c r="D264" s="5">
-        <f>IF(AND(B264&lt;&gt;"",C264&lt;&gt;""),C264-B264+1,"")</f>
+        <f>IF(AND(AK264&lt;&gt;"",AL264&lt;&gt;""),AL264-AK264+1,"")</f>
         <v/>
       </c>
       <c r="E264" s="5">
-        <f>IF(B264&lt;&gt;"",YEAR(B264),"")</f>
+        <f>IF(AK264&lt;&gt;"",YEAR(AK264),"")</f>
         <v/>
       </c>
       <c r="F264" s="6" t="n"/>
@@ -37725,17 +39811,25 @@
         <v/>
       </c>
       <c r="AJ264" s="5" t="n"/>
+      <c r="AK264" s="12">
+        <f>IF(B264="","",IF(ISNUMBER(B264),B264,DATE(VALUE(LEFT(B264,4)),VALUE(MID(B264,6,2)),VALUE(MID(B264,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL264" s="12">
+        <f>IF(C264="","",IF(ISNUMBER(C264),C264,DATE(VALUE(LEFT(C264,4)),VALUE(MID(C264,6,2)),VALUE(MID(C264,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="5" t="n"/>
       <c r="D265" s="5">
-        <f>IF(AND(B265&lt;&gt;"",C265&lt;&gt;""),C265-B265+1,"")</f>
+        <f>IF(AND(AK265&lt;&gt;"",AL265&lt;&gt;""),AL265-AK265+1,"")</f>
         <v/>
       </c>
       <c r="E265" s="5">
-        <f>IF(B265&lt;&gt;"",YEAR(B265),"")</f>
+        <f>IF(AK265&lt;&gt;"",YEAR(AK265),"")</f>
         <v/>
       </c>
       <c r="F265" s="6" t="n"/>
@@ -37823,17 +39917,25 @@
         <v/>
       </c>
       <c r="AJ265" s="5" t="n"/>
+      <c r="AK265" s="12">
+        <f>IF(B265="","",IF(ISNUMBER(B265),B265,DATE(VALUE(LEFT(B265,4)),VALUE(MID(B265,6,2)),VALUE(MID(B265,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL265" s="12">
+        <f>IF(C265="","",IF(ISNUMBER(C265),C265,DATE(VALUE(LEFT(C265,4)),VALUE(MID(C265,6,2)),VALUE(MID(C265,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="5" t="n"/>
       <c r="D266" s="5">
-        <f>IF(AND(B266&lt;&gt;"",C266&lt;&gt;""),C266-B266+1,"")</f>
+        <f>IF(AND(AK266&lt;&gt;"",AL266&lt;&gt;""),AL266-AK266+1,"")</f>
         <v/>
       </c>
       <c r="E266" s="5">
-        <f>IF(B266&lt;&gt;"",YEAR(B266),"")</f>
+        <f>IF(AK266&lt;&gt;"",YEAR(AK266),"")</f>
         <v/>
       </c>
       <c r="F266" s="6" t="n"/>
@@ -37921,17 +40023,25 @@
         <v/>
       </c>
       <c r="AJ266" s="5" t="n"/>
+      <c r="AK266" s="12">
+        <f>IF(B266="","",IF(ISNUMBER(B266),B266,DATE(VALUE(LEFT(B266,4)),VALUE(MID(B266,6,2)),VALUE(MID(B266,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL266" s="12">
+        <f>IF(C266="","",IF(ISNUMBER(C266),C266,DATE(VALUE(LEFT(C266,4)),VALUE(MID(C266,6,2)),VALUE(MID(C266,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="5" t="n"/>
       <c r="D267" s="5">
-        <f>IF(AND(B267&lt;&gt;"",C267&lt;&gt;""),C267-B267+1,"")</f>
+        <f>IF(AND(AK267&lt;&gt;"",AL267&lt;&gt;""),AL267-AK267+1,"")</f>
         <v/>
       </c>
       <c r="E267" s="5">
-        <f>IF(B267&lt;&gt;"",YEAR(B267),"")</f>
+        <f>IF(AK267&lt;&gt;"",YEAR(AK267),"")</f>
         <v/>
       </c>
       <c r="F267" s="6" t="n"/>
@@ -38019,17 +40129,25 @@
         <v/>
       </c>
       <c r="AJ267" s="5" t="n"/>
+      <c r="AK267" s="12">
+        <f>IF(B267="","",IF(ISNUMBER(B267),B267,DATE(VALUE(LEFT(B267,4)),VALUE(MID(B267,6,2)),VALUE(MID(B267,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL267" s="12">
+        <f>IF(C267="","",IF(ISNUMBER(C267),C267,DATE(VALUE(LEFT(C267,4)),VALUE(MID(C267,6,2)),VALUE(MID(C267,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="5" t="n"/>
       <c r="D268" s="5">
-        <f>IF(AND(B268&lt;&gt;"",C268&lt;&gt;""),C268-B268+1,"")</f>
+        <f>IF(AND(AK268&lt;&gt;"",AL268&lt;&gt;""),AL268-AK268+1,"")</f>
         <v/>
       </c>
       <c r="E268" s="5">
-        <f>IF(B268&lt;&gt;"",YEAR(B268),"")</f>
+        <f>IF(AK268&lt;&gt;"",YEAR(AK268),"")</f>
         <v/>
       </c>
       <c r="F268" s="6" t="n"/>
@@ -38117,17 +40235,25 @@
         <v/>
       </c>
       <c r="AJ268" s="5" t="n"/>
+      <c r="AK268" s="12">
+        <f>IF(B268="","",IF(ISNUMBER(B268),B268,DATE(VALUE(LEFT(B268,4)),VALUE(MID(B268,6,2)),VALUE(MID(B268,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL268" s="12">
+        <f>IF(C268="","",IF(ISNUMBER(C268),C268,DATE(VALUE(LEFT(C268,4)),VALUE(MID(C268,6,2)),VALUE(MID(C268,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="5" t="n"/>
       <c r="D269" s="5">
-        <f>IF(AND(B269&lt;&gt;"",C269&lt;&gt;""),C269-B269+1,"")</f>
+        <f>IF(AND(AK269&lt;&gt;"",AL269&lt;&gt;""),AL269-AK269+1,"")</f>
         <v/>
       </c>
       <c r="E269" s="5">
-        <f>IF(B269&lt;&gt;"",YEAR(B269),"")</f>
+        <f>IF(AK269&lt;&gt;"",YEAR(AK269),"")</f>
         <v/>
       </c>
       <c r="F269" s="6" t="n"/>
@@ -38215,17 +40341,25 @@
         <v/>
       </c>
       <c r="AJ269" s="5" t="n"/>
+      <c r="AK269" s="12">
+        <f>IF(B269="","",IF(ISNUMBER(B269),B269,DATE(VALUE(LEFT(B269,4)),VALUE(MID(B269,6,2)),VALUE(MID(B269,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL269" s="12">
+        <f>IF(C269="","",IF(ISNUMBER(C269),C269,DATE(VALUE(LEFT(C269,4)),VALUE(MID(C269,6,2)),VALUE(MID(C269,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="5" t="n"/>
       <c r="D270" s="5">
-        <f>IF(AND(B270&lt;&gt;"",C270&lt;&gt;""),C270-B270+1,"")</f>
+        <f>IF(AND(AK270&lt;&gt;"",AL270&lt;&gt;""),AL270-AK270+1,"")</f>
         <v/>
       </c>
       <c r="E270" s="5">
-        <f>IF(B270&lt;&gt;"",YEAR(B270),"")</f>
+        <f>IF(AK270&lt;&gt;"",YEAR(AK270),"")</f>
         <v/>
       </c>
       <c r="F270" s="6" t="n"/>
@@ -38313,17 +40447,25 @@
         <v/>
       </c>
       <c r="AJ270" s="5" t="n"/>
+      <c r="AK270" s="12">
+        <f>IF(B270="","",IF(ISNUMBER(B270),B270,DATE(VALUE(LEFT(B270,4)),VALUE(MID(B270,6,2)),VALUE(MID(B270,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL270" s="12">
+        <f>IF(C270="","",IF(ISNUMBER(C270),C270,DATE(VALUE(LEFT(C270,4)),VALUE(MID(C270,6,2)),VALUE(MID(C270,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="5" t="n"/>
       <c r="D271" s="5">
-        <f>IF(AND(B271&lt;&gt;"",C271&lt;&gt;""),C271-B271+1,"")</f>
+        <f>IF(AND(AK271&lt;&gt;"",AL271&lt;&gt;""),AL271-AK271+1,"")</f>
         <v/>
       </c>
       <c r="E271" s="5">
-        <f>IF(B271&lt;&gt;"",YEAR(B271),"")</f>
+        <f>IF(AK271&lt;&gt;"",YEAR(AK271),"")</f>
         <v/>
       </c>
       <c r="F271" s="6" t="n"/>
@@ -38411,17 +40553,25 @@
         <v/>
       </c>
       <c r="AJ271" s="5" t="n"/>
+      <c r="AK271" s="12">
+        <f>IF(B271="","",IF(ISNUMBER(B271),B271,DATE(VALUE(LEFT(B271,4)),VALUE(MID(B271,6,2)),VALUE(MID(B271,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL271" s="12">
+        <f>IF(C271="","",IF(ISNUMBER(C271),C271,DATE(VALUE(LEFT(C271,4)),VALUE(MID(C271,6,2)),VALUE(MID(C271,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="5" t="n"/>
       <c r="D272" s="5">
-        <f>IF(AND(B272&lt;&gt;"",C272&lt;&gt;""),C272-B272+1,"")</f>
+        <f>IF(AND(AK272&lt;&gt;"",AL272&lt;&gt;""),AL272-AK272+1,"")</f>
         <v/>
       </c>
       <c r="E272" s="5">
-        <f>IF(B272&lt;&gt;"",YEAR(B272),"")</f>
+        <f>IF(AK272&lt;&gt;"",YEAR(AK272),"")</f>
         <v/>
       </c>
       <c r="F272" s="6" t="n"/>
@@ -38509,17 +40659,25 @@
         <v/>
       </c>
       <c r="AJ272" s="5" t="n"/>
+      <c r="AK272" s="12">
+        <f>IF(B272="","",IF(ISNUMBER(B272),B272,DATE(VALUE(LEFT(B272,4)),VALUE(MID(B272,6,2)),VALUE(MID(B272,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL272" s="12">
+        <f>IF(C272="","",IF(ISNUMBER(C272),C272,DATE(VALUE(LEFT(C272,4)),VALUE(MID(C272,6,2)),VALUE(MID(C272,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="5" t="n"/>
       <c r="D273" s="5">
-        <f>IF(AND(B273&lt;&gt;"",C273&lt;&gt;""),C273-B273+1,"")</f>
+        <f>IF(AND(AK273&lt;&gt;"",AL273&lt;&gt;""),AL273-AK273+1,"")</f>
         <v/>
       </c>
       <c r="E273" s="5">
-        <f>IF(B273&lt;&gt;"",YEAR(B273),"")</f>
+        <f>IF(AK273&lt;&gt;"",YEAR(AK273),"")</f>
         <v/>
       </c>
       <c r="F273" s="6" t="n"/>
@@ -38607,17 +40765,25 @@
         <v/>
       </c>
       <c r="AJ273" s="5" t="n"/>
+      <c r="AK273" s="12">
+        <f>IF(B273="","",IF(ISNUMBER(B273),B273,DATE(VALUE(LEFT(B273,4)),VALUE(MID(B273,6,2)),VALUE(MID(B273,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL273" s="12">
+        <f>IF(C273="","",IF(ISNUMBER(C273),C273,DATE(VALUE(LEFT(C273,4)),VALUE(MID(C273,6,2)),VALUE(MID(C273,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="5" t="n"/>
       <c r="D274" s="5">
-        <f>IF(AND(B274&lt;&gt;"",C274&lt;&gt;""),C274-B274+1,"")</f>
+        <f>IF(AND(AK274&lt;&gt;"",AL274&lt;&gt;""),AL274-AK274+1,"")</f>
         <v/>
       </c>
       <c r="E274" s="5">
-        <f>IF(B274&lt;&gt;"",YEAR(B274),"")</f>
+        <f>IF(AK274&lt;&gt;"",YEAR(AK274),"")</f>
         <v/>
       </c>
       <c r="F274" s="6" t="n"/>
@@ -38705,17 +40871,25 @@
         <v/>
       </c>
       <c r="AJ274" s="5" t="n"/>
+      <c r="AK274" s="12">
+        <f>IF(B274="","",IF(ISNUMBER(B274),B274,DATE(VALUE(LEFT(B274,4)),VALUE(MID(B274,6,2)),VALUE(MID(B274,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL274" s="12">
+        <f>IF(C274="","",IF(ISNUMBER(C274),C274,DATE(VALUE(LEFT(C274,4)),VALUE(MID(C274,6,2)),VALUE(MID(C274,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="5" t="n"/>
       <c r="D275" s="5">
-        <f>IF(AND(B275&lt;&gt;"",C275&lt;&gt;""),C275-B275+1,"")</f>
+        <f>IF(AND(AK275&lt;&gt;"",AL275&lt;&gt;""),AL275-AK275+1,"")</f>
         <v/>
       </c>
       <c r="E275" s="5">
-        <f>IF(B275&lt;&gt;"",YEAR(B275),"")</f>
+        <f>IF(AK275&lt;&gt;"",YEAR(AK275),"")</f>
         <v/>
       </c>
       <c r="F275" s="6" t="n"/>
@@ -38803,17 +40977,25 @@
         <v/>
       </c>
       <c r="AJ275" s="5" t="n"/>
+      <c r="AK275" s="12">
+        <f>IF(B275="","",IF(ISNUMBER(B275),B275,DATE(VALUE(LEFT(B275,4)),VALUE(MID(B275,6,2)),VALUE(MID(B275,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL275" s="12">
+        <f>IF(C275="","",IF(ISNUMBER(C275),C275,DATE(VALUE(LEFT(C275,4)),VALUE(MID(C275,6,2)),VALUE(MID(C275,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="5" t="n"/>
       <c r="D276" s="5">
-        <f>IF(AND(B276&lt;&gt;"",C276&lt;&gt;""),C276-B276+1,"")</f>
+        <f>IF(AND(AK276&lt;&gt;"",AL276&lt;&gt;""),AL276-AK276+1,"")</f>
         <v/>
       </c>
       <c r="E276" s="5">
-        <f>IF(B276&lt;&gt;"",YEAR(B276),"")</f>
+        <f>IF(AK276&lt;&gt;"",YEAR(AK276),"")</f>
         <v/>
       </c>
       <c r="F276" s="6" t="n"/>
@@ -38901,17 +41083,25 @@
         <v/>
       </c>
       <c r="AJ276" s="5" t="n"/>
+      <c r="AK276" s="12">
+        <f>IF(B276="","",IF(ISNUMBER(B276),B276,DATE(VALUE(LEFT(B276,4)),VALUE(MID(B276,6,2)),VALUE(MID(B276,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL276" s="12">
+        <f>IF(C276="","",IF(ISNUMBER(C276),C276,DATE(VALUE(LEFT(C276,4)),VALUE(MID(C276,6,2)),VALUE(MID(C276,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="5" t="n"/>
       <c r="D277" s="5">
-        <f>IF(AND(B277&lt;&gt;"",C277&lt;&gt;""),C277-B277+1,"")</f>
+        <f>IF(AND(AK277&lt;&gt;"",AL277&lt;&gt;""),AL277-AK277+1,"")</f>
         <v/>
       </c>
       <c r="E277" s="5">
-        <f>IF(B277&lt;&gt;"",YEAR(B277),"")</f>
+        <f>IF(AK277&lt;&gt;"",YEAR(AK277),"")</f>
         <v/>
       </c>
       <c r="F277" s="6" t="n"/>
@@ -38999,17 +41189,25 @@
         <v/>
       </c>
       <c r="AJ277" s="5" t="n"/>
+      <c r="AK277" s="12">
+        <f>IF(B277="","",IF(ISNUMBER(B277),B277,DATE(VALUE(LEFT(B277,4)),VALUE(MID(B277,6,2)),VALUE(MID(B277,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL277" s="12">
+        <f>IF(C277="","",IF(ISNUMBER(C277),C277,DATE(VALUE(LEFT(C277,4)),VALUE(MID(C277,6,2)),VALUE(MID(C277,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="5" t="n"/>
       <c r="D278" s="5">
-        <f>IF(AND(B278&lt;&gt;"",C278&lt;&gt;""),C278-B278+1,"")</f>
+        <f>IF(AND(AK278&lt;&gt;"",AL278&lt;&gt;""),AL278-AK278+1,"")</f>
         <v/>
       </c>
       <c r="E278" s="5">
-        <f>IF(B278&lt;&gt;"",YEAR(B278),"")</f>
+        <f>IF(AK278&lt;&gt;"",YEAR(AK278),"")</f>
         <v/>
       </c>
       <c r="F278" s="6" t="n"/>
@@ -39097,17 +41295,25 @@
         <v/>
       </c>
       <c r="AJ278" s="5" t="n"/>
+      <c r="AK278" s="12">
+        <f>IF(B278="","",IF(ISNUMBER(B278),B278,DATE(VALUE(LEFT(B278,4)),VALUE(MID(B278,6,2)),VALUE(MID(B278,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL278" s="12">
+        <f>IF(C278="","",IF(ISNUMBER(C278),C278,DATE(VALUE(LEFT(C278,4)),VALUE(MID(C278,6,2)),VALUE(MID(C278,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="5" t="n"/>
       <c r="D279" s="5">
-        <f>IF(AND(B279&lt;&gt;"",C279&lt;&gt;""),C279-B279+1,"")</f>
+        <f>IF(AND(AK279&lt;&gt;"",AL279&lt;&gt;""),AL279-AK279+1,"")</f>
         <v/>
       </c>
       <c r="E279" s="5">
-        <f>IF(B279&lt;&gt;"",YEAR(B279),"")</f>
+        <f>IF(AK279&lt;&gt;"",YEAR(AK279),"")</f>
         <v/>
       </c>
       <c r="F279" s="6" t="n"/>
@@ -39195,17 +41401,25 @@
         <v/>
       </c>
       <c r="AJ279" s="5" t="n"/>
+      <c r="AK279" s="12">
+        <f>IF(B279="","",IF(ISNUMBER(B279),B279,DATE(VALUE(LEFT(B279,4)),VALUE(MID(B279,6,2)),VALUE(MID(B279,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL279" s="12">
+        <f>IF(C279="","",IF(ISNUMBER(C279),C279,DATE(VALUE(LEFT(C279,4)),VALUE(MID(C279,6,2)),VALUE(MID(C279,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="5" t="n"/>
       <c r="D280" s="5">
-        <f>IF(AND(B280&lt;&gt;"",C280&lt;&gt;""),C280-B280+1,"")</f>
+        <f>IF(AND(AK280&lt;&gt;"",AL280&lt;&gt;""),AL280-AK280+1,"")</f>
         <v/>
       </c>
       <c r="E280" s="5">
-        <f>IF(B280&lt;&gt;"",YEAR(B280),"")</f>
+        <f>IF(AK280&lt;&gt;"",YEAR(AK280),"")</f>
         <v/>
       </c>
       <c r="F280" s="6" t="n"/>
@@ -39293,17 +41507,25 @@
         <v/>
       </c>
       <c r="AJ280" s="5" t="n"/>
+      <c r="AK280" s="12">
+        <f>IF(B280="","",IF(ISNUMBER(B280),B280,DATE(VALUE(LEFT(B280,4)),VALUE(MID(B280,6,2)),VALUE(MID(B280,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL280" s="12">
+        <f>IF(C280="","",IF(ISNUMBER(C280),C280,DATE(VALUE(LEFT(C280,4)),VALUE(MID(C280,6,2)),VALUE(MID(C280,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="5" t="n"/>
       <c r="D281" s="5">
-        <f>IF(AND(B281&lt;&gt;"",C281&lt;&gt;""),C281-B281+1,"")</f>
+        <f>IF(AND(AK281&lt;&gt;"",AL281&lt;&gt;""),AL281-AK281+1,"")</f>
         <v/>
       </c>
       <c r="E281" s="5">
-        <f>IF(B281&lt;&gt;"",YEAR(B281),"")</f>
+        <f>IF(AK281&lt;&gt;"",YEAR(AK281),"")</f>
         <v/>
       </c>
       <c r="F281" s="6" t="n"/>
@@ -39391,17 +41613,25 @@
         <v/>
       </c>
       <c r="AJ281" s="5" t="n"/>
+      <c r="AK281" s="12">
+        <f>IF(B281="","",IF(ISNUMBER(B281),B281,DATE(VALUE(LEFT(B281,4)),VALUE(MID(B281,6,2)),VALUE(MID(B281,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL281" s="12">
+        <f>IF(C281="","",IF(ISNUMBER(C281),C281,DATE(VALUE(LEFT(C281,4)),VALUE(MID(C281,6,2)),VALUE(MID(C281,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="5" t="n"/>
       <c r="D282" s="5">
-        <f>IF(AND(B282&lt;&gt;"",C282&lt;&gt;""),C282-B282+1,"")</f>
+        <f>IF(AND(AK282&lt;&gt;"",AL282&lt;&gt;""),AL282-AK282+1,"")</f>
         <v/>
       </c>
       <c r="E282" s="5">
-        <f>IF(B282&lt;&gt;"",YEAR(B282),"")</f>
+        <f>IF(AK282&lt;&gt;"",YEAR(AK282),"")</f>
         <v/>
       </c>
       <c r="F282" s="6" t="n"/>
@@ -39489,17 +41719,25 @@
         <v/>
       </c>
       <c r="AJ282" s="5" t="n"/>
+      <c r="AK282" s="12">
+        <f>IF(B282="","",IF(ISNUMBER(B282),B282,DATE(VALUE(LEFT(B282,4)),VALUE(MID(B282,6,2)),VALUE(MID(B282,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL282" s="12">
+        <f>IF(C282="","",IF(ISNUMBER(C282),C282,DATE(VALUE(LEFT(C282,4)),VALUE(MID(C282,6,2)),VALUE(MID(C282,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="5" t="n"/>
       <c r="D283" s="5">
-        <f>IF(AND(B283&lt;&gt;"",C283&lt;&gt;""),C283-B283+1,"")</f>
+        <f>IF(AND(AK283&lt;&gt;"",AL283&lt;&gt;""),AL283-AK283+1,"")</f>
         <v/>
       </c>
       <c r="E283" s="5">
-        <f>IF(B283&lt;&gt;"",YEAR(B283),"")</f>
+        <f>IF(AK283&lt;&gt;"",YEAR(AK283),"")</f>
         <v/>
       </c>
       <c r="F283" s="6" t="n"/>
@@ -39587,17 +41825,25 @@
         <v/>
       </c>
       <c r="AJ283" s="5" t="n"/>
+      <c r="AK283" s="12">
+        <f>IF(B283="","",IF(ISNUMBER(B283),B283,DATE(VALUE(LEFT(B283,4)),VALUE(MID(B283,6,2)),VALUE(MID(B283,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL283" s="12">
+        <f>IF(C283="","",IF(ISNUMBER(C283),C283,DATE(VALUE(LEFT(C283,4)),VALUE(MID(C283,6,2)),VALUE(MID(C283,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="5" t="n"/>
       <c r="D284" s="5">
-        <f>IF(AND(B284&lt;&gt;"",C284&lt;&gt;""),C284-B284+1,"")</f>
+        <f>IF(AND(AK284&lt;&gt;"",AL284&lt;&gt;""),AL284-AK284+1,"")</f>
         <v/>
       </c>
       <c r="E284" s="5">
-        <f>IF(B284&lt;&gt;"",YEAR(B284),"")</f>
+        <f>IF(AK284&lt;&gt;"",YEAR(AK284),"")</f>
         <v/>
       </c>
       <c r="F284" s="6" t="n"/>
@@ -39685,17 +41931,25 @@
         <v/>
       </c>
       <c r="AJ284" s="5" t="n"/>
+      <c r="AK284" s="12">
+        <f>IF(B284="","",IF(ISNUMBER(B284),B284,DATE(VALUE(LEFT(B284,4)),VALUE(MID(B284,6,2)),VALUE(MID(B284,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL284" s="12">
+        <f>IF(C284="","",IF(ISNUMBER(C284),C284,DATE(VALUE(LEFT(C284,4)),VALUE(MID(C284,6,2)),VALUE(MID(C284,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="5" t="n"/>
       <c r="D285" s="5">
-        <f>IF(AND(B285&lt;&gt;"",C285&lt;&gt;""),C285-B285+1,"")</f>
+        <f>IF(AND(AK285&lt;&gt;"",AL285&lt;&gt;""),AL285-AK285+1,"")</f>
         <v/>
       </c>
       <c r="E285" s="5">
-        <f>IF(B285&lt;&gt;"",YEAR(B285),"")</f>
+        <f>IF(AK285&lt;&gt;"",YEAR(AK285),"")</f>
         <v/>
       </c>
       <c r="F285" s="6" t="n"/>
@@ -39783,17 +42037,25 @@
         <v/>
       </c>
       <c r="AJ285" s="5" t="n"/>
+      <c r="AK285" s="12">
+        <f>IF(B285="","",IF(ISNUMBER(B285),B285,DATE(VALUE(LEFT(B285,4)),VALUE(MID(B285,6,2)),VALUE(MID(B285,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL285" s="12">
+        <f>IF(C285="","",IF(ISNUMBER(C285),C285,DATE(VALUE(LEFT(C285,4)),VALUE(MID(C285,6,2)),VALUE(MID(C285,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="5" t="n"/>
       <c r="D286" s="5">
-        <f>IF(AND(B286&lt;&gt;"",C286&lt;&gt;""),C286-B286+1,"")</f>
+        <f>IF(AND(AK286&lt;&gt;"",AL286&lt;&gt;""),AL286-AK286+1,"")</f>
         <v/>
       </c>
       <c r="E286" s="5">
-        <f>IF(B286&lt;&gt;"",YEAR(B286),"")</f>
+        <f>IF(AK286&lt;&gt;"",YEAR(AK286),"")</f>
         <v/>
       </c>
       <c r="F286" s="6" t="n"/>
@@ -39881,17 +42143,25 @@
         <v/>
       </c>
       <c r="AJ286" s="5" t="n"/>
+      <c r="AK286" s="12">
+        <f>IF(B286="","",IF(ISNUMBER(B286),B286,DATE(VALUE(LEFT(B286,4)),VALUE(MID(B286,6,2)),VALUE(MID(B286,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL286" s="12">
+        <f>IF(C286="","",IF(ISNUMBER(C286),C286,DATE(VALUE(LEFT(C286,4)),VALUE(MID(C286,6,2)),VALUE(MID(C286,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="5" t="n"/>
       <c r="D287" s="5">
-        <f>IF(AND(B287&lt;&gt;"",C287&lt;&gt;""),C287-B287+1,"")</f>
+        <f>IF(AND(AK287&lt;&gt;"",AL287&lt;&gt;""),AL287-AK287+1,"")</f>
         <v/>
       </c>
       <c r="E287" s="5">
-        <f>IF(B287&lt;&gt;"",YEAR(B287),"")</f>
+        <f>IF(AK287&lt;&gt;"",YEAR(AK287),"")</f>
         <v/>
       </c>
       <c r="F287" s="6" t="n"/>
@@ -39979,17 +42249,25 @@
         <v/>
       </c>
       <c r="AJ287" s="5" t="n"/>
+      <c r="AK287" s="12">
+        <f>IF(B287="","",IF(ISNUMBER(B287),B287,DATE(VALUE(LEFT(B287,4)),VALUE(MID(B287,6,2)),VALUE(MID(B287,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL287" s="12">
+        <f>IF(C287="","",IF(ISNUMBER(C287),C287,DATE(VALUE(LEFT(C287,4)),VALUE(MID(C287,6,2)),VALUE(MID(C287,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="5" t="n"/>
       <c r="D288" s="5">
-        <f>IF(AND(B288&lt;&gt;"",C288&lt;&gt;""),C288-B288+1,"")</f>
+        <f>IF(AND(AK288&lt;&gt;"",AL288&lt;&gt;""),AL288-AK288+1,"")</f>
         <v/>
       </c>
       <c r="E288" s="5">
-        <f>IF(B288&lt;&gt;"",YEAR(B288),"")</f>
+        <f>IF(AK288&lt;&gt;"",YEAR(AK288),"")</f>
         <v/>
       </c>
       <c r="F288" s="6" t="n"/>
@@ -40077,17 +42355,25 @@
         <v/>
       </c>
       <c r="AJ288" s="5" t="n"/>
+      <c r="AK288" s="12">
+        <f>IF(B288="","",IF(ISNUMBER(B288),B288,DATE(VALUE(LEFT(B288,4)),VALUE(MID(B288,6,2)),VALUE(MID(B288,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL288" s="12">
+        <f>IF(C288="","",IF(ISNUMBER(C288),C288,DATE(VALUE(LEFT(C288,4)),VALUE(MID(C288,6,2)),VALUE(MID(C288,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="5" t="n"/>
       <c r="D289" s="5">
-        <f>IF(AND(B289&lt;&gt;"",C289&lt;&gt;""),C289-B289+1,"")</f>
+        <f>IF(AND(AK289&lt;&gt;"",AL289&lt;&gt;""),AL289-AK289+1,"")</f>
         <v/>
       </c>
       <c r="E289" s="5">
-        <f>IF(B289&lt;&gt;"",YEAR(B289),"")</f>
+        <f>IF(AK289&lt;&gt;"",YEAR(AK289),"")</f>
         <v/>
       </c>
       <c r="F289" s="6" t="n"/>
@@ -40175,17 +42461,25 @@
         <v/>
       </c>
       <c r="AJ289" s="5" t="n"/>
+      <c r="AK289" s="12">
+        <f>IF(B289="","",IF(ISNUMBER(B289),B289,DATE(VALUE(LEFT(B289,4)),VALUE(MID(B289,6,2)),VALUE(MID(B289,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL289" s="12">
+        <f>IF(C289="","",IF(ISNUMBER(C289),C289,DATE(VALUE(LEFT(C289,4)),VALUE(MID(C289,6,2)),VALUE(MID(C289,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="5" t="n"/>
       <c r="D290" s="5">
-        <f>IF(AND(B290&lt;&gt;"",C290&lt;&gt;""),C290-B290+1,"")</f>
+        <f>IF(AND(AK290&lt;&gt;"",AL290&lt;&gt;""),AL290-AK290+1,"")</f>
         <v/>
       </c>
       <c r="E290" s="5">
-        <f>IF(B290&lt;&gt;"",YEAR(B290),"")</f>
+        <f>IF(AK290&lt;&gt;"",YEAR(AK290),"")</f>
         <v/>
       </c>
       <c r="F290" s="6" t="n"/>
@@ -40273,17 +42567,25 @@
         <v/>
       </c>
       <c r="AJ290" s="5" t="n"/>
+      <c r="AK290" s="12">
+        <f>IF(B290="","",IF(ISNUMBER(B290),B290,DATE(VALUE(LEFT(B290,4)),VALUE(MID(B290,6,2)),VALUE(MID(B290,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL290" s="12">
+        <f>IF(C290="","",IF(ISNUMBER(C290),C290,DATE(VALUE(LEFT(C290,4)),VALUE(MID(C290,6,2)),VALUE(MID(C290,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="5" t="n"/>
       <c r="D291" s="5">
-        <f>IF(AND(B291&lt;&gt;"",C291&lt;&gt;""),C291-B291+1,"")</f>
+        <f>IF(AND(AK291&lt;&gt;"",AL291&lt;&gt;""),AL291-AK291+1,"")</f>
         <v/>
       </c>
       <c r="E291" s="5">
-        <f>IF(B291&lt;&gt;"",YEAR(B291),"")</f>
+        <f>IF(AK291&lt;&gt;"",YEAR(AK291),"")</f>
         <v/>
       </c>
       <c r="F291" s="6" t="n"/>
@@ -40371,17 +42673,25 @@
         <v/>
       </c>
       <c r="AJ291" s="5" t="n"/>
+      <c r="AK291" s="12">
+        <f>IF(B291="","",IF(ISNUMBER(B291),B291,DATE(VALUE(LEFT(B291,4)),VALUE(MID(B291,6,2)),VALUE(MID(B291,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL291" s="12">
+        <f>IF(C291="","",IF(ISNUMBER(C291),C291,DATE(VALUE(LEFT(C291,4)),VALUE(MID(C291,6,2)),VALUE(MID(C291,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="5" t="n"/>
       <c r="D292" s="5">
-        <f>IF(AND(B292&lt;&gt;"",C292&lt;&gt;""),C292-B292+1,"")</f>
+        <f>IF(AND(AK292&lt;&gt;"",AL292&lt;&gt;""),AL292-AK292+1,"")</f>
         <v/>
       </c>
       <c r="E292" s="5">
-        <f>IF(B292&lt;&gt;"",YEAR(B292),"")</f>
+        <f>IF(AK292&lt;&gt;"",YEAR(AK292),"")</f>
         <v/>
       </c>
       <c r="F292" s="6" t="n"/>
@@ -40469,17 +42779,25 @@
         <v/>
       </c>
       <c r="AJ292" s="5" t="n"/>
+      <c r="AK292" s="12">
+        <f>IF(B292="","",IF(ISNUMBER(B292),B292,DATE(VALUE(LEFT(B292,4)),VALUE(MID(B292,6,2)),VALUE(MID(B292,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL292" s="12">
+        <f>IF(C292="","",IF(ISNUMBER(C292),C292,DATE(VALUE(LEFT(C292,4)),VALUE(MID(C292,6,2)),VALUE(MID(C292,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="5" t="n"/>
       <c r="D293" s="5">
-        <f>IF(AND(B293&lt;&gt;"",C293&lt;&gt;""),C293-B293+1,"")</f>
+        <f>IF(AND(AK293&lt;&gt;"",AL293&lt;&gt;""),AL293-AK293+1,"")</f>
         <v/>
       </c>
       <c r="E293" s="5">
-        <f>IF(B293&lt;&gt;"",YEAR(B293),"")</f>
+        <f>IF(AK293&lt;&gt;"",YEAR(AK293),"")</f>
         <v/>
       </c>
       <c r="F293" s="6" t="n"/>
@@ -40567,17 +42885,25 @@
         <v/>
       </c>
       <c r="AJ293" s="5" t="n"/>
+      <c r="AK293" s="12">
+        <f>IF(B293="","",IF(ISNUMBER(B293),B293,DATE(VALUE(LEFT(B293,4)),VALUE(MID(B293,6,2)),VALUE(MID(B293,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL293" s="12">
+        <f>IF(C293="","",IF(ISNUMBER(C293),C293,DATE(VALUE(LEFT(C293,4)),VALUE(MID(C293,6,2)),VALUE(MID(C293,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="5" t="n"/>
       <c r="D294" s="5">
-        <f>IF(AND(B294&lt;&gt;"",C294&lt;&gt;""),C294-B294+1,"")</f>
+        <f>IF(AND(AK294&lt;&gt;"",AL294&lt;&gt;""),AL294-AK294+1,"")</f>
         <v/>
       </c>
       <c r="E294" s="5">
-        <f>IF(B294&lt;&gt;"",YEAR(B294),"")</f>
+        <f>IF(AK294&lt;&gt;"",YEAR(AK294),"")</f>
         <v/>
       </c>
       <c r="F294" s="6" t="n"/>
@@ -40665,17 +42991,25 @@
         <v/>
       </c>
       <c r="AJ294" s="5" t="n"/>
+      <c r="AK294" s="12">
+        <f>IF(B294="","",IF(ISNUMBER(B294),B294,DATE(VALUE(LEFT(B294,4)),VALUE(MID(B294,6,2)),VALUE(MID(B294,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL294" s="12">
+        <f>IF(C294="","",IF(ISNUMBER(C294),C294,DATE(VALUE(LEFT(C294,4)),VALUE(MID(C294,6,2)),VALUE(MID(C294,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="5" t="n"/>
       <c r="D295" s="5">
-        <f>IF(AND(B295&lt;&gt;"",C295&lt;&gt;""),C295-B295+1,"")</f>
+        <f>IF(AND(AK295&lt;&gt;"",AL295&lt;&gt;""),AL295-AK295+1,"")</f>
         <v/>
       </c>
       <c r="E295" s="5">
-        <f>IF(B295&lt;&gt;"",YEAR(B295),"")</f>
+        <f>IF(AK295&lt;&gt;"",YEAR(AK295),"")</f>
         <v/>
       </c>
       <c r="F295" s="6" t="n"/>
@@ -40763,17 +43097,25 @@
         <v/>
       </c>
       <c r="AJ295" s="5" t="n"/>
+      <c r="AK295" s="12">
+        <f>IF(B295="","",IF(ISNUMBER(B295),B295,DATE(VALUE(LEFT(B295,4)),VALUE(MID(B295,6,2)),VALUE(MID(B295,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL295" s="12">
+        <f>IF(C295="","",IF(ISNUMBER(C295),C295,DATE(VALUE(LEFT(C295,4)),VALUE(MID(C295,6,2)),VALUE(MID(C295,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="5" t="n"/>
       <c r="D296" s="5">
-        <f>IF(AND(B296&lt;&gt;"",C296&lt;&gt;""),C296-B296+1,"")</f>
+        <f>IF(AND(AK296&lt;&gt;"",AL296&lt;&gt;""),AL296-AK296+1,"")</f>
         <v/>
       </c>
       <c r="E296" s="5">
-        <f>IF(B296&lt;&gt;"",YEAR(B296),"")</f>
+        <f>IF(AK296&lt;&gt;"",YEAR(AK296),"")</f>
         <v/>
       </c>
       <c r="F296" s="6" t="n"/>
@@ -40861,17 +43203,25 @@
         <v/>
       </c>
       <c r="AJ296" s="5" t="n"/>
+      <c r="AK296" s="12">
+        <f>IF(B296="","",IF(ISNUMBER(B296),B296,DATE(VALUE(LEFT(B296,4)),VALUE(MID(B296,6,2)),VALUE(MID(B296,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL296" s="12">
+        <f>IF(C296="","",IF(ISNUMBER(C296),C296,DATE(VALUE(LEFT(C296,4)),VALUE(MID(C296,6,2)),VALUE(MID(C296,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="5" t="n"/>
       <c r="D297" s="5">
-        <f>IF(AND(B297&lt;&gt;"",C297&lt;&gt;""),C297-B297+1,"")</f>
+        <f>IF(AND(AK297&lt;&gt;"",AL297&lt;&gt;""),AL297-AK297+1,"")</f>
         <v/>
       </c>
       <c r="E297" s="5">
-        <f>IF(B297&lt;&gt;"",YEAR(B297),"")</f>
+        <f>IF(AK297&lt;&gt;"",YEAR(AK297),"")</f>
         <v/>
       </c>
       <c r="F297" s="6" t="n"/>
@@ -40959,17 +43309,25 @@
         <v/>
       </c>
       <c r="AJ297" s="5" t="n"/>
+      <c r="AK297" s="12">
+        <f>IF(B297="","",IF(ISNUMBER(B297),B297,DATE(VALUE(LEFT(B297,4)),VALUE(MID(B297,6,2)),VALUE(MID(B297,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL297" s="12">
+        <f>IF(C297="","",IF(ISNUMBER(C297),C297,DATE(VALUE(LEFT(C297,4)),VALUE(MID(C297,6,2)),VALUE(MID(C297,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="5" t="n"/>
       <c r="D298" s="5">
-        <f>IF(AND(B298&lt;&gt;"",C298&lt;&gt;""),C298-B298+1,"")</f>
+        <f>IF(AND(AK298&lt;&gt;"",AL298&lt;&gt;""),AL298-AK298+1,"")</f>
         <v/>
       </c>
       <c r="E298" s="5">
-        <f>IF(B298&lt;&gt;"",YEAR(B298),"")</f>
+        <f>IF(AK298&lt;&gt;"",YEAR(AK298),"")</f>
         <v/>
       </c>
       <c r="F298" s="6" t="n"/>
@@ -41057,17 +43415,25 @@
         <v/>
       </c>
       <c r="AJ298" s="5" t="n"/>
+      <c r="AK298" s="12">
+        <f>IF(B298="","",IF(ISNUMBER(B298),B298,DATE(VALUE(LEFT(B298,4)),VALUE(MID(B298,6,2)),VALUE(MID(B298,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL298" s="12">
+        <f>IF(C298="","",IF(ISNUMBER(C298),C298,DATE(VALUE(LEFT(C298,4)),VALUE(MID(C298,6,2)),VALUE(MID(C298,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="5" t="n"/>
       <c r="D299" s="5">
-        <f>IF(AND(B299&lt;&gt;"",C299&lt;&gt;""),C299-B299+1,"")</f>
+        <f>IF(AND(AK299&lt;&gt;"",AL299&lt;&gt;""),AL299-AK299+1,"")</f>
         <v/>
       </c>
       <c r="E299" s="5">
-        <f>IF(B299&lt;&gt;"",YEAR(B299),"")</f>
+        <f>IF(AK299&lt;&gt;"",YEAR(AK299),"")</f>
         <v/>
       </c>
       <c r="F299" s="6" t="n"/>
@@ -41155,17 +43521,25 @@
         <v/>
       </c>
       <c r="AJ299" s="5" t="n"/>
+      <c r="AK299" s="12">
+        <f>IF(B299="","",IF(ISNUMBER(B299),B299,DATE(VALUE(LEFT(B299,4)),VALUE(MID(B299,6,2)),VALUE(MID(B299,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL299" s="12">
+        <f>IF(C299="","",IF(ISNUMBER(C299),C299,DATE(VALUE(LEFT(C299,4)),VALUE(MID(C299,6,2)),VALUE(MID(C299,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="5" t="n"/>
       <c r="D300" s="5">
-        <f>IF(AND(B300&lt;&gt;"",C300&lt;&gt;""),C300-B300+1,"")</f>
+        <f>IF(AND(AK300&lt;&gt;"",AL300&lt;&gt;""),AL300-AK300+1,"")</f>
         <v/>
       </c>
       <c r="E300" s="5">
-        <f>IF(B300&lt;&gt;"",YEAR(B300),"")</f>
+        <f>IF(AK300&lt;&gt;"",YEAR(AK300),"")</f>
         <v/>
       </c>
       <c r="F300" s="6" t="n"/>
@@ -41253,17 +43627,25 @@
         <v/>
       </c>
       <c r="AJ300" s="5" t="n"/>
+      <c r="AK300" s="12">
+        <f>IF(B300="","",IF(ISNUMBER(B300),B300,DATE(VALUE(LEFT(B300,4)),VALUE(MID(B300,6,2)),VALUE(MID(B300,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL300" s="12">
+        <f>IF(C300="","",IF(ISNUMBER(C300),C300,DATE(VALUE(LEFT(C300,4)),VALUE(MID(C300,6,2)),VALUE(MID(C300,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="5" t="n"/>
       <c r="D301" s="5">
-        <f>IF(AND(B301&lt;&gt;"",C301&lt;&gt;""),C301-B301+1,"")</f>
+        <f>IF(AND(AK301&lt;&gt;"",AL301&lt;&gt;""),AL301-AK301+1,"")</f>
         <v/>
       </c>
       <c r="E301" s="5">
-        <f>IF(B301&lt;&gt;"",YEAR(B301),"")</f>
+        <f>IF(AK301&lt;&gt;"",YEAR(AK301),"")</f>
         <v/>
       </c>
       <c r="F301" s="6" t="n"/>
@@ -41351,17 +43733,25 @@
         <v/>
       </c>
       <c r="AJ301" s="5" t="n"/>
+      <c r="AK301" s="12">
+        <f>IF(B301="","",IF(ISNUMBER(B301),B301,DATE(VALUE(LEFT(B301,4)),VALUE(MID(B301,6,2)),VALUE(MID(B301,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL301" s="12">
+        <f>IF(C301="","",IF(ISNUMBER(C301),C301,DATE(VALUE(LEFT(C301,4)),VALUE(MID(C301,6,2)),VALUE(MID(C301,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="5" t="n"/>
       <c r="D302" s="5">
-        <f>IF(AND(B302&lt;&gt;"",C302&lt;&gt;""),C302-B302+1,"")</f>
+        <f>IF(AND(AK302&lt;&gt;"",AL302&lt;&gt;""),AL302-AK302+1,"")</f>
         <v/>
       </c>
       <c r="E302" s="5">
-        <f>IF(B302&lt;&gt;"",YEAR(B302),"")</f>
+        <f>IF(AK302&lt;&gt;"",YEAR(AK302),"")</f>
         <v/>
       </c>
       <c r="F302" s="6" t="n"/>
@@ -41449,17 +43839,25 @@
         <v/>
       </c>
       <c r="AJ302" s="5" t="n"/>
+      <c r="AK302" s="12">
+        <f>IF(B302="","",IF(ISNUMBER(B302),B302,DATE(VALUE(LEFT(B302,4)),VALUE(MID(B302,6,2)),VALUE(MID(B302,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL302" s="12">
+        <f>IF(C302="","",IF(ISNUMBER(C302),C302,DATE(VALUE(LEFT(C302,4)),VALUE(MID(C302,6,2)),VALUE(MID(C302,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="5" t="n"/>
       <c r="D303" s="5">
-        <f>IF(AND(B303&lt;&gt;"",C303&lt;&gt;""),C303-B303+1,"")</f>
+        <f>IF(AND(AK303&lt;&gt;"",AL303&lt;&gt;""),AL303-AK303+1,"")</f>
         <v/>
       </c>
       <c r="E303" s="5">
-        <f>IF(B303&lt;&gt;"",YEAR(B303),"")</f>
+        <f>IF(AK303&lt;&gt;"",YEAR(AK303),"")</f>
         <v/>
       </c>
       <c r="F303" s="6" t="n"/>
@@ -41547,17 +43945,25 @@
         <v/>
       </c>
       <c r="AJ303" s="5" t="n"/>
+      <c r="AK303" s="12">
+        <f>IF(B303="","",IF(ISNUMBER(B303),B303,DATE(VALUE(LEFT(B303,4)),VALUE(MID(B303,6,2)),VALUE(MID(B303,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL303" s="12">
+        <f>IF(C303="","",IF(ISNUMBER(C303),C303,DATE(VALUE(LEFT(C303,4)),VALUE(MID(C303,6,2)),VALUE(MID(C303,9,2)))))</f>
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="5" t="n"/>
       <c r="D304" s="5">
-        <f>IF(AND(B304&lt;&gt;"",C304&lt;&gt;""),C304-B304+1,"")</f>
+        <f>IF(AND(AK304&lt;&gt;"",AL304&lt;&gt;""),AL304-AK304+1,"")</f>
         <v/>
       </c>
       <c r="E304" s="5">
-        <f>IF(B304&lt;&gt;"",YEAR(B304),"")</f>
+        <f>IF(AK304&lt;&gt;"",YEAR(AK304),"")</f>
         <v/>
       </c>
       <c r="F304" s="6" t="n"/>
@@ -41645,9 +44051,17 @@
         <v/>
       </c>
       <c r="AJ304" s="5" t="n"/>
+      <c r="AK304" s="12">
+        <f>IF(B304="","",IF(ISNUMBER(B304),B304,DATE(VALUE(LEFT(B304,4)),VALUE(MID(B304,6,2)),VALUE(MID(B304,9,2)))))</f>
+        <v/>
+      </c>
+      <c r="AL304" s="12">
+        <f>IF(C304="","",IF(ISNUMBER(C304),C304,DATE(VALUE(LEFT(C304,4)),VALUE(MID(C304,6,2)),VALUE(MID(C304,9,2)))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AJ304"/>
+  <autoFilter ref="A4:AL304"/>
   <conditionalFormatting sqref="AB5:AB304">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AB5="X"</formula>

--- a/solutions/tools/tvSearch/idovonal/szolgalatiIdok.xlsx
+++ b/solutions/tools/tvSearch/idovonal/szolgalatiIdok.xlsx
@@ -9418,7 +9418,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Gyermekes jogcím.</t>
+          <t>Gyermekes jogcím. 1998.01.01 ELŐTT: alanyi jogú biztosítás – szolgálati idő elfogadható, bér/járulék NEM vizsgálható (elfogadott_bér = 0). 1998.01.01-TŐL: nyugdíjjárulék levonásra kerül a GYES összegéből → járulékalap elfogadható.</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12399,7 @@
         <v/>
       </c>
       <c r="AH5" s="6">
-        <f>IF(S5="","",IF(OR(I5=0,V5="IGEN",W5="IGEN"),0,IF(AND(K5&lt;&gt;"IGEN",L5="IGEN",U5="NEM"),0,S5)))</f>
+        <f>IF(S5="","",IF(OR(I5=0,V5="IGEN",W5="IGEN"),0,IF(AND(K5&lt;&gt;"IGEN",L5="IGEN",U5="NEM"),0,IF(AND(H5="GYES",E5&lt;1998),0,S5))))</f>
         <v/>
       </c>
       <c r="AI5" s="6">
@@ -12519,7 +12519,7 @@
         <v/>
       </c>
       <c r="AH6" s="6">
-        <f>IF(S6="","",IF(OR(I6=0,V6="IGEN",W6="IGEN"),0,IF(AND(K6&lt;&gt;"IGEN",L6="IGEN",U6="NEM"),0,S6)))</f>
+        <f>IF(S6="","",IF(OR(I6=0,V6="IGEN",W6="IGEN"),0,IF(AND(K6&lt;&gt;"IGEN",L6="IGEN",U6="NEM"),0,IF(AND(H6="GYES",E6&lt;1998),0,S6))))</f>
         <v/>
       </c>
       <c r="AI6" s="6">
@@ -12639,7 +12639,7 @@
         <v/>
       </c>
       <c r="AH7" s="6">
-        <f>IF(S7="","",IF(OR(I7=0,V7="IGEN",W7="IGEN"),0,IF(AND(K7&lt;&gt;"IGEN",L7="IGEN",U7="NEM"),0,S7)))</f>
+        <f>IF(S7="","",IF(OR(I7=0,V7="IGEN",W7="IGEN"),0,IF(AND(K7&lt;&gt;"IGEN",L7="IGEN",U7="NEM"),0,IF(AND(H7="GYES",E7&lt;1998),0,S7))))</f>
         <v/>
       </c>
       <c r="AI7" s="6">
@@ -12759,7 +12759,7 @@
         <v/>
       </c>
       <c r="AH8" s="6">
-        <f>IF(S8="","",IF(OR(I8=0,V8="IGEN",W8="IGEN"),0,IF(AND(K8&lt;&gt;"IGEN",L8="IGEN",U8="NEM"),0,S8)))</f>
+        <f>IF(S8="","",IF(OR(I8=0,V8="IGEN",W8="IGEN"),0,IF(AND(K8&lt;&gt;"IGEN",L8="IGEN",U8="NEM"),0,IF(AND(H8="GYES",E8&lt;1998),0,S8))))</f>
         <v/>
       </c>
       <c r="AI8" s="6">
@@ -12879,7 +12879,7 @@
         <v/>
       </c>
       <c r="AH9" s="6">
-        <f>IF(S9="","",IF(OR(I9=0,V9="IGEN",W9="IGEN"),0,IF(AND(K9&lt;&gt;"IGEN",L9="IGEN",U9="NEM"),0,S9)))</f>
+        <f>IF(S9="","",IF(OR(I9=0,V9="IGEN",W9="IGEN"),0,IF(AND(K9&lt;&gt;"IGEN",L9="IGEN",U9="NEM"),0,IF(AND(H9="GYES",E9&lt;1998),0,S9))))</f>
         <v/>
       </c>
       <c r="AI9" s="6">
@@ -12999,7 +12999,7 @@
         <v/>
       </c>
       <c r="AH10" s="6">
-        <f>IF(S10="","",IF(OR(I10=0,V10="IGEN",W10="IGEN"),0,IF(AND(K10&lt;&gt;"IGEN",L10="IGEN",U10="NEM"),0,S10)))</f>
+        <f>IF(S10="","",IF(OR(I10=0,V10="IGEN",W10="IGEN"),0,IF(AND(K10&lt;&gt;"IGEN",L10="IGEN",U10="NEM"),0,IF(AND(H10="GYES",E10&lt;1998),0,S10))))</f>
         <v/>
       </c>
       <c r="AI10" s="6">
@@ -13119,7 +13119,7 @@
         <v/>
       </c>
       <c r="AH11" s="6">
-        <f>IF(S11="","",IF(OR(I11=0,V11="IGEN",W11="IGEN"),0,IF(AND(K11&lt;&gt;"IGEN",L11="IGEN",U11="NEM"),0,S11)))</f>
+        <f>IF(S11="","",IF(OR(I11=0,V11="IGEN",W11="IGEN"),0,IF(AND(K11&lt;&gt;"IGEN",L11="IGEN",U11="NEM"),0,IF(AND(H11="GYES",E11&lt;1998),0,S11))))</f>
         <v/>
       </c>
       <c r="AI11" s="6">
@@ -13239,7 +13239,7 @@
         <v/>
       </c>
       <c r="AH12" s="6">
-        <f>IF(S12="","",IF(OR(I12=0,V12="IGEN",W12="IGEN"),0,IF(AND(K12&lt;&gt;"IGEN",L12="IGEN",U12="NEM"),0,S12)))</f>
+        <f>IF(S12="","",IF(OR(I12=0,V12="IGEN",W12="IGEN"),0,IF(AND(K12&lt;&gt;"IGEN",L12="IGEN",U12="NEM"),0,IF(AND(H12="GYES",E12&lt;1998),0,S12))))</f>
         <v/>
       </c>
       <c r="AI12" s="6">
@@ -13359,7 +13359,7 @@
         <v/>
       </c>
       <c r="AH13" s="6">
-        <f>IF(S13="","",IF(OR(I13=0,V13="IGEN",W13="IGEN"),0,IF(AND(K13&lt;&gt;"IGEN",L13="IGEN",U13="NEM"),0,S13)))</f>
+        <f>IF(S13="","",IF(OR(I13=0,V13="IGEN",W13="IGEN"),0,IF(AND(K13&lt;&gt;"IGEN",L13="IGEN",U13="NEM"),0,IF(AND(H13="GYES",E13&lt;1998),0,S13))))</f>
         <v/>
       </c>
       <c r="AI13" s="6">
@@ -13479,7 +13479,7 @@
         <v/>
       </c>
       <c r="AH14" s="6">
-        <f>IF(S14="","",IF(OR(I14=0,V14="IGEN",W14="IGEN"),0,IF(AND(K14&lt;&gt;"IGEN",L14="IGEN",U14="NEM"),0,S14)))</f>
+        <f>IF(S14="","",IF(OR(I14=0,V14="IGEN",W14="IGEN"),0,IF(AND(K14&lt;&gt;"IGEN",L14="IGEN",U14="NEM"),0,IF(AND(H14="GYES",E14&lt;1998),0,S14))))</f>
         <v/>
       </c>
       <c r="AI14" s="6">
@@ -13599,7 +13599,7 @@
         <v/>
       </c>
       <c r="AH15" s="6">
-        <f>IF(S15="","",IF(OR(I15=0,V15="IGEN",W15="IGEN"),0,IF(AND(K15&lt;&gt;"IGEN",L15="IGEN",U15="NEM"),0,S15)))</f>
+        <f>IF(S15="","",IF(OR(I15=0,V15="IGEN",W15="IGEN"),0,IF(AND(K15&lt;&gt;"IGEN",L15="IGEN",U15="NEM"),0,IF(AND(H15="GYES",E15&lt;1998),0,S15))))</f>
         <v/>
       </c>
       <c r="AI15" s="6">
@@ -13719,7 +13719,7 @@
         <v/>
       </c>
       <c r="AH16" s="6">
-        <f>IF(S16="","",IF(OR(I16=0,V16="IGEN",W16="IGEN"),0,IF(AND(K16&lt;&gt;"IGEN",L16="IGEN",U16="NEM"),0,S16)))</f>
+        <f>IF(S16="","",IF(OR(I16=0,V16="IGEN",W16="IGEN"),0,IF(AND(K16&lt;&gt;"IGEN",L16="IGEN",U16="NEM"),0,IF(AND(H16="GYES",E16&lt;1998),0,S16))))</f>
         <v/>
       </c>
       <c r="AI16" s="6">
@@ -13839,7 +13839,7 @@
         <v/>
       </c>
       <c r="AH17" s="6">
-        <f>IF(S17="","",IF(OR(I17=0,V17="IGEN",W17="IGEN"),0,IF(AND(K17&lt;&gt;"IGEN",L17="IGEN",U17="NEM"),0,S17)))</f>
+        <f>IF(S17="","",IF(OR(I17=0,V17="IGEN",W17="IGEN"),0,IF(AND(K17&lt;&gt;"IGEN",L17="IGEN",U17="NEM"),0,IF(AND(H17="GYES",E17&lt;1998),0,S17))))</f>
         <v/>
       </c>
       <c r="AI17" s="6">
@@ -13959,7 +13959,7 @@
         <v/>
       </c>
       <c r="AH18" s="6">
-        <f>IF(S18="","",IF(OR(I18=0,V18="IGEN",W18="IGEN"),0,IF(AND(K18&lt;&gt;"IGEN",L18="IGEN",U18="NEM"),0,S18)))</f>
+        <f>IF(S18="","",IF(OR(I18=0,V18="IGEN",W18="IGEN"),0,IF(AND(K18&lt;&gt;"IGEN",L18="IGEN",U18="NEM"),0,IF(AND(H18="GYES",E18&lt;1998),0,S18))))</f>
         <v/>
       </c>
       <c r="AI18" s="6">
@@ -14079,7 +14079,7 @@
         <v/>
       </c>
       <c r="AH19" s="6">
-        <f>IF(S19="","",IF(OR(I19=0,V19="IGEN",W19="IGEN"),0,IF(AND(K19&lt;&gt;"IGEN",L19="IGEN",U19="NEM"),0,S19)))</f>
+        <f>IF(S19="","",IF(OR(I19=0,V19="IGEN",W19="IGEN"),0,IF(AND(K19&lt;&gt;"IGEN",L19="IGEN",U19="NEM"),0,IF(AND(H19="GYES",E19&lt;1998),0,S19))))</f>
         <v/>
       </c>
       <c r="AI19" s="6">
@@ -14199,7 +14199,7 @@
         <v/>
       </c>
       <c r="AH20" s="6">
-        <f>IF(S20="","",IF(OR(I20=0,V20="IGEN",W20="IGEN"),0,IF(AND(K20&lt;&gt;"IGEN",L20="IGEN",U20="NEM"),0,S20)))</f>
+        <f>IF(S20="","",IF(OR(I20=0,V20="IGEN",W20="IGEN"),0,IF(AND(K20&lt;&gt;"IGEN",L20="IGEN",U20="NEM"),0,IF(AND(H20="GYES",E20&lt;1998),0,S20))))</f>
         <v/>
       </c>
       <c r="AI20" s="6">
@@ -14319,7 +14319,7 @@
         <v/>
       </c>
       <c r="AH21" s="6">
-        <f>IF(S21="","",IF(OR(I21=0,V21="IGEN",W21="IGEN"),0,IF(AND(K21&lt;&gt;"IGEN",L21="IGEN",U21="NEM"),0,S21)))</f>
+        <f>IF(S21="","",IF(OR(I21=0,V21="IGEN",W21="IGEN"),0,IF(AND(K21&lt;&gt;"IGEN",L21="IGEN",U21="NEM"),0,IF(AND(H21="GYES",E21&lt;1998),0,S21))))</f>
         <v/>
       </c>
       <c r="AI21" s="6">
@@ -14439,7 +14439,7 @@
         <v/>
       </c>
       <c r="AH22" s="6">
-        <f>IF(S22="","",IF(OR(I22=0,V22="IGEN",W22="IGEN"),0,IF(AND(K22&lt;&gt;"IGEN",L22="IGEN",U22="NEM"),0,S22)))</f>
+        <f>IF(S22="","",IF(OR(I22=0,V22="IGEN",W22="IGEN"),0,IF(AND(K22&lt;&gt;"IGEN",L22="IGEN",U22="NEM"),0,IF(AND(H22="GYES",E22&lt;1998),0,S22))))</f>
         <v/>
       </c>
       <c r="AI22" s="6">
@@ -14559,7 +14559,7 @@
         <v/>
       </c>
       <c r="AH23" s="6">
-        <f>IF(S23="","",IF(OR(I23=0,V23="IGEN",W23="IGEN"),0,IF(AND(K23&lt;&gt;"IGEN",L23="IGEN",U23="NEM"),0,S23)))</f>
+        <f>IF(S23="","",IF(OR(I23=0,V23="IGEN",W23="IGEN"),0,IF(AND(K23&lt;&gt;"IGEN",L23="IGEN",U23="NEM"),0,IF(AND(H23="GYES",E23&lt;1998),0,S23))))</f>
         <v/>
       </c>
       <c r="AI23" s="6">
@@ -14679,7 +14679,7 @@
         <v/>
       </c>
       <c r="AH24" s="6">
-        <f>IF(S24="","",IF(OR(I24=0,V24="IGEN",W24="IGEN"),0,IF(AND(K24&lt;&gt;"IGEN",L24="IGEN",U24="NEM"),0,S24)))</f>
+        <f>IF(S24="","",IF(OR(I24=0,V24="IGEN",W24="IGEN"),0,IF(AND(K24&lt;&gt;"IGEN",L24="IGEN",U24="NEM"),0,IF(AND(H24="GYES",E24&lt;1998),0,S24))))</f>
         <v/>
       </c>
       <c r="AI24" s="6">
@@ -14799,7 +14799,7 @@
         <v/>
       </c>
       <c r="AH25" s="6">
-        <f>IF(S25="","",IF(OR(I25=0,V25="IGEN",W25="IGEN"),0,IF(AND(K25&lt;&gt;"IGEN",L25="IGEN",U25="NEM"),0,S25)))</f>
+        <f>IF(S25="","",IF(OR(I25=0,V25="IGEN",W25="IGEN"),0,IF(AND(K25&lt;&gt;"IGEN",L25="IGEN",U25="NEM"),0,IF(AND(H25="GYES",E25&lt;1998),0,S25))))</f>
         <v/>
       </c>
       <c r="AI25" s="6">
@@ -14919,7 +14919,7 @@
         <v/>
       </c>
       <c r="AH26" s="6">
-        <f>IF(S26="","",IF(OR(I26=0,V26="IGEN",W26="IGEN"),0,IF(AND(K26&lt;&gt;"IGEN",L26="IGEN",U26="NEM"),0,S26)))</f>
+        <f>IF(S26="","",IF(OR(I26=0,V26="IGEN",W26="IGEN"),0,IF(AND(K26&lt;&gt;"IGEN",L26="IGEN",U26="NEM"),0,IF(AND(H26="GYES",E26&lt;1998),0,S26))))</f>
         <v/>
       </c>
       <c r="AI26" s="6">
@@ -15039,7 +15039,7 @@
         <v/>
       </c>
       <c r="AH27" s="6">
-        <f>IF(S27="","",IF(OR(I27=0,V27="IGEN",W27="IGEN"),0,IF(AND(K27&lt;&gt;"IGEN",L27="IGEN",U27="NEM"),0,S27)))</f>
+        <f>IF(S27="","",IF(OR(I27=0,V27="IGEN",W27="IGEN"),0,IF(AND(K27&lt;&gt;"IGEN",L27="IGEN",U27="NEM"),0,IF(AND(H27="GYES",E27&lt;1998),0,S27))))</f>
         <v/>
       </c>
       <c r="AI27" s="6">
@@ -15159,7 +15159,7 @@
         <v/>
       </c>
       <c r="AH28" s="6">
-        <f>IF(S28="","",IF(OR(I28=0,V28="IGEN",W28="IGEN"),0,IF(AND(K28&lt;&gt;"IGEN",L28="IGEN",U28="NEM"),0,S28)))</f>
+        <f>IF(S28="","",IF(OR(I28=0,V28="IGEN",W28="IGEN"),0,IF(AND(K28&lt;&gt;"IGEN",L28="IGEN",U28="NEM"),0,IF(AND(H28="GYES",E28&lt;1998),0,S28))))</f>
         <v/>
       </c>
       <c r="AI28" s="6">
@@ -15279,7 +15279,7 @@
         <v/>
       </c>
       <c r="AH29" s="6">
-        <f>IF(S29="","",IF(OR(I29=0,V29="IGEN",W29="IGEN"),0,IF(AND(K29&lt;&gt;"IGEN",L29="IGEN",U29="NEM"),0,S29)))</f>
+        <f>IF(S29="","",IF(OR(I29=0,V29="IGEN",W29="IGEN"),0,IF(AND(K29&lt;&gt;"IGEN",L29="IGEN",U29="NEM"),0,IF(AND(H29="GYES",E29&lt;1998),0,S29))))</f>
         <v/>
       </c>
       <c r="AI29" s="6">
@@ -15399,7 +15399,7 @@
         <v/>
       </c>
       <c r="AH30" s="6">
-        <f>IF(S30="","",IF(OR(I30=0,V30="IGEN",W30="IGEN"),0,IF(AND(K30&lt;&gt;"IGEN",L30="IGEN",U30="NEM"),0,S30)))</f>
+        <f>IF(S30="","",IF(OR(I30=0,V30="IGEN",W30="IGEN"),0,IF(AND(K30&lt;&gt;"IGEN",L30="IGEN",U30="NEM"),0,IF(AND(H30="GYES",E30&lt;1998),0,S30))))</f>
         <v/>
       </c>
       <c r="AI30" s="6">
@@ -15519,7 +15519,7 @@
         <v/>
       </c>
       <c r="AH31" s="6">
-        <f>IF(S31="","",IF(OR(I31=0,V31="IGEN",W31="IGEN"),0,IF(AND(K31&lt;&gt;"IGEN",L31="IGEN",U31="NEM"),0,S31)))</f>
+        <f>IF(S31="","",IF(OR(I31=0,V31="IGEN",W31="IGEN"),0,IF(AND(K31&lt;&gt;"IGEN",L31="IGEN",U31="NEM"),0,IF(AND(H31="GYES",E31&lt;1998),0,S31))))</f>
         <v/>
       </c>
       <c r="AI31" s="6">
@@ -15639,7 +15639,7 @@
         <v/>
       </c>
       <c r="AH32" s="6">
-        <f>IF(S32="","",IF(OR(I32=0,V32="IGEN",W32="IGEN"),0,IF(AND(K32&lt;&gt;"IGEN",L32="IGEN",U32="NEM"),0,S32)))</f>
+        <f>IF(S32="","",IF(OR(I32=0,V32="IGEN",W32="IGEN"),0,IF(AND(K32&lt;&gt;"IGEN",L32="IGEN",U32="NEM"),0,IF(AND(H32="GYES",E32&lt;1998),0,S32))))</f>
         <v/>
       </c>
       <c r="AI32" s="6">
@@ -15759,7 +15759,7 @@
         <v/>
       </c>
       <c r="AH33" s="6">
-        <f>IF(S33="","",IF(OR(I33=0,V33="IGEN",W33="IGEN"),0,IF(AND(K33&lt;&gt;"IGEN",L33="IGEN",U33="NEM"),0,S33)))</f>
+        <f>IF(S33="","",IF(OR(I33=0,V33="IGEN",W33="IGEN"),0,IF(AND(K33&lt;&gt;"IGEN",L33="IGEN",U33="NEM"),0,IF(AND(H33="GYES",E33&lt;1998),0,S33))))</f>
         <v/>
       </c>
       <c r="AI33" s="6">
@@ -15879,7 +15879,7 @@
         <v/>
       </c>
       <c r="AH34" s="6">
-        <f>IF(S34="","",IF(OR(I34=0,V34="IGEN",W34="IGEN"),0,IF(AND(K34&lt;&gt;"IGEN",L34="IGEN",U34="NEM"),0,S34)))</f>
+        <f>IF(S34="","",IF(OR(I34=0,V34="IGEN",W34="IGEN"),0,IF(AND(K34&lt;&gt;"IGEN",L34="IGEN",U34="NEM"),0,IF(AND(H34="GYES",E34&lt;1998),0,S34))))</f>
         <v/>
       </c>
       <c r="AI34" s="6">
@@ -15999,7 +15999,7 @@
         <v/>
       </c>
       <c r="AH35" s="6">
-        <f>IF(S35="","",IF(OR(I35=0,V35="IGEN",W35="IGEN"),0,IF(AND(K35&lt;&gt;"IGEN",L35="IGEN",U35="NEM"),0,S35)))</f>
+        <f>IF(S35="","",IF(OR(I35=0,V35="IGEN",W35="IGEN"),0,IF(AND(K35&lt;&gt;"IGEN",L35="IGEN",U35="NEM"),0,IF(AND(H35="GYES",E35&lt;1998),0,S35))))</f>
         <v/>
       </c>
       <c r="AI35" s="6">
@@ -16119,7 +16119,7 @@
         <v/>
       </c>
       <c r="AH36" s="6">
-        <f>IF(S36="","",IF(OR(I36=0,V36="IGEN",W36="IGEN"),0,IF(AND(K36&lt;&gt;"IGEN",L36="IGEN",U36="NEM"),0,S36)))</f>
+        <f>IF(S36="","",IF(OR(I36=0,V36="IGEN",W36="IGEN"),0,IF(AND(K36&lt;&gt;"IGEN",L36="IGEN",U36="NEM"),0,IF(AND(H36="GYES",E36&lt;1998),0,S36))))</f>
         <v/>
       </c>
       <c r="AI36" s="6">
@@ -16239,7 +16239,7 @@
         <v/>
       </c>
       <c r="AH37" s="6">
-        <f>IF(S37="","",IF(OR(I37=0,V37="IGEN",W37="IGEN"),0,IF(AND(K37&lt;&gt;"IGEN",L37="IGEN",U37="NEM"),0,S37)))</f>
+        <f>IF(S37="","",IF(OR(I37=0,V37="IGEN",W37="IGEN"),0,IF(AND(K37&lt;&gt;"IGEN",L37="IGEN",U37="NEM"),0,IF(AND(H37="GYES",E37&lt;1998),0,S37))))</f>
         <v/>
       </c>
       <c r="AI37" s="6">
@@ -16359,7 +16359,7 @@
         <v/>
       </c>
       <c r="AH38" s="6">
-        <f>IF(S38="","",IF(OR(I38=0,V38="IGEN",W38="IGEN"),0,IF(AND(K38&lt;&gt;"IGEN",L38="IGEN",U38="NEM"),0,S38)))</f>
+        <f>IF(S38="","",IF(OR(I38=0,V38="IGEN",W38="IGEN"),0,IF(AND(K38&lt;&gt;"IGEN",L38="IGEN",U38="NEM"),0,IF(AND(H38="GYES",E38&lt;1998),0,S38))))</f>
         <v/>
       </c>
       <c r="AI38" s="6">
@@ -16479,7 +16479,7 @@
         <v/>
       </c>
       <c r="AH39" s="6">
-        <f>IF(S39="","",IF(OR(I39=0,V39="IGEN",W39="IGEN"),0,IF(AND(K39&lt;&gt;"IGEN",L39="IGEN",U39="NEM"),0,S39)))</f>
+        <f>IF(S39="","",IF(OR(I39=0,V39="IGEN",W39="IGEN"),0,IF(AND(K39&lt;&gt;"IGEN",L39="IGEN",U39="NEM"),0,IF(AND(H39="GYES",E39&lt;1998),0,S39))))</f>
         <v/>
       </c>
       <c r="AI39" s="6">
@@ -16599,7 +16599,7 @@
         <v/>
       </c>
       <c r="AH40" s="6">
-        <f>IF(S40="","",IF(OR(I40=0,V40="IGEN",W40="IGEN"),0,IF(AND(K40&lt;&gt;"IGEN",L40="IGEN",U40="NEM"),0,S40)))</f>
+        <f>IF(S40="","",IF(OR(I40=0,V40="IGEN",W40="IGEN"),0,IF(AND(K40&lt;&gt;"IGEN",L40="IGEN",U40="NEM"),0,IF(AND(H40="GYES",E40&lt;1998),0,S40))))</f>
         <v/>
       </c>
       <c r="AI40" s="6">
@@ -16719,7 +16719,7 @@
         <v/>
       </c>
       <c r="AH41" s="6">
-        <f>IF(S41="","",IF(OR(I41=0,V41="IGEN",W41="IGEN"),0,IF(AND(K41&lt;&gt;"IGEN",L41="IGEN",U41="NEM"),0,S41)))</f>
+        <f>IF(S41="","",IF(OR(I41=0,V41="IGEN",W41="IGEN"),0,IF(AND(K41&lt;&gt;"IGEN",L41="IGEN",U41="NEM"),0,IF(AND(H41="GYES",E41&lt;1998),0,S41))))</f>
         <v/>
       </c>
       <c r="AI41" s="6">
@@ -16839,7 +16839,7 @@
         <v/>
       </c>
       <c r="AH42" s="6">
-        <f>IF(S42="","",IF(OR(I42=0,V42="IGEN",W42="IGEN"),0,IF(AND(K42&lt;&gt;"IGEN",L42="IGEN",U42="NEM"),0,S42)))</f>
+        <f>IF(S42="","",IF(OR(I42=0,V42="IGEN",W42="IGEN"),0,IF(AND(K42&lt;&gt;"IGEN",L42="IGEN",U42="NEM"),0,IF(AND(H42="GYES",E42&lt;1998),0,S42))))</f>
         <v/>
       </c>
       <c r="AI42" s="6">
@@ -16959,7 +16959,7 @@
         <v/>
       </c>
       <c r="AH43" s="6">
-        <f>IF(S43="","",IF(OR(I43=0,V43="IGEN",W43="IGEN"),0,IF(AND(K43&lt;&gt;"IGEN",L43="IGEN",U43="NEM"),0,S43)))</f>
+        <f>IF(S43="","",IF(OR(I43=0,V43="IGEN",W43="IGEN"),0,IF(AND(K43&lt;&gt;"IGEN",L43="IGEN",U43="NEM"),0,IF(AND(H43="GYES",E43&lt;1998),0,S43))))</f>
         <v/>
       </c>
       <c r="AI43" s="6">
@@ -17079,7 +17079,7 @@
         <v/>
       </c>
       <c r="AH44" s="6">
-        <f>IF(S44="","",IF(OR(I44=0,V44="IGEN",W44="IGEN"),0,IF(AND(K44&lt;&gt;"IGEN",L44="IGEN",U44="NEM"),0,S44)))</f>
+        <f>IF(S44="","",IF(OR(I44=0,V44="IGEN",W44="IGEN"),0,IF(AND(K44&lt;&gt;"IGEN",L44="IGEN",U44="NEM"),0,IF(AND(H44="GYES",E44&lt;1998),0,S44))))</f>
         <v/>
       </c>
       <c r="AI44" s="6">
@@ -17199,7 +17199,7 @@
         <v/>
       </c>
       <c r="AH45" s="6">
-        <f>IF(S45="","",IF(OR(I45=0,V45="IGEN",W45="IGEN"),0,IF(AND(K45&lt;&gt;"IGEN",L45="IGEN",U45="NEM"),0,S45)))</f>
+        <f>IF(S45="","",IF(OR(I45=0,V45="IGEN",W45="IGEN"),0,IF(AND(K45&lt;&gt;"IGEN",L45="IGEN",U45="NEM"),0,IF(AND(H45="GYES",E45&lt;1998),0,S45))))</f>
         <v/>
       </c>
       <c r="AI45" s="6">
@@ -17319,7 +17319,7 @@
         <v/>
       </c>
       <c r="AH46" s="6">
-        <f>IF(S46="","",IF(OR(I46=0,V46="IGEN",W46="IGEN"),0,IF(AND(K46&lt;&gt;"IGEN",L46="IGEN",U46="NEM"),0,S46)))</f>
+        <f>IF(S46="","",IF(OR(I46=0,V46="IGEN",W46="IGEN"),0,IF(AND(K46&lt;&gt;"IGEN",L46="IGEN",U46="NEM"),0,IF(AND(H46="GYES",E46&lt;1998),0,S46))))</f>
         <v/>
       </c>
       <c r="AI46" s="6">
@@ -17439,7 +17439,7 @@
         <v/>
       </c>
       <c r="AH47" s="6">
-        <f>IF(S47="","",IF(OR(I47=0,V47="IGEN",W47="IGEN"),0,IF(AND(K47&lt;&gt;"IGEN",L47="IGEN",U47="NEM"),0,S47)))</f>
+        <f>IF(S47="","",IF(OR(I47=0,V47="IGEN",W47="IGEN"),0,IF(AND(K47&lt;&gt;"IGEN",L47="IGEN",U47="NEM"),0,IF(AND(H47="GYES",E47&lt;1998),0,S47))))</f>
         <v/>
       </c>
       <c r="AI47" s="6">
@@ -17559,7 +17559,7 @@
         <v/>
       </c>
       <c r="AH48" s="6">
-        <f>IF(S48="","",IF(OR(I48=0,V48="IGEN",W48="IGEN"),0,IF(AND(K48&lt;&gt;"IGEN",L48="IGEN",U48="NEM"),0,S48)))</f>
+        <f>IF(S48="","",IF(OR(I48=0,V48="IGEN",W48="IGEN"),0,IF(AND(K48&lt;&gt;"IGEN",L48="IGEN",U48="NEM"),0,IF(AND(H48="GYES",E48&lt;1998),0,S48))))</f>
         <v/>
       </c>
       <c r="AI48" s="6">
@@ -17679,7 +17679,7 @@
         <v/>
       </c>
       <c r="AH49" s="6">
-        <f>IF(S49="","",IF(OR(I49=0,V49="IGEN",W49="IGEN"),0,IF(AND(K49&lt;&gt;"IGEN",L49="IGEN",U49="NEM"),0,S49)))</f>
+        <f>IF(S49="","",IF(OR(I49=0,V49="IGEN",W49="IGEN"),0,IF(AND(K49&lt;&gt;"IGEN",L49="IGEN",U49="NEM"),0,IF(AND(H49="GYES",E49&lt;1998),0,S49))))</f>
         <v/>
       </c>
       <c r="AI49" s="6">
@@ -17799,7 +17799,7 @@
         <v/>
       </c>
       <c r="AH50" s="6">
-        <f>IF(S50="","",IF(OR(I50=0,V50="IGEN",W50="IGEN"),0,IF(AND(K50&lt;&gt;"IGEN",L50="IGEN",U50="NEM"),0,S50)))</f>
+        <f>IF(S50="","",IF(OR(I50=0,V50="IGEN",W50="IGEN"),0,IF(AND(K50&lt;&gt;"IGEN",L50="IGEN",U50="NEM"),0,IF(AND(H50="GYES",E50&lt;1998),0,S50))))</f>
         <v/>
       </c>
       <c r="AI50" s="6">
@@ -17919,7 +17919,7 @@
         <v/>
       </c>
       <c r="AH51" s="6">
-        <f>IF(S51="","",IF(OR(I51=0,V51="IGEN",W51="IGEN"),0,IF(AND(K51&lt;&gt;"IGEN",L51="IGEN",U51="NEM"),0,S51)))</f>
+        <f>IF(S51="","",IF(OR(I51=0,V51="IGEN",W51="IGEN"),0,IF(AND(K51&lt;&gt;"IGEN",L51="IGEN",U51="NEM"),0,IF(AND(H51="GYES",E51&lt;1998),0,S51))))</f>
         <v/>
       </c>
       <c r="AI51" s="6">
@@ -18039,7 +18039,7 @@
         <v/>
       </c>
       <c r="AH52" s="6">
-        <f>IF(S52="","",IF(OR(I52=0,V52="IGEN",W52="IGEN"),0,IF(AND(K52&lt;&gt;"IGEN",L52="IGEN",U52="NEM"),0,S52)))</f>
+        <f>IF(S52="","",IF(OR(I52=0,V52="IGEN",W52="IGEN"),0,IF(AND(K52&lt;&gt;"IGEN",L52="IGEN",U52="NEM"),0,IF(AND(H52="GYES",E52&lt;1998),0,S52))))</f>
         <v/>
       </c>
       <c r="AI52" s="6">
@@ -18159,7 +18159,7 @@
         <v/>
       </c>
       <c r="AH53" s="6">
-        <f>IF(S53="","",IF(OR(I53=0,V53="IGEN",W53="IGEN"),0,IF(AND(K53&lt;&gt;"IGEN",L53="IGEN",U53="NEM"),0,S53)))</f>
+        <f>IF(S53="","",IF(OR(I53=0,V53="IGEN",W53="IGEN"),0,IF(AND(K53&lt;&gt;"IGEN",L53="IGEN",U53="NEM"),0,IF(AND(H53="GYES",E53&lt;1998),0,S53))))</f>
         <v/>
       </c>
       <c r="AI53" s="6">
@@ -18279,7 +18279,7 @@
         <v/>
       </c>
       <c r="AH54" s="6">
-        <f>IF(S54="","",IF(OR(I54=0,V54="IGEN",W54="IGEN"),0,IF(AND(K54&lt;&gt;"IGEN",L54="IGEN",U54="NEM"),0,S54)))</f>
+        <f>IF(S54="","",IF(OR(I54=0,V54="IGEN",W54="IGEN"),0,IF(AND(K54&lt;&gt;"IGEN",L54="IGEN",U54="NEM"),0,IF(AND(H54="GYES",E54&lt;1998),0,S54))))</f>
         <v/>
       </c>
       <c r="AI54" s="6">
@@ -18399,7 +18399,7 @@
         <v/>
       </c>
       <c r="AH55" s="6">
-        <f>IF(S55="","",IF(OR(I55=0,V55="IGEN",W55="IGEN"),0,IF(AND(K55&lt;&gt;"IGEN",L55="IGEN",U55="NEM"),0,S55)))</f>
+        <f>IF(S55="","",IF(OR(I55=0,V55="IGEN",W55="IGEN"),0,IF(AND(K55&lt;&gt;"IGEN",L55="IGEN",U55="NEM"),0,IF(AND(H55="GYES",E55&lt;1998),0,S55))))</f>
         <v/>
       </c>
       <c r="AI55" s="6">
@@ -18519,7 +18519,7 @@
         <v/>
       </c>
       <c r="AH56" s="6">
-        <f>IF(S56="","",IF(OR(I56=0,V56="IGEN",W56="IGEN"),0,IF(AND(K56&lt;&gt;"IGEN",L56="IGEN",U56="NEM"),0,S56)))</f>
+        <f>IF(S56="","",IF(OR(I56=0,V56="IGEN",W56="IGEN"),0,IF(AND(K56&lt;&gt;"IGEN",L56="IGEN",U56="NEM"),0,IF(AND(H56="GYES",E56&lt;1998),0,S56))))</f>
         <v/>
       </c>
       <c r="AI56" s="6">
@@ -18639,7 +18639,7 @@
         <v/>
       </c>
       <c r="AH57" s="6">
-        <f>IF(S57="","",IF(OR(I57=0,V57="IGEN",W57="IGEN"),0,IF(AND(K57&lt;&gt;"IGEN",L57="IGEN",U57="NEM"),0,S57)))</f>
+        <f>IF(S57="","",IF(OR(I57=0,V57="IGEN",W57="IGEN"),0,IF(AND(K57&lt;&gt;"IGEN",L57="IGEN",U57="NEM"),0,IF(AND(H57="GYES",E57&lt;1998),0,S57))))</f>
         <v/>
       </c>
       <c r="AI57" s="6">
@@ -18759,7 +18759,7 @@
         <v/>
       </c>
       <c r="AH58" s="6">
-        <f>IF(S58="","",IF(OR(I58=0,V58="IGEN",W58="IGEN"),0,IF(AND(K58&lt;&gt;"IGEN",L58="IGEN",U58="NEM"),0,S58)))</f>
+        <f>IF(S58="","",IF(OR(I58=0,V58="IGEN",W58="IGEN"),0,IF(AND(K58&lt;&gt;"IGEN",L58="IGEN",U58="NEM"),0,IF(AND(H58="GYES",E58&lt;1998),0,S58))))</f>
         <v/>
       </c>
       <c r="AI58" s="6">
@@ -18879,7 +18879,7 @@
         <v/>
       </c>
       <c r="AH59" s="6">
-        <f>IF(S59="","",IF(OR(I59=0,V59="IGEN",W59="IGEN"),0,IF(AND(K59&lt;&gt;"IGEN",L59="IGEN",U59="NEM"),0,S59)))</f>
+        <f>IF(S59="","",IF(OR(I59=0,V59="IGEN",W59="IGEN"),0,IF(AND(K59&lt;&gt;"IGEN",L59="IGEN",U59="NEM"),0,IF(AND(H59="GYES",E59&lt;1998),0,S59))))</f>
         <v/>
       </c>
       <c r="AI59" s="6">
@@ -18999,7 +18999,7 @@
         <v/>
       </c>
       <c r="AH60" s="6">
-        <f>IF(S60="","",IF(OR(I60=0,V60="IGEN",W60="IGEN"),0,IF(AND(K60&lt;&gt;"IGEN",L60="IGEN",U60="NEM"),0,S60)))</f>
+        <f>IF(S60="","",IF(OR(I60=0,V60="IGEN",W60="IGEN"),0,IF(AND(K60&lt;&gt;"IGEN",L60="IGEN",U60="NEM"),0,IF(AND(H60="GYES",E60&lt;1998),0,S60))))</f>
         <v/>
       </c>
       <c r="AI60" s="6">
@@ -19119,7 +19119,7 @@
         <v/>
       </c>
       <c r="AH61" s="6">
-        <f>IF(S61="","",IF(OR(I61=0,V61="IGEN",W61="IGEN"),0,IF(AND(K61&lt;&gt;"IGEN",L61="IGEN",U61="NEM"),0,S61)))</f>
+        <f>IF(S61="","",IF(OR(I61=0,V61="IGEN",W61="IGEN"),0,IF(AND(K61&lt;&gt;"IGEN",L61="IGEN",U61="NEM"),0,IF(AND(H61="GYES",E61&lt;1998),0,S61))))</f>
         <v/>
       </c>
       <c r="AI61" s="6">
@@ -19239,7 +19239,7 @@
         <v/>
       </c>
       <c r="AH62" s="6">
-        <f>IF(S62="","",IF(OR(I62=0,V62="IGEN",W62="IGEN"),0,IF(AND(K62&lt;&gt;"IGEN",L62="IGEN",U62="NEM"),0,S62)))</f>
+        <f>IF(S62="","",IF(OR(I62=0,V62="IGEN",W62="IGEN"),0,IF(AND(K62&lt;&gt;"IGEN",L62="IGEN",U62="NEM"),0,IF(AND(H62="GYES",E62&lt;1998),0,S62))))</f>
         <v/>
       </c>
       <c r="AI62" s="6">
@@ -19359,7 +19359,7 @@
         <v/>
       </c>
       <c r="AH63" s="6">
-        <f>IF(S63="","",IF(OR(I63=0,V63="IGEN",W63="IGEN"),0,IF(AND(K63&lt;&gt;"IGEN",L63="IGEN",U63="NEM"),0,S63)))</f>
+        <f>IF(S63="","",IF(OR(I63=0,V63="IGEN",W63="IGEN"),0,IF(AND(K63&lt;&gt;"IGEN",L63="IGEN",U63="NEM"),0,IF(AND(H63="GYES",E63&lt;1998),0,S63))))</f>
         <v/>
       </c>
       <c r="AI63" s="6">
@@ -19479,7 +19479,7 @@
         <v/>
       </c>
       <c r="AH64" s="6">
-        <f>IF(S64="","",IF(OR(I64=0,V64="IGEN",W64="IGEN"),0,IF(AND(K64&lt;&gt;"IGEN",L64="IGEN",U64="NEM"),0,S64)))</f>
+        <f>IF(S64="","",IF(OR(I64=0,V64="IGEN",W64="IGEN"),0,IF(AND(K64&lt;&gt;"IGEN",L64="IGEN",U64="NEM"),0,IF(AND(H64="GYES",E64&lt;1998),0,S64))))</f>
         <v/>
       </c>
       <c r="AI64" s="6">
@@ -19599,7 +19599,7 @@
         <v/>
       </c>
       <c r="AH65" s="6">
-        <f>IF(S65="","",IF(OR(I65=0,V65="IGEN",W65="IGEN"),0,IF(AND(K65&lt;&gt;"IGEN",L65="IGEN",U65="NEM"),0,S65)))</f>
+        <f>IF(S65="","",IF(OR(I65=0,V65="IGEN",W65="IGEN"),0,IF(AND(K65&lt;&gt;"IGEN",L65="IGEN",U65="NEM"),0,IF(AND(H65="GYES",E65&lt;1998),0,S65))))</f>
         <v/>
       </c>
       <c r="AI65" s="6">
@@ -19719,7 +19719,7 @@
         <v/>
       </c>
       <c r="AH66" s="6">
-        <f>IF(S66="","",IF(OR(I66=0,V66="IGEN",W66="IGEN"),0,IF(AND(K66&lt;&gt;"IGEN",L66="IGEN",U66="NEM"),0,S66)))</f>
+        <f>IF(S66="","",IF(OR(I66=0,V66="IGEN",W66="IGEN"),0,IF(AND(K66&lt;&gt;"IGEN",L66="IGEN",U66="NEM"),0,IF(AND(H66="GYES",E66&lt;1998),0,S66))))</f>
         <v/>
       </c>
       <c r="AI66" s="6">
@@ -19839,7 +19839,7 @@
         <v/>
       </c>
       <c r="AH67" s="6">
-        <f>IF(S67="","",IF(OR(I67=0,V67="IGEN",W67="IGEN"),0,IF(AND(K67&lt;&gt;"IGEN",L67="IGEN",U67="NEM"),0,S67)))</f>
+        <f>IF(S67="","",IF(OR(I67=0,V67="IGEN",W67="IGEN"),0,IF(AND(K67&lt;&gt;"IGEN",L67="IGEN",U67="NEM"),0,IF(AND(H67="GYES",E67&lt;1998),0,S67))))</f>
         <v/>
       </c>
       <c r="AI67" s="6">
@@ -19959,7 +19959,7 @@
         <v/>
       </c>
       <c r="AH68" s="6">
-        <f>IF(S68="","",IF(OR(I68=0,V68="IGEN",W68="IGEN"),0,IF(AND(K68&lt;&gt;"IGEN",L68="IGEN",U68="NEM"),0,S68)))</f>
+        <f>IF(S68="","",IF(OR(I68=0,V68="IGEN",W68="IGEN"),0,IF(AND(K68&lt;&gt;"IGEN",L68="IGEN",U68="NEM"),0,IF(AND(H68="GYES",E68&lt;1998),0,S68))))</f>
         <v/>
       </c>
       <c r="AI68" s="6">
@@ -20079,7 +20079,7 @@
         <v/>
       </c>
       <c r="AH69" s="6">
-        <f>IF(S69="","",IF(OR(I69=0,V69="IGEN",W69="IGEN"),0,IF(AND(K69&lt;&gt;"IGEN",L69="IGEN",U69="NEM"),0,S69)))</f>
+        <f>IF(S69="","",IF(OR(I69=0,V69="IGEN",W69="IGEN"),0,IF(AND(K69&lt;&gt;"IGEN",L69="IGEN",U69="NEM"),0,IF(AND(H69="GYES",E69&lt;1998),0,S69))))</f>
         <v/>
       </c>
       <c r="AI69" s="6">
@@ -20199,7 +20199,7 @@
         <v/>
       </c>
       <c r="AH70" s="6">
-        <f>IF(S70="","",IF(OR(I70=0,V70="IGEN",W70="IGEN"),0,IF(AND(K70&lt;&gt;"IGEN",L70="IGEN",U70="NEM"),0,S70)))</f>
+        <f>IF(S70="","",IF(OR(I70=0,V70="IGEN",W70="IGEN"),0,IF(AND(K70&lt;&gt;"IGEN",L70="IGEN",U70="NEM"),0,IF(AND(H70="GYES",E70&lt;1998),0,S70))))</f>
         <v/>
       </c>
       <c r="AI70" s="6">
@@ -20319,7 +20319,7 @@
         <v/>
       </c>
       <c r="AH71" s="6">
-        <f>IF(S71="","",IF(OR(I71=0,V71="IGEN",W71="IGEN"),0,IF(AND(K71&lt;&gt;"IGEN",L71="IGEN",U71="NEM"),0,S71)))</f>
+        <f>IF(S71="","",IF(OR(I71=0,V71="IGEN",W71="IGEN"),0,IF(AND(K71&lt;&gt;"IGEN",L71="IGEN",U71="NEM"),0,IF(AND(H71="GYES",E71&lt;1998),0,S71))))</f>
         <v/>
       </c>
       <c r="AI71" s="6">
@@ -20439,7 +20439,7 @@
         <v/>
       </c>
       <c r="AH72" s="6">
-        <f>IF(S72="","",IF(OR(I72=0,V72="IGEN",W72="IGEN"),0,IF(AND(K72&lt;&gt;"IGEN",L72="IGEN",U72="NEM"),0,S72)))</f>
+        <f>IF(S72="","",IF(OR(I72=0,V72="IGEN",W72="IGEN"),0,IF(AND(K72&lt;&gt;"IGEN",L72="IGEN",U72="NEM"),0,IF(AND(H72="GYES",E72&lt;1998),0,S72))))</f>
         <v/>
       </c>
       <c r="AI72" s="6">
@@ -20559,7 +20559,7 @@
         <v/>
       </c>
       <c r="AH73" s="6">
-        <f>IF(S73="","",IF(OR(I73=0,V73="IGEN",W73="IGEN"),0,IF(AND(K73&lt;&gt;"IGEN",L73="IGEN",U73="NEM"),0,S73)))</f>
+        <f>IF(S73="","",IF(OR(I73=0,V73="IGEN",W73="IGEN"),0,IF(AND(K73&lt;&gt;"IGEN",L73="IGEN",U73="NEM"),0,IF(AND(H73="GYES",E73&lt;1998),0,S73))))</f>
         <v/>
       </c>
       <c r="AI73" s="6">
@@ -20679,7 +20679,7 @@
         <v/>
       </c>
       <c r="AH74" s="6">
-        <f>IF(S74="","",IF(OR(I74=0,V74="IGEN",W74="IGEN"),0,IF(AND(K74&lt;&gt;"IGEN",L74="IGEN",U74="NEM"),0,S74)))</f>
+        <f>IF(S74="","",IF(OR(I74=0,V74="IGEN",W74="IGEN"),0,IF(AND(K74&lt;&gt;"IGEN",L74="IGEN",U74="NEM"),0,IF(AND(H74="GYES",E74&lt;1998),0,S74))))</f>
         <v/>
       </c>
       <c r="AI74" s="6">
@@ -20799,7 +20799,7 @@
         <v/>
       </c>
       <c r="AH75" s="6">
-        <f>IF(S75="","",IF(OR(I75=0,V75="IGEN",W75="IGEN"),0,IF(AND(K75&lt;&gt;"IGEN",L75="IGEN",U75="NEM"),0,S75)))</f>
+        <f>IF(S75="","",IF(OR(I75=0,V75="IGEN",W75="IGEN"),0,IF(AND(K75&lt;&gt;"IGEN",L75="IGEN",U75="NEM"),0,IF(AND(H75="GYES",E75&lt;1998),0,S75))))</f>
         <v/>
       </c>
       <c r="AI75" s="6">
@@ -20919,7 +20919,7 @@
         <v/>
       </c>
       <c r="AH76" s="6">
-        <f>IF(S76="","",IF(OR(I76=0,V76="IGEN",W76="IGEN"),0,IF(AND(K76&lt;&gt;"IGEN",L76="IGEN",U76="NEM"),0,S76)))</f>
+        <f>IF(S76="","",IF(OR(I76=0,V76="IGEN",W76="IGEN"),0,IF(AND(K76&lt;&gt;"IGEN",L76="IGEN",U76="NEM"),0,IF(AND(H76="GYES",E76&lt;1998),0,S76))))</f>
         <v/>
       </c>
       <c r="AI76" s="6">
@@ -21039,7 +21039,7 @@
         <v/>
       </c>
       <c r="AH77" s="6">
-        <f>IF(S77="","",IF(OR(I77=0,V77="IGEN",W77="IGEN"),0,IF(AND(K77&lt;&gt;"IGEN",L77="IGEN",U77="NEM"),0,S77)))</f>
+        <f>IF(S77="","",IF(OR(I77=0,V77="IGEN",W77="IGEN"),0,IF(AND(K77&lt;&gt;"IGEN",L77="IGEN",U77="NEM"),0,IF(AND(H77="GYES",E77&lt;1998),0,S77))))</f>
         <v/>
       </c>
       <c r="AI77" s="6">
@@ -21159,7 +21159,7 @@
         <v/>
       </c>
       <c r="AH78" s="6">
-        <f>IF(S78="","",IF(OR(I78=0,V78="IGEN",W78="IGEN"),0,IF(AND(K78&lt;&gt;"IGEN",L78="IGEN",U78="NEM"),0,S78)))</f>
+        <f>IF(S78="","",IF(OR(I78=0,V78="IGEN",W78="IGEN"),0,IF(AND(K78&lt;&gt;"IGEN",L78="IGEN",U78="NEM"),0,IF(AND(H78="GYES",E78&lt;1998),0,S78))))</f>
         <v/>
       </c>
       <c r="AI78" s="6">
@@ -21279,7 +21279,7 @@
         <v/>
       </c>
       <c r="AH79" s="6">
-        <f>IF(S79="","",IF(OR(I79=0,V79="IGEN",W79="IGEN"),0,IF(AND(K79&lt;&gt;"IGEN",L79="IGEN",U79="NEM"),0,S79)))</f>
+        <f>IF(S79="","",IF(OR(I79=0,V79="IGEN",W79="IGEN"),0,IF(AND(K79&lt;&gt;"IGEN",L79="IGEN",U79="NEM"),0,IF(AND(H79="GYES",E79&lt;1998),0,S79))))</f>
         <v/>
       </c>
       <c r="AI79" s="6">
@@ -21399,7 +21399,7 @@
         <v/>
       </c>
       <c r="AH80" s="6">
-        <f>IF(S80="","",IF(OR(I80=0,V80="IGEN",W80="IGEN"),0,IF(AND(K80&lt;&gt;"IGEN",L80="IGEN",U80="NEM"),0,S80)))</f>
+        <f>IF(S80="","",IF(OR(I80=0,V80="IGEN",W80="IGEN"),0,IF(AND(K80&lt;&gt;"IGEN",L80="IGEN",U80="NEM"),0,IF(AND(H80="GYES",E80&lt;1998),0,S80))))</f>
         <v/>
       </c>
       <c r="AI80" s="6">
@@ -21519,7 +21519,7 @@
         <v/>
       </c>
       <c r="AH81" s="6">
-        <f>IF(S81="","",IF(OR(I81=0,V81="IGEN",W81="IGEN"),0,IF(AND(K81&lt;&gt;"IGEN",L81="IGEN",U81="NEM"),0,S81)))</f>
+        <f>IF(S81="","",IF(OR(I81=0,V81="IGEN",W81="IGEN"),0,IF(AND(K81&lt;&gt;"IGEN",L81="IGEN",U81="NEM"),0,IF(AND(H81="GYES",E81&lt;1998),0,S81))))</f>
         <v/>
       </c>
       <c r="AI81" s="6">
@@ -21639,7 +21639,7 @@
         <v/>
       </c>
       <c r="AH82" s="6">
-        <f>IF(S82="","",IF(OR(I82=0,V82="IGEN",W82="IGEN"),0,IF(AND(K82&lt;&gt;"IGEN",L82="IGEN",U82="NEM"),0,S82)))</f>
+        <f>IF(S82="","",IF(OR(I82=0,V82="IGEN",W82="IGEN"),0,IF(AND(K82&lt;&gt;"IGEN",L82="IGEN",U82="NEM"),0,IF(AND(H82="GYES",E82&lt;1998),0,S82))))</f>
         <v/>
       </c>
       <c r="AI82" s="6">
@@ -21759,7 +21759,7 @@
         <v/>
       </c>
       <c r="AH83" s="6">
-        <f>IF(S83="","",IF(OR(I83=0,V83="IGEN",W83="IGEN"),0,IF(AND(K83&lt;&gt;"IGEN",L83="IGEN",U83="NEM"),0,S83)))</f>
+        <f>IF(S83="","",IF(OR(I83=0,V83="IGEN",W83="IGEN"),0,IF(AND(K83&lt;&gt;"IGEN",L83="IGEN",U83="NEM"),0,IF(AND(H83="GYES",E83&lt;1998),0,S83))))</f>
         <v/>
       </c>
       <c r="AI83" s="6">
@@ -21879,7 +21879,7 @@
         <v/>
       </c>
       <c r="AH84" s="6">
-        <f>IF(S84="","",IF(OR(I84=0,V84="IGEN",W84="IGEN"),0,IF(AND(K84&lt;&gt;"IGEN",L84="IGEN",U84="NEM"),0,S84)))</f>
+        <f>IF(S84="","",IF(OR(I84=0,V84="IGEN",W84="IGEN"),0,IF(AND(K84&lt;&gt;"IGEN",L84="IGEN",U84="NEM"),0,IF(AND(H84="GYES",E84&lt;1998),0,S84))))</f>
         <v/>
       </c>
       <c r="AI84" s="6">
@@ -21999,7 +21999,7 @@
         <v/>
       </c>
       <c r="AH85" s="6">
-        <f>IF(S85="","",IF(OR(I85=0,V85="IGEN",W85="IGEN"),0,IF(AND(K85&lt;&gt;"IGEN",L85="IGEN",U85="NEM"),0,S85)))</f>
+        <f>IF(S85="","",IF(OR(I85=0,V85="IGEN",W85="IGEN"),0,IF(AND(K85&lt;&gt;"IGEN",L85="IGEN",U85="NEM"),0,IF(AND(H85="GYES",E85&lt;1998),0,S85))))</f>
         <v/>
       </c>
       <c r="AI85" s="6">
@@ -22119,7 +22119,7 @@
         <v/>
       </c>
       <c r="AH86" s="6">
-        <f>IF(S86="","",IF(OR(I86=0,V86="IGEN",W86="IGEN"),0,IF(AND(K86&lt;&gt;"IGEN",L86="IGEN",U86="NEM"),0,S86)))</f>
+        <f>IF(S86="","",IF(OR(I86=0,V86="IGEN",W86="IGEN"),0,IF(AND(K86&lt;&gt;"IGEN",L86="IGEN",U86="NEM"),0,IF(AND(H86="GYES",E86&lt;1998),0,S86))))</f>
         <v/>
       </c>
       <c r="AI86" s="6">
@@ -22239,7 +22239,7 @@
         <v/>
       </c>
       <c r="AH87" s="6">
-        <f>IF(S87="","",IF(OR(I87=0,V87="IGEN",W87="IGEN"),0,IF(AND(K87&lt;&gt;"IGEN",L87="IGEN",U87="NEM"),0,S87)))</f>
+        <f>IF(S87="","",IF(OR(I87=0,V87="IGEN",W87="IGEN"),0,IF(AND(K87&lt;&gt;"IGEN",L87="IGEN",U87="NEM"),0,IF(AND(H87="GYES",E87&lt;1998),0,S87))))</f>
         <v/>
       </c>
       <c r="AI87" s="6">
@@ -22359,7 +22359,7 @@
         <v/>
       </c>
       <c r="AH88" s="6">
-        <f>IF(S88="","",IF(OR(I88=0,V88="IGEN",W88="IGEN"),0,IF(AND(K88&lt;&gt;"IGEN",L88="IGEN",U88="NEM"),0,S88)))</f>
+        <f>IF(S88="","",IF(OR(I88=0,V88="IGEN",W88="IGEN"),0,IF(AND(K88&lt;&gt;"IGEN",L88="IGEN",U88="NEM"),0,IF(AND(H88="GYES",E88&lt;1998),0,S88))))</f>
         <v/>
       </c>
       <c r="AI88" s="6">
@@ -22479,7 +22479,7 @@
         <v/>
       </c>
       <c r="AH89" s="6">
-        <f>IF(S89="","",IF(OR(I89=0,V89="IGEN",W89="IGEN"),0,IF(AND(K89&lt;&gt;"IGEN",L89="IGEN",U89="NEM"),0,S89)))</f>
+        <f>IF(S89="","",IF(OR(I89=0,V89="IGEN",W89="IGEN"),0,IF(AND(K89&lt;&gt;"IGEN",L89="IGEN",U89="NEM"),0,IF(AND(H89="GYES",E89&lt;1998),0,S89))))</f>
         <v/>
       </c>
       <c r="AI89" s="6">
@@ -22599,7 +22599,7 @@
         <v/>
       </c>
       <c r="AH90" s="6">
-        <f>IF(S90="","",IF(OR(I90=0,V90="IGEN",W90="IGEN"),0,IF(AND(K90&lt;&gt;"IGEN",L90="IGEN",U90="NEM"),0,S90)))</f>
+        <f>IF(S90="","",IF(OR(I90=0,V90="IGEN",W90="IGEN"),0,IF(AND(K90&lt;&gt;"IGEN",L90="IGEN",U90="NEM"),0,IF(AND(H90="GYES",E90&lt;1998),0,S90))))</f>
         <v/>
       </c>
       <c r="AI90" s="6">
@@ -22719,7 +22719,7 @@
         <v/>
       </c>
       <c r="AH91" s="6">
-        <f>IF(S91="","",IF(OR(I91=0,V91="IGEN",W91="IGEN"),0,IF(AND(K91&lt;&gt;"IGEN",L91="IGEN",U91="NEM"),0,S91)))</f>
+        <f>IF(S91="","",IF(OR(I91=0,V91="IGEN",W91="IGEN"),0,IF(AND(K91&lt;&gt;"IGEN",L91="IGEN",U91="NEM"),0,IF(AND(H91="GYES",E91&lt;1998),0,S91))))</f>
         <v/>
       </c>
       <c r="AI91" s="6">
@@ -22839,7 +22839,7 @@
         <v/>
       </c>
       <c r="AH92" s="6">
-        <f>IF(S92="","",IF(OR(I92=0,V92="IGEN",W92="IGEN"),0,IF(AND(K92&lt;&gt;"IGEN",L92="IGEN",U92="NEM"),0,S92)))</f>
+        <f>IF(S92="","",IF(OR(I92=0,V92="IGEN",W92="IGEN"),0,IF(AND(K92&lt;&gt;"IGEN",L92="IGEN",U92="NEM"),0,IF(AND(H92="GYES",E92&lt;1998),0,S92))))</f>
         <v/>
       </c>
       <c r="AI92" s="6">
@@ -22959,7 +22959,7 @@
         <v/>
       </c>
       <c r="AH93" s="6">
-        <f>IF(S93="","",IF(OR(I93=0,V93="IGEN",W93="IGEN"),0,IF(AND(K93&lt;&gt;"IGEN",L93="IGEN",U93="NEM"),0,S93)))</f>
+        <f>IF(S93="","",IF(OR(I93=0,V93="IGEN",W93="IGEN"),0,IF(AND(K93&lt;&gt;"IGEN",L93="IGEN",U93="NEM"),0,IF(AND(H93="GYES",E93&lt;1998),0,S93))))</f>
         <v/>
       </c>
       <c r="AI93" s="6">
@@ -23079,7 +23079,7 @@
         <v/>
       </c>
       <c r="AH94" s="6">
-        <f>IF(S94="","",IF(OR(I94=0,V94="IGEN",W94="IGEN"),0,IF(AND(K94&lt;&gt;"IGEN",L94="IGEN",U94="NEM"),0,S94)))</f>
+        <f>IF(S94="","",IF(OR(I94=0,V94="IGEN",W94="IGEN"),0,IF(AND(K94&lt;&gt;"IGEN",L94="IGEN",U94="NEM"),0,IF(AND(H94="GYES",E94&lt;1998),0,S94))))</f>
         <v/>
       </c>
       <c r="AI94" s="6">
@@ -23199,7 +23199,7 @@
         <v/>
       </c>
       <c r="AH95" s="6">
-        <f>IF(S95="","",IF(OR(I95=0,V95="IGEN",W95="IGEN"),0,IF(AND(K95&lt;&gt;"IGEN",L95="IGEN",U95="NEM"),0,S95)))</f>
+        <f>IF(S95="","",IF(OR(I95=0,V95="IGEN",W95="IGEN"),0,IF(AND(K95&lt;&gt;"IGEN",L95="IGEN",U95="NEM"),0,IF(AND(H95="GYES",E95&lt;1998),0,S95))))</f>
         <v/>
       </c>
       <c r="AI95" s="6">
@@ -23319,7 +23319,7 @@
         <v/>
       </c>
       <c r="AH96" s="6">
-        <f>IF(S96="","",IF(OR(I96=0,V96="IGEN",W96="IGEN"),0,IF(AND(K96&lt;&gt;"IGEN",L96="IGEN",U96="NEM"),0,S96)))</f>
+        <f>IF(S96="","",IF(OR(I96=0,V96="IGEN",W96="IGEN"),0,IF(AND(K96&lt;&gt;"IGEN",L96="IGEN",U96="NEM"),0,IF(AND(H96="GYES",E96&lt;1998),0,S96))))</f>
         <v/>
       </c>
       <c r="AI96" s="6">
@@ -23439,7 +23439,7 @@
         <v/>
       </c>
       <c r="AH97" s="6">
-        <f>IF(S97="","",IF(OR(I97=0,V97="IGEN",W97="IGEN"),0,IF(AND(K97&lt;&gt;"IGEN",L97="IGEN",U97="NEM"),0,S97)))</f>
+        <f>IF(S97="","",IF(OR(I97=0,V97="IGEN",W97="IGEN"),0,IF(AND(K97&lt;&gt;"IGEN",L97="IGEN",U97="NEM"),0,IF(AND(H97="GYES",E97&lt;1998),0,S97))))</f>
         <v/>
       </c>
       <c r="AI97" s="6">
@@ -23559,7 +23559,7 @@
         <v/>
       </c>
       <c r="AH98" s="6">
-        <f>IF(S98="","",IF(OR(I98=0,V98="IGEN",W98="IGEN"),0,IF(AND(K98&lt;&gt;"IGEN",L98="IGEN",U98="NEM"),0,S98)))</f>
+        <f>IF(S98="","",IF(OR(I98=0,V98="IGEN",W98="IGEN"),0,IF(AND(K98&lt;&gt;"IGEN",L98="IGEN",U98="NEM"),0,IF(AND(H98="GYES",E98&lt;1998),0,S98))))</f>
         <v/>
       </c>
       <c r="AI98" s="6">
@@ -23679,7 +23679,7 @@
         <v/>
       </c>
       <c r="AH99" s="6">
-        <f>IF(S99="","",IF(OR(I99=0,V99="IGEN",W99="IGEN"),0,IF(AND(K99&lt;&gt;"IGEN",L99="IGEN",U99="NEM"),0,S99)))</f>
+        <f>IF(S99="","",IF(OR(I99=0,V99="IGEN",W99="IGEN"),0,IF(AND(K99&lt;&gt;"IGEN",L99="IGEN",U99="NEM"),0,IF(AND(H99="GYES",E99&lt;1998),0,S99))))</f>
         <v/>
       </c>
       <c r="AI99" s="6">
@@ -23799,7 +23799,7 @@
         <v/>
       </c>
       <c r="AH100" s="6">
-        <f>IF(S100="","",IF(OR(I100=0,V100="IGEN",W100="IGEN"),0,IF(AND(K100&lt;&gt;"IGEN",L100="IGEN",U100="NEM"),0,S100)))</f>
+        <f>IF(S100="","",IF(OR(I100=0,V100="IGEN",W100="IGEN"),0,IF(AND(K100&lt;&gt;"IGEN",L100="IGEN",U100="NEM"),0,IF(AND(H100="GYES",E100&lt;1998),0,S100))))</f>
         <v/>
       </c>
       <c r="AI100" s="6">
@@ -23919,7 +23919,7 @@
         <v/>
       </c>
       <c r="AH101" s="6">
-        <f>IF(S101="","",IF(OR(I101=0,V101="IGEN",W101="IGEN"),0,IF(AND(K101&lt;&gt;"IGEN",L101="IGEN",U101="NEM"),0,S101)))</f>
+        <f>IF(S101="","",IF(OR(I101=0,V101="IGEN",W101="IGEN"),0,IF(AND(K101&lt;&gt;"IGEN",L101="IGEN",U101="NEM"),0,IF(AND(H101="GYES",E101&lt;1998),0,S101))))</f>
         <v/>
       </c>
       <c r="AI101" s="6">
@@ -24039,7 +24039,7 @@
         <v/>
       </c>
       <c r="AH102" s="6">
-        <f>IF(S102="","",IF(OR(I102=0,V102="IGEN",W102="IGEN"),0,IF(AND(K102&lt;&gt;"IGEN",L102="IGEN",U102="NEM"),0,S102)))</f>
+        <f>IF(S102="","",IF(OR(I102=0,V102="IGEN",W102="IGEN"),0,IF(AND(K102&lt;&gt;"IGEN",L102="IGEN",U102="NEM"),0,IF(AND(H102="GYES",E102&lt;1998),0,S102))))</f>
         <v/>
       </c>
       <c r="AI102" s="6">
@@ -24159,7 +24159,7 @@
         <v/>
       </c>
       <c r="AH103" s="6">
-        <f>IF(S103="","",IF(OR(I103=0,V103="IGEN",W103="IGEN"),0,IF(AND(K103&lt;&gt;"IGEN",L103="IGEN",U103="NEM"),0,S103)))</f>
+        <f>IF(S103="","",IF(OR(I103=0,V103="IGEN",W103="IGEN"),0,IF(AND(K103&lt;&gt;"IGEN",L103="IGEN",U103="NEM"),0,IF(AND(H103="GYES",E103&lt;1998),0,S103))))</f>
         <v/>
       </c>
       <c r="AI103" s="6">
@@ -24279,7 +24279,7 @@
         <v/>
       </c>
       <c r="AH104" s="6">
-        <f>IF(S104="","",IF(OR(I104=0,V104="IGEN",W104="IGEN"),0,IF(AND(K104&lt;&gt;"IGEN",L104="IGEN",U104="NEM"),0,S104)))</f>
+        <f>IF(S104="","",IF(OR(I104=0,V104="IGEN",W104="IGEN"),0,IF(AND(K104&lt;&gt;"IGEN",L104="IGEN",U104="NEM"),0,IF(AND(H104="GYES",E104&lt;1998),0,S104))))</f>
         <v/>
       </c>
       <c r="AI104" s="6">
@@ -24399,7 +24399,7 @@
         <v/>
       </c>
       <c r="AH105" s="6">
-        <f>IF(S105="","",IF(OR(I105=0,V105="IGEN",W105="IGEN"),0,IF(AND(K105&lt;&gt;"IGEN",L105="IGEN",U105="NEM"),0,S105)))</f>
+        <f>IF(S105="","",IF(OR(I105=0,V105="IGEN",W105="IGEN"),0,IF(AND(K105&lt;&gt;"IGEN",L105="IGEN",U105="NEM"),0,IF(AND(H105="GYES",E105&lt;1998),0,S105))))</f>
         <v/>
       </c>
       <c r="AI105" s="6">
@@ -24519,7 +24519,7 @@
         <v/>
       </c>
       <c r="AH106" s="6">
-        <f>IF(S106="","",IF(OR(I106=0,V106="IGEN",W106="IGEN"),0,IF(AND(K106&lt;&gt;"IGEN",L106="IGEN",U106="NEM"),0,S106)))</f>
+        <f>IF(S106="","",IF(OR(I106=0,V106="IGEN",W106="IGEN"),0,IF(AND(K106&lt;&gt;"IGEN",L106="IGEN",U106="NEM"),0,IF(AND(H106="GYES",E106&lt;1998),0,S106))))</f>
         <v/>
       </c>
       <c r="AI106" s="6">
@@ -24639,7 +24639,7 @@
         <v/>
       </c>
       <c r="AH107" s="6">
-        <f>IF(S107="","",IF(OR(I107=0,V107="IGEN",W107="IGEN"),0,IF(AND(K107&lt;&gt;"IGEN",L107="IGEN",U107="NEM"),0,S107)))</f>
+        <f>IF(S107="","",IF(OR(I107=0,V107="IGEN",W107="IGEN"),0,IF(AND(K107&lt;&gt;"IGEN",L107="IGEN",U107="NEM"),0,IF(AND(H107="GYES",E107&lt;1998),0,S107))))</f>
         <v/>
       </c>
       <c r="AI107" s="6">
@@ -24759,7 +24759,7 @@
         <v/>
       </c>
       <c r="AH108" s="6">
-        <f>IF(S108="","",IF(OR(I108=0,V108="IGEN",W108="IGEN"),0,IF(AND(K108&lt;&gt;"IGEN",L108="IGEN",U108="NEM"),0,S108)))</f>
+        <f>IF(S108="","",IF(OR(I108=0,V108="IGEN",W108="IGEN"),0,IF(AND(K108&lt;&gt;"IGEN",L108="IGEN",U108="NEM"),0,IF(AND(H108="GYES",E108&lt;1998),0,S108))))</f>
         <v/>
       </c>
       <c r="AI108" s="6">
@@ -24879,7 +24879,7 @@
         <v/>
       </c>
       <c r="AH109" s="6">
-        <f>IF(S109="","",IF(OR(I109=0,V109="IGEN",W109="IGEN"),0,IF(AND(K109&lt;&gt;"IGEN",L109="IGEN",U109="NEM"),0,S109)))</f>
+        <f>IF(S109="","",IF(OR(I109=0,V109="IGEN",W109="IGEN"),0,IF(AND(K109&lt;&gt;"IGEN",L109="IGEN",U109="NEM"),0,IF(AND(H109="GYES",E109&lt;1998),0,S109))))</f>
         <v/>
       </c>
       <c r="AI109" s="6">
@@ -24999,7 +24999,7 @@
         <v/>
       </c>
       <c r="AH110" s="6">
-        <f>IF(S110="","",IF(OR(I110=0,V110="IGEN",W110="IGEN"),0,IF(AND(K110&lt;&gt;"IGEN",L110="IGEN",U110="NEM"),0,S110)))</f>
+        <f>IF(S110="","",IF(OR(I110=0,V110="IGEN",W110="IGEN"),0,IF(AND(K110&lt;&gt;"IGEN",L110="IGEN",U110="NEM"),0,IF(AND(H110="GYES",E110&lt;1998),0,S110))))</f>
         <v/>
       </c>
       <c r="AI110" s="6">
@@ -25119,7 +25119,7 @@
         <v/>
       </c>
       <c r="AH111" s="6">
-        <f>IF(S111="","",IF(OR(I111=0,V111="IGEN",W111="IGEN"),0,IF(AND(K111&lt;&gt;"IGEN",L111="IGEN",U111="NEM"),0,S111)))</f>
+        <f>IF(S111="","",IF(OR(I111=0,V111="IGEN",W111="IGEN"),0,IF(AND(K111&lt;&gt;"IGEN",L111="IGEN",U111="NEM"),0,IF(AND(H111="GYES",E111&lt;1998),0,S111))))</f>
         <v/>
       </c>
       <c r="AI111" s="6">
@@ -25239,7 +25239,7 @@
         <v/>
       </c>
       <c r="AH112" s="6">
-        <f>IF(S112="","",IF(OR(I112=0,V112="IGEN",W112="IGEN"),0,IF(AND(K112&lt;&gt;"IGEN",L112="IGEN",U112="NEM"),0,S112)))</f>
+        <f>IF(S112="","",IF(OR(I112=0,V112="IGEN",W112="IGEN"),0,IF(AND(K112&lt;&gt;"IGEN",L112="IGEN",U112="NEM"),0,IF(AND(H112="GYES",E112&lt;1998),0,S112))))</f>
         <v/>
       </c>
       <c r="AI112" s="6">
@@ -25359,7 +25359,7 @@
         <v/>
       </c>
       <c r="AH113" s="6">
-        <f>IF(S113="","",IF(OR(I113=0,V113="IGEN",W113="IGEN"),0,IF(AND(K113&lt;&gt;"IGEN",L113="IGEN",U113="NEM"),0,S113)))</f>
+        <f>IF(S113="","",IF(OR(I113=0,V113="IGEN",W113="IGEN"),0,IF(AND(K113&lt;&gt;"IGEN",L113="IGEN",U113="NEM"),0,IF(AND(H113="GYES",E113&lt;1998),0,S113))))</f>
         <v/>
       </c>
       <c r="AI113" s="6">
@@ -25479,7 +25479,7 @@
         <v/>
       </c>
       <c r="AH114" s="6">
-        <f>IF(S114="","",IF(OR(I114=0,V114="IGEN",W114="IGEN"),0,IF(AND(K114&lt;&gt;"IGEN",L114="IGEN",U114="NEM"),0,S114)))</f>
+        <f>IF(S114="","",IF(OR(I114=0,V114="IGEN",W114="IGEN"),0,IF(AND(K114&lt;&gt;"IGEN",L114="IGEN",U114="NEM"),0,IF(AND(H114="GYES",E114&lt;1998),0,S114))))</f>
         <v/>
       </c>
       <c r="AI114" s="6">
@@ -25599,7 +25599,7 @@
         <v/>
       </c>
       <c r="AH115" s="6">
-        <f>IF(S115="","",IF(OR(I115=0,V115="IGEN",W115="IGEN"),0,IF(AND(K115&lt;&gt;"IGEN",L115="IGEN",U115="NEM"),0,S115)))</f>
+        <f>IF(S115="","",IF(OR(I115=0,V115="IGEN",W115="IGEN"),0,IF(AND(K115&lt;&gt;"IGEN",L115="IGEN",U115="NEM"),0,IF(AND(H115="GYES",E115&lt;1998),0,S115))))</f>
         <v/>
       </c>
       <c r="AI115" s="6">
@@ -25719,7 +25719,7 @@
         <v/>
       </c>
       <c r="AH116" s="6">
-        <f>IF(S116="","",IF(OR(I116=0,V116="IGEN",W116="IGEN"),0,IF(AND(K116&lt;&gt;"IGEN",L116="IGEN",U116="NEM"),0,S116)))</f>
+        <f>IF(S116="","",IF(OR(I116=0,V116="IGEN",W116="IGEN"),0,IF(AND(K116&lt;&gt;"IGEN",L116="IGEN",U116="NEM"),0,IF(AND(H116="GYES",E116&lt;1998),0,S116))))</f>
         <v/>
       </c>
       <c r="AI116" s="6">
@@ -25839,7 +25839,7 @@
         <v/>
       </c>
       <c r="AH117" s="6">
-        <f>IF(S117="","",IF(OR(I117=0,V117="IGEN",W117="IGEN"),0,IF(AND(K117&lt;&gt;"IGEN",L117="IGEN",U117="NEM"),0,S117)))</f>
+        <f>IF(S117="","",IF(OR(I117=0,V117="IGEN",W117="IGEN"),0,IF(AND(K117&lt;&gt;"IGEN",L117="IGEN",U117="NEM"),0,IF(AND(H117="GYES",E117&lt;1998),0,S117))))</f>
         <v/>
       </c>
       <c r="AI117" s="6">
@@ -25959,7 +25959,7 @@
         <v/>
       </c>
       <c r="AH118" s="6">
-        <f>IF(S118="","",IF(OR(I118=0,V118="IGEN",W118="IGEN"),0,IF(AND(K118&lt;&gt;"IGEN",L118="IGEN",U118="NEM"),0,S118)))</f>
+        <f>IF(S118="","",IF(OR(I118=0,V118="IGEN",W118="IGEN"),0,IF(AND(K118&lt;&gt;"IGEN",L118="IGEN",U118="NEM"),0,IF(AND(H118="GYES",E118&lt;1998),0,S118))))</f>
         <v/>
       </c>
       <c r="AI118" s="6">
@@ -26079,7 +26079,7 @@
         <v/>
       </c>
       <c r="AH119" s="6">
-        <f>IF(S119="","",IF(OR(I119=0,V119="IGEN",W119="IGEN"),0,IF(AND(K119&lt;&gt;"IGEN",L119="IGEN",U119="NEM"),0,S119)))</f>
+        <f>IF(S119="","",IF(OR(I119=0,V119="IGEN",W119="IGEN"),0,IF(AND(K119&lt;&gt;"IGEN",L119="IGEN",U119="NEM"),0,IF(AND(H119="GYES",E119&lt;1998),0,S119))))</f>
         <v/>
       </c>
       <c r="AI119" s="6">
@@ -26199,7 +26199,7 @@
         <v/>
       </c>
       <c r="AH120" s="6">
-        <f>IF(S120="","",IF(OR(I120=0,V120="IGEN",W120="IGEN"),0,IF(AND(K120&lt;&gt;"IGEN",L120="IGEN",U120="NEM"),0,S120)))</f>
+        <f>IF(S120="","",IF(OR(I120=0,V120="IGEN",W120="IGEN"),0,IF(AND(K120&lt;&gt;"IGEN",L120="IGEN",U120="NEM"),0,IF(AND(H120="GYES",E120&lt;1998),0,S120))))</f>
         <v/>
       </c>
       <c r="AI120" s="6">
@@ -26319,7 +26319,7 @@
         <v/>
       </c>
       <c r="AH121" s="6">
-        <f>IF(S121="","",IF(OR(I121=0,V121="IGEN",W121="IGEN"),0,IF(AND(K121&lt;&gt;"IGEN",L121="IGEN",U121="NEM"),0,S121)))</f>
+        <f>IF(S121="","",IF(OR(I121=0,V121="IGEN",W121="IGEN"),0,IF(AND(K121&lt;&gt;"IGEN",L121="IGEN",U121="NEM"),0,IF(AND(H121="GYES",E121&lt;1998),0,S121))))</f>
         <v/>
       </c>
       <c r="AI121" s="6">
@@ -26439,7 +26439,7 @@
         <v/>
       </c>
       <c r="AH122" s="6">
-        <f>IF(S122="","",IF(OR(I122=0,V122="IGEN",W122="IGEN"),0,IF(AND(K122&lt;&gt;"IGEN",L122="IGEN",U122="NEM"),0,S122)))</f>
+        <f>IF(S122="","",IF(OR(I122=0,V122="IGEN",W122="IGEN"),0,IF(AND(K122&lt;&gt;"IGEN",L122="IGEN",U122="NEM"),0,IF(AND(H122="GYES",E122&lt;1998),0,S122))))</f>
         <v/>
       </c>
       <c r="AI122" s="6">
@@ -26559,7 +26559,7 @@
         <v/>
       </c>
       <c r="AH123" s="6">
-        <f>IF(S123="","",IF(OR(I123=0,V123="IGEN",W123="IGEN"),0,IF(AND(K123&lt;&gt;"IGEN",L123="IGEN",U123="NEM"),0,S123)))</f>
+        <f>IF(S123="","",IF(OR(I123=0,V123="IGEN",W123="IGEN"),0,IF(AND(K123&lt;&gt;"IGEN",L123="IGEN",U123="NEM"),0,IF(AND(H123="GYES",E123&lt;1998),0,S123))))</f>
         <v/>
       </c>
       <c r="AI123" s="6">
@@ -26679,7 +26679,7 @@
         <v/>
       </c>
       <c r="AH124" s="6">
-        <f>IF(S124="","",IF(OR(I124=0,V124="IGEN",W124="IGEN"),0,IF(AND(K124&lt;&gt;"IGEN",L124="IGEN",U124="NEM"),0,S124)))</f>
+        <f>IF(S124="","",IF(OR(I124=0,V124="IGEN",W124="IGEN"),0,IF(AND(K124&lt;&gt;"IGEN",L124="IGEN",U124="NEM"),0,IF(AND(H124="GYES",E124&lt;1998),0,S124))))</f>
         <v/>
       </c>
       <c r="AI124" s="6">
@@ -26799,7 +26799,7 @@
         <v/>
       </c>
       <c r="AH125" s="6">
-        <f>IF(S125="","",IF(OR(I125=0,V125="IGEN",W125="IGEN"),0,IF(AND(K125&lt;&gt;"IGEN",L125="IGEN",U125="NEM"),0,S125)))</f>
+        <f>IF(S125="","",IF(OR(I125=0,V125="IGEN",W125="IGEN"),0,IF(AND(K125&lt;&gt;"IGEN",L125="IGEN",U125="NEM"),0,IF(AND(H125="GYES",E125&lt;1998),0,S125))))</f>
         <v/>
       </c>
       <c r="AI125" s="6">
@@ -26919,7 +26919,7 @@
         <v/>
       </c>
       <c r="AH126" s="6">
-        <f>IF(S126="","",IF(OR(I126=0,V126="IGEN",W126="IGEN"),0,IF(AND(K126&lt;&gt;"IGEN",L126="IGEN",U126="NEM"),0,S126)))</f>
+        <f>IF(S126="","",IF(OR(I126=0,V126="IGEN",W126="IGEN"),0,IF(AND(K126&lt;&gt;"IGEN",L126="IGEN",U126="NEM"),0,IF(AND(H126="GYES",E126&lt;1998),0,S126))))</f>
         <v/>
       </c>
       <c r="AI126" s="6">
@@ -27039,7 +27039,7 @@
         <v/>
       </c>
       <c r="AH127" s="6">
-        <f>IF(S127="","",IF(OR(I127=0,V127="IGEN",W127="IGEN"),0,IF(AND(K127&lt;&gt;"IGEN",L127="IGEN",U127="NEM"),0,S127)))</f>
+        <f>IF(S127="","",IF(OR(I127=0,V127="IGEN",W127="IGEN"),0,IF(AND(K127&lt;&gt;"IGEN",L127="IGEN",U127="NEM"),0,IF(AND(H127="GYES",E127&lt;1998),0,S127))))</f>
         <v/>
       </c>
       <c r="AI127" s="6">
@@ -27159,7 +27159,7 @@
         <v/>
       </c>
       <c r="AH128" s="6">
-        <f>IF(S128="","",IF(OR(I128=0,V128="IGEN",W128="IGEN"),0,IF(AND(K128&lt;&gt;"IGEN",L128="IGEN",U128="NEM"),0,S128)))</f>
+        <f>IF(S128="","",IF(OR(I128=0,V128="IGEN",W128="IGEN"),0,IF(AND(K128&lt;&gt;"IGEN",L128="IGEN",U128="NEM"),0,IF(AND(H128="GYES",E128&lt;1998),0,S128))))</f>
         <v/>
       </c>
       <c r="AI128" s="6">
@@ -27279,7 +27279,7 @@
         <v/>
       </c>
       <c r="AH129" s="6">
-        <f>IF(S129="","",IF(OR(I129=0,V129="IGEN",W129="IGEN"),0,IF(AND(K129&lt;&gt;"IGEN",L129="IGEN",U129="NEM"),0,S129)))</f>
+        <f>IF(S129="","",IF(OR(I129=0,V129="IGEN",W129="IGEN"),0,IF(AND(K129&lt;&gt;"IGEN",L129="IGEN",U129="NEM"),0,IF(AND(H129="GYES",E129&lt;1998),0,S129))))</f>
         <v/>
       </c>
       <c r="AI129" s="6">
@@ -27399,7 +27399,7 @@
         <v/>
       </c>
       <c r="AH130" s="6">
-        <f>IF(S130="","",IF(OR(I130=0,V130="IGEN",W130="IGEN"),0,IF(AND(K130&lt;&gt;"IGEN",L130="IGEN",U130="NEM"),0,S130)))</f>
+        <f>IF(S130="","",IF(OR(I130=0,V130="IGEN",W130="IGEN"),0,IF(AND(K130&lt;&gt;"IGEN",L130="IGEN",U130="NEM"),0,IF(AND(H130="GYES",E130&lt;1998),0,S130))))</f>
         <v/>
       </c>
       <c r="AI130" s="6">
@@ -27519,7 +27519,7 @@
         <v/>
       </c>
       <c r="AH131" s="6">
-        <f>IF(S131="","",IF(OR(I131=0,V131="IGEN",W131="IGEN"),0,IF(AND(K131&lt;&gt;"IGEN",L131="IGEN",U131="NEM"),0,S131)))</f>
+        <f>IF(S131="","",IF(OR(I131=0,V131="IGEN",W131="IGEN"),0,IF(AND(K131&lt;&gt;"IGEN",L131="IGEN",U131="NEM"),0,IF(AND(H131="GYES",E131&lt;1998),0,S131))))</f>
         <v/>
       </c>
       <c r="AI131" s="6">
@@ -27639,7 +27639,7 @@
         <v/>
       </c>
       <c r="AH132" s="6">
-        <f>IF(S132="","",IF(OR(I132=0,V132="IGEN",W132="IGEN"),0,IF(AND(K132&lt;&gt;"IGEN",L132="IGEN",U132="NEM"),0,S132)))</f>
+        <f>IF(S132="","",IF(OR(I132=0,V132="IGEN",W132="IGEN"),0,IF(AND(K132&lt;&gt;"IGEN",L132="IGEN",U132="NEM"),0,IF(AND(H132="GYES",E132&lt;1998),0,S132))))</f>
         <v/>
       </c>
       <c r="AI132" s="6">
@@ -27759,7 +27759,7 @@
         <v/>
       </c>
       <c r="AH133" s="6">
-        <f>IF(S133="","",IF(OR(I133=0,V133="IGEN",W133="IGEN"),0,IF(AND(K133&lt;&gt;"IGEN",L133="IGEN",U133="NEM"),0,S133)))</f>
+        <f>IF(S133="","",IF(OR(I133=0,V133="IGEN",W133="IGEN"),0,IF(AND(K133&lt;&gt;"IGEN",L133="IGEN",U133="NEM"),0,IF(AND(H133="GYES",E133&lt;1998),0,S133))))</f>
         <v/>
       </c>
       <c r="AI133" s="6">
@@ -27879,7 +27879,7 @@
         <v/>
       </c>
       <c r="AH134" s="6">
-        <f>IF(S134="","",IF(OR(I134=0,V134="IGEN",W134="IGEN"),0,IF(AND(K134&lt;&gt;"IGEN",L134="IGEN",U134="NEM"),0,S134)))</f>
+        <f>IF(S134="","",IF(OR(I134=0,V134="IGEN",W134="IGEN"),0,IF(AND(K134&lt;&gt;"IGEN",L134="IGEN",U134="NEM"),0,IF(AND(H134="GYES",E134&lt;1998),0,S134))))</f>
         <v/>
       </c>
       <c r="AI134" s="6">
@@ -27999,7 +27999,7 @@
         <v/>
       </c>
       <c r="AH135" s="6">
-        <f>IF(S135="","",IF(OR(I135=0,V135="IGEN",W135="IGEN"),0,IF(AND(K135&lt;&gt;"IGEN",L135="IGEN",U135="NEM"),0,S135)))</f>
+        <f>IF(S135="","",IF(OR(I135=0,V135="IGEN",W135="IGEN"),0,IF(AND(K135&lt;&gt;"IGEN",L135="IGEN",U135="NEM"),0,IF(AND(H135="GYES",E135&lt;1998),0,S135))))</f>
         <v/>
       </c>
       <c r="AI135" s="6">
@@ -28119,7 +28119,7 @@
         <v/>
       </c>
       <c r="AH136" s="6">
-        <f>IF(S136="","",IF(OR(I136=0,V136="IGEN",W136="IGEN"),0,IF(AND(K136&lt;&gt;"IGEN",L136="IGEN",U136="NEM"),0,S136)))</f>
+        <f>IF(S136="","",IF(OR(I136=0,V136="IGEN",W136="IGEN"),0,IF(AND(K136&lt;&gt;"IGEN",L136="IGEN",U136="NEM"),0,IF(AND(H136="GYES",E136&lt;1998),0,S136))))</f>
         <v/>
       </c>
       <c r="AI136" s="6">
@@ -28239,7 +28239,7 @@
         <v/>
       </c>
       <c r="AH137" s="6">
-        <f>IF(S137="","",IF(OR(I137=0,V137="IGEN",W137="IGEN"),0,IF(AND(K137&lt;&gt;"IGEN",L137="IGEN",U137="NEM"),0,S137)))</f>
+        <f>IF(S137="","",IF(OR(I137=0,V137="IGEN",W137="IGEN"),0,IF(AND(K137&lt;&gt;"IGEN",L137="IGEN",U137="NEM"),0,IF(AND(H137="GYES",E137&lt;1998),0,S137))))</f>
         <v/>
       </c>
       <c r="AI137" s="6">
@@ -28359,7 +28359,7 @@
         <v/>
       </c>
       <c r="AH138" s="6">
-        <f>IF(S138="","",IF(OR(I138=0,V138="IGEN",W138="IGEN"),0,IF(AND(K138&lt;&gt;"IGEN",L138="IGEN",U138="NEM"),0,S138)))</f>
+        <f>IF(S138="","",IF(OR(I138=0,V138="IGEN",W138="IGEN"),0,IF(AND(K138&lt;&gt;"IGEN",L138="IGEN",U138="NEM"),0,IF(AND(H138="GYES",E138&lt;1998),0,S138))))</f>
         <v/>
       </c>
       <c r="AI138" s="6">
@@ -28479,7 +28479,7 @@
         <v/>
       </c>
       <c r="AH139" s="6">
-        <f>IF(S139="","",IF(OR(I139=0,V139="IGEN",W139="IGEN"),0,IF(AND(K139&lt;&gt;"IGEN",L139="IGEN",U139="NEM"),0,S139)))</f>
+        <f>IF(S139="","",IF(OR(I139=0,V139="IGEN",W139="IGEN"),0,IF(AND(K139&lt;&gt;"IGEN",L139="IGEN",U139="NEM"),0,IF(AND(H139="GYES",E139&lt;1998),0,S139))))</f>
         <v/>
       </c>
       <c r="AI139" s="6">
@@ -28599,7 +28599,7 @@
         <v/>
       </c>
       <c r="AH140" s="6">
-        <f>IF(S140="","",IF(OR(I140=0,V140="IGEN",W140="IGEN"),0,IF(AND(K140&lt;&gt;"IGEN",L140="IGEN",U140="NEM"),0,S140)))</f>
+        <f>IF(S140="","",IF(OR(I140=0,V140="IGEN",W140="IGEN"),0,IF(AND(K140&lt;&gt;"IGEN",L140="IGEN",U140="NEM"),0,IF(AND(H140="GYES",E140&lt;1998),0,S140))))</f>
         <v/>
       </c>
       <c r="AI140" s="6">
@@ -28719,7 +28719,7 @@
         <v/>
       </c>
       <c r="AH141" s="6">
-        <f>IF(S141="","",IF(OR(I141=0,V141="IGEN",W141="IGEN"),0,IF(AND(K141&lt;&gt;"IGEN",L141="IGEN",U141="NEM"),0,S141)))</f>
+        <f>IF(S141="","",IF(OR(I141=0,V141="IGEN",W141="IGEN"),0,IF(AND(K141&lt;&gt;"IGEN",L141="IGEN",U141="NEM"),0,IF(AND(H141="GYES",E141&lt;1998),0,S141))))</f>
         <v/>
       </c>
       <c r="AI141" s="6">
@@ -28839,7 +28839,7 @@
         <v/>
       </c>
       <c r="AH142" s="6">
-        <f>IF(S142="","",IF(OR(I142=0,V142="IGEN",W142="IGEN"),0,IF(AND(K142&lt;&gt;"IGEN",L142="IGEN",U142="NEM"),0,S142)))</f>
+        <f>IF(S142="","",IF(OR(I142=0,V142="IGEN",W142="IGEN"),0,IF(AND(K142&lt;&gt;"IGEN",L142="IGEN",U142="NEM"),0,IF(AND(H142="GYES",E142&lt;1998),0,S142))))</f>
         <v/>
       </c>
       <c r="AI142" s="6">
@@ -28959,7 +28959,7 @@
         <v/>
       </c>
       <c r="AH143" s="6">
-        <f>IF(S143="","",IF(OR(I143=0,V143="IGEN",W143="IGEN"),0,IF(AND(K143&lt;&gt;"IGEN",L143="IGEN",U143="NEM"),0,S143)))</f>
+        <f>IF(S143="","",IF(OR(I143=0,V143="IGEN",W143="IGEN"),0,IF(AND(K143&lt;&gt;"IGEN",L143="IGEN",U143="NEM"),0,IF(AND(H143="GYES",E143&lt;1998),0,S143))))</f>
         <v/>
       </c>
       <c r="AI143" s="6">
@@ -29079,7 +29079,7 @@
         <v/>
       </c>
       <c r="AH144" s="6">
-        <f>IF(S144="","",IF(OR(I144=0,V144="IGEN",W144="IGEN"),0,IF(AND(K144&lt;&gt;"IGEN",L144="IGEN",U144="NEM"),0,S144)))</f>
+        <f>IF(S144="","",IF(OR(I144=0,V144="IGEN",W144="IGEN"),0,IF(AND(K144&lt;&gt;"IGEN",L144="IGEN",U144="NEM"),0,IF(AND(H144="GYES",E144&lt;1998),0,S144))))</f>
         <v/>
       </c>
       <c r="AI144" s="6">
@@ -29199,7 +29199,7 @@
         <v/>
       </c>
       <c r="AH145" s="6">
-        <f>IF(S145="","",IF(OR(I145=0,V145="IGEN",W145="IGEN"),0,IF(AND(K145&lt;&gt;"IGEN",L145="IGEN",U145="NEM"),0,S145)))</f>
+        <f>IF(S145="","",IF(OR(I145=0,V145="IGEN",W145="IGEN"),0,IF(AND(K145&lt;&gt;"IGEN",L145="IGEN",U145="NEM"),0,IF(AND(H145="GYES",E145&lt;1998),0,S145))))</f>
         <v/>
       </c>
       <c r="AI145" s="6">
@@ -29319,7 +29319,7 @@
         <v/>
       </c>
       <c r="AH146" s="6">
-        <f>IF(S146="","",IF(OR(I146=0,V146="IGEN",W146="IGEN"),0,IF(AND(K146&lt;&gt;"IGEN",L146="IGEN",U146="NEM"),0,S146)))</f>
+        <f>IF(S146="","",IF(OR(I146=0,V146="IGEN",W146="IGEN"),0,IF(AND(K146&lt;&gt;"IGEN",L146="IGEN",U146="NEM"),0,IF(AND(H146="GYES",E146&lt;1998),0,S146))))</f>
         <v/>
       </c>
       <c r="AI146" s="6">
@@ -29439,7 +29439,7 @@
         <v/>
       </c>
       <c r="AH147" s="6">
-        <f>IF(S147="","",IF(OR(I147=0,V147="IGEN",W147="IGEN"),0,IF(AND(K147&lt;&gt;"IGEN",L147="IGEN",U147="NEM"),0,S147)))</f>
+        <f>IF(S147="","",IF(OR(I147=0,V147="IGEN",W147="IGEN"),0,IF(AND(K147&lt;&gt;"IGEN",L147="IGEN",U147="NEM"),0,IF(AND(H147="GYES",E147&lt;1998),0,S147))))</f>
         <v/>
       </c>
       <c r="AI147" s="6">
@@ -29559,7 +29559,7 @@
         <v/>
       </c>
       <c r="AH148" s="6">
-        <f>IF(S148="","",IF(OR(I148=0,V148="IGEN",W148="IGEN"),0,IF(AND(K148&lt;&gt;"IGEN",L148="IGEN",U148="NEM"),0,S148)))</f>
+        <f>IF(S148="","",IF(OR(I148=0,V148="IGEN",W148="IGEN"),0,IF(AND(K148&lt;&gt;"IGEN",L148="IGEN",U148="NEM"),0,IF(AND(H148="GYES",E148&lt;1998),0,S148))))</f>
         <v/>
       </c>
       <c r="AI148" s="6">
@@ -29679,7 +29679,7 @@
         <v/>
       </c>
       <c r="AH149" s="6">
-        <f>IF(S149="","",IF(OR(I149=0,V149="IGEN",W149="IGEN"),0,IF(AND(K149&lt;&gt;"IGEN",L149="IGEN",U149="NEM"),0,S149)))</f>
+        <f>IF(S149="","",IF(OR(I149=0,V149="IGEN",W149="IGEN"),0,IF(AND(K149&lt;&gt;"IGEN",L149="IGEN",U149="NEM"),0,IF(AND(H149="GYES",E149&lt;1998),0,S149))))</f>
         <v/>
       </c>
       <c r="AI149" s="6">
@@ -29799,7 +29799,7 @@
         <v/>
       </c>
       <c r="AH150" s="6">
-        <f>IF(S150="","",IF(OR(I150=0,V150="IGEN",W150="IGEN"),0,IF(AND(K150&lt;&gt;"IGEN",L150="IGEN",U150="NEM"),0,S150)))</f>
+        <f>IF(S150="","",IF(OR(I150=0,V150="IGEN",W150="IGEN"),0,IF(AND(K150&lt;&gt;"IGEN",L150="IGEN",U150="NEM"),0,IF(AND(H150="GYES",E150&lt;1998),0,S150))))</f>
         <v/>
       </c>
       <c r="AI150" s="6">
@@ -29919,7 +29919,7 @@
         <v/>
       </c>
       <c r="AH151" s="6">
-        <f>IF(S151="","",IF(OR(I151=0,V151="IGEN",W151="IGEN"),0,IF(AND(K151&lt;&gt;"IGEN",L151="IGEN",U151="NEM"),0,S151)))</f>
+        <f>IF(S151="","",IF(OR(I151=0,V151="IGEN",W151="IGEN"),0,IF(AND(K151&lt;&gt;"IGEN",L151="IGEN",U151="NEM"),0,IF(AND(H151="GYES",E151&lt;1998),0,S151))))</f>
         <v/>
       </c>
       <c r="AI151" s="6">
@@ -30039,7 +30039,7 @@
         <v/>
       </c>
       <c r="AH152" s="6">
-        <f>IF(S152="","",IF(OR(I152=0,V152="IGEN",W152="IGEN"),0,IF(AND(K152&lt;&gt;"IGEN",L152="IGEN",U152="NEM"),0,S152)))</f>
+        <f>IF(S152="","",IF(OR(I152=0,V152="IGEN",W152="IGEN"),0,IF(AND(K152&lt;&gt;"IGEN",L152="IGEN",U152="NEM"),0,IF(AND(H152="GYES",E152&lt;1998),0,S152))))</f>
         <v/>
       </c>
       <c r="AI152" s="6">
@@ -30159,7 +30159,7 @@
         <v/>
       </c>
       <c r="AH153" s="6">
-        <f>IF(S153="","",IF(OR(I153=0,V153="IGEN",W153="IGEN"),0,IF(AND(K153&lt;&gt;"IGEN",L153="IGEN",U153="NEM"),0,S153)))</f>
+        <f>IF(S153="","",IF(OR(I153=0,V153="IGEN",W153="IGEN"),0,IF(AND(K153&lt;&gt;"IGEN",L153="IGEN",U153="NEM"),0,IF(AND(H153="GYES",E153&lt;1998),0,S153))))</f>
         <v/>
       </c>
       <c r="AI153" s="6">
@@ -30279,7 +30279,7 @@
         <v/>
       </c>
       <c r="AH154" s="6">
-        <f>IF(S154="","",IF(OR(I154=0,V154="IGEN",W154="IGEN"),0,IF(AND(K154&lt;&gt;"IGEN",L154="IGEN",U154="NEM"),0,S154)))</f>
+        <f>IF(S154="","",IF(OR(I154=0,V154="IGEN",W154="IGEN"),0,IF(AND(K154&lt;&gt;"IGEN",L154="IGEN",U154="NEM"),0,IF(AND(H154="GYES",E154&lt;1998),0,S154))))</f>
         <v/>
       </c>
       <c r="AI154" s="6">
@@ -30399,7 +30399,7 @@
         <v/>
       </c>
       <c r="AH155" s="6">
-        <f>IF(S155="","",IF(OR(I155=0,V155="IGEN",W155="IGEN"),0,IF(AND(K155&lt;&gt;"IGEN",L155="IGEN",U155="NEM"),0,S155)))</f>
+        <f>IF(S155="","",IF(OR(I155=0,V155="IGEN",W155="IGEN"),0,IF(AND(K155&lt;&gt;"IGEN",L155="IGEN",U155="NEM"),0,IF(AND(H155="GYES",E155&lt;1998),0,S155))))</f>
         <v/>
       </c>
       <c r="AI155" s="6">
@@ -30519,7 +30519,7 @@
         <v/>
       </c>
       <c r="AH156" s="6">
-        <f>IF(S156="","",IF(OR(I156=0,V156="IGEN",W156="IGEN"),0,IF(AND(K156&lt;&gt;"IGEN",L156="IGEN",U156="NEM"),0,S156)))</f>
+        <f>IF(S156="","",IF(OR(I156=0,V156="IGEN",W156="IGEN"),0,IF(AND(K156&lt;&gt;"IGEN",L156="IGEN",U156="NEM"),0,IF(AND(H156="GYES",E156&lt;1998),0,S156))))</f>
         <v/>
       </c>
       <c r="AI156" s="6">
@@ -30639,7 +30639,7 @@
         <v/>
       </c>
       <c r="AH157" s="6">
-        <f>IF(S157="","",IF(OR(I157=0,V157="IGEN",W157="IGEN"),0,IF(AND(K157&lt;&gt;"IGEN",L157="IGEN",U157="NEM"),0,S157)))</f>
+        <f>IF(S157="","",IF(OR(I157=0,V157="IGEN",W157="IGEN"),0,IF(AND(K157&lt;&gt;"IGEN",L157="IGEN",U157="NEM"),0,IF(AND(H157="GYES",E157&lt;1998),0,S157))))</f>
         <v/>
       </c>
       <c r="AI157" s="6">
@@ -30759,7 +30759,7 @@
         <v/>
       </c>
       <c r="AH158" s="6">
-        <f>IF(S158="","",IF(OR(I158=0,V158="IGEN",W158="IGEN"),0,IF(AND(K158&lt;&gt;"IGEN",L158="IGEN",U158="NEM"),0,S158)))</f>
+        <f>IF(S158="","",IF(OR(I158=0,V158="IGEN",W158="IGEN"),0,IF(AND(K158&lt;&gt;"IGEN",L158="IGEN",U158="NEM"),0,IF(AND(H158="GYES",E158&lt;1998),0,S158))))</f>
         <v/>
       </c>
       <c r="AI158" s="6">
@@ -30879,7 +30879,7 @@
         <v/>
       </c>
       <c r="AH159" s="6">
-        <f>IF(S159="","",IF(OR(I159=0,V159="IGEN",W159="IGEN"),0,IF(AND(K159&lt;&gt;"IGEN",L159="IGEN",U159="NEM"),0,S159)))</f>
+        <f>IF(S159="","",IF(OR(I159=0,V159="IGEN",W159="IGEN"),0,IF(AND(K159&lt;&gt;"IGEN",L159="IGEN",U159="NEM"),0,IF(AND(H159="GYES",E159&lt;1998),0,S159))))</f>
         <v/>
       </c>
       <c r="AI159" s="6">
@@ -30999,7 +30999,7 @@
         <v/>
       </c>
       <c r="AH160" s="6">
-        <f>IF(S160="","",IF(OR(I160=0,V160="IGEN",W160="IGEN"),0,IF(AND(K160&lt;&gt;"IGEN",L160="IGEN",U160="NEM"),0,S160)))</f>
+        <f>IF(S160="","",IF(OR(I160=0,V160="IGEN",W160="IGEN"),0,IF(AND(K160&lt;&gt;"IGEN",L160="IGEN",U160="NEM"),0,IF(AND(H160="GYES",E160&lt;1998),0,S160))))</f>
         <v/>
       </c>
       <c r="AI160" s="6">
@@ -31119,7 +31119,7 @@
         <v/>
       </c>
       <c r="AH161" s="6">
-        <f>IF(S161="","",IF(OR(I161=0,V161="IGEN",W161="IGEN"),0,IF(AND(K161&lt;&gt;"IGEN",L161="IGEN",U161="NEM"),0,S161)))</f>
+        <f>IF(S161="","",IF(OR(I161=0,V161="IGEN",W161="IGEN"),0,IF(AND(K161&lt;&gt;"IGEN",L161="IGEN",U161="NEM"),0,IF(AND(H161="GYES",E161&lt;1998),0,S161))))</f>
         <v/>
       </c>
       <c r="AI161" s="6">
@@ -31239,7 +31239,7 @@
         <v/>
       </c>
       <c r="AH162" s="6">
-        <f>IF(S162="","",IF(OR(I162=0,V162="IGEN",W162="IGEN"),0,IF(AND(K162&lt;&gt;"IGEN",L162="IGEN",U162="NEM"),0,S162)))</f>
+        <f>IF(S162="","",IF(OR(I162=0,V162="IGEN",W162="IGEN"),0,IF(AND(K162&lt;&gt;"IGEN",L162="IGEN",U162="NEM"),0,IF(AND(H162="GYES",E162&lt;1998),0,S162))))</f>
         <v/>
       </c>
       <c r="AI162" s="6">
@@ -31359,7 +31359,7 @@
         <v/>
       </c>
       <c r="AH163" s="6">
-        <f>IF(S163="","",IF(OR(I163=0,V163="IGEN",W163="IGEN"),0,IF(AND(K163&lt;&gt;"IGEN",L163="IGEN",U163="NEM"),0,S163)))</f>
+        <f>IF(S163="","",IF(OR(I163=0,V163="IGEN",W163="IGEN"),0,IF(AND(K163&lt;&gt;"IGEN",L163="IGEN",U163="NEM"),0,IF(AND(H163="GYES",E163&lt;1998),0,S163))))</f>
         <v/>
       </c>
       <c r="AI163" s="6">
@@ -31479,7 +31479,7 @@
         <v/>
       </c>
       <c r="AH164" s="6">
-        <f>IF(S164="","",IF(OR(I164=0,V164="IGEN",W164="IGEN"),0,IF(AND(K164&lt;&gt;"IGEN",L164="IGEN",U164="NEM"),0,S164)))</f>
+        <f>IF(S164="","",IF(OR(I164=0,V164="IGEN",W164="IGEN"),0,IF(AND(K164&lt;&gt;"IGEN",L164="IGEN",U164="NEM"),0,IF(AND(H164="GYES",E164&lt;1998),0,S164))))</f>
         <v/>
       </c>
       <c r="AI164" s="6">
@@ -31599,7 +31599,7 @@
         <v/>
       </c>
       <c r="AH165" s="6">
-        <f>IF(S165="","",IF(OR(I165=0,V165="IGEN",W165="IGEN"),0,IF(AND(K165&lt;&gt;"IGEN",L165="IGEN",U165="NEM"),0,S165)))</f>
+        <f>IF(S165="","",IF(OR(I165=0,V165="IGEN",W165="IGEN"),0,IF(AND(K165&lt;&gt;"IGEN",L165="IGEN",U165="NEM"),0,IF(AND(H165="GYES",E165&lt;1998),0,S165))))</f>
         <v/>
       </c>
       <c r="AI165" s="6">
@@ -31719,7 +31719,7 @@
         <v/>
       </c>
       <c r="AH166" s="6">
-        <f>IF(S166="","",IF(OR(I166=0,V166="IGEN",W166="IGEN"),0,IF(AND(K166&lt;&gt;"IGEN",L166="IGEN",U166="NEM"),0,S166)))</f>
+        <f>IF(S166="","",IF(OR(I166=0,V166="IGEN",W166="IGEN"),0,IF(AND(K166&lt;&gt;"IGEN",L166="IGEN",U166="NEM"),0,IF(AND(H166="GYES",E166&lt;1998),0,S166))))</f>
         <v/>
       </c>
       <c r="AI166" s="6">
@@ -31839,7 +31839,7 @@
         <v/>
       </c>
       <c r="AH167" s="6">
-        <f>IF(S167="","",IF(OR(I167=0,V167="IGEN",W167="IGEN"),0,IF(AND(K167&lt;&gt;"IGEN",L167="IGEN",U167="NEM"),0,S167)))</f>
+        <f>IF(S167="","",IF(OR(I167=0,V167="IGEN",W167="IGEN"),0,IF(AND(K167&lt;&gt;"IGEN",L167="IGEN",U167="NEM"),0,IF(AND(H167="GYES",E167&lt;1998),0,S167))))</f>
         <v/>
       </c>
       <c r="AI167" s="6">
@@ -31959,7 +31959,7 @@
         <v/>
       </c>
       <c r="AH168" s="6">
-        <f>IF(S168="","",IF(OR(I168=0,V168="IGEN",W168="IGEN"),0,IF(AND(K168&lt;&gt;"IGEN",L168="IGEN",U168="NEM"),0,S168)))</f>
+        <f>IF(S168="","",IF(OR(I168=0,V168="IGEN",W168="IGEN"),0,IF(AND(K168&lt;&gt;"IGEN",L168="IGEN",U168="NEM"),0,IF(AND(H168="GYES",E168&lt;1998),0,S168))))</f>
         <v/>
       </c>
       <c r="AI168" s="6">
@@ -32079,7 +32079,7 @@
         <v/>
       </c>
       <c r="AH169" s="6">
-        <f>IF(S169="","",IF(OR(I169=0,V169="IGEN",W169="IGEN"),0,IF(AND(K169&lt;&gt;"IGEN",L169="IGEN",U169="NEM"),0,S169)))</f>
+        <f>IF(S169="","",IF(OR(I169=0,V169="IGEN",W169="IGEN"),0,IF(AND(K169&lt;&gt;"IGEN",L169="IGEN",U169="NEM"),0,IF(AND(H169="GYES",E169&lt;1998),0,S169))))</f>
         <v/>
       </c>
       <c r="AI169" s="6">
@@ -32199,7 +32199,7 @@
         <v/>
       </c>
       <c r="AH170" s="6">
-        <f>IF(S170="","",IF(OR(I170=0,V170="IGEN",W170="IGEN"),0,IF(AND(K170&lt;&gt;"IGEN",L170="IGEN",U170="NEM"),0,S170)))</f>
+        <f>IF(S170="","",IF(OR(I170=0,V170="IGEN",W170="IGEN"),0,IF(AND(K170&lt;&gt;"IGEN",L170="IGEN",U170="NEM"),0,IF(AND(H170="GYES",E170&lt;1998),0,S170))))</f>
         <v/>
       </c>
       <c r="AI170" s="6">
@@ -32319,7 +32319,7 @@
         <v/>
       </c>
       <c r="AH171" s="6">
-        <f>IF(S171="","",IF(OR(I171=0,V171="IGEN",W171="IGEN"),0,IF(AND(K171&lt;&gt;"IGEN",L171="IGEN",U171="NEM"),0,S171)))</f>
+        <f>IF(S171="","",IF(OR(I171=0,V171="IGEN",W171="IGEN"),0,IF(AND(K171&lt;&gt;"IGEN",L171="IGEN",U171="NEM"),0,IF(AND(H171="GYES",E171&lt;1998),0,S171))))</f>
         <v/>
       </c>
       <c r="AI171" s="6">
@@ -32439,7 +32439,7 @@
         <v/>
       </c>
       <c r="AH172" s="6">
-        <f>IF(S172="","",IF(OR(I172=0,V172="IGEN",W172="IGEN"),0,IF(AND(K172&lt;&gt;"IGEN",L172="IGEN",U172="NEM"),0,S172)))</f>
+        <f>IF(S172="","",IF(OR(I172=0,V172="IGEN",W172="IGEN"),0,IF(AND(K172&lt;&gt;"IGEN",L172="IGEN",U172="NEM"),0,IF(AND(H172="GYES",E172&lt;1998),0,S172))))</f>
         <v/>
       </c>
       <c r="AI172" s="6">
@@ -32559,7 +32559,7 @@
         <v/>
       </c>
       <c r="AH173" s="6">
-        <f>IF(S173="","",IF(OR(I173=0,V173="IGEN",W173="IGEN"),0,IF(AND(K173&lt;&gt;"IGEN",L173="IGEN",U173="NEM"),0,S173)))</f>
+        <f>IF(S173="","",IF(OR(I173=0,V173="IGEN",W173="IGEN"),0,IF(AND(K173&lt;&gt;"IGEN",L173="IGEN",U173="NEM"),0,IF(AND(H173="GYES",E173&lt;1998),0,S173))))</f>
         <v/>
       </c>
       <c r="AI173" s="6">
@@ -32679,7 +32679,7 @@
         <v/>
       </c>
       <c r="AH174" s="6">
-        <f>IF(S174="","",IF(OR(I174=0,V174="IGEN",W174="IGEN"),0,IF(AND(K174&lt;&gt;"IGEN",L174="IGEN",U174="NEM"),0,S174)))</f>
+        <f>IF(S174="","",IF(OR(I174=0,V174="IGEN",W174="IGEN"),0,IF(AND(K174&lt;&gt;"IGEN",L174="IGEN",U174="NEM"),0,IF(AND(H174="GYES",E174&lt;1998),0,S174))))</f>
         <v/>
       </c>
       <c r="AI174" s="6">
@@ -32799,7 +32799,7 @@
         <v/>
       </c>
       <c r="AH175" s="6">
-        <f>IF(S175="","",IF(OR(I175=0,V175="IGEN",W175="IGEN"),0,IF(AND(K175&lt;&gt;"IGEN",L175="IGEN",U175="NEM"),0,S175)))</f>
+        <f>IF(S175="","",IF(OR(I175=0,V175="IGEN",W175="IGEN"),0,IF(AND(K175&lt;&gt;"IGEN",L175="IGEN",U175="NEM"),0,IF(AND(H175="GYES",E175&lt;1998),0,S175))))</f>
         <v/>
       </c>
       <c r="AI175" s="6">
@@ -32919,7 +32919,7 @@
         <v/>
       </c>
       <c r="AH176" s="6">
-        <f>IF(S176="","",IF(OR(I176=0,V176="IGEN",W176="IGEN"),0,IF(AND(K176&lt;&gt;"IGEN",L176="IGEN",U176="NEM"),0,S176)))</f>
+        <f>IF(S176="","",IF(OR(I176=0,V176="IGEN",W176="IGEN"),0,IF(AND(K176&lt;&gt;"IGEN",L176="IGEN",U176="NEM"),0,IF(AND(H176="GYES",E176&lt;1998),0,S176))))</f>
         <v/>
       </c>
       <c r="AI176" s="6">
@@ -33039,7 +33039,7 @@
         <v/>
       </c>
       <c r="AH177" s="6">
-        <f>IF(S177="","",IF(OR(I177=0,V177="IGEN",W177="IGEN"),0,IF(AND(K177&lt;&gt;"IGEN",L177="IGEN",U177="NEM"),0,S177)))</f>
+        <f>IF(S177="","",IF(OR(I177=0,V177="IGEN",W177="IGEN"),0,IF(AND(K177&lt;&gt;"IGEN",L177="IGEN",U177="NEM"),0,IF(AND(H177="GYES",E177&lt;1998),0,S177))))</f>
         <v/>
       </c>
       <c r="AI177" s="6">
@@ -33159,7 +33159,7 @@
         <v/>
       </c>
       <c r="AH178" s="6">
-        <f>IF(S178="","",IF(OR(I178=0,V178="IGEN",W178="IGEN"),0,IF(AND(K178&lt;&gt;"IGEN",L178="IGEN",U178="NEM"),0,S178)))</f>
+        <f>IF(S178="","",IF(OR(I178=0,V178="IGEN",W178="IGEN"),0,IF(AND(K178&lt;&gt;"IGEN",L178="IGEN",U178="NEM"),0,IF(AND(H178="GYES",E178&lt;1998),0,S178))))</f>
         <v/>
       </c>
       <c r="AI178" s="6">
@@ -33279,7 +33279,7 @@
         <v/>
       </c>
       <c r="AH179" s="6">
-        <f>IF(S179="","",IF(OR(I179=0,V179="IGEN",W179="IGEN"),0,IF(AND(K179&lt;&gt;"IGEN",L179="IGEN",U179="NEM"),0,S179)))</f>
+        <f>IF(S179="","",IF(OR(I179=0,V179="IGEN",W179="IGEN"),0,IF(AND(K179&lt;&gt;"IGEN",L179="IGEN",U179="NEM"),0,IF(AND(H179="GYES",E179&lt;1998),0,S179))))</f>
         <v/>
       </c>
       <c r="AI179" s="6">
@@ -33399,7 +33399,7 @@
         <v/>
       </c>
       <c r="AH180" s="6">
-        <f>IF(S180="","",IF(OR(I180=0,V180="IGEN",W180="IGEN"),0,IF(AND(K180&lt;&gt;"IGEN",L180="IGEN",U180="NEM"),0,S180)))</f>
+        <f>IF(S180="","",IF(OR(I180=0,V180="IGEN",W180="IGEN"),0,IF(AND(K180&lt;&gt;"IGEN",L180="IGEN",U180="NEM"),0,IF(AND(H180="GYES",E180&lt;1998),0,S180))))</f>
         <v/>
       </c>
       <c r="AI180" s="6">
@@ -33519,7 +33519,7 @@
         <v/>
       </c>
       <c r="AH181" s="6">
-        <f>IF(S181="","",IF(OR(I181=0,V181="IGEN",W181="IGEN"),0,IF(AND(K181&lt;&gt;"IGEN",L181="IGEN",U181="NEM"),0,S181)))</f>
+        <f>IF(S181="","",IF(OR(I181=0,V181="IGEN",W181="IGEN"),0,IF(AND(K181&lt;&gt;"IGEN",L181="IGEN",U181="NEM"),0,IF(AND(H181="GYES",E181&lt;1998),0,S181))))</f>
         <v/>
       </c>
       <c r="AI181" s="6">
@@ -33639,7 +33639,7 @@
         <v/>
       </c>
       <c r="AH182" s="6">
-        <f>IF(S182="","",IF(OR(I182=0,V182="IGEN",W182="IGEN"),0,IF(AND(K182&lt;&gt;"IGEN",L182="IGEN",U182="NEM"),0,S182)))</f>
+        <f>IF(S182="","",IF(OR(I182=0,V182="IGEN",W182="IGEN"),0,IF(AND(K182&lt;&gt;"IGEN",L182="IGEN",U182="NEM"),0,IF(AND(H182="GYES",E182&lt;1998),0,S182))))</f>
         <v/>
       </c>
       <c r="AI182" s="6">
@@ -33759,7 +33759,7 @@
         <v/>
       </c>
       <c r="AH183" s="6">
-        <f>IF(S183="","",IF(OR(I183=0,V183="IGEN",W183="IGEN"),0,IF(AND(K183&lt;&gt;"IGEN",L183="IGEN",U183="NEM"),0,S183)))</f>
+        <f>IF(S183="","",IF(OR(I183=0,V183="IGEN",W183="IGEN"),0,IF(AND(K183&lt;&gt;"IGEN",L183="IGEN",U183="NEM"),0,IF(AND(H183="GYES",E183&lt;1998),0,S183))))</f>
         <v/>
       </c>
       <c r="AI183" s="6">
@@ -33879,7 +33879,7 @@
         <v/>
       </c>
       <c r="AH184" s="6">
-        <f>IF(S184="","",IF(OR(I184=0,V184="IGEN",W184="IGEN"),0,IF(AND(K184&lt;&gt;"IGEN",L184="IGEN",U184="NEM"),0,S184)))</f>
+        <f>IF(S184="","",IF(OR(I184=0,V184="IGEN",W184="IGEN"),0,IF(AND(K184&lt;&gt;"IGEN",L184="IGEN",U184="NEM"),0,IF(AND(H184="GYES",E184&lt;1998),0,S184))))</f>
         <v/>
       </c>
       <c r="AI184" s="6">
@@ -33999,7 +33999,7 @@
         <v/>
       </c>
       <c r="AH185" s="6">
-        <f>IF(S185="","",IF(OR(I185=0,V185="IGEN",W185="IGEN"),0,IF(AND(K185&lt;&gt;"IGEN",L185="IGEN",U185="NEM"),0,S185)))</f>
+        <f>IF(S185="","",IF(OR(I185=0,V185="IGEN",W185="IGEN"),0,IF(AND(K185&lt;&gt;"IGEN",L185="IGEN",U185="NEM"),0,IF(AND(H185="GYES",E185&lt;1998),0,S185))))</f>
         <v/>
       </c>
       <c r="AI185" s="6">
@@ -34119,7 +34119,7 @@
         <v/>
       </c>
       <c r="AH186" s="6">
-        <f>IF(S186="","",IF(OR(I186=0,V186="IGEN",W186="IGEN"),0,IF(AND(K186&lt;&gt;"IGEN",L186="IGEN",U186="NEM"),0,S186)))</f>
+        <f>IF(S186="","",IF(OR(I186=0,V186="IGEN",W186="IGEN"),0,IF(AND(K186&lt;&gt;"IGEN",L186="IGEN",U186="NEM"),0,IF(AND(H186="GYES",E186&lt;1998),0,S186))))</f>
         <v/>
       </c>
       <c r="AI186" s="6">
@@ -34239,7 +34239,7 @@
         <v/>
       </c>
       <c r="AH187" s="6">
-        <f>IF(S187="","",IF(OR(I187=0,V187="IGEN",W187="IGEN"),0,IF(AND(K187&lt;&gt;"IGEN",L187="IGEN",U187="NEM"),0,S187)))</f>
+        <f>IF(S187="","",IF(OR(I187=0,V187="IGEN",W187="IGEN"),0,IF(AND(K187&lt;&gt;"IGEN",L187="IGEN",U187="NEM"),0,IF(AND(H187="GYES",E187&lt;1998),0,S187))))</f>
         <v/>
       </c>
       <c r="AI187" s="6">
@@ -34359,7 +34359,7 @@
         <v/>
       </c>
       <c r="AH188" s="6">
-        <f>IF(S188="","",IF(OR(I188=0,V188="IGEN",W188="IGEN"),0,IF(AND(K188&lt;&gt;"IGEN",L188="IGEN",U188="NEM"),0,S188)))</f>
+        <f>IF(S188="","",IF(OR(I188=0,V188="IGEN",W188="IGEN"),0,IF(AND(K188&lt;&gt;"IGEN",L188="IGEN",U188="NEM"),0,IF(AND(H188="GYES",E188&lt;1998),0,S188))))</f>
         <v/>
       </c>
       <c r="AI188" s="6">
@@ -34479,7 +34479,7 @@
         <v/>
       </c>
       <c r="AH189" s="6">
-        <f>IF(S189="","",IF(OR(I189=0,V189="IGEN",W189="IGEN"),0,IF(AND(K189&lt;&gt;"IGEN",L189="IGEN",U189="NEM"),0,S189)))</f>
+        <f>IF(S189="","",IF(OR(I189=0,V189="IGEN",W189="IGEN"),0,IF(AND(K189&lt;&gt;"IGEN",L189="IGEN",U189="NEM"),0,IF(AND(H189="GYES",E189&lt;1998),0,S189))))</f>
         <v/>
       </c>
       <c r="AI189" s="6">
@@ -34599,7 +34599,7 @@
         <v/>
       </c>
       <c r="AH190" s="6">
-        <f>IF(S190="","",IF(OR(I190=0,V190="IGEN",W190="IGEN"),0,IF(AND(K190&lt;&gt;"IGEN",L190="IGEN",U190="NEM"),0,S190)))</f>
+        <f>IF(S190="","",IF(OR(I190=0,V190="IGEN",W190="IGEN"),0,IF(AND(K190&lt;&gt;"IGEN",L190="IGEN",U190="NEM"),0,IF(AND(H190="GYES",E190&lt;1998),0,S190))))</f>
         <v/>
       </c>
       <c r="AI190" s="6">
@@ -34719,7 +34719,7 @@
         <v/>
       </c>
       <c r="AH191" s="6">
-        <f>IF(S191="","",IF(OR(I191=0,V191="IGEN",W191="IGEN"),0,IF(AND(K191&lt;&gt;"IGEN",L191="IGEN",U191="NEM"),0,S191)))</f>
+        <f>IF(S191="","",IF(OR(I191=0,V191="IGEN",W191="IGEN"),0,IF(AND(K191&lt;&gt;"IGEN",L191="IGEN",U191="NEM"),0,IF(AND(H191="GYES",E191&lt;1998),0,S191))))</f>
         <v/>
       </c>
       <c r="AI191" s="6">
@@ -34839,7 +34839,7 @@
         <v/>
       </c>
       <c r="AH192" s="6">
-        <f>IF(S192="","",IF(OR(I192=0,V192="IGEN",W192="IGEN"),0,IF(AND(K192&lt;&gt;"IGEN",L192="IGEN",U192="NEM"),0,S192)))</f>
+        <f>IF(S192="","",IF(OR(I192=0,V192="IGEN",W192="IGEN"),0,IF(AND(K192&lt;&gt;"IGEN",L192="IGEN",U192="NEM"),0,IF(AND(H192="GYES",E192&lt;1998),0,S192))))</f>
         <v/>
       </c>
       <c r="AI192" s="6">
@@ -34959,7 +34959,7 @@
         <v/>
       </c>
       <c r="AH193" s="6">
-        <f>IF(S193="","",IF(OR(I193=0,V193="IGEN",W193="IGEN"),0,IF(AND(K193&lt;&gt;"IGEN",L193="IGEN",U193="NEM"),0,S193)))</f>
+        <f>IF(S193="","",IF(OR(I193=0,V193="IGEN",W193="IGEN"),0,IF(AND(K193&lt;&gt;"IGEN",L193="IGEN",U193="NEM"),0,IF(AND(H193="GYES",E193&lt;1998),0,S193))))</f>
         <v/>
       </c>
       <c r="AI193" s="6">
@@ -35079,7 +35079,7 @@
         <v/>
       </c>
       <c r="AH194" s="6">
-        <f>IF(S194="","",IF(OR(I194=0,V194="IGEN",W194="IGEN"),0,IF(AND(K194&lt;&gt;"IGEN",L194="IGEN",U194="NEM"),0,S194)))</f>
+        <f>IF(S194="","",IF(OR(I194=0,V194="IGEN",W194="IGEN"),0,IF(AND(K194&lt;&gt;"IGEN",L194="IGEN",U194="NEM"),0,IF(AND(H194="GYES",E194&lt;1998),0,S194))))</f>
         <v/>
       </c>
       <c r="AI194" s="6">
@@ -35199,7 +35199,7 @@
         <v/>
       </c>
       <c r="AH195" s="6">
-        <f>IF(S195="","",IF(OR(I195=0,V195="IGEN",W195="IGEN"),0,IF(AND(K195&lt;&gt;"IGEN",L195="IGEN",U195="NEM"),0,S195)))</f>
+        <f>IF(S195="","",IF(OR(I195=0,V195="IGEN",W195="IGEN"),0,IF(AND(K195&lt;&gt;"IGEN",L195="IGEN",U195="NEM"),0,IF(AND(H195="GYES",E195&lt;1998),0,S195))))</f>
         <v/>
       </c>
       <c r="AI195" s="6">
@@ -35319,7 +35319,7 @@
         <v/>
       </c>
       <c r="AH196" s="6">
-        <f>IF(S196="","",IF(OR(I196=0,V196="IGEN",W196="IGEN"),0,IF(AND(K196&lt;&gt;"IGEN",L196="IGEN",U196="NEM"),0,S196)))</f>
+        <f>IF(S196="","",IF(OR(I196=0,V196="IGEN",W196="IGEN"),0,IF(AND(K196&lt;&gt;"IGEN",L196="IGEN",U196="NEM"),0,IF(AND(H196="GYES",E196&lt;1998),0,S196))))</f>
         <v/>
       </c>
       <c r="AI196" s="6">
@@ -35439,7 +35439,7 @@
         <v/>
       </c>
       <c r="AH197" s="6">
-        <f>IF(S197="","",IF(OR(I197=0,V197="IGEN",W197="IGEN"),0,IF(AND(K197&lt;&gt;"IGEN",L197="IGEN",U197="NEM"),0,S197)))</f>
+        <f>IF(S197="","",IF(OR(I197=0,V197="IGEN",W197="IGEN"),0,IF(AND(K197&lt;&gt;"IGEN",L197="IGEN",U197="NEM"),0,IF(AND(H197="GYES",E197&lt;1998),0,S197))))</f>
         <v/>
       </c>
       <c r="AI197" s="6">
@@ -35559,7 +35559,7 @@
         <v/>
       </c>
       <c r="AH198" s="6">
-        <f>IF(S198="","",IF(OR(I198=0,V198="IGEN",W198="IGEN"),0,IF(AND(K198&lt;&gt;"IGEN",L198="IGEN",U198="NEM"),0,S198)))</f>
+        <f>IF(S198="","",IF(OR(I198=0,V198="IGEN",W198="IGEN"),0,IF(AND(K198&lt;&gt;"IGEN",L198="IGEN",U198="NEM"),0,IF(AND(H198="GYES",E198&lt;1998),0,S198))))</f>
         <v/>
       </c>
       <c r="AI198" s="6">
@@ -35679,7 +35679,7 @@
         <v/>
       </c>
       <c r="AH199" s="6">
-        <f>IF(S199="","",IF(OR(I199=0,V199="IGEN",W199="IGEN"),0,IF(AND(K199&lt;&gt;"IGEN",L199="IGEN",U199="NEM"),0,S199)))</f>
+        <f>IF(S199="","",IF(OR(I199=0,V199="IGEN",W199="IGEN"),0,IF(AND(K199&lt;&gt;"IGEN",L199="IGEN",U199="NEM"),0,IF(AND(H199="GYES",E199&lt;1998),0,S199))))</f>
         <v/>
       </c>
       <c r="AI199" s="6">
@@ -35799,7 +35799,7 @@
         <v/>
       </c>
       <c r="AH200" s="6">
-        <f>IF(S200="","",IF(OR(I200=0,V200="IGEN",W200="IGEN"),0,IF(AND(K200&lt;&gt;"IGEN",L200="IGEN",U200="NEM"),0,S200)))</f>
+        <f>IF(S200="","",IF(OR(I200=0,V200="IGEN",W200="IGEN"),0,IF(AND(K200&lt;&gt;"IGEN",L200="IGEN",U200="NEM"),0,IF(AND(H200="GYES",E200&lt;1998),0,S200))))</f>
         <v/>
       </c>
       <c r="AI200" s="6">
@@ -35919,7 +35919,7 @@
         <v/>
       </c>
       <c r="AH201" s="6">
-        <f>IF(S201="","",IF(OR(I201=0,V201="IGEN",W201="IGEN"),0,IF(AND(K201&lt;&gt;"IGEN",L201="IGEN",U201="NEM"),0,S201)))</f>
+        <f>IF(S201="","",IF(OR(I201=0,V201="IGEN",W201="IGEN"),0,IF(AND(K201&lt;&gt;"IGEN",L201="IGEN",U201="NEM"),0,IF(AND(H201="GYES",E201&lt;1998),0,S201))))</f>
         <v/>
       </c>
       <c r="AI201" s="6">
@@ -36039,7 +36039,7 @@
         <v/>
       </c>
       <c r="AH202" s="6">
-        <f>IF(S202="","",IF(OR(I202=0,V202="IGEN",W202="IGEN"),0,IF(AND(K202&lt;&gt;"IGEN",L202="IGEN",U202="NEM"),0,S202)))</f>
+        <f>IF(S202="","",IF(OR(I202=0,V202="IGEN",W202="IGEN"),0,IF(AND(K202&lt;&gt;"IGEN",L202="IGEN",U202="NEM"),0,IF(AND(H202="GYES",E202&lt;1998),0,S202))))</f>
         <v/>
       </c>
       <c r="AI202" s="6">
@@ -36159,7 +36159,7 @@
         <v/>
       </c>
       <c r="AH203" s="6">
-        <f>IF(S203="","",IF(OR(I203=0,V203="IGEN",W203="IGEN"),0,IF(AND(K203&lt;&gt;"IGEN",L203="IGEN",U203="NEM"),0,S203)))</f>
+        <f>IF(S203="","",IF(OR(I203=0,V203="IGEN",W203="IGEN"),0,IF(AND(K203&lt;&gt;"IGEN",L203="IGEN",U203="NEM"),0,IF(AND(H203="GYES",E203&lt;1998),0,S203))))</f>
         <v/>
       </c>
       <c r="AI203" s="6">
@@ -36279,7 +36279,7 @@
         <v/>
       </c>
       <c r="AH204" s="6">
-        <f>IF(S204="","",IF(OR(I204=0,V204="IGEN",W204="IGEN"),0,IF(AND(K204&lt;&gt;"IGEN",L204="IGEN",U204="NEM"),0,S204)))</f>
+        <f>IF(S204="","",IF(OR(I204=0,V204="IGEN",W204="IGEN"),0,IF(AND(K204&lt;&gt;"IGEN",L204="IGEN",U204="NEM"),0,IF(AND(H204="GYES",E204&lt;1998),0,S204))))</f>
         <v/>
       </c>
       <c r="AI204" s="6">
@@ -36399,7 +36399,7 @@
         <v/>
       </c>
       <c r="AH205" s="6">
-        <f>IF(S205="","",IF(OR(I205=0,V205="IGEN",W205="IGEN"),0,IF(AND(K205&lt;&gt;"IGEN",L205="IGEN",U205="NEM"),0,S205)))</f>
+        <f>IF(S205="","",IF(OR(I205=0,V205="IGEN",W205="IGEN"),0,IF(AND(K205&lt;&gt;"IGEN",L205="IGEN",U205="NEM"),0,IF(AND(H205="GYES",E205&lt;1998),0,S205))))</f>
         <v/>
       </c>
       <c r="AI205" s="6">
@@ -36519,7 +36519,7 @@
         <v/>
       </c>
       <c r="AH206" s="6">
-        <f>IF(S206="","",IF(OR(I206=0,V206="IGEN",W206="IGEN"),0,IF(AND(K206&lt;&gt;"IGEN",L206="IGEN",U206="NEM"),0,S206)))</f>
+        <f>IF(S206="","",IF(OR(I206=0,V206="IGEN",W206="IGEN"),0,IF(AND(K206&lt;&gt;"IGEN",L206="IGEN",U206="NEM"),0,IF(AND(H206="GYES",E206&lt;1998),0,S206))))</f>
         <v/>
       </c>
       <c r="AI206" s="6">
@@ -36639,7 +36639,7 @@
         <v/>
       </c>
       <c r="AH207" s="6">
-        <f>IF(S207="","",IF(OR(I207=0,V207="IGEN",W207="IGEN"),0,IF(AND(K207&lt;&gt;"IGEN",L207="IGEN",U207="NEM"),0,S207)))</f>
+        <f>IF(S207="","",IF(OR(I207=0,V207="IGEN",W207="IGEN"),0,IF(AND(K207&lt;&gt;"IGEN",L207="IGEN",U207="NEM"),0,IF(AND(H207="GYES",E207&lt;1998),0,S207))))</f>
         <v/>
       </c>
       <c r="AI207" s="6">
@@ -36759,7 +36759,7 @@
         <v/>
       </c>
       <c r="AH208" s="6">
-        <f>IF(S208="","",IF(OR(I208=0,V208="IGEN",W208="IGEN"),0,IF(AND(K208&lt;&gt;"IGEN",L208="IGEN",U208="NEM"),0,S208)))</f>
+        <f>IF(S208="","",IF(OR(I208=0,V208="IGEN",W208="IGEN"),0,IF(AND(K208&lt;&gt;"IGEN",L208="IGEN",U208="NEM"),0,IF(AND(H208="GYES",E208&lt;1998),0,S208))))</f>
         <v/>
       </c>
       <c r="AI208" s="6">
@@ -36879,7 +36879,7 @@
         <v/>
       </c>
       <c r="AH209" s="6">
-        <f>IF(S209="","",IF(OR(I209=0,V209="IGEN",W209="IGEN"),0,IF(AND(K209&lt;&gt;"IGEN",L209="IGEN",U209="NEM"),0,S209)))</f>
+        <f>IF(S209="","",IF(OR(I209=0,V209="IGEN",W209="IGEN"),0,IF(AND(K209&lt;&gt;"IGEN",L209="IGEN",U209="NEM"),0,IF(AND(H209="GYES",E209&lt;1998),0,S209))))</f>
         <v/>
       </c>
       <c r="AI209" s="6">
@@ -36999,7 +36999,7 @@
         <v/>
       </c>
       <c r="AH210" s="6">
-        <f>IF(S210="","",IF(OR(I210=0,V210="IGEN",W210="IGEN"),0,IF(AND(K210&lt;&gt;"IGEN",L210="IGEN",U210="NEM"),0,S210)))</f>
+        <f>IF(S210="","",IF(OR(I210=0,V210="IGEN",W210="IGEN"),0,IF(AND(K210&lt;&gt;"IGEN",L210="IGEN",U210="NEM"),0,IF(AND(H210="GYES",E210&lt;1998),0,S210))))</f>
         <v/>
       </c>
       <c r="AI210" s="6">
@@ -37119,7 +37119,7 @@
         <v/>
       </c>
       <c r="AH211" s="6">
-        <f>IF(S211="","",IF(OR(I211=0,V211="IGEN",W211="IGEN"),0,IF(AND(K211&lt;&gt;"IGEN",L211="IGEN",U211="NEM"),0,S211)))</f>
+        <f>IF(S211="","",IF(OR(I211=0,V211="IGEN",W211="IGEN"),0,IF(AND(K211&lt;&gt;"IGEN",L211="IGEN",U211="NEM"),0,IF(AND(H211="GYES",E211&lt;1998),0,S211))))</f>
         <v/>
       </c>
       <c r="AI211" s="6">
@@ -37239,7 +37239,7 @@
         <v/>
       </c>
       <c r="AH212" s="6">
-        <f>IF(S212="","",IF(OR(I212=0,V212="IGEN",W212="IGEN"),0,IF(AND(K212&lt;&gt;"IGEN",L212="IGEN",U212="NEM"),0,S212)))</f>
+        <f>IF(S212="","",IF(OR(I212=0,V212="IGEN",W212="IGEN"),0,IF(AND(K212&lt;&gt;"IGEN",L212="IGEN",U212="NEM"),0,IF(AND(H212="GYES",E212&lt;1998),0,S212))))</f>
         <v/>
       </c>
       <c r="AI212" s="6">
@@ -37359,7 +37359,7 @@
         <v/>
       </c>
       <c r="AH213" s="6">
-        <f>IF(S213="","",IF(OR(I213=0,V213="IGEN",W213="IGEN"),0,IF(AND(K213&lt;&gt;"IGEN",L213="IGEN",U213="NEM"),0,S213)))</f>
+        <f>IF(S213="","",IF(OR(I213=0,V213="IGEN",W213="IGEN"),0,IF(AND(K213&lt;&gt;"IGEN",L213="IGEN",U213="NEM"),0,IF(AND(H213="GYES",E213&lt;1998),0,S213))))</f>
         <v/>
       </c>
       <c r="AI213" s="6">
@@ -37479,7 +37479,7 @@
         <v/>
       </c>
       <c r="AH214" s="6">
-        <f>IF(S214="","",IF(OR(I214=0,V214="IGEN",W214="IGEN"),0,IF(AND(K214&lt;&gt;"IGEN",L214="IGEN",U214="NEM"),0,S214)))</f>
+        <f>IF(S214="","",IF(OR(I214=0,V214="IGEN",W214="IGEN"),0,IF(AND(K214&lt;&gt;"IGEN",L214="IGEN",U214="NEM"),0,IF(AND(H214="GYES",E214&lt;1998),0,S214))))</f>
         <v/>
       </c>
       <c r="AI214" s="6">
@@ -37599,7 +37599,7 @@
         <v/>
       </c>
       <c r="AH215" s="6">
-        <f>IF(S215="","",IF(OR(I215=0,V215="IGEN",W215="IGEN"),0,IF(AND(K215&lt;&gt;"IGEN",L215="IGEN",U215="NEM"),0,S215)))</f>
+        <f>IF(S215="","",IF(OR(I215=0,V215="IGEN",W215="IGEN"),0,IF(AND(K215&lt;&gt;"IGEN",L215="IGEN",U215="NEM"),0,IF(AND(H215="GYES",E215&lt;1998),0,S215))))</f>
         <v/>
       </c>
       <c r="AI215" s="6">
@@ -37719,7 +37719,7 @@
         <v/>
       </c>
       <c r="AH216" s="6">
-        <f>IF(S216="","",IF(OR(I216=0,V216="IGEN",W216="IGEN"),0,IF(AND(K216&lt;&gt;"IGEN",L216="IGEN",U216="NEM"),0,S216)))</f>
+        <f>IF(S216="","",IF(OR(I216=0,V216="IGEN",W216="IGEN"),0,IF(AND(K216&lt;&gt;"IGEN",L216="IGEN",U216="NEM"),0,IF(AND(H216="GYES",E216&lt;1998),0,S216))))</f>
         <v/>
       </c>
       <c r="AI216" s="6">
@@ -37839,7 +37839,7 @@
         <v/>
       </c>
       <c r="AH217" s="6">
-        <f>IF(S217="","",IF(OR(I217=0,V217="IGEN",W217="IGEN"),0,IF(AND(K217&lt;&gt;"IGEN",L217="IGEN",U217="NEM"),0,S217)))</f>
+        <f>IF(S217="","",IF(OR(I217=0,V217="IGEN",W217="IGEN"),0,IF(AND(K217&lt;&gt;"IGEN",L217="IGEN",U217="NEM"),0,IF(AND(H217="GYES",E217&lt;1998),0,S217))))</f>
         <v/>
       </c>
       <c r="AI217" s="6">
@@ -37959,7 +37959,7 @@
         <v/>
       </c>
       <c r="AH218" s="6">
-        <f>IF(S218="","",IF(OR(I218=0,V218="IGEN",W218="IGEN"),0,IF(AND(K218&lt;&gt;"IGEN",L218="IGEN",U218="NEM"),0,S218)))</f>
+        <f>IF(S218="","",IF(OR(I218=0,V218="IGEN",W218="IGEN"),0,IF(AND(K218&lt;&gt;"IGEN",L218="IGEN",U218="NEM"),0,IF(AND(H218="GYES",E218&lt;1998),0,S218))))</f>
         <v/>
       </c>
       <c r="AI218" s="6">
@@ -38079,7 +38079,7 @@
         <v/>
       </c>
       <c r="AH219" s="6">
-        <f>IF(S219="","",IF(OR(I219=0,V219="IGEN",W219="IGEN"),0,IF(AND(K219&lt;&gt;"IGEN",L219="IGEN",U219="NEM"),0,S219)))</f>
+        <f>IF(S219="","",IF(OR(I219=0,V219="IGEN",W219="IGEN"),0,IF(AND(K219&lt;&gt;"IGEN",L219="IGEN",U219="NEM"),0,IF(AND(H219="GYES",E219&lt;1998),0,S219))))</f>
         <v/>
       </c>
       <c r="AI219" s="6">
@@ -38199,7 +38199,7 @@
         <v/>
       </c>
       <c r="AH220" s="6">
-        <f>IF(S220="","",IF(OR(I220=0,V220="IGEN",W220="IGEN"),0,IF(AND(K220&lt;&gt;"IGEN",L220="IGEN",U220="NEM"),0,S220)))</f>
+        <f>IF(S220="","",IF(OR(I220=0,V220="IGEN",W220="IGEN"),0,IF(AND(K220&lt;&gt;"IGEN",L220="IGEN",U220="NEM"),0,IF(AND(H220="GYES",E220&lt;1998),0,S220))))</f>
         <v/>
       </c>
       <c r="AI220" s="6">
@@ -38319,7 +38319,7 @@
         <v/>
       </c>
       <c r="AH221" s="6">
-        <f>IF(S221="","",IF(OR(I221=0,V221="IGEN",W221="IGEN"),0,IF(AND(K221&lt;&gt;"IGEN",L221="IGEN",U221="NEM"),0,S221)))</f>
+        <f>IF(S221="","",IF(OR(I221=0,V221="IGEN",W221="IGEN"),0,IF(AND(K221&lt;&gt;"IGEN",L221="IGEN",U221="NEM"),0,IF(AND(H221="GYES",E221&lt;1998),0,S221))))</f>
         <v/>
       </c>
       <c r="AI221" s="6">
@@ -38439,7 +38439,7 @@
         <v/>
       </c>
       <c r="AH222" s="6">
-        <f>IF(S222="","",IF(OR(I222=0,V222="IGEN",W222="IGEN"),0,IF(AND(K222&lt;&gt;"IGEN",L222="IGEN",U222="NEM"),0,S222)))</f>
+        <f>IF(S222="","",IF(OR(I222=0,V222="IGEN",W222="IGEN"),0,IF(AND(K222&lt;&gt;"IGEN",L222="IGEN",U222="NEM"),0,IF(AND(H222="GYES",E222&lt;1998),0,S222))))</f>
         <v/>
       </c>
       <c r="AI222" s="6">
@@ -38559,7 +38559,7 @@
         <v/>
       </c>
       <c r="AH223" s="6">
-        <f>IF(S223="","",IF(OR(I223=0,V223="IGEN",W223="IGEN"),0,IF(AND(K223&lt;&gt;"IGEN",L223="IGEN",U223="NEM"),0,S223)))</f>
+        <f>IF(S223="","",IF(OR(I223=0,V223="IGEN",W223="IGEN"),0,IF(AND(K223&lt;&gt;"IGEN",L223="IGEN",U223="NEM"),0,IF(AND(H223="GYES",E223&lt;1998),0,S223))))</f>
         <v/>
       </c>
       <c r="AI223" s="6">
@@ -38679,7 +38679,7 @@
         <v/>
       </c>
       <c r="AH224" s="6">
-        <f>IF(S224="","",IF(OR(I224=0,V224="IGEN",W224="IGEN"),0,IF(AND(K224&lt;&gt;"IGEN",L224="IGEN",U224="NEM"),0,S224)))</f>
+        <f>IF(S224="","",IF(OR(I224=0,V224="IGEN",W224="IGEN"),0,IF(AND(K224&lt;&gt;"IGEN",L224="IGEN",U224="NEM"),0,IF(AND(H224="GYES",E224&lt;1998),0,S224))))</f>
         <v/>
       </c>
       <c r="AI224" s="6">
@@ -38799,7 +38799,7 @@
         <v/>
       </c>
       <c r="AH225" s="6">
-        <f>IF(S225="","",IF(OR(I225=0,V225="IGEN",W225="IGEN"),0,IF(AND(K225&lt;&gt;"IGEN",L225="IGEN",U225="NEM"),0,S225)))</f>
+        <f>IF(S225="","",IF(OR(I225=0,V225="IGEN",W225="IGEN"),0,IF(AND(K225&lt;&gt;"IGEN",L225="IGEN",U225="NEM"),0,IF(AND(H225="GYES",E225&lt;1998),0,S225))))</f>
         <v/>
       </c>
       <c r="AI225" s="6">
@@ -38919,7 +38919,7 @@
         <v/>
       </c>
       <c r="AH226" s="6">
-        <f>IF(S226="","",IF(OR(I226=0,V226="IGEN",W226="IGEN"),0,IF(AND(K226&lt;&gt;"IGEN",L226="IGEN",U226="NEM"),0,S226)))</f>
+        <f>IF(S226="","",IF(OR(I226=0,V226="IGEN",W226="IGEN"),0,IF(AND(K226&lt;&gt;"IGEN",L226="IGEN",U226="NEM"),0,IF(AND(H226="GYES",E226&lt;1998),0,S226))))</f>
         <v/>
       </c>
       <c r="AI226" s="6">
@@ -39039,7 +39039,7 @@
         <v/>
       </c>
       <c r="AH227" s="6">
-        <f>IF(S227="","",IF(OR(I227=0,V227="IGEN",W227="IGEN"),0,IF(AND(K227&lt;&gt;"IGEN",L227="IGEN",U227="NEM"),0,S227)))</f>
+        <f>IF(S227="","",IF(OR(I227=0,V227="IGEN",W227="IGEN"),0,IF(AND(K227&lt;&gt;"IGEN",L227="IGEN",U227="NEM"),0,IF(AND(H227="GYES",E227&lt;1998),0,S227))))</f>
         <v/>
       </c>
       <c r="AI227" s="6">
@@ -39159,7 +39159,7 @@
         <v/>
       </c>
       <c r="AH228" s="6">
-        <f>IF(S228="","",IF(OR(I228=0,V228="IGEN",W228="IGEN"),0,IF(AND(K228&lt;&gt;"IGEN",L228="IGEN",U228="NEM"),0,S228)))</f>
+        <f>IF(S228="","",IF(OR(I228=0,V228="IGEN",W228="IGEN"),0,IF(AND(K228&lt;&gt;"IGEN",L228="IGEN",U228="NEM"),0,IF(AND(H228="GYES",E228&lt;1998),0,S228))))</f>
         <v/>
       </c>
       <c r="AI228" s="6">
@@ -39279,7 +39279,7 @@
         <v/>
       </c>
       <c r="AH229" s="6">
-        <f>IF(S229="","",IF(OR(I229=0,V229="IGEN",W229="IGEN"),0,IF(AND(K229&lt;&gt;"IGEN",L229="IGEN",U229="NEM"),0,S229)))</f>
+        <f>IF(S229="","",IF(OR(I229=0,V229="IGEN",W229="IGEN"),0,IF(AND(K229&lt;&gt;"IGEN",L229="IGEN",U229="NEM"),0,IF(AND(H229="GYES",E229&lt;1998),0,S229))))</f>
         <v/>
       </c>
       <c r="AI229" s="6">
@@ -39399,7 +39399,7 @@
         <v/>
       </c>
       <c r="AH230" s="6">
-        <f>IF(S230="","",IF(OR(I230=0,V230="IGEN",W230="IGEN"),0,IF(AND(K230&lt;&gt;"IGEN",L230="IGEN",U230="NEM"),0,S230)))</f>
+        <f>IF(S230="","",IF(OR(I230=0,V230="IGEN",W230="IGEN"),0,IF(AND(K230&lt;&gt;"IGEN",L230="IGEN",U230="NEM"),0,IF(AND(H230="GYES",E230&lt;1998),0,S230))))</f>
         <v/>
       </c>
       <c r="AI230" s="6">
@@ -39519,7 +39519,7 @@
         <v/>
       </c>
       <c r="AH231" s="6">
-        <f>IF(S231="","",IF(OR(I231=0,V231="IGEN",W231="IGEN"),0,IF(AND(K231&lt;&gt;"IGEN",L231="IGEN",U231="NEM"),0,S231)))</f>
+        <f>IF(S231="","",IF(OR(I231=0,V231="IGEN",W231="IGEN"),0,IF(AND(K231&lt;&gt;"IGEN",L231="IGEN",U231="NEM"),0,IF(AND(H231="GYES",E231&lt;1998),0,S231))))</f>
         <v/>
       </c>
       <c r="AI231" s="6">
@@ -39639,7 +39639,7 @@
         <v/>
       </c>
       <c r="AH232" s="6">
-        <f>IF(S232="","",IF(OR(I232=0,V232="IGEN",W232="IGEN"),0,IF(AND(K232&lt;&gt;"IGEN",L232="IGEN",U232="NEM"),0,S232)))</f>
+        <f>IF(S232="","",IF(OR(I232=0,V232="IGEN",W232="IGEN"),0,IF(AND(K232&lt;&gt;"IGEN",L232="IGEN",U232="NEM"),0,IF(AND(H232="GYES",E232&lt;1998),0,S232))))</f>
         <v/>
       </c>
       <c r="AI232" s="6">
@@ -39759,7 +39759,7 @@
         <v/>
       </c>
       <c r="AH233" s="6">
-        <f>IF(S233="","",IF(OR(I233=0,V233="IGEN",W233="IGEN"),0,IF(AND(K233&lt;&gt;"IGEN",L233="IGEN",U233="NEM"),0,S233)))</f>
+        <f>IF(S233="","",IF(OR(I233=0,V233="IGEN",W233="IGEN"),0,IF(AND(K233&lt;&gt;"IGEN",L233="IGEN",U233="NEM"),0,IF(AND(H233="GYES",E233&lt;1998),0,S233))))</f>
         <v/>
       </c>
       <c r="AI233" s="6">
@@ -39879,7 +39879,7 @@
         <v/>
       </c>
       <c r="AH234" s="6">
-        <f>IF(S234="","",IF(OR(I234=0,V234="IGEN",W234="IGEN"),0,IF(AND(K234&lt;&gt;"IGEN",L234="IGEN",U234="NEM"),0,S234)))</f>
+        <f>IF(S234="","",IF(OR(I234=0,V234="IGEN",W234="IGEN"),0,IF(AND(K234&lt;&gt;"IGEN",L234="IGEN",U234="NEM"),0,IF(AND(H234="GYES",E234&lt;1998),0,S234))))</f>
         <v/>
       </c>
       <c r="AI234" s="6">
@@ -39999,7 +39999,7 @@
         <v/>
       </c>
       <c r="AH235" s="6">
-        <f>IF(S235="","",IF(OR(I235=0,V235="IGEN",W235="IGEN"),0,IF(AND(K235&lt;&gt;"IGEN",L235="IGEN",U235="NEM"),0,S235)))</f>
+        <f>IF(S235="","",IF(OR(I235=0,V235="IGEN",W235="IGEN"),0,IF(AND(K235&lt;&gt;"IGEN",L235="IGEN",U235="NEM"),0,IF(AND(H235="GYES",E235&lt;1998),0,S235))))</f>
         <v/>
       </c>
       <c r="AI235" s="6">
@@ -40119,7 +40119,7 @@
         <v/>
       </c>
       <c r="AH236" s="6">
-        <f>IF(S236="","",IF(OR(I236=0,V236="IGEN",W236="IGEN"),0,IF(AND(K236&lt;&gt;"IGEN",L236="IGEN",U236="NEM"),0,S236)))</f>
+        <f>IF(S236="","",IF(OR(I236=0,V236="IGEN",W236="IGEN"),0,IF(AND(K236&lt;&gt;"IGEN",L236="IGEN",U236="NEM"),0,IF(AND(H236="GYES",E236&lt;1998),0,S236))))</f>
         <v/>
       </c>
       <c r="AI236" s="6">
@@ -40239,7 +40239,7 @@
         <v/>
       </c>
       <c r="AH237" s="6">
-        <f>IF(S237="","",IF(OR(I237=0,V237="IGEN",W237="IGEN"),0,IF(AND(K237&lt;&gt;"IGEN",L237="IGEN",U237="NEM"),0,S237)))</f>
+        <f>IF(S237="","",IF(OR(I237=0,V237="IGEN",W237="IGEN"),0,IF(AND(K237&lt;&gt;"IGEN",L237="IGEN",U237="NEM"),0,IF(AND(H237="GYES",E237&lt;1998),0,S237))))</f>
         <v/>
       </c>
       <c r="AI237" s="6">
@@ -40359,7 +40359,7 @@
         <v/>
       </c>
       <c r="AH238" s="6">
-        <f>IF(S238="","",IF(OR(I238=0,V238="IGEN",W238="IGEN"),0,IF(AND(K238&lt;&gt;"IGEN",L238="IGEN",U238="NEM"),0,S238)))</f>
+        <f>IF(S238="","",IF(OR(I238=0,V238="IGEN",W238="IGEN"),0,IF(AND(K238&lt;&gt;"IGEN",L238="IGEN",U238="NEM"),0,IF(AND(H238="GYES",E238&lt;1998),0,S238))))</f>
         <v/>
       </c>
       <c r="AI238" s="6">
@@ -40479,7 +40479,7 @@
         <v/>
       </c>
       <c r="AH239" s="6">
-        <f>IF(S239="","",IF(OR(I239=0,V239="IGEN",W239="IGEN"),0,IF(AND(K239&lt;&gt;"IGEN",L239="IGEN",U239="NEM"),0,S239)))</f>
+        <f>IF(S239="","",IF(OR(I239=0,V239="IGEN",W239="IGEN"),0,IF(AND(K239&lt;&gt;"IGEN",L239="IGEN",U239="NEM"),0,IF(AND(H239="GYES",E239&lt;1998),0,S239))))</f>
         <v/>
       </c>
       <c r="AI239" s="6">
@@ -40599,7 +40599,7 @@
         <v/>
       </c>
       <c r="AH240" s="6">
-        <f>IF(S240="","",IF(OR(I240=0,V240="IGEN",W240="IGEN"),0,IF(AND(K240&lt;&gt;"IGEN",L240="IGEN",U240="NEM"),0,S240)))</f>
+        <f>IF(S240="","",IF(OR(I240=0,V240="IGEN",W240="IGEN"),0,IF(AND(K240&lt;&gt;"IGEN",L240="IGEN",U240="NEM"),0,IF(AND(H240="GYES",E240&lt;1998),0,S240))))</f>
         <v/>
       </c>
       <c r="AI240" s="6">
@@ -40719,7 +40719,7 @@
         <v/>
       </c>
       <c r="AH241" s="6">
-        <f>IF(S241="","",IF(OR(I241=0,V241="IGEN",W241="IGEN"),0,IF(AND(K241&lt;&gt;"IGEN",L241="IGEN",U241="NEM"),0,S241)))</f>
+        <f>IF(S241="","",IF(OR(I241=0,V241="IGEN",W241="IGEN"),0,IF(AND(K241&lt;&gt;"IGEN",L241="IGEN",U241="NEM"),0,IF(AND(H241="GYES",E241&lt;1998),0,S241))))</f>
         <v/>
       </c>
       <c r="AI241" s="6">
@@ -40839,7 +40839,7 @@
         <v/>
       </c>
       <c r="AH242" s="6">
-        <f>IF(S242="","",IF(OR(I242=0,V242="IGEN",W242="IGEN"),0,IF(AND(K242&lt;&gt;"IGEN",L242="IGEN",U242="NEM"),0,S242)))</f>
+        <f>IF(S242="","",IF(OR(I242=0,V242="IGEN",W242="IGEN"),0,IF(AND(K242&lt;&gt;"IGEN",L242="IGEN",U242="NEM"),0,IF(AND(H242="GYES",E242&lt;1998),0,S242))))</f>
         <v/>
       </c>
       <c r="AI242" s="6">
@@ -40959,7 +40959,7 @@
         <v/>
       </c>
       <c r="AH243" s="6">
-        <f>IF(S243="","",IF(OR(I243=0,V243="IGEN",W243="IGEN"),0,IF(AND(K243&lt;&gt;"IGEN",L243="IGEN",U243="NEM"),0,S243)))</f>
+        <f>IF(S243="","",IF(OR(I243=0,V243="IGEN",W243="IGEN"),0,IF(AND(K243&lt;&gt;"IGEN",L243="IGEN",U243="NEM"),0,IF(AND(H243="GYES",E243&lt;1998),0,S243))))</f>
         <v/>
       </c>
       <c r="AI243" s="6">
@@ -41079,7 +41079,7 @@
         <v/>
       </c>
       <c r="AH244" s="6">
-        <f>IF(S244="","",IF(OR(I244=0,V244="IGEN",W244="IGEN"),0,IF(AND(K244&lt;&gt;"IGEN",L244="IGEN",U244="NEM"),0,S244)))</f>
+        <f>IF(S244="","",IF(OR(I244=0,V244="IGEN",W244="IGEN"),0,IF(AND(K244&lt;&gt;"IGEN",L244="IGEN",U244="NEM"),0,IF(AND(H244="GYES",E244&lt;1998),0,S244))))</f>
         <v/>
       </c>
       <c r="AI244" s="6">
@@ -41199,7 +41199,7 @@
         <v/>
       </c>
       <c r="AH245" s="6">
-        <f>IF(S245="","",IF(OR(I245=0,V245="IGEN",W245="IGEN"),0,IF(AND(K245&lt;&gt;"IGEN",L245="IGEN",U245="NEM"),0,S245)))</f>
+        <f>IF(S245="","",IF(OR(I245=0,V245="IGEN",W245="IGEN"),0,IF(AND(K245&lt;&gt;"IGEN",L245="IGEN",U245="NEM"),0,IF(AND(H245="GYES",E245&lt;1998),0,S245))))</f>
         <v/>
       </c>
       <c r="AI245" s="6">
@@ -41319,7 +41319,7 @@
         <v/>
       </c>
       <c r="AH246" s="6">
-        <f>IF(S246="","",IF(OR(I246=0,V246="IGEN",W246="IGEN"),0,IF(AND(K246&lt;&gt;"IGEN",L246="IGEN",U246="NEM"),0,S246)))</f>
+        <f>IF(S246="","",IF(OR(I246=0,V246="IGEN",W246="IGEN"),0,IF(AND(K246&lt;&gt;"IGEN",L246="IGEN",U246="NEM"),0,IF(AND(H246="GYES",E246&lt;1998),0,S246))))</f>
         <v/>
       </c>
       <c r="AI246" s="6">
@@ -41439,7 +41439,7 @@
         <v/>
       </c>
       <c r="AH247" s="6">
-        <f>IF(S247="","",IF(OR(I247=0,V247="IGEN",W247="IGEN"),0,IF(AND(K247&lt;&gt;"IGEN",L247="IGEN",U247="NEM"),0,S247)))</f>
+        <f>IF(S247="","",IF(OR(I247=0,V247="IGEN",W247="IGEN"),0,IF(AND(K247&lt;&gt;"IGEN",L247="IGEN",U247="NEM"),0,IF(AND(H247="GYES",E247&lt;1998),0,S247))))</f>
         <v/>
       </c>
       <c r="AI247" s="6">
@@ -41559,7 +41559,7 @@
         <v/>
       </c>
       <c r="AH248" s="6">
-        <f>IF(S248="","",IF(OR(I248=0,V248="IGEN",W248="IGEN"),0,IF(AND(K248&lt;&gt;"IGEN",L248="IGEN",U248="NEM"),0,S248)))</f>
+        <f>IF(S248="","",IF(OR(I248=0,V248="IGEN",W248="IGEN"),0,IF(AND(K248&lt;&gt;"IGEN",L248="IGEN",U248="NEM"),0,IF(AND(H248="GYES",E248&lt;1998),0,S248))))</f>
         <v/>
       </c>
       <c r="AI248" s="6">
@@ -41679,7 +41679,7 @@
         <v/>
       </c>
       <c r="AH249" s="6">
-        <f>IF(S249="","",IF(OR(I249=0,V249="IGEN",W249="IGEN"),0,IF(AND(K249&lt;&gt;"IGEN",L249="IGEN",U249="NEM"),0,S249)))</f>
+        <f>IF(S249="","",IF(OR(I249=0,V249="IGEN",W249="IGEN"),0,IF(AND(K249&lt;&gt;"IGEN",L249="IGEN",U249="NEM"),0,IF(AND(H249="GYES",E249&lt;1998),0,S249))))</f>
         <v/>
       </c>
       <c r="AI249" s="6">
@@ -41799,7 +41799,7 @@
         <v/>
       </c>
       <c r="AH250" s="6">
-        <f>IF(S250="","",IF(OR(I250=0,V250="IGEN",W250="IGEN"),0,IF(AND(K250&lt;&gt;"IGEN",L250="IGEN",U250="NEM"),0,S250)))</f>
+        <f>IF(S250="","",IF(OR(I250=0,V250="IGEN",W250="IGEN"),0,IF(AND(K250&lt;&gt;"IGEN",L250="IGEN",U250="NEM"),0,IF(AND(H250="GYES",E250&lt;1998),0,S250))))</f>
         <v/>
       </c>
       <c r="AI250" s="6">
@@ -41919,7 +41919,7 @@
         <v/>
       </c>
       <c r="AH251" s="6">
-        <f>IF(S251="","",IF(OR(I251=0,V251="IGEN",W251="IGEN"),0,IF(AND(K251&lt;&gt;"IGEN",L251="IGEN",U251="NEM"),0,S251)))</f>
+        <f>IF(S251="","",IF(OR(I251=0,V251="IGEN",W251="IGEN"),0,IF(AND(K251&lt;&gt;"IGEN",L251="IGEN",U251="NEM"),0,IF(AND(H251="GYES",E251&lt;1998),0,S251))))</f>
         <v/>
       </c>
       <c r="AI251" s="6">
@@ -42039,7 +42039,7 @@
         <v/>
       </c>
       <c r="AH252" s="6">
-        <f>IF(S252="","",IF(OR(I252=0,V252="IGEN",W252="IGEN"),0,IF(AND(K252&lt;&gt;"IGEN",L252="IGEN",U252="NEM"),0,S252)))</f>
+        <f>IF(S252="","",IF(OR(I252=0,V252="IGEN",W252="IGEN"),0,IF(AND(K252&lt;&gt;"IGEN",L252="IGEN",U252="NEM"),0,IF(AND(H252="GYES",E252&lt;1998),0,S252))))</f>
         <v/>
       </c>
       <c r="AI252" s="6">
@@ -42159,7 +42159,7 @@
         <v/>
       </c>
       <c r="AH253" s="6">
-        <f>IF(S253="","",IF(OR(I253=0,V253="IGEN",W253="IGEN"),0,IF(AND(K253&lt;&gt;"IGEN",L253="IGEN",U253="NEM"),0,S253)))</f>
+        <f>IF(S253="","",IF(OR(I253=0,V253="IGEN",W253="IGEN"),0,IF(AND(K253&lt;&gt;"IGEN",L253="IGEN",U253="NEM"),0,IF(AND(H253="GYES",E253&lt;1998),0,S253))))</f>
         <v/>
       </c>
       <c r="AI253" s="6">
@@ -42279,7 +42279,7 @@
         <v/>
       </c>
       <c r="AH254" s="6">
-        <f>IF(S254="","",IF(OR(I254=0,V254="IGEN",W254="IGEN"),0,IF(AND(K254&lt;&gt;"IGEN",L254="IGEN",U254="NEM"),0,S254)))</f>
+        <f>IF(S254="","",IF(OR(I254=0,V254="IGEN",W254="IGEN"),0,IF(AND(K254&lt;&gt;"IGEN",L254="IGEN",U254="NEM"),0,IF(AND(H254="GYES",E254&lt;1998),0,S254))))</f>
         <v/>
       </c>
       <c r="AI254" s="6">
@@ -42399,7 +42399,7 @@
         <v/>
       </c>
       <c r="AH255" s="6">
-        <f>IF(S255="","",IF(OR(I255=0,V255="IGEN",W255="IGEN"),0,IF(AND(K255&lt;&gt;"IGEN",L255="IGEN",U255="NEM"),0,S255)))</f>
+        <f>IF(S255="","",IF(OR(I255=0,V255="IGEN",W255="IGEN"),0,IF(AND(K255&lt;&gt;"IGEN",L255="IGEN",U255="NEM"),0,IF(AND(H255="GYES",E255&lt;1998),0,S255))))</f>
         <v/>
       </c>
       <c r="AI255" s="6">
@@ -42519,7 +42519,7 @@
         <v/>
       </c>
       <c r="AH256" s="6">
-        <f>IF(S256="","",IF(OR(I256=0,V256="IGEN",W256="IGEN"),0,IF(AND(K256&lt;&gt;"IGEN",L256="IGEN",U256="NEM"),0,S256)))</f>
+        <f>IF(S256="","",IF(OR(I256=0,V256="IGEN",W256="IGEN"),0,IF(AND(K256&lt;&gt;"IGEN",L256="IGEN",U256="NEM"),0,IF(AND(H256="GYES",E256&lt;1998),0,S256))))</f>
         <v/>
       </c>
       <c r="AI256" s="6">
@@ -42639,7 +42639,7 @@
         <v/>
       </c>
       <c r="AH257" s="6">
-        <f>IF(S257="","",IF(OR(I257=0,V257="IGEN",W257="IGEN"),0,IF(AND(K257&lt;&gt;"IGEN",L257="IGEN",U257="NEM"),0,S257)))</f>
+        <f>IF(S257="","",IF(OR(I257=0,V257="IGEN",W257="IGEN"),0,IF(AND(K257&lt;&gt;"IGEN",L257="IGEN",U257="NEM"),0,IF(AND(H257="GYES",E257&lt;1998),0,S257))))</f>
         <v/>
       </c>
       <c r="AI257" s="6">
@@ -42759,7 +42759,7 @@
         <v/>
       </c>
       <c r="AH258" s="6">
-        <f>IF(S258="","",IF(OR(I258=0,V258="IGEN",W258="IGEN"),0,IF(AND(K258&lt;&gt;"IGEN",L258="IGEN",U258="NEM"),0,S258)))</f>
+        <f>IF(S258="","",IF(OR(I258=0,V258="IGEN",W258="IGEN"),0,IF(AND(K258&lt;&gt;"IGEN",L258="IGEN",U258="NEM"),0,IF(AND(H258="GYES",E258&lt;1998),0,S258))))</f>
         <v/>
       </c>
       <c r="AI258" s="6">
@@ -42879,7 +42879,7 @@
         <v/>
       </c>
       <c r="AH259" s="6">
-        <f>IF(S259="","",IF(OR(I259=0,V259="IGEN",W259="IGEN"),0,IF(AND(K259&lt;&gt;"IGEN",L259="IGEN",U259="NEM"),0,S259)))</f>
+        <f>IF(S259="","",IF(OR(I259=0,V259="IGEN",W259="IGEN"),0,IF(AND(K259&lt;&gt;"IGEN",L259="IGEN",U259="NEM"),0,IF(AND(H259="GYES",E259&lt;1998),0,S259))))</f>
         <v/>
       </c>
       <c r="AI259" s="6">
@@ -42999,7 +42999,7 @@
         <v/>
       </c>
       <c r="AH260" s="6">
-        <f>IF(S260="","",IF(OR(I260=0,V260="IGEN",W260="IGEN"),0,IF(AND(K260&lt;&gt;"IGEN",L260="IGEN",U260="NEM"),0,S260)))</f>
+        <f>IF(S260="","",IF(OR(I260=0,V260="IGEN",W260="IGEN"),0,IF(AND(K260&lt;&gt;"IGEN",L260="IGEN",U260="NEM"),0,IF(AND(H260="GYES",E260&lt;1998),0,S260))))</f>
         <v/>
       </c>
       <c r="AI260" s="6">
@@ -43119,7 +43119,7 @@
         <v/>
       </c>
       <c r="AH261" s="6">
-        <f>IF(S261="","",IF(OR(I261=0,V261="IGEN",W261="IGEN"),0,IF(AND(K261&lt;&gt;"IGEN",L261="IGEN",U261="NEM"),0,S261)))</f>
+        <f>IF(S261="","",IF(OR(I261=0,V261="IGEN",W261="IGEN"),0,IF(AND(K261&lt;&gt;"IGEN",L261="IGEN",U261="NEM"),0,IF(AND(H261="GYES",E261&lt;1998),0,S261))))</f>
         <v/>
       </c>
       <c r="AI261" s="6">
@@ -43239,7 +43239,7 @@
         <v/>
       </c>
       <c r="AH262" s="6">
-        <f>IF(S262="","",IF(OR(I262=0,V262="IGEN",W262="IGEN"),0,IF(AND(K262&lt;&gt;"IGEN",L262="IGEN",U262="NEM"),0,S262)))</f>
+        <f>IF(S262="","",IF(OR(I262=0,V262="IGEN",W262="IGEN"),0,IF(AND(K262&lt;&gt;"IGEN",L262="IGEN",U262="NEM"),0,IF(AND(H262="GYES",E262&lt;1998),0,S262))))</f>
         <v/>
       </c>
       <c r="AI262" s="6">
@@ -43359,7 +43359,7 @@
         <v/>
       </c>
       <c r="AH263" s="6">
-        <f>IF(S263="","",IF(OR(I263=0,V263="IGEN",W263="IGEN"),0,IF(AND(K263&lt;&gt;"IGEN",L263="IGEN",U263="NEM"),0,S263)))</f>
+        <f>IF(S263="","",IF(OR(I263=0,V263="IGEN",W263="IGEN"),0,IF(AND(K263&lt;&gt;"IGEN",L263="IGEN",U263="NEM"),0,IF(AND(H263="GYES",E263&lt;1998),0,S263))))</f>
         <v/>
       </c>
       <c r="AI263" s="6">
@@ -43479,7 +43479,7 @@
         <v/>
       </c>
       <c r="AH264" s="6">
-        <f>IF(S264="","",IF(OR(I264=0,V264="IGEN",W264="IGEN"),0,IF(AND(K264&lt;&gt;"IGEN",L264="IGEN",U264="NEM"),0,S264)))</f>
+        <f>IF(S264="","",IF(OR(I264=0,V264="IGEN",W264="IGEN"),0,IF(AND(K264&lt;&gt;"IGEN",L264="IGEN",U264="NEM"),0,IF(AND(H264="GYES",E264&lt;1998),0,S264))))</f>
         <v/>
       </c>
       <c r="AI264" s="6">
@@ -43599,7 +43599,7 @@
         <v/>
       </c>
       <c r="AH265" s="6">
-        <f>IF(S265="","",IF(OR(I265=0,V265="IGEN",W265="IGEN"),0,IF(AND(K265&lt;&gt;"IGEN",L265="IGEN",U265="NEM"),0,S265)))</f>
+        <f>IF(S265="","",IF(OR(I265=0,V265="IGEN",W265="IGEN"),0,IF(AND(K265&lt;&gt;"IGEN",L265="IGEN",U265="NEM"),0,IF(AND(H265="GYES",E265&lt;1998),0,S265))))</f>
         <v/>
       </c>
       <c r="AI265" s="6">
@@ -43719,7 +43719,7 @@
         <v/>
       </c>
       <c r="AH266" s="6">
-        <f>IF(S266="","",IF(OR(I266=0,V266="IGEN",W266="IGEN"),0,IF(AND(K266&lt;&gt;"IGEN",L266="IGEN",U266="NEM"),0,S266)))</f>
+        <f>IF(S266="","",IF(OR(I266=0,V266="IGEN",W266="IGEN"),0,IF(AND(K266&lt;&gt;"IGEN",L266="IGEN",U266="NEM"),0,IF(AND(H266="GYES",E266&lt;1998),0,S266))))</f>
         <v/>
       </c>
       <c r="AI266" s="6">
@@ -43839,7 +43839,7 @@
         <v/>
       </c>
       <c r="AH267" s="6">
-        <f>IF(S267="","",IF(OR(I267=0,V267="IGEN",W267="IGEN"),0,IF(AND(K267&lt;&gt;"IGEN",L267="IGEN",U267="NEM"),0,S267)))</f>
+        <f>IF(S267="","",IF(OR(I267=0,V267="IGEN",W267="IGEN"),0,IF(AND(K267&lt;&gt;"IGEN",L267="IGEN",U267="NEM"),0,IF(AND(H267="GYES",E267&lt;1998),0,S267))))</f>
         <v/>
       </c>
       <c r="AI267" s="6">
@@ -43959,7 +43959,7 @@
         <v/>
       </c>
       <c r="AH268" s="6">
-        <f>IF(S268="","",IF(OR(I268=0,V268="IGEN",W268="IGEN"),0,IF(AND(K268&lt;&gt;"IGEN",L268="IGEN",U268="NEM"),0,S268)))</f>
+        <f>IF(S268="","",IF(OR(I268=0,V268="IGEN",W268="IGEN"),0,IF(AND(K268&lt;&gt;"IGEN",L268="IGEN",U268="NEM"),0,IF(AND(H268="GYES",E268&lt;1998),0,S268))))</f>
         <v/>
       </c>
       <c r="AI268" s="6">
@@ -44079,7 +44079,7 @@
         <v/>
       </c>
       <c r="AH269" s="6">
-        <f>IF(S269="","",IF(OR(I269=0,V269="IGEN",W269="IGEN"),0,IF(AND(K269&lt;&gt;"IGEN",L269="IGEN",U269="NEM"),0,S269)))</f>
+        <f>IF(S269="","",IF(OR(I269=0,V269="IGEN",W269="IGEN"),0,IF(AND(K269&lt;&gt;"IGEN",L269="IGEN",U269="NEM"),0,IF(AND(H269="GYES",E269&lt;1998),0,S269))))</f>
         <v/>
       </c>
       <c r="AI269" s="6">
@@ -44199,7 +44199,7 @@
         <v/>
       </c>
       <c r="AH270" s="6">
-        <f>IF(S270="","",IF(OR(I270=0,V270="IGEN",W270="IGEN"),0,IF(AND(K270&lt;&gt;"IGEN",L270="IGEN",U270="NEM"),0,S270)))</f>
+        <f>IF(S270="","",IF(OR(I270=0,V270="IGEN",W270="IGEN"),0,IF(AND(K270&lt;&gt;"IGEN",L270="IGEN",U270="NEM"),0,IF(AND(H270="GYES",E270&lt;1998),0,S270))))</f>
         <v/>
       </c>
       <c r="AI270" s="6">
@@ -44319,7 +44319,7 @@
         <v/>
       </c>
       <c r="AH271" s="6">
-        <f>IF(S271="","",IF(OR(I271=0,V271="IGEN",W271="IGEN"),0,IF(AND(K271&lt;&gt;"IGEN",L271="IGEN",U271="NEM"),0,S271)))</f>
+        <f>IF(S271="","",IF(OR(I271=0,V271="IGEN",W271="IGEN"),0,IF(AND(K271&lt;&gt;"IGEN",L271="IGEN",U271="NEM"),0,IF(AND(H271="GYES",E271&lt;1998),0,S271))))</f>
         <v/>
       </c>
       <c r="AI271" s="6">
@@ -44439,7 +44439,7 @@
         <v/>
       </c>
       <c r="AH272" s="6">
-        <f>IF(S272="","",IF(OR(I272=0,V272="IGEN",W272="IGEN"),0,IF(AND(K272&lt;&gt;"IGEN",L272="IGEN",U272="NEM"),0,S272)))</f>
+        <f>IF(S272="","",IF(OR(I272=0,V272="IGEN",W272="IGEN"),0,IF(AND(K272&lt;&gt;"IGEN",L272="IGEN",U272="NEM"),0,IF(AND(H272="GYES",E272&lt;1998),0,S272))))</f>
         <v/>
       </c>
       <c r="AI272" s="6">
@@ -44559,7 +44559,7 @@
         <v/>
       </c>
       <c r="AH273" s="6">
-        <f>IF(S273="","",IF(OR(I273=0,V273="IGEN",W273="IGEN"),0,IF(AND(K273&lt;&gt;"IGEN",L273="IGEN",U273="NEM"),0,S273)))</f>
+        <f>IF(S273="","",IF(OR(I273=0,V273="IGEN",W273="IGEN"),0,IF(AND(K273&lt;&gt;"IGEN",L273="IGEN",U273="NEM"),0,IF(AND(H273="GYES",E273&lt;1998),0,S273))))</f>
         <v/>
       </c>
       <c r="AI273" s="6">
@@ -44679,7 +44679,7 @@
         <v/>
       </c>
       <c r="AH274" s="6">
-        <f>IF(S274="","",IF(OR(I274=0,V274="IGEN",W274="IGEN"),0,IF(AND(K274&lt;&gt;"IGEN",L274="IGEN",U274="NEM"),0,S274)))</f>
+        <f>IF(S274="","",IF(OR(I274=0,V274="IGEN",W274="IGEN"),0,IF(AND(K274&lt;&gt;"IGEN",L274="IGEN",U274="NEM"),0,IF(AND(H274="GYES",E274&lt;1998),0,S274))))</f>
         <v/>
       </c>
       <c r="AI274" s="6">
@@ -44799,7 +44799,7 @@
         <v/>
       </c>
       <c r="AH275" s="6">
-        <f>IF(S275="","",IF(OR(I275=0,V275="IGEN",W275="IGEN"),0,IF(AND(K275&lt;&gt;"IGEN",L275="IGEN",U275="NEM"),0,S275)))</f>
+        <f>IF(S275="","",IF(OR(I275=0,V275="IGEN",W275="IGEN"),0,IF(AND(K275&lt;&gt;"IGEN",L275="IGEN",U275="NEM"),0,IF(AND(H275="GYES",E275&lt;1998),0,S275))))</f>
         <v/>
       </c>
       <c r="AI275" s="6">
@@ -44919,7 +44919,7 @@
         <v/>
       </c>
       <c r="AH276" s="6">
-        <f>IF(S276="","",IF(OR(I276=0,V276="IGEN",W276="IGEN"),0,IF(AND(K276&lt;&gt;"IGEN",L276="IGEN",U276="NEM"),0,S276)))</f>
+        <f>IF(S276="","",IF(OR(I276=0,V276="IGEN",W276="IGEN"),0,IF(AND(K276&lt;&gt;"IGEN",L276="IGEN",U276="NEM"),0,IF(AND(H276="GYES",E276&lt;1998),0,S276))))</f>
         <v/>
       </c>
       <c r="AI276" s="6">
@@ -45039,7 +45039,7 @@
         <v/>
       </c>
       <c r="AH277" s="6">
-        <f>IF(S277="","",IF(OR(I277=0,V277="IGEN",W277="IGEN"),0,IF(AND(K277&lt;&gt;"IGEN",L277="IGEN",U277="NEM"),0,S277)))</f>
+        <f>IF(S277="","",IF(OR(I277=0,V277="IGEN",W277="IGEN"),0,IF(AND(K277&lt;&gt;"IGEN",L277="IGEN",U277="NEM"),0,IF(AND(H277="GYES",E277&lt;1998),0,S277))))</f>
         <v/>
       </c>
       <c r="AI277" s="6">
@@ -45159,7 +45159,7 @@
         <v/>
       </c>
       <c r="AH278" s="6">
-        <f>IF(S278="","",IF(OR(I278=0,V278="IGEN",W278="IGEN"),0,IF(AND(K278&lt;&gt;"IGEN",L278="IGEN",U278="NEM"),0,S278)))</f>
+        <f>IF(S278="","",IF(OR(I278=0,V278="IGEN",W278="IGEN"),0,IF(AND(K278&lt;&gt;"IGEN",L278="IGEN",U278="NEM"),0,IF(AND(H278="GYES",E278&lt;1998),0,S278))))</f>
         <v/>
       </c>
       <c r="AI278" s="6">
@@ -45279,7 +45279,7 @@
         <v/>
       </c>
       <c r="AH279" s="6">
-        <f>IF(S279="","",IF(OR(I279=0,V279="IGEN",W279="IGEN"),0,IF(AND(K279&lt;&gt;"IGEN",L279="IGEN",U279="NEM"),0,S279)))</f>
+        <f>IF(S279="","",IF(OR(I279=0,V279="IGEN",W279="IGEN"),0,IF(AND(K279&lt;&gt;"IGEN",L279="IGEN",U279="NEM"),0,IF(AND(H279="GYES",E279&lt;1998),0,S279))))</f>
         <v/>
       </c>
       <c r="AI279" s="6">
@@ -45399,7 +45399,7 @@
         <v/>
       </c>
       <c r="AH280" s="6">
-        <f>IF(S280="","",IF(OR(I280=0,V280="IGEN",W280="IGEN"),0,IF(AND(K280&lt;&gt;"IGEN",L280="IGEN",U280="NEM"),0,S280)))</f>
+        <f>IF(S280="","",IF(OR(I280=0,V280="IGEN",W280="IGEN"),0,IF(AND(K280&lt;&gt;"IGEN",L280="IGEN",U280="NEM"),0,IF(AND(H280="GYES",E280&lt;1998),0,S280))))</f>
         <v/>
       </c>
       <c r="AI280" s="6">
@@ -45519,7 +45519,7 @@
         <v/>
       </c>
       <c r="AH281" s="6">
-        <f>IF(S281="","",IF(OR(I281=0,V281="IGEN",W281="IGEN"),0,IF(AND(K281&lt;&gt;"IGEN",L281="IGEN",U281="NEM"),0,S281)))</f>
+        <f>IF(S281="","",IF(OR(I281=0,V281="IGEN",W281="IGEN"),0,IF(AND(K281&lt;&gt;"IGEN",L281="IGEN",U281="NEM"),0,IF(AND(H281="GYES",E281&lt;1998),0,S281))))</f>
         <v/>
       </c>
       <c r="AI281" s="6">
@@ -45639,7 +45639,7 @@
         <v/>
       </c>
       <c r="AH282" s="6">
-        <f>IF(S282="","",IF(OR(I282=0,V282="IGEN",W282="IGEN"),0,IF(AND(K282&lt;&gt;"IGEN",L282="IGEN",U282="NEM"),0,S282)))</f>
+        <f>IF(S282="","",IF(OR(I282=0,V282="IGEN",W282="IGEN"),0,IF(AND(K282&lt;&gt;"IGEN",L282="IGEN",U282="NEM"),0,IF(AND(H282="GYES",E282&lt;1998),0,S282))))</f>
         <v/>
       </c>
       <c r="AI282" s="6">
@@ -45759,7 +45759,7 @@
         <v/>
       </c>
       <c r="AH283" s="6">
-        <f>IF(S283="","",IF(OR(I283=0,V283="IGEN",W283="IGEN"),0,IF(AND(K283&lt;&gt;"IGEN",L283="IGEN",U283="NEM"),0,S283)))</f>
+        <f>IF(S283="","",IF(OR(I283=0,V283="IGEN",W283="IGEN"),0,IF(AND(K283&lt;&gt;"IGEN",L283="IGEN",U283="NEM"),0,IF(AND(H283="GYES",E283&lt;1998),0,S283))))</f>
         <v/>
       </c>
       <c r="AI283" s="6">
@@ -45879,7 +45879,7 @@
         <v/>
       </c>
       <c r="AH284" s="6">
-        <f>IF(S284="","",IF(OR(I284=0,V284="IGEN",W284="IGEN"),0,IF(AND(K284&lt;&gt;"IGEN",L284="IGEN",U284="NEM"),0,S284)))</f>
+        <f>IF(S284="","",IF(OR(I284=0,V284="IGEN",W284="IGEN"),0,IF(AND(K284&lt;&gt;"IGEN",L284="IGEN",U284="NEM"),0,IF(AND(H284="GYES",E284&lt;1998),0,S284))))</f>
         <v/>
       </c>
       <c r="AI284" s="6">
@@ -45999,7 +45999,7 @@
         <v/>
       </c>
       <c r="AH285" s="6">
-        <f>IF(S285="","",IF(OR(I285=0,V285="IGEN",W285="IGEN"),0,IF(AND(K285&lt;&gt;"IGEN",L285="IGEN",U285="NEM"),0,S285)))</f>
+        <f>IF(S285="","",IF(OR(I285=0,V285="IGEN",W285="IGEN"),0,IF(AND(K285&lt;&gt;"IGEN",L285="IGEN",U285="NEM"),0,IF(AND(H285="GYES",E285&lt;1998),0,S285))))</f>
         <v/>
       </c>
       <c r="AI285" s="6">
@@ -46119,7 +46119,7 @@
         <v/>
       </c>
       <c r="AH286" s="6">
-        <f>IF(S286="","",IF(OR(I286=0,V286="IGEN",W286="IGEN"),0,IF(AND(K286&lt;&gt;"IGEN",L286="IGEN",U286="NEM"),0,S286)))</f>
+        <f>IF(S286="","",IF(OR(I286=0,V286="IGEN",W286="IGEN"),0,IF(AND(K286&lt;&gt;"IGEN",L286="IGEN",U286="NEM"),0,IF(AND(H286="GYES",E286&lt;1998),0,S286))))</f>
         <v/>
       </c>
       <c r="AI286" s="6">
@@ -46239,7 +46239,7 @@
         <v/>
       </c>
       <c r="AH287" s="6">
-        <f>IF(S287="","",IF(OR(I287=0,V287="IGEN",W287="IGEN"),0,IF(AND(K287&lt;&gt;"IGEN",L287="IGEN",U287="NEM"),0,S287)))</f>
+        <f>IF(S287="","",IF(OR(I287=0,V287="IGEN",W287="IGEN"),0,IF(AND(K287&lt;&gt;"IGEN",L287="IGEN",U287="NEM"),0,IF(AND(H287="GYES",E287&lt;1998),0,S287))))</f>
         <v/>
       </c>
       <c r="AI287" s="6">
@@ -46359,7 +46359,7 @@
         <v/>
       </c>
       <c r="AH288" s="6">
-        <f>IF(S288="","",IF(OR(I288=0,V288="IGEN",W288="IGEN"),0,IF(AND(K288&lt;&gt;"IGEN",L288="IGEN",U288="NEM"),0,S288)))</f>
+        <f>IF(S288="","",IF(OR(I288=0,V288="IGEN",W288="IGEN"),0,IF(AND(K288&lt;&gt;"IGEN",L288="IGEN",U288="NEM"),0,IF(AND(H288="GYES",E288&lt;1998),0,S288))))</f>
         <v/>
       </c>
       <c r="AI288" s="6">
@@ -46479,7 +46479,7 @@
         <v/>
       </c>
       <c r="AH289" s="6">
-        <f>IF(S289="","",IF(OR(I289=0,V289="IGEN",W289="IGEN"),0,IF(AND(K289&lt;&gt;"IGEN",L289="IGEN",U289="NEM"),0,S289)))</f>
+        <f>IF(S289="","",IF(OR(I289=0,V289="IGEN",W289="IGEN"),0,IF(AND(K289&lt;&gt;"IGEN",L289="IGEN",U289="NEM"),0,IF(AND(H289="GYES",E289&lt;1998),0,S289))))</f>
         <v/>
       </c>
       <c r="AI289" s="6">
@@ -46599,7 +46599,7 @@
         <v/>
       </c>
       <c r="AH290" s="6">
-        <f>IF(S290="","",IF(OR(I290=0,V290="IGEN",W290="IGEN"),0,IF(AND(K290&lt;&gt;"IGEN",L290="IGEN",U290="NEM"),0,S290)))</f>
+        <f>IF(S290="","",IF(OR(I290=0,V290="IGEN",W290="IGEN"),0,IF(AND(K290&lt;&gt;"IGEN",L290="IGEN",U290="NEM"),0,IF(AND(H290="GYES",E290&lt;1998),0,S290))))</f>
         <v/>
       </c>
       <c r="AI290" s="6">
@@ -46719,7 +46719,7 @@
         <v/>
       </c>
       <c r="AH291" s="6">
-        <f>IF(S291="","",IF(OR(I291=0,V291="IGEN",W291="IGEN"),0,IF(AND(K291&lt;&gt;"IGEN",L291="IGEN",U291="NEM"),0,S291)))</f>
+        <f>IF(S291="","",IF(OR(I291=0,V291="IGEN",W291="IGEN"),0,IF(AND(K291&lt;&gt;"IGEN",L291="IGEN",U291="NEM"),0,IF(AND(H291="GYES",E291&lt;1998),0,S291))))</f>
         <v/>
       </c>
       <c r="AI291" s="6">
@@ -46839,7 +46839,7 @@
         <v/>
       </c>
       <c r="AH292" s="6">
-        <f>IF(S292="","",IF(OR(I292=0,V292="IGEN",W292="IGEN"),0,IF(AND(K292&lt;&gt;"IGEN",L292="IGEN",U292="NEM"),0,S292)))</f>
+        <f>IF(S292="","",IF(OR(I292=0,V292="IGEN",W292="IGEN"),0,IF(AND(K292&lt;&gt;"IGEN",L292="IGEN",U292="NEM"),0,IF(AND(H292="GYES",E292&lt;1998),0,S292))))</f>
         <v/>
       </c>
       <c r="AI292" s="6">
@@ -46959,7 +46959,7 @@
         <v/>
       </c>
       <c r="AH293" s="6">
-        <f>IF(S293="","",IF(OR(I293=0,V293="IGEN",W293="IGEN"),0,IF(AND(K293&lt;&gt;"IGEN",L293="IGEN",U293="NEM"),0,S293)))</f>
+        <f>IF(S293="","",IF(OR(I293=0,V293="IGEN",W293="IGEN"),0,IF(AND(K293&lt;&gt;"IGEN",L293="IGEN",U293="NEM"),0,IF(AND(H293="GYES",E293&lt;1998),0,S293))))</f>
         <v/>
       </c>
       <c r="AI293" s="6">
@@ -47079,7 +47079,7 @@
         <v/>
       </c>
       <c r="AH294" s="6">
-        <f>IF(S294="","",IF(OR(I294=0,V294="IGEN",W294="IGEN"),0,IF(AND(K294&lt;&gt;"IGEN",L294="IGEN",U294="NEM"),0,S294)))</f>
+        <f>IF(S294="","",IF(OR(I294=0,V294="IGEN",W294="IGEN"),0,IF(AND(K294&lt;&gt;"IGEN",L294="IGEN",U294="NEM"),0,IF(AND(H294="GYES",E294&lt;1998),0,S294))))</f>
         <v/>
       </c>
       <c r="AI294" s="6">
@@ -47199,7 +47199,7 @@
         <v/>
       </c>
       <c r="AH295" s="6">
-        <f>IF(S295="","",IF(OR(I295=0,V295="IGEN",W295="IGEN"),0,IF(AND(K295&lt;&gt;"IGEN",L295="IGEN",U295="NEM"),0,S295)))</f>
+        <f>IF(S295="","",IF(OR(I295=0,V295="IGEN",W295="IGEN"),0,IF(AND(K295&lt;&gt;"IGEN",L295="IGEN",U295="NEM"),0,IF(AND(H295="GYES",E295&lt;1998),0,S295))))</f>
         <v/>
       </c>
       <c r="AI295" s="6">
@@ -47319,7 +47319,7 @@
         <v/>
       </c>
       <c r="AH296" s="6">
-        <f>IF(S296="","",IF(OR(I296=0,V296="IGEN",W296="IGEN"),0,IF(AND(K296&lt;&gt;"IGEN",L296="IGEN",U296="NEM"),0,S296)))</f>
+        <f>IF(S296="","",IF(OR(I296=0,V296="IGEN",W296="IGEN"),0,IF(AND(K296&lt;&gt;"IGEN",L296="IGEN",U296="NEM"),0,IF(AND(H296="GYES",E296&lt;1998),0,S296))))</f>
         <v/>
       </c>
       <c r="AI296" s="6">
@@ -47439,7 +47439,7 @@
         <v/>
       </c>
       <c r="AH297" s="6">
-        <f>IF(S297="","",IF(OR(I297=0,V297="IGEN",W297="IGEN"),0,IF(AND(K297&lt;&gt;"IGEN",L297="IGEN",U297="NEM"),0,S297)))</f>
+        <f>IF(S297="","",IF(OR(I297=0,V297="IGEN",W297="IGEN"),0,IF(AND(K297&lt;&gt;"IGEN",L297="IGEN",U297="NEM"),0,IF(AND(H297="GYES",E297&lt;1998),0,S297))))</f>
         <v/>
       </c>
       <c r="AI297" s="6">
@@ -47559,7 +47559,7 @@
         <v/>
       </c>
       <c r="AH298" s="6">
-        <f>IF(S298="","",IF(OR(I298=0,V298="IGEN",W298="IGEN"),0,IF(AND(K298&lt;&gt;"IGEN",L298="IGEN",U298="NEM"),0,S298)))</f>
+        <f>IF(S298="","",IF(OR(I298=0,V298="IGEN",W298="IGEN"),0,IF(AND(K298&lt;&gt;"IGEN",L298="IGEN",U298="NEM"),0,IF(AND(H298="GYES",E298&lt;1998),0,S298))))</f>
         <v/>
       </c>
       <c r="AI298" s="6">
@@ -47679,7 +47679,7 @@
         <v/>
       </c>
       <c r="AH299" s="6">
-        <f>IF(S299="","",IF(OR(I299=0,V299="IGEN",W299="IGEN"),0,IF(AND(K299&lt;&gt;"IGEN",L299="IGEN",U299="NEM"),0,S299)))</f>
+        <f>IF(S299="","",IF(OR(I299=0,V299="IGEN",W299="IGEN"),0,IF(AND(K299&lt;&gt;"IGEN",L299="IGEN",U299="NEM"),0,IF(AND(H299="GYES",E299&lt;1998),0,S299))))</f>
         <v/>
       </c>
       <c r="AI299" s="6">
@@ -47799,7 +47799,7 @@
         <v/>
       </c>
       <c r="AH300" s="6">
-        <f>IF(S300="","",IF(OR(I300=0,V300="IGEN",W300="IGEN"),0,IF(AND(K300&lt;&gt;"IGEN",L300="IGEN",U300="NEM"),0,S300)))</f>
+        <f>IF(S300="","",IF(OR(I300=0,V300="IGEN",W300="IGEN"),0,IF(AND(K300&lt;&gt;"IGEN",L300="IGEN",U300="NEM"),0,IF(AND(H300="GYES",E300&lt;1998),0,S300))))</f>
         <v/>
       </c>
       <c r="AI300" s="6">
@@ -47919,7 +47919,7 @@
         <v/>
       </c>
       <c r="AH301" s="6">
-        <f>IF(S301="","",IF(OR(I301=0,V301="IGEN",W301="IGEN"),0,IF(AND(K301&lt;&gt;"IGEN",L301="IGEN",U301="NEM"),0,S301)))</f>
+        <f>IF(S301="","",IF(OR(I301=0,V301="IGEN",W301="IGEN"),0,IF(AND(K301&lt;&gt;"IGEN",L301="IGEN",U301="NEM"),0,IF(AND(H301="GYES",E301&lt;1998),0,S301))))</f>
         <v/>
       </c>
       <c r="AI301" s="6">
@@ -48039,7 +48039,7 @@
         <v/>
       </c>
       <c r="AH302" s="6">
-        <f>IF(S302="","",IF(OR(I302=0,V302="IGEN",W302="IGEN"),0,IF(AND(K302&lt;&gt;"IGEN",L302="IGEN",U302="NEM"),0,S302)))</f>
+        <f>IF(S302="","",IF(OR(I302=0,V302="IGEN",W302="IGEN"),0,IF(AND(K302&lt;&gt;"IGEN",L302="IGEN",U302="NEM"),0,IF(AND(H302="GYES",E302&lt;1998),0,S302))))</f>
         <v/>
       </c>
       <c r="AI302" s="6">
@@ -48159,7 +48159,7 @@
         <v/>
       </c>
       <c r="AH303" s="6">
-        <f>IF(S303="","",IF(OR(I303=0,V303="IGEN",W303="IGEN"),0,IF(AND(K303&lt;&gt;"IGEN",L303="IGEN",U303="NEM"),0,S303)))</f>
+        <f>IF(S303="","",IF(OR(I303=0,V303="IGEN",W303="IGEN"),0,IF(AND(K303&lt;&gt;"IGEN",L303="IGEN",U303="NEM"),0,IF(AND(H303="GYES",E303&lt;1998),0,S303))))</f>
         <v/>
       </c>
       <c r="AI303" s="6">
@@ -48279,7 +48279,7 @@
         <v/>
       </c>
       <c r="AH304" s="6">
-        <f>IF(S304="","",IF(OR(I304=0,V304="IGEN",W304="IGEN"),0,IF(AND(K304&lt;&gt;"IGEN",L304="IGEN",U304="NEM"),0,S304)))</f>
+        <f>IF(S304="","",IF(OR(I304=0,V304="IGEN",W304="IGEN"),0,IF(AND(K304&lt;&gt;"IGEN",L304="IGEN",U304="NEM"),0,IF(AND(H304="GYES",E304&lt;1998),0,S304))))</f>
         <v/>
       </c>
       <c r="AI304" s="6">
